--- a/template.xlsx
+++ b/template.xlsx
@@ -16,7 +16,7 @@
     <sheet name="工作表3" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$195</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'合同 '!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">发票!$A$1:$E$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">装箱单!$A$1:$L$36</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="322">
   <si>
     <t>销 售 合 同
 SALES CONTRACT</t>
@@ -696,6 +696,9 @@
   </si>
   <si>
     <t>LS一55白</t>
+  </si>
+  <si>
+    <t>DG一28白</t>
   </si>
   <si>
     <t>DG一23</t>
@@ -2691,7 +2694,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{3EAFBEDC-4926-44BF-979A-54807F21602F}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{4D404418-3AA8-4C88-844C-D511EA24324D}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2700,7 +2703,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{D2D4257C-61DB-4445-B219-105AA042FF5C}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{7D26F90E-4EA0-4EA0-8992-6E73FC61EE30}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -6370,7 +6373,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P222"/>
+  <dimension ref="A1:P223"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.4" style="2" customWidth="1"/>
@@ -6495,7 +6498,7 @@
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="17">
-        <f t="shared" ref="K6:K57" si="1">J6*F6</f>
+        <f t="shared" ref="K6:K58" si="1">J6*F6</f>
         <v>0</v>
       </c>
       <c r="L6" s="17">
@@ -6503,11 +6506,11 @@
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f t="shared" ref="M6:M57" si="3">J6*I6</f>
+        <f t="shared" ref="M6:M58" si="3">J6*I6</f>
         <v>0</v>
       </c>
       <c r="N6" s="18">
-        <f t="shared" ref="N6:N57" si="4">M6+J6</f>
+        <f t="shared" ref="N6:N58" si="4">M6+J6</f>
         <v>0</v>
       </c>
     </row>
@@ -8593,19 +8596,19 @@
       </c>
       <c r="J53" s="8"/>
       <c r="K53" s="17">
-        <f>J53*F53</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L53" s="17">
-        <f>K53+J53/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M53" s="16">
-        <f>J53*I53</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N53" s="18">
-        <f>M53+J53</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8636,19 +8639,19 @@
       </c>
       <c r="J54" s="8"/>
       <c r="K54" s="17">
-        <f>J54*F54</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L54" s="17">
-        <f>K54+J54/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M54" s="16">
-        <f>J54*I54</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N54" s="18">
-        <f>M54+J54</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8681,19 +8684,19 @@
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="17">
-        <f>J55*F55</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L55" s="17">
-        <f>K55+J55/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M55" s="16">
-        <f>J55*I55</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N55" s="18">
-        <f>M55+J55</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8726,19 +8729,19 @@
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="17">
-        <f>J56*F56</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L56" s="17">
-        <f>K56+J56/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M56" s="16">
-        <f>J56*I56</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N56" s="18">
-        <f>M56+J56</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8771,19 +8774,19 @@
       </c>
       <c r="J57" s="8"/>
       <c r="K57" s="17">
-        <f>J57*F57</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L57" s="17">
-        <f>K57+J57/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M57" s="16">
-        <f>J57*I57</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N57" s="18">
-        <f>M57+J57</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8816,19 +8819,19 @@
       </c>
       <c r="J58" s="24"/>
       <c r="K58" s="17">
-        <f>J58*F58</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L58" s="17">
-        <f>K58+J58/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M58" s="16">
-        <f>J58*I58</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N58" s="18">
-        <f>M58+J58</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8847,7 +8850,7 @@
       <c r="J59" s="24"/>
       <c r="K59" s="24"/>
       <c r="L59" s="17">
-        <f>K59+J59/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M59" s="24"/>
@@ -8868,7 +8871,7 @@
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
       <c r="L60" s="17">
-        <f>K60+J60/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M60" s="15"/>
@@ -8908,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="17">
-        <f>K61+J61/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M61" s="16">
@@ -8953,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="17">
-        <f>K62+J62/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M62" s="16">
@@ -8998,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="17">
-        <f>K63+J63/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M63" s="16">
@@ -9042,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="17">
-        <f>K64+J64/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M64" s="16">
@@ -9067,7 +9070,7 @@
       <c r="G65" s="13"/>
       <c r="H65" s="15"/>
       <c r="L65" s="17">
-        <f>K65+J65/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M65" s="2"/>
@@ -9106,7 +9109,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="17">
-        <f>K66+J66/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M66" s="16">
@@ -9151,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="17">
-        <f>K67+J67/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M67" s="16">
@@ -9196,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="17">
-        <f>K68+J68/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M68" s="16">
@@ -9239,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="17">
-        <f>K69+J69/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M69" s="16">
@@ -9443,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="17">
-        <f t="shared" ref="L74:L93" si="12">K74+J74/2</f>
+        <f>K74+J74/2</f>
         <v>0</v>
       </c>
       <c r="M74" s="16">
@@ -9488,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="17">
-        <f t="shared" si="12"/>
+        <f>K75+J75/2</f>
         <v>0</v>
       </c>
       <c r="M75" s="16">
@@ -9533,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="17">
-        <f t="shared" si="12"/>
+        <f>K76+J76/2</f>
         <v>0</v>
       </c>
       <c r="M76" s="16">
@@ -9578,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="17">
-        <f t="shared" si="12"/>
+        <f>K77+J77/2</f>
         <v>0</v>
       </c>
       <c r="M77" s="16">
@@ -9623,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="17">
-        <f t="shared" si="12"/>
+        <f>K78+J78/2</f>
         <v>0</v>
       </c>
       <c r="M78" s="16">
@@ -9653,7 +9656,7 @@
         <v>8.4</v>
       </c>
       <c r="G79" s="13">
-        <f t="shared" ref="G79:G88" si="13">I79-1</f>
+        <f t="shared" ref="G79:G83" si="12">I79-1</f>
         <v>89</v>
       </c>
       <c r="H79" s="15">
@@ -9668,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="17">
-        <f t="shared" si="12"/>
+        <f>K79+J79/2</f>
         <v>0</v>
       </c>
       <c r="M79" s="16">
@@ -9698,7 +9701,7 @@
         <v>6.3</v>
       </c>
       <c r="G80" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="H80" s="15">
@@ -9713,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="17">
-        <f t="shared" si="12"/>
+        <f>K80+J80/2</f>
         <v>0</v>
       </c>
       <c r="M80" s="16">
@@ -9743,7 +9746,7 @@
         <v>8.4</v>
       </c>
       <c r="G81" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>91</v>
       </c>
       <c r="H81" s="15">
@@ -9758,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="17">
-        <f t="shared" si="12"/>
+        <f>K81+J81/2</f>
         <v>0</v>
       </c>
       <c r="M81" s="16">
@@ -9788,7 +9791,7 @@
         <v>10.4</v>
       </c>
       <c r="G82" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>76</v>
       </c>
       <c r="H82" s="15">
@@ -9803,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="17">
-        <f t="shared" si="12"/>
+        <f>K82+J82/2</f>
         <v>0</v>
       </c>
       <c r="M82" s="16">
@@ -9817,7 +9820,7 @@
     </row>
     <row r="83" s="2" customFormat="1" spans="1:14">
       <c r="A83" s="12"/>
-      <c r="B83" s="31" t="s">
+      <c r="B83" s="29" t="s">
         <v>209</v>
       </c>
       <c r="C83" s="29" t="s">
@@ -9830,35 +9833,23 @@
         <v>129</v>
       </c>
       <c r="F83" s="7">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" si="13"/>
-        <v>113</v>
+        <f t="shared" si="12"/>
+        <v>89</v>
       </c>
       <c r="H83" s="15">
         <v>0.08</v>
       </c>
       <c r="I83" s="13">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="J83" s="8"/>
-      <c r="K83" s="17">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L83" s="17">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="16">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N83" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="K83" s="17"/>
+      <c r="L83" s="17"/>
+      <c r="M83" s="16"/>
+      <c r="N83" s="18"/>
     </row>
     <row r="84" s="2" customFormat="1" spans="1:14">
       <c r="A84" s="12"/>
@@ -9872,81 +9863,81 @@
         <v>136</v>
       </c>
       <c r="E84" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="7">
+        <v>10.2</v>
+      </c>
+      <c r="G84" s="13">
+        <f t="shared" ref="G84:G89" si="13">I84-1</f>
+        <v>113</v>
+      </c>
+      <c r="H84" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I84" s="13">
+        <v>114</v>
+      </c>
+      <c r="J84" s="8"/>
+      <c r="K84" s="17">
+        <f>J84*F84</f>
+        <v>0</v>
+      </c>
+      <c r="L84" s="17">
+        <f t="shared" ref="L84:L94" si="14">K84+J84/2</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="16">
+        <f>J84*I84</f>
+        <v>0</v>
+      </c>
+      <c r="N84" s="18">
+        <f>M84+J84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" spans="1:14">
+      <c r="A85" s="12"/>
+      <c r="B85" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="F84" s="7">
+      <c r="C85" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="F85" s="7">
         <v>7.2</v>
       </c>
-      <c r="G84" s="13">
+      <c r="G85" s="13">
         <f t="shared" si="13"/>
         <v>73</v>
       </c>
-      <c r="H84" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I84" s="13">
-        <v>74</v>
-      </c>
-      <c r="J84" s="8"/>
-      <c r="K84" s="17">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L84" s="17">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="16">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N84" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" s="2" customFormat="1" spans="1:14">
-      <c r="A85" s="12"/>
-      <c r="B85" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="C85" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="F85" s="7">
-        <v>6.9</v>
-      </c>
-      <c r="G85" s="13">
-        <f t="shared" si="13"/>
-        <v>73.7</v>
-      </c>
       <c r="H85" s="15">
         <v>0.08</v>
       </c>
       <c r="I85" s="13">
-        <v>74.7</v>
+        <v>74</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="17">
-        <f t="shared" si="10"/>
+        <f>J85*F85</f>
         <v>0</v>
       </c>
       <c r="L85" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M85" s="16">
-        <f t="shared" si="11"/>
+        <f>J85*I85</f>
         <v>0</v>
       </c>
       <c r="N85" s="18">
-        <f t="shared" si="8"/>
+        <f>M85+J85</f>
         <v>0</v>
       </c>
     </row>
@@ -9965,33 +9956,33 @@
         <v>129</v>
       </c>
       <c r="F86" s="7">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="G86" s="13">
         <f t="shared" si="13"/>
-        <v>74.1</v>
+        <v>73.7</v>
       </c>
       <c r="H86" s="15">
         <v>0.08</v>
       </c>
       <c r="I86" s="13">
-        <v>75.1</v>
+        <v>74.7</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="17">
-        <f t="shared" si="10"/>
+        <f>J86*F86</f>
         <v>0</v>
       </c>
       <c r="L86" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M86" s="16">
-        <f t="shared" si="11"/>
+        <f>J86*I86</f>
         <v>0</v>
       </c>
       <c r="N86" s="18">
-        <f t="shared" si="8"/>
+        <f>M86+J86</f>
         <v>0</v>
       </c>
     </row>
@@ -10007,36 +9998,36 @@
         <v>136</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F87" s="7">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="G87" s="13">
         <f t="shared" si="13"/>
-        <v>58.1</v>
+        <v>74.1</v>
       </c>
       <c r="H87" s="15">
         <v>0.08</v>
       </c>
       <c r="I87" s="13">
-        <v>59.1</v>
+        <v>75.1</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="17">
-        <f t="shared" si="10"/>
+        <f>J87*F87</f>
         <v>0</v>
       </c>
       <c r="L87" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M87" s="16">
-        <f t="shared" si="11"/>
+        <f>J87*I87</f>
         <v>0</v>
       </c>
       <c r="N87" s="18">
-        <f t="shared" si="8"/>
+        <f>M87+J87</f>
         <v>0</v>
       </c>
     </row>
@@ -10059,126 +10050,126 @@
       </c>
       <c r="G88" s="13">
         <f t="shared" si="13"/>
-        <v>124</v>
+        <v>58.1</v>
       </c>
       <c r="H88" s="15">
         <v>0.08</v>
       </c>
       <c r="I88" s="13">
-        <v>125</v>
+        <v>59.1</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="17">
-        <f t="shared" si="10"/>
+        <f>J88*F88</f>
         <v>0</v>
       </c>
       <c r="L88" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M88" s="16">
-        <f t="shared" si="11"/>
+        <f>J88*I88</f>
         <v>0</v>
       </c>
       <c r="N88" s="18">
-        <f t="shared" si="8"/>
+        <f>M88+J88</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" spans="1:14">
       <c r="A89" s="12"/>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>217</v>
+      <c r="C89" s="29" t="s">
+        <v>205</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E89" s="12"/>
+      <c r="E89" s="30" t="s">
+        <v>127</v>
+      </c>
       <c r="F89" s="7">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G89" s="13">
-        <v>80</v>
+        <f t="shared" si="13"/>
+        <v>124</v>
       </c>
       <c r="H89" s="15">
         <v>0.08</v>
       </c>
       <c r="I89" s="13">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="17">
-        <f t="shared" si="10"/>
+        <f>J89*F89</f>
         <v>0</v>
       </c>
       <c r="L89" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M89" s="16">
-        <f t="shared" si="11"/>
+        <f>J89*I89</f>
         <v>0</v>
       </c>
       <c r="N89" s="18">
-        <f t="shared" si="8"/>
+        <f>M89+J89</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" spans="1:14">
       <c r="A90" s="12"/>
-      <c r="B90" s="19" t="s">
-        <v>196</v>
+      <c r="B90" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E90" s="14" t="s">
-        <v>197</v>
-      </c>
+      <c r="E90" s="12"/>
       <c r="F90" s="7">
         <v>6.3</v>
       </c>
       <c r="G90" s="13">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H90" s="15">
         <v>0.08</v>
       </c>
-      <c r="I90" s="16">
-        <f t="shared" ref="I90:I93" si="14">G90*(1+H90)</f>
-        <v>73.44</v>
+      <c r="I90" s="13">
+        <v>81</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="17">
-        <f t="shared" si="10"/>
+        <f>J90*F90</f>
         <v>0</v>
       </c>
       <c r="L90" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M90" s="16">
-        <f t="shared" si="11"/>
+        <f>J90*I90</f>
         <v>0</v>
       </c>
       <c r="N90" s="18">
-        <f t="shared" si="8"/>
+        <f>M90+J90</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" spans="1:14">
       <c r="A91" s="12"/>
       <c r="B91" s="19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>136</v>
@@ -10187,43 +10178,43 @@
         <v>197</v>
       </c>
       <c r="F91" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G91" s="13">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H91" s="15">
         <v>0.08</v>
       </c>
       <c r="I91" s="16">
-        <f t="shared" si="14"/>
-        <v>79.92</v>
+        <f t="shared" ref="I91:I94" si="15">G91*(1+H91)</f>
+        <v>73.44</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="17">
-        <f t="shared" si="10"/>
+        <f>J91*F91</f>
         <v>0</v>
       </c>
       <c r="L91" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M91" s="16">
-        <f t="shared" si="11"/>
+        <f>J91*I91</f>
         <v>0</v>
       </c>
       <c r="N91" s="18">
-        <f t="shared" si="8"/>
+        <f>M91+J91</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" spans="1:14">
       <c r="A92" s="12"/>
       <c r="B92" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>136</v>
@@ -10235,40 +10226,40 @@
         <v>7.5</v>
       </c>
       <c r="G92" s="13">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H92" s="15">
         <v>0.08</v>
       </c>
       <c r="I92" s="16">
-        <f t="shared" si="14"/>
-        <v>88.56</v>
+        <f t="shared" si="15"/>
+        <v>79.92</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="17">
-        <f t="shared" si="10"/>
+        <f>J92*F92</f>
         <v>0</v>
       </c>
       <c r="L92" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M92" s="16">
-        <f t="shared" si="11"/>
+        <f>J92*I92</f>
         <v>0</v>
       </c>
       <c r="N92" s="18">
-        <f t="shared" si="8"/>
+        <f>M92+J92</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" s="2" customFormat="1" spans="1:14">
       <c r="A93" s="12"/>
-      <c r="B93" s="12" t="s">
-        <v>200</v>
+      <c r="B93" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>136</v>
@@ -10277,136 +10268,136 @@
         <v>197</v>
       </c>
       <c r="F93" s="7">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G93" s="13">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H93" s="15">
         <v>0.08</v>
       </c>
       <c r="I93" s="16">
-        <f t="shared" si="14"/>
-        <v>97.2</v>
+        <f t="shared" si="15"/>
+        <v>88.56</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="17">
-        <f t="shared" si="10"/>
+        <f>J93*F93</f>
         <v>0</v>
       </c>
       <c r="L93" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M93" s="16">
-        <f t="shared" si="11"/>
+        <f>J93*I93</f>
         <v>0</v>
       </c>
       <c r="N93" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
+        <f>M93+J93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" spans="1:14">
       <c r="A94" s="12"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="23" t="s">
+      <c r="B94" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J94" s="24"/>
-      <c r="K94" s="24"/>
+      <c r="D94" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F94" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="G94" s="13">
+        <v>90</v>
+      </c>
+      <c r="H94" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I94" s="16">
+        <f t="shared" si="15"/>
+        <v>97.2</v>
+      </c>
+      <c r="J94" s="8"/>
+      <c r="K94" s="17">
+        <f>J94*F94</f>
+        <v>0</v>
+      </c>
       <c r="L94" s="17">
-        <f t="shared" ref="L94:L97" si="15">K94+J94/2</f>
-        <v>0</v>
-      </c>
-      <c r="M94" s="24"/>
-      <c r="N94" s="24"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="16">
+        <f>J94*I94</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="18">
+        <f>M94+J94</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="12"/>
-      <c r="B95" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="7"/>
       <c r="G95" s="13"/>
       <c r="H95" s="15"/>
-      <c r="I95" s="16"/>
-      <c r="J95" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="K95" s="17"/>
+      <c r="I95" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="J95" s="24"/>
+      <c r="K95" s="24"/>
       <c r="L95" s="17">
-        <v>0</v>
-      </c>
-      <c r="M95" s="16"/>
-      <c r="N95" s="18">
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L95:L98" si="16">K95+J95/2</f>
+        <v>0</v>
+      </c>
+      <c r="M95" s="24"/>
+      <c r="N95" s="24"/>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="12"/>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="15"/>
+      <c r="I96" s="16"/>
+      <c r="J96" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F96" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G96" s="13">
-        <v>50.5</v>
-      </c>
-      <c r="H96" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I96" s="16">
-        <f>G96*(1+H96)</f>
-        <v>54.54</v>
-      </c>
-      <c r="J96" s="8"/>
-      <c r="K96" s="17">
-        <f>J96*F96</f>
-        <v>0</v>
-      </c>
+      <c r="K96" s="17"/>
       <c r="L96" s="17">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="16">
-        <f>J96*I96</f>
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M96" s="16"/>
       <c r="N96" s="18">
-        <f>M96+J96</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="12"/>
       <c r="B97" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>217</v>
+        <v>222</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E97" s="14" t="s">
         <v>197</v>
@@ -10430,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="L97" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M97" s="16">
@@ -10444,24 +10435,48 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="12"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="12"/>
-      <c r="D98" s="12"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="23" t="s">
+      <c r="B98" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C98" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
+      <c r="D98" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F98" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G98" s="13">
+        <v>50.5</v>
+      </c>
+      <c r="H98" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I98" s="16">
+        <f>G98*(1+H98)</f>
+        <v>54.54</v>
+      </c>
+      <c r="J98" s="8"/>
+      <c r="K98" s="17">
+        <f>J98*F98</f>
+        <v>0</v>
+      </c>
       <c r="L98" s="17">
-        <f t="shared" ref="L98:L160" si="16">K98+J98/2</f>
-        <v>0</v>
-      </c>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="16">
+        <f>J98*I98</f>
+        <v>0</v>
+      </c>
+      <c r="N98" s="18">
+        <f>M98+J98</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="12"/>
@@ -10472,88 +10487,64 @@
       <c r="F99" s="7"/>
       <c r="G99" s="13"/>
       <c r="H99" s="15"/>
-      <c r="I99" s="16"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="17"/>
+      <c r="I99" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="J99" s="24"/>
+      <c r="K99" s="24"/>
       <c r="L99" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="16"/>
-      <c r="N99" s="18"/>
+        <f t="shared" ref="L99:L161" si="17">K99+J99/2</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="24"/>
+      <c r="N99" s="24"/>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="12"/>
-      <c r="B100" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="7"/>
       <c r="G100" s="13"/>
       <c r="H100" s="15"/>
       <c r="I100" s="16"/>
       <c r="J100" s="8"/>
       <c r="K100" s="17"/>
       <c r="L100" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M100" s="16"/>
-      <c r="N100" s="18">
-        <f t="shared" ref="N100:N113" si="17">M100+J100</f>
-        <v>0</v>
-      </c>
+      <c r="N100" s="18"/>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="12"/>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="C101" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F101" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G101" s="13">
-        <v>51</v>
-      </c>
-      <c r="H101" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I101" s="16">
-        <f t="shared" ref="I101:I113" si="18">G101*(1+H101)</f>
-        <v>55.08</v>
-      </c>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="15"/>
+      <c r="I101" s="16"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="17">
-        <f t="shared" ref="K101:K113" si="19">J101*F101</f>
-        <v>0</v>
-      </c>
+      <c r="K101" s="17"/>
       <c r="L101" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M101" s="16">
-        <f t="shared" ref="M101:M113" si="20">J101*I101</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M101" s="16"/>
       <c r="N101" s="18">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="14" customHeight="1" spans="1:14">
+        <f t="shared" ref="N101:N114" si="18">M101+J101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102" s="12"/>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="19" t="s">
         <v>225</v>
       </c>
       <c r="C102" s="8" t="s">
@@ -10569,36 +10560,36 @@
         <v>4.5</v>
       </c>
       <c r="G102" s="13">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H102" s="15">
         <v>0.08</v>
       </c>
       <c r="I102" s="16">
-        <f t="shared" si="18"/>
-        <v>58.32</v>
+        <f t="shared" ref="I102:I114" si="19">G102*(1+H102)</f>
+        <v>55.08</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="K102:K114" si="20">J102*F102</f>
         <v>0</v>
       </c>
       <c r="L102" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M102" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="M102:M114" si="21">J102*I102</f>
         <v>0</v>
       </c>
       <c r="N102" s="18">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="14" customHeight="1" spans="1:14">
       <c r="A103" s="12"/>
-      <c r="B103" s="19" t="s">
+      <c r="B103" s="12" t="s">
         <v>226</v>
       </c>
       <c r="C103" s="8" t="s">
@@ -10611,33 +10602,33 @@
         <v>197</v>
       </c>
       <c r="F103" s="7">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="G103" s="13">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="H103" s="15">
         <v>0.08</v>
       </c>
       <c r="I103" s="16">
-        <f t="shared" si="18"/>
-        <v>65.88</v>
+        <f t="shared" si="19"/>
+        <v>58.32</v>
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L103" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M103" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N103" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10659,30 +10650,30 @@
         <v>5.5</v>
       </c>
       <c r="G104" s="13">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H104" s="15">
         <v>0.08</v>
       </c>
       <c r="I104" s="16">
-        <f t="shared" si="18"/>
-        <v>69.12</v>
+        <f t="shared" si="19"/>
+        <v>65.88</v>
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L104" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M104" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N104" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10700,27 +10691,34 @@
       <c r="E105" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F105" s="7"/>
-      <c r="G105" s="13"/>
+      <c r="F105" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="G105" s="13">
+        <v>64</v>
+      </c>
       <c r="H105" s="15">
         <v>0.08</v>
       </c>
-      <c r="I105" s="16"/>
+      <c r="I105" s="16">
+        <f t="shared" si="19"/>
+        <v>69.12</v>
+      </c>
       <c r="J105" s="8"/>
       <c r="K105" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L105" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M105" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N105" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10738,40 +10736,33 @@
       <c r="E106" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F106" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="G106" s="13">
-        <v>69</v>
-      </c>
+      <c r="F106" s="7"/>
+      <c r="G106" s="13"/>
       <c r="H106" s="15">
         <v>0.08</v>
       </c>
-      <c r="I106" s="16">
-        <f t="shared" si="18"/>
-        <v>74.52</v>
-      </c>
+      <c r="I106" s="16"/>
       <c r="J106" s="8"/>
       <c r="K106" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L106" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M106" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N106" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="12"/>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="19" t="s">
         <v>230</v>
       </c>
       <c r="C107" s="8" t="s">
@@ -10787,36 +10778,36 @@
         <v>6.5</v>
       </c>
       <c r="G107" s="13">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H107" s="15">
         <v>0.08</v>
       </c>
       <c r="I107" s="16">
-        <f t="shared" si="18"/>
-        <v>77.76</v>
+        <f t="shared" si="19"/>
+        <v>74.52</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L107" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M107" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N107" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="12"/>
-      <c r="B108" s="19" t="s">
+      <c r="B108" s="12" t="s">
         <v>231</v>
       </c>
       <c r="C108" s="8" t="s">
@@ -10829,33 +10820,33 @@
         <v>197</v>
       </c>
       <c r="F108" s="7">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G108" s="13">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H108" s="15">
         <v>0.08</v>
       </c>
       <c r="I108" s="16">
-        <f t="shared" si="18"/>
-        <v>97.2</v>
+        <f t="shared" si="19"/>
+        <v>77.76</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L108" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M108" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N108" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10877,36 +10868,36 @@
         <v>8.5</v>
       </c>
       <c r="G109" s="13">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H109" s="15">
         <v>0.08</v>
       </c>
       <c r="I109" s="16">
+        <f t="shared" si="19"/>
+        <v>97.2</v>
+      </c>
+      <c r="J109" s="8"/>
+      <c r="K109" s="17">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L109" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N109" s="18">
         <f t="shared" si="18"/>
-        <v>100.44</v>
-      </c>
-      <c r="J109" s="32"/>
-      <c r="K109" s="17">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="L109" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="16">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="N109" s="18">
-        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="12"/>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="19" t="s">
         <v>233</v>
       </c>
       <c r="C110" s="8" t="s">
@@ -10916,35 +10907,42 @@
         <v>126</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F110" s="7"/>
-      <c r="G110" s="13"/>
+        <v>197</v>
+      </c>
+      <c r="F110" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="G110" s="13">
+        <v>93</v>
+      </c>
       <c r="H110" s="15">
         <v>0.08</v>
       </c>
-      <c r="I110" s="16"/>
-      <c r="J110" s="8"/>
+      <c r="I110" s="16">
+        <f t="shared" si="19"/>
+        <v>100.44</v>
+      </c>
+      <c r="J110" s="32"/>
       <c r="K110" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L110" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M110" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N110" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="12"/>
-      <c r="B111" s="19" t="s">
+      <c r="B111" s="12" t="s">
         <v>234</v>
       </c>
       <c r="C111" s="8" t="s">
@@ -10956,34 +10954,27 @@
       <c r="E111" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F111" s="7">
-        <v>6.8</v>
-      </c>
-      <c r="G111" s="13">
-        <v>71</v>
-      </c>
+      <c r="F111" s="7"/>
+      <c r="G111" s="13"/>
       <c r="H111" s="15">
         <v>0.08</v>
       </c>
-      <c r="I111" s="16">
-        <f t="shared" si="18"/>
-        <v>76.68</v>
-      </c>
+      <c r="I111" s="16"/>
       <c r="J111" s="8"/>
       <c r="K111" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L111" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M111" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N111" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -11005,36 +10996,36 @@
         <v>6.8</v>
       </c>
       <c r="G112" s="13">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H112" s="15">
         <v>0.08</v>
       </c>
       <c r="I112" s="16">
-        <f t="shared" si="18"/>
-        <v>79.92</v>
+        <f t="shared" si="19"/>
+        <v>76.68</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L112" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M112" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N112" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="12"/>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="19" t="s">
         <v>236</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -11046,135 +11037,135 @@
       <c r="E113" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F113" s="7"/>
-      <c r="G113" s="13"/>
+      <c r="F113" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G113" s="13">
+        <v>74</v>
+      </c>
       <c r="H113" s="15">
         <v>0.08</v>
       </c>
-      <c r="I113" s="16"/>
+      <c r="I113" s="16">
+        <f t="shared" si="19"/>
+        <v>79.92</v>
+      </c>
       <c r="J113" s="8"/>
       <c r="K113" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L113" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M113" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N113" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="12"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="12"/>
-      <c r="E114" s="12"/>
+      <c r="B114" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="F114" s="7"/>
       <c r="G114" s="13"/>
-      <c r="H114" s="15"/>
-      <c r="I114" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="J114" s="24"/>
-      <c r="K114" s="24"/>
+      <c r="H114" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I114" s="16"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="17">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="L114" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M114" s="24"/>
-      <c r="N114" s="24"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M114" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N114" s="18">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="12"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
       <c r="F115" s="7"/>
       <c r="G115" s="13"/>
       <c r="H115" s="15"/>
-      <c r="I115" s="16"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="17"/>
+      <c r="I115" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="J115" s="24"/>
+      <c r="K115" s="24"/>
       <c r="L115" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M115" s="16"/>
-      <c r="N115" s="18">
-        <f t="shared" ref="N115:N122" si="21">M115+J115</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="12"/>
-      <c r="B116" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="11"/>
+      <c r="F116" s="7"/>
       <c r="G116" s="13"/>
       <c r="H116" s="15"/>
       <c r="I116" s="16"/>
-      <c r="J116" s="4"/>
+      <c r="J116" s="8"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M116" s="16"/>
       <c r="N116" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="N116:N123" si="22">M116+J116</f>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="12"/>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C117" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E117" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F117" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G117" s="13">
-        <v>31.5</v>
-      </c>
-      <c r="H117" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I117" s="16">
-        <f t="shared" ref="I117:I122" si="22">G117*(1+H117)</f>
-        <v>34.02</v>
-      </c>
-      <c r="J117" s="8"/>
-      <c r="K117" s="17">
-        <f t="shared" ref="K117:K122" si="23">J117*F117</f>
-        <v>0</v>
-      </c>
+      <c r="C117" s="10"/>
+      <c r="D117" s="10"/>
+      <c r="E117" s="10"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="13"/>
+      <c r="H117" s="15"/>
+      <c r="I117" s="16"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="17"/>
       <c r="L117" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="16">
-        <f t="shared" ref="M117:M122" si="24">J117*I117</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M117" s="16"/>
       <c r="N117" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11193,33 +11184,33 @@
         <v>197</v>
       </c>
       <c r="F118" s="7">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G118" s="13">
-        <v>42.5</v>
+        <v>31.5</v>
       </c>
       <c r="H118" s="15">
         <v>0.08</v>
       </c>
       <c r="I118" s="16">
-        <f t="shared" si="22"/>
-        <v>45.9</v>
+        <f t="shared" ref="I118:I123" si="23">G118*(1+H118)</f>
+        <v>34.02</v>
       </c>
       <c r="J118" s="8"/>
       <c r="K118" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="K118:K123" si="24">J118*F118</f>
         <v>0</v>
       </c>
       <c r="L118" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M118" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="M118:M123" si="25">J118*I118</f>
         <v>0</v>
       </c>
       <c r="N118" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11235,40 +11226,41 @@
         <v>123</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="F119" s="7">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G119" s="13">
-        <v>47</v>
+        <v>42.5</v>
       </c>
       <c r="H119" s="15">
         <v>0.08</v>
       </c>
       <c r="I119" s="16">
+        <f t="shared" si="23"/>
+        <v>45.9</v>
+      </c>
+      <c r="J119" s="8"/>
+      <c r="K119" s="17">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="L119" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="16">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N119" s="18">
         <f t="shared" si="22"/>
-        <v>50.76</v>
-      </c>
-      <c r="J119" s="4"/>
-      <c r="K119" s="17">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="L119" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="16">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="N119" s="18">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:14">
+      <c r="A120" s="12"/>
       <c r="B120" s="19" t="s">
         <v>241</v>
       </c>
@@ -11278,40 +11270,42 @@
       <c r="D120" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E120" s="12"/>
+      <c r="E120" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="F120" s="7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G120" s="13">
-        <v>52</v>
-      </c>
-      <c r="H120" s="33">
-        <v>0.095</v>
+        <v>47</v>
+      </c>
+      <c r="H120" s="15">
+        <v>0.08</v>
       </c>
       <c r="I120" s="16">
-        <f t="shared" si="22"/>
-        <v>56.94</v>
+        <f t="shared" si="23"/>
+        <v>50.76</v>
       </c>
       <c r="J120" s="4"/>
       <c r="K120" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L120" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M120" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N120" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:14">
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="19" t="s">
         <v>242</v>
       </c>
       <c r="C121" s="8" t="s">
@@ -11322,39 +11316,38 @@
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" s="13">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="H121" s="33">
         <v>0.095</v>
       </c>
       <c r="I121" s="16">
-        <f t="shared" si="22"/>
-        <v>37.23</v>
+        <f t="shared" si="23"/>
+        <v>56.94</v>
       </c>
       <c r="J121" s="4"/>
       <c r="K121" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L121" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M121" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N121" s="18">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" s="3" customFormat="1" spans="1:14">
-      <c r="A122" s="26"/>
-      <c r="B122" s="19" t="s">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="B122" s="12" t="s">
         <v>243</v>
       </c>
       <c r="C122" s="8" t="s">
@@ -11364,119 +11357,117 @@
         <v>123</v>
       </c>
       <c r="E122" s="12"/>
-      <c r="F122" s="34">
+      <c r="F122" s="7">
+        <v>3</v>
+      </c>
+      <c r="G122" s="13">
+        <v>34</v>
+      </c>
+      <c r="H122" s="33">
+        <v>0.095</v>
+      </c>
+      <c r="I122" s="16">
+        <f t="shared" si="23"/>
+        <v>37.23</v>
+      </c>
+      <c r="J122" s="4"/>
+      <c r="K122" s="17">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="L122" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="16">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N122" s="18">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" s="3" customFormat="1" spans="1:14">
+      <c r="A123" s="26"/>
+      <c r="B123" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E123" s="12"/>
+      <c r="F123" s="34">
         <v>2.5</v>
       </c>
-      <c r="G122" s="27">
+      <c r="G123" s="27">
         <v>40.5</v>
       </c>
-      <c r="H122" s="35">
+      <c r="H123" s="35">
         <v>0.1</v>
       </c>
-      <c r="I122" s="16">
+      <c r="I123" s="16">
+        <f t="shared" si="23"/>
+        <v>44.55</v>
+      </c>
+      <c r="J123" s="8"/>
+      <c r="K123" s="17">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="L123" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="16">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N123" s="18">
         <f t="shared" si="22"/>
-        <v>44.55</v>
-      </c>
-      <c r="J122" s="8"/>
-      <c r="K122" s="17">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="L122" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M122" s="16">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="N122" s="18">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="B123" s="12"/>
-      <c r="C123" s="12"/>
-      <c r="D123" s="12"/>
-      <c r="E123" s="12"/>
-      <c r="I123" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="J123" s="36"/>
-      <c r="K123" s="36"/>
-      <c r="L123" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M123" s="36"/>
-      <c r="N123" s="36"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="124" spans="1:14">
-      <c r="B124" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="11"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="I124" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="J124" s="36"/>
+      <c r="K124" s="36"/>
       <c r="L124" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N124" s="18">
-        <f t="shared" ref="N124:N162" si="25">M124+J124</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="36"/>
+      <c r="N124" s="36"/>
     </row>
     <row r="125" spans="1:14">
-      <c r="A125" s="12"/>
-      <c r="B125" s="19" t="s">
+      <c r="B125" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="C125" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F125" s="7">
-        <v>4</v>
-      </c>
-      <c r="G125" s="13">
-        <v>58</v>
-      </c>
-      <c r="H125" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I125" s="16">
-        <f>G125*(1+H125)</f>
-        <v>62.64</v>
-      </c>
-      <c r="J125" s="8"/>
-      <c r="K125" s="17">
-        <f>J125*F125</f>
-        <v>0</v>
-      </c>
+      <c r="C125" s="10"/>
+      <c r="D125" s="10"/>
+      <c r="E125" s="10"/>
+      <c r="F125" s="11"/>
       <c r="L125" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M125" s="16">
-        <f>J125*I125</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N125" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="N125:N163" si="26">M125+J125</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="12"/>
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="19" t="s">
         <v>246</v>
       </c>
       <c r="C126" s="8" t="s">
@@ -11485,19 +11476,21 @@
       <c r="D126" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E126" s="12"/>
+      <c r="E126" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="F126" s="7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G126" s="13">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H126" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I126" s="16">
         <f>G126*(1+H126)</f>
-        <v>82.5</v>
+        <v>62.64</v>
       </c>
       <c r="J126" s="8"/>
       <c r="K126" s="17">
@@ -11505,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M126" s="16">
@@ -11513,105 +11506,103 @@
         <v>0</v>
       </c>
       <c r="N126" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="12"/>
-      <c r="B127" s="10" t="s">
+      <c r="B127" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C127" s="10"/>
-      <c r="D127" s="10"/>
-      <c r="E127" s="10"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="13"/>
-      <c r="H127" s="15"/>
-      <c r="I127" s="16"/>
+      <c r="C127" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E127" s="12"/>
+      <c r="F127" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="G127" s="13">
+        <v>75</v>
+      </c>
+      <c r="H127" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I127" s="16">
+        <f>G127*(1+H127)</f>
+        <v>82.5</v>
+      </c>
       <c r="J127" s="8"/>
-      <c r="K127" s="17"/>
+      <c r="K127" s="17">
+        <f>J127*F127</f>
+        <v>0</v>
+      </c>
       <c r="L127" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M127" s="16"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="16">
+        <f>J127*I127</f>
+        <v>0</v>
+      </c>
       <c r="N127" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="12"/>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="C128" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="E128" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F128" s="7">
-        <v>6</v>
-      </c>
-      <c r="G128" s="13">
-        <v>163.5</v>
-      </c>
-      <c r="H128" s="15">
-        <v>0.11</v>
-      </c>
-      <c r="I128" s="16">
-        <f>G128*(1+H128)</f>
-        <v>181.485</v>
-      </c>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="13"/>
+      <c r="H128" s="15"/>
+      <c r="I128" s="16"/>
       <c r="J128" s="8"/>
-      <c r="K128" s="17">
-        <f>J128*F128</f>
-        <v>0</v>
-      </c>
+      <c r="K128" s="17"/>
       <c r="L128" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M128" s="16">
-        <f>J128*I128</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="16"/>
       <c r="N128" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="12"/>
-      <c r="B129" s="4" t="s">
-        <v>250</v>
+      <c r="B129" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E129" s="4">
         <v>1000</v>
       </c>
       <c r="F129" s="7">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G129" s="13">
-        <v>159.1</v>
+        <v>163.5</v>
       </c>
       <c r="H129" s="15">
         <v>0.11</v>
       </c>
       <c r="I129" s="16">
         <f>G129*(1+H129)</f>
-        <v>176.601</v>
+        <v>181.485</v>
       </c>
       <c r="J129" s="8"/>
       <c r="K129" s="17">
@@ -11619,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M129" s="16">
@@ -11627,20 +11618,20 @@
         <v>0</v>
       </c>
       <c r="N129" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="12"/>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="4" t="s">
         <v>251</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E130" s="4">
         <v>1000</v>
@@ -11649,14 +11640,14 @@
         <v>3.5</v>
       </c>
       <c r="G130" s="13">
-        <v>124.7</v>
+        <v>159.1</v>
       </c>
       <c r="H130" s="15">
         <v>0.11</v>
       </c>
       <c r="I130" s="16">
         <f>G130*(1+H130)</f>
-        <v>138.417</v>
+        <v>176.601</v>
       </c>
       <c r="J130" s="8"/>
       <c r="K130" s="17">
@@ -11664,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M130" s="16">
@@ -11672,20 +11663,20 @@
         <v>0</v>
       </c>
       <c r="N130" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="12"/>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="2" t="s">
         <v>252</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E131" s="4">
         <v>1000</v>
@@ -11694,14 +11685,14 @@
         <v>3.5</v>
       </c>
       <c r="G131" s="13">
-        <v>93.5</v>
+        <v>124.7</v>
       </c>
       <c r="H131" s="15">
         <v>0.11</v>
       </c>
       <c r="I131" s="16">
         <f>G131*(1+H131)</f>
-        <v>103.785</v>
+        <v>138.417</v>
       </c>
       <c r="J131" s="8"/>
       <c r="K131" s="17">
@@ -11709,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M131" s="16">
@@ -11717,131 +11708,129 @@
         <v>0</v>
       </c>
       <c r="N131" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="12"/>
-      <c r="B132" s="10" t="s">
+      <c r="B132" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C132" s="10"/>
-      <c r="D132" s="10"/>
-      <c r="E132" s="10"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="15"/>
-      <c r="I132" s="16"/>
+      <c r="C132" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E132" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F132" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="G132" s="13">
+        <v>93.5</v>
+      </c>
+      <c r="H132" s="15">
+        <v>0.11</v>
+      </c>
+      <c r="I132" s="16">
+        <f>G132*(1+H132)</f>
+        <v>103.785</v>
+      </c>
       <c r="J132" s="8"/>
-      <c r="K132" s="17"/>
+      <c r="K132" s="17">
+        <f>J132*F132</f>
+        <v>0</v>
+      </c>
       <c r="L132" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M132" s="16"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="16">
+        <f>J132*I132</f>
+        <v>0</v>
+      </c>
       <c r="N132" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:14">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="12"/>
+      <c r="B133" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B133" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="F133" s="7">
-        <v>8</v>
-      </c>
-      <c r="G133" s="13">
-        <f t="shared" ref="G133:G140" si="26">I133/(1+H133)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H133" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I133" s="16">
-        <v>140</v>
-      </c>
+      <c r="C133" s="10"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="15"/>
+      <c r="I133" s="16"/>
       <c r="J133" s="8"/>
-      <c r="K133" s="17">
-        <f t="shared" ref="K133:K157" si="27">J133*F133</f>
-        <v>0</v>
-      </c>
+      <c r="K133" s="17"/>
       <c r="L133" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M133" s="16">
-        <f t="shared" ref="M133:M157" si="28">J133*I133</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="16"/>
       <c r="N133" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B134" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>256</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="F134" s="7">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G134" s="13">
-        <f t="shared" si="26"/>
-        <v>153.752212389381</v>
+        <f t="shared" ref="G134:G141" si="27">I134/(1+H134)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H134" s="15">
         <v>0.13</v>
       </c>
       <c r="I134" s="16">
-        <v>173.74</v>
+        <v>140</v>
       </c>
       <c r="J134" s="8"/>
       <c r="K134" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="K134:K158" si="28">J134*F134</f>
         <v>0</v>
       </c>
       <c r="L134" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M134" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="M134:M158" si="29">J134*I134</f>
         <v>0</v>
       </c>
       <c r="N134" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B135" s="14" t="s">
         <v>259</v>
@@ -11850,139 +11839,139 @@
         <v>101</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="F135" s="7">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="G135" s="13">
-        <f t="shared" si="26"/>
-        <v>176.991150442478</v>
+        <f t="shared" si="27"/>
+        <v>153.752212389381</v>
       </c>
       <c r="H135" s="15">
         <v>0.13</v>
       </c>
       <c r="I135" s="16">
-        <v>200</v>
+        <v>173.74</v>
       </c>
       <c r="J135" s="8"/>
       <c r="K135" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L135" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M135" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N135" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E136" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F136" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G136" s="13">
-        <f t="shared" si="26"/>
-        <v>123.893805309735</v>
+        <f t="shared" si="27"/>
+        <v>176.991150442478</v>
       </c>
       <c r="H136" s="15">
         <v>0.13</v>
       </c>
       <c r="I136" s="16">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J136" s="8"/>
       <c r="K136" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L136" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M136" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N136" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E137" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F137" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G137" s="13">
-        <f t="shared" si="26"/>
-        <v>230.088495575221</v>
+        <f t="shared" si="27"/>
+        <v>123.893805309735</v>
       </c>
       <c r="H137" s="15">
         <v>0.13</v>
       </c>
       <c r="I137" s="16">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="J137" s="8"/>
       <c r="K137" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L137" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M137" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N137" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B138" s="14" t="s">
         <v>264</v>
@@ -11991,45 +11980,45 @@
         <v>101</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="F138" s="7">
         <v>8</v>
       </c>
       <c r="G138" s="13">
-        <f t="shared" si="26"/>
-        <v>115.929203539823</v>
+        <f t="shared" si="27"/>
+        <v>230.088495575221</v>
       </c>
       <c r="H138" s="15">
         <v>0.13</v>
       </c>
       <c r="I138" s="16">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="J138" s="8"/>
       <c r="K138" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L138" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M138" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N138" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B139" s="14" t="s">
         <v>265</v>
@@ -12038,932 +12027,935 @@
         <v>101</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="F139" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G139" s="13">
-        <f t="shared" si="26"/>
-        <v>88.495575221239</v>
+        <f t="shared" si="27"/>
+        <v>115.929203539823</v>
       </c>
       <c r="H139" s="15">
         <v>0.13</v>
       </c>
       <c r="I139" s="16">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="J139" s="8"/>
       <c r="K139" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L139" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M139" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N139" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:14">
-      <c r="A140" s="14"/>
+      <c r="A140" s="14" t="s">
+        <v>255</v>
+      </c>
       <c r="B140" s="14" t="s">
         <v>266</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>267</v>
+        <v>101</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="F140" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G140" s="13">
-        <f t="shared" si="26"/>
-        <v>129.203539823009</v>
+        <f t="shared" si="27"/>
+        <v>88.495575221239</v>
       </c>
       <c r="H140" s="15">
         <v>0.13</v>
       </c>
       <c r="I140" s="16">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="17">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="L140" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M140" s="16">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="N140" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
+      <c r="A141" s="14"/>
+      <c r="B141" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E141" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F141" s="7">
+        <v>7</v>
+      </c>
+      <c r="G141" s="13">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="L140" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M140" s="16">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="N140" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
-      <c r="A141" s="12"/>
-      <c r="B141" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E141" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="F141" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="G141" s="13">
-        <v>140</v>
+        <v>129.203539823009</v>
       </c>
       <c r="H141" s="15">
         <v>0.13</v>
       </c>
       <c r="I141" s="16">
-        <f>G141*(1+H141)</f>
-        <v>158.2</v>
+        <v>146</v>
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L141" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M141" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N141" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" s="3" customFormat="1" spans="1:14">
-      <c r="A142" s="26"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
+      <c r="A142" s="12"/>
       <c r="B142" s="12" t="s">
         <v>269</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F142" s="34">
-        <v>7.5</v>
+        <v>258</v>
+      </c>
+      <c r="F142" s="7">
+        <v>9.5</v>
       </c>
       <c r="G142" s="13">
-        <f>I142/(1+H142)</f>
-        <v>103.371681415929</v>
-      </c>
-      <c r="H142" s="35">
+        <v>140</v>
+      </c>
+      <c r="H142" s="15">
         <v>0.13</v>
       </c>
-      <c r="I142" s="37">
-        <v>116.81</v>
-      </c>
-      <c r="J142" s="34"/>
-      <c r="K142" s="38">
-        <f t="shared" si="27"/>
+      <c r="I142" s="16">
+        <f>G142*(1+H142)</f>
+        <v>158.2</v>
+      </c>
+      <c r="J142" s="8"/>
+      <c r="K142" s="17">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L142" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M142" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M142" s="16">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N142" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" s="3" customFormat="1" spans="1:14">
       <c r="A143" s="26"/>
-      <c r="B143" s="14" t="s">
+      <c r="B143" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C143" s="12" t="s">
-        <v>271</v>
+      <c r="C143" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E143" s="14" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="F143" s="34">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="G143" s="13">
         <f>I143/(1+H143)</f>
-        <v>132.743362831858</v>
+        <v>103.371681415929</v>
       </c>
       <c r="H143" s="35">
         <v>0.13</v>
       </c>
       <c r="I143" s="37">
-        <v>150</v>
+        <v>116.81</v>
       </c>
       <c r="J143" s="34"/>
       <c r="K143" s="38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L143" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M143" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N143" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" s="3" customFormat="1" spans="1:14">
       <c r="A144" s="26"/>
       <c r="B144" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>96</v>
+        <v>271</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="F144" s="34">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="G144" s="13">
-        <v>145</v>
+        <f>I144/(1+H144)</f>
+        <v>132.743362831858</v>
       </c>
       <c r="H144" s="35">
         <v>0.13</v>
       </c>
-      <c r="I144" s="16">
-        <f>G144*(1+H144)</f>
-        <v>163.85</v>
+      <c r="I144" s="37">
+        <v>150</v>
       </c>
       <c r="J144" s="34"/>
       <c r="K144" s="38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L144" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M144" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N144" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" s="3" customFormat="1" spans="1:15">
       <c r="A145" s="26"/>
       <c r="B145" s="14" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E145" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F145" s="34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G145" s="13">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="H145" s="35">
         <v>0.13</v>
       </c>
       <c r="I145" s="16">
         <f>G145*(1+H145)</f>
-        <v>114.13</v>
+        <v>163.85</v>
       </c>
       <c r="J145" s="34"/>
       <c r="K145" s="38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L145" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M145" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N145" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" s="3" customFormat="1" spans="1:15">
       <c r="A146" s="26"/>
-      <c r="B146" s="12" t="s">
+      <c r="B146" s="14" t="s">
         <v>273</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E146" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F146" s="34">
-        <v>6</v>
-      </c>
-      <c r="G146" s="27">
-        <v>115</v>
+        <v>4</v>
+      </c>
+      <c r="G146" s="13">
+        <v>101</v>
       </c>
       <c r="H146" s="35">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I146" s="16">
         <f>G146*(1+H146)</f>
-        <v>124.2</v>
-      </c>
-      <c r="J146" s="8"/>
-      <c r="K146" s="17">
-        <f t="shared" si="27"/>
+        <v>114.13</v>
+      </c>
+      <c r="J146" s="34"/>
+      <c r="K146" s="38">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L146" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M146" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M146" s="37">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N146" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" s="3" customFormat="1" spans="1:15">
-      <c r="A147" s="14"/>
-      <c r="B147" s="14" t="s">
-        <v>261</v>
+      <c r="A147" s="26"/>
+      <c r="B147" s="12" t="s">
+        <v>274</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E147" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F147" s="7">
-        <v>4</v>
-      </c>
-      <c r="G147" s="13">
-        <f>I147/(1+H147)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H147" s="15">
-        <v>0.13</v>
+      <c r="F147" s="34">
+        <v>6</v>
+      </c>
+      <c r="G147" s="27">
+        <v>115</v>
+      </c>
+      <c r="H147" s="35">
+        <v>0.08</v>
       </c>
       <c r="I147" s="16">
-        <v>140</v>
+        <f>G147*(1+H147)</f>
+        <v>124.2</v>
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L147" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M147" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N147" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="O147" s="2"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="148" s="3" customFormat="1" spans="1:15">
-      <c r="A148" s="26"/>
-      <c r="B148" s="12" t="s">
-        <v>274</v>
+      <c r="A148" s="14"/>
+      <c r="B148" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>275</v>
+        <v>96</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="E148" s="14"/>
-      <c r="F148" s="34">
-        <v>11</v>
-      </c>
-      <c r="G148" s="27">
-        <f>I148-1</f>
-        <v>177.5</v>
-      </c>
-      <c r="H148" s="35"/>
+        <v>263</v>
+      </c>
+      <c r="E148" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F148" s="7">
+        <v>4</v>
+      </c>
+      <c r="G148" s="13">
+        <f>I148/(1+H148)</f>
+        <v>123.893805309735</v>
+      </c>
+      <c r="H148" s="15">
+        <v>0.13</v>
+      </c>
       <c r="I148" s="16">
-        <v>178.5</v>
+        <v>140</v>
       </c>
       <c r="J148" s="8"/>
       <c r="K148" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L148" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M148" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N148" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="O148" s="2"/>
     </row>
     <row r="149" s="3" customFormat="1" spans="1:15">
       <c r="A149" s="26"/>
       <c r="B149" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D149" s="13" t="s">
         <v>277</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>278</v>
       </c>
       <c r="E149" s="14"/>
       <c r="F149" s="34">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G149" s="27">
         <f>I149-1</f>
-        <v>127.5</v>
+        <v>177.5</v>
       </c>
       <c r="H149" s="35"/>
       <c r="I149" s="16">
-        <v>128.5</v>
+        <v>178.5</v>
       </c>
       <c r="J149" s="8"/>
       <c r="K149" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L149" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M149" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N149" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" s="3" customFormat="1" spans="1:15">
-      <c r="A150" s="14"/>
-      <c r="B150" s="14" t="s">
-        <v>259</v>
+      <c r="A150" s="26"/>
+      <c r="B150" s="12" t="s">
+        <v>278</v>
       </c>
       <c r="C150" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D150" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E150" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F150" s="7">
-        <v>6</v>
-      </c>
-      <c r="G150" s="13">
-        <f>I150/(1+H150)</f>
-        <v>176.991150442478</v>
-      </c>
-      <c r="H150" s="15">
-        <v>0.13</v>
-      </c>
+      <c r="E150" s="14"/>
+      <c r="F150" s="34">
+        <v>8</v>
+      </c>
+      <c r="G150" s="27">
+        <f>I150-1</f>
+        <v>127.5</v>
+      </c>
+      <c r="H150" s="35"/>
       <c r="I150" s="16">
-        <v>200</v>
+        <v>128.5</v>
       </c>
       <c r="J150" s="8"/>
       <c r="K150" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L150" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M150" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N150" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="3" customFormat="1" spans="1:15">
       <c r="A151" s="14"/>
       <c r="B151" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D151" s="13" t="s">
         <v>261</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>262</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F151" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G151" s="13">
         <f>I151/(1+H151)</f>
-        <v>123.893805309735</v>
+        <v>176.991150442478</v>
       </c>
       <c r="H151" s="15">
         <v>0.13</v>
       </c>
       <c r="I151" s="16">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J151" s="8"/>
       <c r="K151" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L151" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M151" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N151" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
-      <c r="A152" s="26"/>
-      <c r="B152" s="12" t="s">
-        <v>273</v>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" s="3" customFormat="1" spans="1:15">
+      <c r="A152" s="14"/>
+      <c r="B152" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F152" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G152" s="13">
-        <v>115</v>
+        <f>I152/(1+H152)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H152" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I152" s="16">
-        <f>G152*(1+H152)</f>
-        <v>124.2</v>
+        <v>140</v>
       </c>
       <c r="J152" s="8"/>
       <c r="K152" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L152" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M152" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N152" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" s="3" customFormat="1" spans="1:15">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
       <c r="A153" s="26"/>
-      <c r="B153" s="19" t="s">
+      <c r="B153" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C153" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C153" s="8" t="s">
-        <v>279</v>
-      </c>
       <c r="D153" s="13" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="F153" s="7">
         <v>6</v>
       </c>
       <c r="G153" s="13">
-        <f>I153-1</f>
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H153" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I153" s="16">
-        <v>108</v>
+        <f>G153*(1+H153)</f>
+        <v>124.2</v>
       </c>
       <c r="J153" s="8"/>
       <c r="K153" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L153" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M153" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N153" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" s="3" customFormat="1" spans="1:15">
       <c r="A154" s="26"/>
-      <c r="B154" s="12" t="s">
-        <v>269</v>
+      <c r="B154" s="19" t="s">
+        <v>281</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="F154" s="7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G154" s="13">
         <f>I154-1</f>
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H154" s="15">
         <v>0.13</v>
       </c>
-      <c r="I154" s="39">
-        <v>135</v>
-      </c>
-      <c r="J154" s="34"/>
-      <c r="K154" s="38">
-        <f t="shared" si="27"/>
+      <c r="I154" s="16">
+        <v>108</v>
+      </c>
+      <c r="J154" s="8"/>
+      <c r="K154" s="17">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L154" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M154" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M154" s="16">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N154" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" s="3" customFormat="1" spans="1:15">
-      <c r="A155" s="12"/>
-      <c r="B155" s="19" t="s">
-        <v>268</v>
+      <c r="A155" s="26"/>
+      <c r="B155" s="12" t="s">
+        <v>270</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E155" s="14" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="F155" s="7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G155" s="13">
         <f>I155-1</f>
-        <v>150.2</v>
+        <v>134</v>
       </c>
       <c r="H155" s="15">
         <v>0.13</v>
       </c>
-      <c r="I155" s="16">
-        <v>151.2</v>
-      </c>
-      <c r="J155" s="8"/>
-      <c r="K155" s="17">
-        <f t="shared" si="27"/>
+      <c r="I155" s="39">
+        <v>135</v>
+      </c>
+      <c r="J155" s="34"/>
+      <c r="K155" s="38">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L155" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M155" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M155" s="37">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N155" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" s="3" customFormat="1" spans="1:15">
-      <c r="A156" s="26"/>
-      <c r="B156" s="12" t="s">
-        <v>281</v>
+      <c r="A156" s="12"/>
+      <c r="B156" s="19" t="s">
+        <v>269</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="F156" s="7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G156" s="13">
         <f>I156-1</f>
-        <v>134</v>
+        <v>150.2</v>
       </c>
       <c r="H156" s="15">
         <v>0.13</v>
       </c>
       <c r="I156" s="16">
-        <v>135</v>
+        <v>151.2</v>
       </c>
       <c r="J156" s="8"/>
-      <c r="K156" s="38">
-        <f t="shared" si="27"/>
+      <c r="K156" s="17">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L156" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M156" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M156" s="16">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N156" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" s="3" customFormat="1" spans="1:15">
       <c r="A157" s="26"/>
       <c r="B157" s="12" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>197</v>
       </c>
       <c r="F157" s="7">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G157" s="13">
         <f>I157-1</f>
-        <v>177.2</v>
+        <v>134</v>
       </c>
       <c r="H157" s="15">
         <v>0.13</v>
       </c>
       <c r="I157" s="16">
-        <v>178.2</v>
+        <v>135</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="38">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L157" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M157" s="37">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N157" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" s="3" customFormat="1" spans="1:15">
       <c r="A158" s="26"/>
-      <c r="B158" s="26"/>
-      <c r="C158" s="26"/>
-      <c r="D158" s="26"/>
-      <c r="E158" s="26"/>
-      <c r="F158" s="34"/>
-      <c r="G158" s="27"/>
-      <c r="H158" s="35"/>
-      <c r="I158" s="16"/>
+      <c r="B158" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E158" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F158" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="G158" s="13">
+        <f>I158-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H158" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I158" s="16">
+        <v>178.2</v>
+      </c>
       <c r="J158" s="8"/>
-      <c r="K158" s="17"/>
+      <c r="K158" s="38">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="L158" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M158" s="16"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M158" s="37">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="N158" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" s="3" customFormat="1" spans="1:15">
       <c r="A159" s="26"/>
-      <c r="B159" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="C159" s="10"/>
-      <c r="D159" s="10"/>
-      <c r="E159" s="10"/>
-      <c r="F159" s="11"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="26"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="26"/>
+      <c r="F159" s="34"/>
       <c r="G159" s="27"/>
       <c r="H159" s="35"/>
       <c r="I159" s="16"/>
       <c r="J159" s="8"/>
       <c r="K159" s="17"/>
       <c r="L159" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M159" s="16"/>
       <c r="N159" s="18">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15">
-      <c r="B160" s="40" t="s">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" s="3" customFormat="1" spans="1:15">
+      <c r="A160" s="26"/>
+      <c r="B160" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="C160" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D160" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E160" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F160" s="7">
-        <v>8</v>
-      </c>
-      <c r="G160" s="13">
-        <v>90</v>
-      </c>
-      <c r="H160" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I160" s="16">
-        <f>G160*(1+H160)</f>
-        <v>97.2</v>
-      </c>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="11"/>
+      <c r="G160" s="27"/>
+      <c r="H160" s="35"/>
+      <c r="I160" s="16"/>
       <c r="J160" s="8"/>
-      <c r="K160" s="17">
-        <f>J160*F160</f>
-        <v>0</v>
-      </c>
+      <c r="K160" s="17"/>
       <c r="L160" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M160" s="16">
-        <f>J160*I160</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M160" s="16"/>
       <c r="N160" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -12975,7 +12967,7 @@
         <v>94</v>
       </c>
       <c r="D161" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E161" s="41">
         <v>1000</v>
@@ -12984,14 +12976,14 @@
         <v>8</v>
       </c>
       <c r="G161" s="13">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H161" s="15">
         <v>0.08</v>
       </c>
       <c r="I161" s="16">
         <f>G161*(1+H161)</f>
-        <v>99.36</v>
+        <v>97.2</v>
       </c>
       <c r="J161" s="8"/>
       <c r="K161" s="17">
@@ -12999,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="17">
-        <f t="shared" ref="L161:L190" si="29">K161+J161/2</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M161" s="16">
@@ -13007,7 +12999,7 @@
         <v>0</v>
       </c>
       <c r="N161" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -13019,23 +13011,23 @@
         <v>94</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E162" s="41">
         <v>1000</v>
       </c>
       <c r="F162" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G162" s="13">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H162" s="15">
         <v>0.08</v>
       </c>
       <c r="I162" s="16">
         <f>G162*(1+H162)</f>
-        <v>93.96</v>
+        <v>99.36</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="17">
@@ -13043,7 +13035,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="L162:L191" si="30">K162+J162/2</f>
         <v>0</v>
       </c>
       <c r="M162" s="16">
@@ -13051,73 +13043,73 @@
         <v>0</v>
       </c>
       <c r="N162" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:14">
-      <c r="B163" s="10" t="s">
+      <c r="B163" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="C163" s="10"/>
-      <c r="D163" s="10"/>
-      <c r="E163" s="10"/>
-      <c r="F163" s="11"/>
-      <c r="G163" s="13"/>
-      <c r="H163" s="15"/>
-      <c r="I163" s="16"/>
+      <c r="C163" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E163" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F163" s="7">
+        <v>7</v>
+      </c>
+      <c r="G163" s="13">
+        <v>87</v>
+      </c>
+      <c r="H163" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I163" s="16">
+        <f>G163*(1+H163)</f>
+        <v>93.96</v>
+      </c>
       <c r="J163" s="8"/>
-      <c r="K163" s="17"/>
+      <c r="K163" s="17">
+        <f>J163*F163</f>
+        <v>0</v>
+      </c>
       <c r="L163" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M163" s="16"/>
-      <c r="N163" s="18"/>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M163" s="16">
+        <f>J163*I163</f>
+        <v>0</v>
+      </c>
+      <c r="N163" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="164" spans="1:14">
-      <c r="B164" s="40" t="s">
+      <c r="B164" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C164" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="E164" s="41">
-        <v>300</v>
-      </c>
-      <c r="F164" s="7">
-        <v>4.65</v>
-      </c>
-      <c r="G164" s="13">
-        <v>61.5</v>
-      </c>
-      <c r="H164" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="I164" s="16">
-        <f>G164*(1+H164)</f>
-        <v>67.65</v>
-      </c>
+      <c r="C164" s="10"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="10"/>
+      <c r="F164" s="11"/>
+      <c r="G164" s="13"/>
+      <c r="H164" s="15"/>
+      <c r="I164" s="16"/>
       <c r="J164" s="8"/>
-      <c r="K164" s="17">
-        <f>J164*F164</f>
-        <v>0</v>
-      </c>
+      <c r="K164" s="17"/>
       <c r="L164" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M164" s="16">
-        <f>J164*I164</f>
-        <v>0</v>
-      </c>
-      <c r="N164" s="18">
-        <f t="shared" ref="N164:N190" si="30">M164+J164</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="16"/>
+      <c r="N164" s="18"/>
     </row>
     <row r="165" spans="1:14">
       <c r="B165" s="40" t="s">
@@ -13127,23 +13119,23 @@
         <v>93</v>
       </c>
       <c r="D165" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E165" s="41">
         <v>300</v>
       </c>
       <c r="F165" s="7">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="G165" s="13">
-        <v>64.5</v>
+        <v>61.5</v>
       </c>
       <c r="H165" s="15">
         <v>0.1</v>
       </c>
       <c r="I165" s="16">
         <f>G165*(1+H165)</f>
-        <v>70.95</v>
+        <v>67.65</v>
       </c>
       <c r="J165" s="8"/>
       <c r="K165" s="17">
@@ -13151,7 +13143,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M165" s="16">
@@ -13159,36 +13151,35 @@
         <v>0</v>
       </c>
       <c r="N165" s="18">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" s="3" customFormat="1" spans="1:14">
-      <c r="A166" s="26"/>
-      <c r="B166" s="36" t="s">
+        <f t="shared" ref="N165:N191" si="31">M165+J165</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14">
+      <c r="B166" s="40" t="s">
         <v>289</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E166" s="41">
         <v>300</v>
       </c>
       <c r="F166" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="G166" s="27">
-        <v>76.5</v>
-      </c>
-      <c r="H166" s="35">
+        <v>5.15</v>
+      </c>
+      <c r="G166" s="13">
+        <v>64.5</v>
+      </c>
+      <c r="H166" s="15">
         <v>0.1</v>
       </c>
       <c r="I166" s="16">
         <f>G166*(1+H166)</f>
-        <v>84.15</v>
+        <v>70.95</v>
       </c>
       <c r="J166" s="8"/>
       <c r="K166" s="17">
@@ -13196,7 +13187,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M166" s="16">
@@ -13204,36 +13195,36 @@
         <v>0</v>
       </c>
       <c r="N166" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="167" s="3" customFormat="1" spans="1:14">
       <c r="A167" s="26"/>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="36" t="s">
         <v>290</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E167" s="41">
         <v>300</v>
       </c>
       <c r="F167" s="7">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="G167" s="27">
-        <v>94.5</v>
+        <v>76.5</v>
       </c>
       <c r="H167" s="35">
         <v>0.1</v>
       </c>
       <c r="I167" s="16">
         <f>G167*(1+H167)</f>
-        <v>103.95</v>
+        <v>84.15</v>
       </c>
       <c r="J167" s="8"/>
       <c r="K167" s="17">
@@ -13241,7 +13232,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M167" s="16">
@@ -13249,222 +13240,223 @@
         <v>0</v>
       </c>
       <c r="N167" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" s="3" customFormat="1" spans="1:14">
       <c r="A168" s="26"/>
-      <c r="B168" s="27"/>
-      <c r="C168" s="27"/>
-      <c r="D168" s="27"/>
-      <c r="E168" s="27"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="27"/>
-      <c r="H168" s="35"/>
-      <c r="I168" s="16"/>
+      <c r="B168" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E168" s="41">
+        <v>300</v>
+      </c>
+      <c r="F168" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="G168" s="27">
+        <v>94.5</v>
+      </c>
+      <c r="H168" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="I168" s="16">
+        <f>G168*(1+H168)</f>
+        <v>103.95</v>
+      </c>
       <c r="J168" s="8"/>
-      <c r="K168" s="17"/>
+      <c r="K168" s="17">
+        <f>J168*F168</f>
+        <v>0</v>
+      </c>
       <c r="L168" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M168" s="16"/>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M168" s="16">
+        <f>J168*I168</f>
+        <v>0</v>
+      </c>
       <c r="N168" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" s="3" customFormat="1" spans="1:14">
       <c r="A169" s="26"/>
-      <c r="B169" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C169" s="42"/>
-      <c r="D169" s="42"/>
-      <c r="E169" s="42"/>
-      <c r="F169" s="43"/>
+      <c r="B169" s="27"/>
+      <c r="C169" s="27"/>
+      <c r="D169" s="27"/>
+      <c r="E169" s="27"/>
+      <c r="F169" s="27"/>
       <c r="G169" s="27"/>
       <c r="H169" s="35"/>
       <c r="I169" s="16"/>
       <c r="J169" s="8"/>
       <c r="K169" s="17"/>
       <c r="L169" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M169" s="16"/>
       <c r="N169" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" s="3" customFormat="1" spans="1:14">
+      <c r="A170" s="26"/>
+      <c r="B170" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C170" s="42"/>
+      <c r="D170" s="42"/>
+      <c r="E170" s="42"/>
+      <c r="F170" s="43"/>
+      <c r="G170" s="27"/>
+      <c r="H170" s="35"/>
+      <c r="I170" s="16"/>
+      <c r="J170" s="8"/>
+      <c r="K170" s="17"/>
+      <c r="L170" s="17">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:14">
-      <c r="B170" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="E170" s="41">
-        <v>500</v>
-      </c>
-      <c r="F170" s="7">
-        <v>5</v>
-      </c>
-      <c r="G170" s="13">
-        <v>67.5</v>
-      </c>
-      <c r="H170" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I170" s="16">
-        <f t="shared" ref="I170:I190" si="31">G170*(1+H170)</f>
-        <v>72.9</v>
-      </c>
-      <c r="J170" s="8"/>
-      <c r="K170" s="17">
-        <f t="shared" ref="K170:K190" si="32">J170*F170</f>
-        <v>0</v>
-      </c>
-      <c r="L170" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M170" s="16">
-        <f t="shared" ref="M170:M190" si="33">J170*I170</f>
-        <v>0</v>
-      </c>
+      <c r="M170" s="16"/>
       <c r="N170" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="B171" s="40" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D171" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E171" s="41">
         <v>500</v>
       </c>
       <c r="F171" s="7">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="G171" s="13">
-        <v>79</v>
+        <v>67.5</v>
       </c>
       <c r="H171" s="15">
         <v>0.08</v>
       </c>
       <c r="I171" s="16">
-        <f t="shared" si="31"/>
-        <v>85.32</v>
+        <f t="shared" ref="I171:I191" si="32">G171*(1+H171)</f>
+        <v>72.9</v>
       </c>
       <c r="J171" s="8"/>
       <c r="K171" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="K171:K191" si="33">J171*F171</f>
         <v>0</v>
       </c>
       <c r="L171" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M171" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="M171:M191" si="34">J171*I171</f>
         <v>0</v>
       </c>
       <c r="N171" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:14">
-      <c r="B172" s="41" t="s">
+      <c r="B172" s="40" t="s">
         <v>295</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E172" s="41">
         <v>500</v>
       </c>
-      <c r="F172" s="7"/>
-      <c r="G172" s="13"/>
+      <c r="F172" s="7">
+        <v>6.2</v>
+      </c>
+      <c r="G172" s="13">
+        <v>79</v>
+      </c>
       <c r="H172" s="15">
         <v>0.08</v>
       </c>
-      <c r="I172" s="16"/>
+      <c r="I172" s="16">
+        <f t="shared" si="32"/>
+        <v>85.32</v>
+      </c>
       <c r="J172" s="8"/>
       <c r="K172" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L172" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M172" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N172" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:14">
-      <c r="B173" s="40" t="s">
+      <c r="B173" s="41" t="s">
         <v>296</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E173" s="41">
         <v>500</v>
       </c>
-      <c r="F173" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="G173" s="13">
-        <v>105</v>
-      </c>
+      <c r="F173" s="7"/>
+      <c r="G173" s="13"/>
       <c r="H173" s="15">
         <v>0.08</v>
       </c>
-      <c r="I173" s="16">
-        <f t="shared" si="31"/>
-        <v>113.4</v>
-      </c>
+      <c r="I173" s="16"/>
       <c r="J173" s="8"/>
       <c r="K173" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L173" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M173" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N173" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -13476,83 +13468,83 @@
         <v>94</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E174" s="41">
         <v>500</v>
       </c>
       <c r="F174" s="7">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G174" s="13">
-        <v>117.5</v>
+        <v>105</v>
       </c>
       <c r="H174" s="15">
         <v>0.08</v>
       </c>
       <c r="I174" s="16">
-        <f t="shared" si="31"/>
-        <v>126.9</v>
+        <f t="shared" si="32"/>
+        <v>113.4</v>
       </c>
       <c r="J174" s="8"/>
       <c r="K174" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L174" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M174" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N174" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:14">
-      <c r="B175" s="41" t="s">
+      <c r="B175" s="40" t="s">
         <v>298</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E175" s="41">
         <v>500</v>
       </c>
       <c r="F175" s="7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G175" s="13">
-        <v>122.5</v>
+        <v>117.5</v>
       </c>
       <c r="H175" s="15">
         <v>0.08</v>
       </c>
       <c r="I175" s="16">
-        <f t="shared" si="31"/>
-        <v>132.3</v>
+        <f t="shared" si="32"/>
+        <v>126.9</v>
       </c>
       <c r="J175" s="8"/>
       <c r="K175" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L175" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M175" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N175" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -13563,429 +13555,438 @@
       <c r="C176" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D176" s="41" t="s">
-        <v>300</v>
+      <c r="D176" s="13" t="s">
+        <v>294</v>
       </c>
       <c r="E176" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F176" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G176" s="13">
-        <v>100</v>
+        <v>122.5</v>
       </c>
       <c r="H176" s="15">
         <v>0.08</v>
       </c>
       <c r="I176" s="16">
-        <f t="shared" si="31"/>
-        <v>108</v>
+        <f t="shared" si="32"/>
+        <v>132.3</v>
       </c>
       <c r="J176" s="8"/>
       <c r="K176" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L176" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M176" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N176" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:14">
-      <c r="B177" s="6" t="s">
-        <v>301</v>
+      <c r="B177" s="41" t="s">
+        <v>300</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D177" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E177" s="41">
         <v>5000</v>
       </c>
       <c r="F177" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G177" s="13">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="H177" s="15">
         <v>0.08</v>
       </c>
       <c r="I177" s="16">
-        <f t="shared" si="31"/>
-        <v>156.6</v>
+        <f t="shared" si="32"/>
+        <v>108</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L177" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M177" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N177" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:14">
-      <c r="B178" s="41" t="s">
+      <c r="B178" s="6" t="s">
         <v>302</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D178" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E178" s="41">
         <v>5000</v>
       </c>
       <c r="F178" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G178" s="13">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="H178" s="15">
         <v>0.08</v>
       </c>
       <c r="I178" s="16">
-        <f t="shared" si="31"/>
-        <v>145.8</v>
+        <f t="shared" si="32"/>
+        <v>156.6</v>
       </c>
       <c r="J178" s="8"/>
       <c r="K178" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L178" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M178" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N178" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:14">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6" t="s">
+      <c r="B179" s="41" t="s">
         <v>303</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D179" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E179" s="41">
         <v>5000</v>
       </c>
       <c r="F179" s="7">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="G179" s="13">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="H179" s="15">
         <v>0.08</v>
       </c>
       <c r="I179" s="16">
-        <f t="shared" si="31"/>
-        <v>189</v>
+        <f t="shared" si="32"/>
+        <v>145.8</v>
       </c>
       <c r="J179" s="8"/>
       <c r="K179" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L179" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M179" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N179" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:14">
-      <c r="B180" s="41" t="s">
+      <c r="A180" s="6"/>
+      <c r="B180" s="6" t="s">
         <v>304</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D180" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E180" s="41">
         <v>5000</v>
       </c>
       <c r="F180" s="7">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="G180" s="13">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H180" s="15">
         <v>0.08</v>
       </c>
       <c r="I180" s="16">
-        <f t="shared" si="31"/>
-        <v>172.8</v>
+        <f t="shared" si="32"/>
+        <v>189</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L180" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M180" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N180" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:14">
-      <c r="B181" s="44" t="s">
+      <c r="B181" s="41" t="s">
         <v>305</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D181" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E181" s="41">
         <v>5000</v>
       </c>
       <c r="F181" s="7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G181" s="13">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="H181" s="15">
         <v>0.08</v>
       </c>
       <c r="I181" s="16">
-        <f t="shared" si="31"/>
-        <v>205.2</v>
+        <f t="shared" si="32"/>
+        <v>172.8</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L181" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M181" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N181" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:14">
-      <c r="B182" s="41" t="s">
+      <c r="B182" s="44" t="s">
         <v>306</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D182" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E182" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F182" s="7">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="G182" s="13">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="H182" s="15">
         <v>0.08</v>
       </c>
       <c r="I182" s="16">
-        <f t="shared" si="31"/>
-        <v>58.32</v>
+        <f t="shared" si="32"/>
+        <v>205.2</v>
       </c>
       <c r="J182" s="8"/>
       <c r="K182" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L182" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M182" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N182" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:14">
-      <c r="B183" s="40" t="s">
+      <c r="B183" s="41" t="s">
         <v>307</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D183" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E183" s="41">
         <v>1000</v>
       </c>
       <c r="F183" s="7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G183" s="13">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H183" s="15">
         <v>0.08</v>
       </c>
       <c r="I183" s="16">
-        <f t="shared" si="31"/>
-        <v>62.64</v>
+        <f t="shared" si="32"/>
+        <v>58.32</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L183" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M183" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N183" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:14">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6" t="s">
+      <c r="B184" s="40" t="s">
         <v>308</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D184" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E184" s="41">
         <v>1000</v>
       </c>
       <c r="F184" s="7">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="G184" s="13">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H184" s="15">
         <v>0.08</v>
       </c>
       <c r="I184" s="16">
-        <f t="shared" si="31"/>
-        <v>68.04</v>
+        <f t="shared" si="32"/>
+        <v>62.64</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L184" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M184" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N184" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:14">
-      <c r="B185" s="41" t="s">
+      <c r="A185" s="6"/>
+      <c r="B185" s="6" t="s">
         <v>309</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D185" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E185" s="41">
         <v>1000</v>
       </c>
-      <c r="F185" s="7"/>
-      <c r="G185" s="13"/>
-      <c r="H185" s="15"/>
-      <c r="I185" s="16"/>
+      <c r="F185" s="7">
+        <v>3.3</v>
+      </c>
+      <c r="G185" s="13">
+        <v>63</v>
+      </c>
+      <c r="H185" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I185" s="16">
+        <f t="shared" si="32"/>
+        <v>68.04</v>
+      </c>
       <c r="J185" s="8"/>
       <c r="K185" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L185" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M185" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N185" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -13997,7 +13998,7 @@
         <v>94</v>
       </c>
       <c r="D186" s="41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E186" s="41">
         <v>1000</v>
@@ -14008,75 +14009,66 @@
       <c r="I186" s="16"/>
       <c r="J186" s="8"/>
       <c r="K186" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L186" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M186" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N186" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:14">
-      <c r="B187" s="40" t="s">
+      <c r="B187" s="41" t="s">
         <v>311</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D187" s="13" t="s">
-        <v>313</v>
+        <v>94</v>
+      </c>
+      <c r="D187" s="41" t="s">
+        <v>301</v>
       </c>
       <c r="E187" s="41">
-        <v>2000</v>
-      </c>
-      <c r="F187" s="7">
-        <v>5</v>
-      </c>
-      <c r="G187" s="13">
-        <v>140</v>
-      </c>
-      <c r="H187" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I187" s="16">
-        <f t="shared" si="31"/>
-        <v>151.2</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F187" s="7"/>
+      <c r="G187" s="13"/>
+      <c r="H187" s="15"/>
+      <c r="I187" s="16"/>
       <c r="J187" s="8"/>
       <c r="K187" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L187" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M187" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N187" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:14">
       <c r="B188" s="40" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C188" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D188" s="13" t="s">
         <v>314</v>
-      </c>
-      <c r="D188" s="13" t="s">
-        <v>313</v>
       </c>
       <c r="E188" s="41">
         <v>2000</v>
@@ -14091,149 +14083,172 @@
         <v>0.08</v>
       </c>
       <c r="I188" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>151.2</v>
       </c>
       <c r="J188" s="8"/>
       <c r="K188" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L188" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M188" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N188" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:14">
-      <c r="B189" s="41" t="s">
-        <v>311</v>
+      <c r="B189" s="40" t="s">
+        <v>312</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>96</v>
+        <v>315</v>
       </c>
       <c r="D189" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E189" s="41">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F189" s="7">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G189" s="13">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="H189" s="15">
         <v>0.08</v>
       </c>
       <c r="I189" s="16">
-        <f t="shared" si="31"/>
-        <v>75.6</v>
+        <f t="shared" si="32"/>
+        <v>151.2</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L189" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M189" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N189" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="B190" s="41" t="s">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D190" s="13" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="E190" s="41">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F190" s="7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G190" s="13">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H190" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I190" s="16">
-        <f t="shared" si="31"/>
-        <v>114.13</v>
+        <f t="shared" si="32"/>
+        <v>75.6</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="17">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="L190" s="17">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M190" s="16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N190" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14">
+      <c r="B191" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E191" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F191" s="7">
+        <v>4</v>
+      </c>
+      <c r="G191" s="13">
+        <v>101</v>
+      </c>
+      <c r="H191" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I191" s="16">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="L190" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M190" s="16">
+        <v>114.13</v>
+      </c>
+      <c r="J191" s="8"/>
+      <c r="K191" s="17">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="N190" s="18">
+      <c r="L191" s="17">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:14">
-      <c r="F191" s="7"/>
-      <c r="G191" s="13"/>
-      <c r="H191" s="15"/>
-      <c r="J191" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="K191" s="17">
-        <f>SUM(J6:J189)</f>
-        <v>0</v>
-      </c>
-      <c r="L191" s="6" t="s">
-        <v>316</v>
+      <c r="M191" s="16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N191" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:14">
-      <c r="A192" s="45"/>
-      <c r="B192" s="45"/>
-      <c r="C192" s="45"/>
-      <c r="D192" s="45"/>
-      <c r="E192" s="45"/>
       <c r="F192" s="7"/>
       <c r="G192" s="13"/>
       <c r="H192" s="15"/>
-      <c r="I192" s="45"/>
-      <c r="J192" s="41" t="s">
+      <c r="J192" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="K192" s="17">
+        <f>SUM(J6:J190)</f>
+        <v>0</v>
+      </c>
+      <c r="L192" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="K192" s="7">
-        <f>SUM(K6:K189)</f>
-        <v>0</v>
-      </c>
-      <c r="L192" s="6" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -14242,21 +14257,20 @@
       <c r="C193" s="45"/>
       <c r="D193" s="45"/>
       <c r="E193" s="45"/>
-      <c r="F193" s="45"/>
+      <c r="F193" s="7"/>
       <c r="G193" s="13"/>
       <c r="H193" s="15"/>
       <c r="I193" s="45"/>
       <c r="J193" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="K193" s="7">
+        <f>SUM(K6:K190)</f>
+        <v>0</v>
+      </c>
+      <c r="L193" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="K193" s="4">
-        <f>SUM(L:L)</f>
-        <v>0</v>
-      </c>
-      <c r="L193" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="M193" s="41"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="45"/>
@@ -14271,11 +14285,13 @@
       <c r="J194" s="41" t="s">
         <v>320</v>
       </c>
-      <c r="K194" s="45">
-        <f>SUM(N5:N190)</f>
-        <v>0</v>
-      </c>
-      <c r="L194" s="45"/>
+      <c r="K194" s="4">
+        <f>SUM(L:L)</f>
+        <v>0</v>
+      </c>
+      <c r="L194" s="46" t="s">
+        <v>319</v>
+      </c>
       <c r="M194" s="41"/>
     </row>
     <row r="195" spans="1:13">
@@ -14288,8 +14304,13 @@
       <c r="G195" s="13"/>
       <c r="H195" s="15"/>
       <c r="I195" s="45"/>
-      <c r="J195" s="45"/>
-      <c r="K195" s="45"/>
+      <c r="J195" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="K195" s="45">
+        <f>SUM(N5:N191)</f>
+        <v>0</v>
+      </c>
       <c r="L195" s="45"/>
       <c r="M195" s="41"/>
     </row>
@@ -14315,7 +14336,7 @@
       <c r="D197" s="45"/>
       <c r="E197" s="45"/>
       <c r="F197" s="45"/>
-      <c r="G197" s="45"/>
+      <c r="G197" s="13"/>
       <c r="H197" s="15"/>
       <c r="I197" s="45"/>
       <c r="J197" s="45"/>
@@ -14350,9 +14371,7 @@
       <c r="I199" s="45"/>
       <c r="J199" s="45"/>
       <c r="K199" s="45"/>
-      <c r="L199" s="45" t="s">
-        <v>220</v>
-      </c>
+      <c r="L199" s="45"/>
       <c r="M199" s="41"/>
     </row>
     <row r="200" spans="1:13">
@@ -14363,11 +14382,13 @@
       <c r="E200" s="45"/>
       <c r="F200" s="45"/>
       <c r="G200" s="45"/>
-      <c r="H200" s="45"/>
+      <c r="H200" s="15"/>
       <c r="I200" s="45"/>
       <c r="J200" s="45"/>
       <c r="K200" s="45"/>
-      <c r="L200" s="45"/>
+      <c r="L200" s="45" t="s">
+        <v>221</v>
+      </c>
       <c r="M200" s="41"/>
     </row>
     <row r="201" spans="1:13">
@@ -14415,33 +14436,48 @@
       <c r="L203" s="45"/>
       <c r="M203" s="41"/>
     </row>
-    <row r="205" spans="1:13">
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-    </row>
-    <row r="207" spans="1:13">
-      <c r="J207" s="6"/>
+    <row r="204" spans="1:13">
+      <c r="A204" s="45"/>
+      <c r="B204" s="45"/>
+      <c r="C204" s="45"/>
+      <c r="D204" s="45"/>
+      <c r="E204" s="45"/>
+      <c r="F204" s="45"/>
+      <c r="G204" s="45"/>
+      <c r="H204" s="45"/>
+      <c r="I204" s="45"/>
+      <c r="J204" s="45"/>
+      <c r="K204" s="45"/>
+      <c r="L204" s="45"/>
+      <c r="M204" s="41"/>
+    </row>
+    <row r="206" spans="1:13">
+      <c r="B206" s="6"/>
+      <c r="C206" s="6"/>
+      <c r="D206" s="6"/>
+      <c r="E206" s="6"/>
     </row>
     <row r="208" spans="1:13">
-      <c r="K208" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="209" spans="2:5">
-      <c r="B209" s="6"/>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-    </row>
-    <row r="222" spans="2:5">
-      <c r="E222" s="2" t="s">
-        <v>220</v>
+      <c r="J208" s="6"/>
+    </row>
+    <row r="209" spans="2:11">
+      <c r="K209" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="210" spans="2:11">
+      <c r="B210" s="6"/>
+      <c r="C210" s="6"/>
+      <c r="D210" s="6"/>
+      <c r="E210" s="6"/>
+    </row>
+    <row r="223" spans="2:11">
+      <c r="E223" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P194" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P195" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14460,7 +14496,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N190,工作表2!N6:N190&gt;0,"")</f>
+        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N191,工作表2!N6:N191&gt;0,"")</f>
         <v/>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -16,7 +16,7 @@
     <sheet name="工作表3" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$196</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'合同 '!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">发票!$A$1:$E$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">装箱单!$A$1:$L$36</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="322">
   <si>
     <t>销 售 合 同
 SALES CONTRACT</t>
@@ -872,6 +872,9 @@
     <t>4安甘蔗杯蓋</t>
   </si>
   <si>
+    <t>6"甘蔗旦碟</t>
+  </si>
+  <si>
     <t>7"甘蔗圓碟</t>
   </si>
   <si>
@@ -912,9 +915,6 @@
   </si>
   <si>
     <t>浙江福昌环保科技有限公司</t>
-  </si>
-  <si>
-    <t>6"甘蔗旦碟</t>
   </si>
   <si>
     <t>9"甘蔗三格圓碟</t>
@@ -2694,7 +2694,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{4D404418-3AA8-4C88-844C-D511EA24324D}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{180168D4-10D2-47BE-9C9D-5E3511E756DE}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2703,7 +2703,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{7D26F90E-4EA0-4EA0-8992-6E73FC61EE30}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{CB28540B-C89E-4051-8639-73313546CA54}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -6373,7 +6373,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P223"/>
+  <dimension ref="A1:P224"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.4" style="2" customWidth="1"/>
@@ -9269,7 +9269,7 @@
       <c r="J70" s="8"/>
       <c r="K70" s="17"/>
       <c r="L70" s="17">
-        <f>K70+J70/2</f>
+        <f t="shared" ref="L70:L82" si="9">K70+J70/2</f>
         <v>0</v>
       </c>
       <c r="M70" s="16"/>
@@ -9302,20 +9302,20 @@
         <v>0.08</v>
       </c>
       <c r="I71" s="16">
-        <f t="shared" ref="I71:I78" si="9">G71*(1+H71)</f>
+        <f t="shared" ref="I71:I78" si="10">G71*(1+H71)</f>
         <v>73.44</v>
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="17">
-        <f t="shared" ref="K71:K93" si="10">J71*F71</f>
+        <f t="shared" ref="K71:K93" si="11">J71*F71</f>
         <v>0</v>
       </c>
       <c r="L71" s="17">
-        <f>K71+J71/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M71" s="16">
-        <f t="shared" ref="M71:M93" si="11">J71*I71</f>
+        <f t="shared" ref="M71:M93" si="12">J71*I71</f>
         <v>0</v>
       </c>
       <c r="N71" s="18">
@@ -9347,20 +9347,20 @@
         <v>0.08</v>
       </c>
       <c r="I72" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>79.92</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L72" s="17">
-        <f>K72+J72/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M72" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N72" s="18">
@@ -9392,20 +9392,20 @@
         <v>0.08</v>
       </c>
       <c r="I73" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>88.56</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L73" s="17">
-        <f>K73+J73/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M73" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N73" s="18">
@@ -9437,20 +9437,20 @@
         <v>0.08</v>
       </c>
       <c r="I74" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>97.2</v>
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L74" s="17">
-        <f>K74+J74/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M74" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N74" s="18">
@@ -9482,20 +9482,20 @@
         <v>0.08</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>65.88</v>
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L75" s="17">
-        <f>K75+J75/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N75" s="18">
@@ -9527,20 +9527,20 @@
         <v>0.08</v>
       </c>
       <c r="I76" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>63.72</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L76" s="17">
-        <f>K76+J76/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M76" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N76" s="18">
@@ -9572,20 +9572,20 @@
         <v>0.08</v>
       </c>
       <c r="I77" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>65.88</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L77" s="17">
-        <f>K77+J77/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M77" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N77" s="18">
@@ -9617,20 +9617,20 @@
         <v>0.08</v>
       </c>
       <c r="I78" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>63.72</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L78" s="17">
-        <f>K78+J78/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M78" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N78" s="18">
@@ -9656,7 +9656,7 @@
         <v>8.4</v>
       </c>
       <c r="G79" s="13">
-        <f t="shared" ref="G79:G83" si="12">I79-1</f>
+        <f t="shared" ref="G79:G83" si="13">I79-1</f>
         <v>89</v>
       </c>
       <c r="H79" s="15">
@@ -9667,15 +9667,15 @@
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L79" s="17">
-        <f>K79+J79/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M79" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N79" s="18">
@@ -9701,7 +9701,7 @@
         <v>6.3</v>
       </c>
       <c r="G80" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>69</v>
       </c>
       <c r="H80" s="15">
@@ -9712,15 +9712,15 @@
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L80" s="17">
-        <f>K80+J80/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M80" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N80" s="18">
@@ -9746,7 +9746,7 @@
         <v>8.4</v>
       </c>
       <c r="G81" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>91</v>
       </c>
       <c r="H81" s="15">
@@ -9757,15 +9757,15 @@
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L81" s="17">
-        <f>K81+J81/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M81" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N81" s="18">
@@ -9791,7 +9791,7 @@
         <v>10.4</v>
       </c>
       <c r="G82" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>76</v>
       </c>
       <c r="H82" s="15">
@@ -9802,15 +9802,15 @@
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L82" s="17">
-        <f>K82+J82/2</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M82" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N82" s="18">
@@ -9836,7 +9836,7 @@
         <v>11.4</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>89</v>
       </c>
       <c r="H83" s="15">
@@ -9869,7 +9869,7 @@
         <v>10.2</v>
       </c>
       <c r="G84" s="13">
-        <f t="shared" ref="G84:G89" si="13">I84-1</f>
+        <f t="shared" ref="G84:G89" si="14">I84-1</f>
         <v>113</v>
       </c>
       <c r="H84" s="15">
@@ -9880,19 +9880,19 @@
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="17">
-        <f>J84*F84</f>
+        <f t="shared" ref="K84:K94" si="15">J84*F84</f>
         <v>0</v>
       </c>
       <c r="L84" s="17">
-        <f t="shared" ref="L84:L94" si="14">K84+J84/2</f>
+        <f t="shared" ref="L84:L94" si="16">K84+J84/2</f>
         <v>0</v>
       </c>
       <c r="M84" s="16">
-        <f>J84*I84</f>
+        <f t="shared" ref="M84:M94" si="17">J84*I84</f>
         <v>0</v>
       </c>
       <c r="N84" s="18">
-        <f>M84+J84</f>
+        <f t="shared" ref="N84:N94" si="18">M84+J84</f>
         <v>0</v>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
         <v>7.2</v>
       </c>
       <c r="G85" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>73</v>
       </c>
       <c r="H85" s="15">
@@ -9925,19 +9925,19 @@
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="17">
-        <f>J85*F85</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L85" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M85" s="16">
-        <f>J85*I85</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N85" s="18">
-        <f>M85+J85</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         <v>6.9</v>
       </c>
       <c r="G86" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>73.7</v>
       </c>
       <c r="H86" s="15">
@@ -9970,19 +9970,19 @@
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="17">
-        <f>J86*F86</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L86" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M86" s="16">
-        <f>J86*I86</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N86" s="18">
-        <f>M86+J86</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>9.9</v>
       </c>
       <c r="G87" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>74.1</v>
       </c>
       <c r="H87" s="15">
@@ -10015,19 +10015,19 @@
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="17">
-        <f>J87*F87</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L87" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M87" s="16">
-        <f>J87*I87</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N87" s="18">
-        <f>M87+J87</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
         <v>7.8</v>
       </c>
       <c r="G88" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>58.1</v>
       </c>
       <c r="H88" s="15">
@@ -10060,19 +10060,19 @@
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="17">
-        <f>J88*F88</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L88" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M88" s="16">
-        <f>J88*I88</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N88" s="18">
-        <f>M88+J88</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10094,7 +10094,7 @@
         <v>7.8</v>
       </c>
       <c r="G89" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>124</v>
       </c>
       <c r="H89" s="15">
@@ -10105,19 +10105,19 @@
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="17">
-        <f>J89*F89</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L89" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M89" s="16">
-        <f>J89*I89</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N89" s="18">
-        <f>M89+J89</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10147,19 +10147,19 @@
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="17">
-        <f>J90*F90</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L90" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M90" s="16">
-        <f>J90*I90</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N90" s="18">
-        <f>M90+J90</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10187,24 +10187,24 @@
         <v>0.08</v>
       </c>
       <c r="I91" s="16">
-        <f t="shared" ref="I91:I94" si="15">G91*(1+H91)</f>
+        <f t="shared" ref="I91:I94" si="19">G91*(1+H91)</f>
         <v>73.44</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="17">
-        <f>J91*F91</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L91" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M91" s="16">
-        <f>J91*I91</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N91" s="18">
-        <f>M91+J91</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10232,24 +10232,24 @@
         <v>0.08</v>
       </c>
       <c r="I92" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>79.92</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="17">
-        <f>J92*F92</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L92" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M92" s="16">
-        <f>J92*I92</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N92" s="18">
-        <f>M92+J92</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10277,24 +10277,24 @@
         <v>0.08</v>
       </c>
       <c r="I93" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>88.56</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="17">
-        <f>J93*F93</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L93" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M93" s="16">
-        <f>J93*I93</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N93" s="18">
-        <f>M93+J93</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10322,24 +10322,24 @@
         <v>0.08</v>
       </c>
       <c r="I94" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>97.2</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="17">
-        <f>J94*F94</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L94" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M94" s="16">
-        <f>J94*I94</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N94" s="18">
-        <f>M94+J94</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       <c r="J95" s="24"/>
       <c r="K95" s="24"/>
       <c r="L95" s="17">
-        <f t="shared" ref="L95:L98" si="16">K95+J95/2</f>
+        <f t="shared" ref="L95:L98" si="20">K95+J95/2</f>
         <v>0</v>
       </c>
       <c r="M95" s="24"/>
@@ -10421,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="L97" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M97" s="16">
@@ -10466,7 +10466,7 @@
         <v>0</v>
       </c>
       <c r="L98" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M98" s="16">
@@ -10493,7 +10493,7 @@
       <c r="J99" s="24"/>
       <c r="K99" s="24"/>
       <c r="L99" s="17">
-        <f t="shared" ref="L99:L161" si="17">K99+J99/2</f>
+        <f t="shared" ref="L99:L162" si="21">K99+J99/2</f>
         <v>0</v>
       </c>
       <c r="M99" s="24"/>
@@ -10512,7 +10512,7 @@
       <c r="J100" s="8"/>
       <c r="K100" s="17"/>
       <c r="L100" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M100" s="16"/>
@@ -10533,12 +10533,12 @@
       <c r="J101" s="8"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M101" s="16"/>
       <c r="N101" s="18">
-        <f t="shared" ref="N101:N114" si="18">M101+J101</f>
+        <f t="shared" ref="N101:N114" si="22">M101+J101</f>
         <v>0</v>
       </c>
     </row>
@@ -10566,24 +10566,24 @@
         <v>0.08</v>
       </c>
       <c r="I102" s="16">
-        <f t="shared" ref="I102:I114" si="19">G102*(1+H102)</f>
+        <f t="shared" ref="I102:I114" si="23">G102*(1+H102)</f>
         <v>55.08</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="17">
-        <f t="shared" ref="K102:K114" si="20">J102*F102</f>
+        <f t="shared" ref="K102:K114" si="24">J102*F102</f>
         <v>0</v>
       </c>
       <c r="L102" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M102" s="16">
-        <f t="shared" ref="M102:M114" si="21">J102*I102</f>
+        <f t="shared" ref="M102:M114" si="25">J102*I102</f>
         <v>0</v>
       </c>
       <c r="N102" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10611,24 +10611,24 @@
         <v>0.08</v>
       </c>
       <c r="I103" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>58.32</v>
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L103" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M103" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N103" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10656,24 +10656,24 @@
         <v>0.08</v>
       </c>
       <c r="I104" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>65.88</v>
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L104" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M104" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N104" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10701,24 +10701,24 @@
         <v>0.08</v>
       </c>
       <c r="I105" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>69.12</v>
       </c>
       <c r="J105" s="8"/>
       <c r="K105" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L105" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M105" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N105" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10744,19 +10744,19 @@
       <c r="I106" s="16"/>
       <c r="J106" s="8"/>
       <c r="K106" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L106" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M106" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N106" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10784,24 +10784,24 @@
         <v>0.08</v>
       </c>
       <c r="I107" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>74.52</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L107" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M107" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N107" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10829,24 +10829,24 @@
         <v>0.08</v>
       </c>
       <c r="I108" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>77.76</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L108" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M108" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N108" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10874,24 +10874,24 @@
         <v>0.08</v>
       </c>
       <c r="I109" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>97.2</v>
       </c>
       <c r="J109" s="8"/>
       <c r="K109" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L109" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M109" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N109" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10919,24 +10919,24 @@
         <v>0.08</v>
       </c>
       <c r="I110" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>100.44</v>
       </c>
       <c r="J110" s="32"/>
       <c r="K110" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L110" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M110" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N110" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10962,19 +10962,19 @@
       <c r="I111" s="16"/>
       <c r="J111" s="8"/>
       <c r="K111" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L111" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M111" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N111" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11002,24 +11002,24 @@
         <v>0.08</v>
       </c>
       <c r="I112" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>76.68</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L112" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M112" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N112" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11047,24 +11047,24 @@
         <v>0.08</v>
       </c>
       <c r="I113" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>79.92</v>
       </c>
       <c r="J113" s="8"/>
       <c r="K113" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L113" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M113" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N113" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11090,19 +11090,19 @@
       <c r="I114" s="16"/>
       <c r="J114" s="8"/>
       <c r="K114" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L114" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M114" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N114" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
       <c r="J115" s="24"/>
       <c r="K115" s="24"/>
       <c r="L115" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M115" s="24"/>
@@ -11136,12 +11136,12 @@
       <c r="J116" s="8"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M116" s="16"/>
       <c r="N116" s="18">
-        <f t="shared" ref="N116:N123" si="22">M116+J116</f>
+        <f t="shared" ref="N116:N123" si="26">M116+J116</f>
         <v>0</v>
       </c>
     </row>
@@ -11160,12 +11160,12 @@
       <c r="J117" s="4"/>
       <c r="K117" s="17"/>
       <c r="L117" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M117" s="16"/>
       <c r="N117" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11193,24 +11193,24 @@
         <v>0.08</v>
       </c>
       <c r="I118" s="16">
-        <f t="shared" ref="I118:I123" si="23">G118*(1+H118)</f>
+        <f t="shared" ref="I118:I123" si="27">G118*(1+H118)</f>
         <v>34.02</v>
       </c>
       <c r="J118" s="8"/>
       <c r="K118" s="17">
-        <f t="shared" ref="K118:K123" si="24">J118*F118</f>
+        <f t="shared" ref="K118:K123" si="28">J118*F118</f>
         <v>0</v>
       </c>
       <c r="L118" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M118" s="16">
-        <f t="shared" ref="M118:M123" si="25">J118*I118</f>
+        <f t="shared" ref="M118:M123" si="29">J118*I118</f>
         <v>0</v>
       </c>
       <c r="N118" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11238,24 +11238,24 @@
         <v>0.08</v>
       </c>
       <c r="I119" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>45.9</v>
       </c>
       <c r="J119" s="8"/>
       <c r="K119" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L119" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M119" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N119" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11283,24 +11283,24 @@
         <v>0.08</v>
       </c>
       <c r="I120" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>50.76</v>
       </c>
       <c r="J120" s="4"/>
       <c r="K120" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L120" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M120" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N120" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11325,24 +11325,24 @@
         <v>0.095</v>
       </c>
       <c r="I121" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>56.94</v>
       </c>
       <c r="J121" s="4"/>
       <c r="K121" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L121" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M121" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N121" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11367,24 +11367,24 @@
         <v>0.095</v>
       </c>
       <c r="I122" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>37.23</v>
       </c>
       <c r="J122" s="4"/>
       <c r="K122" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L122" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M122" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N122" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11410,24 +11410,24 @@
         <v>0.1</v>
       </c>
       <c r="I123" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>44.55</v>
       </c>
       <c r="J123" s="8"/>
       <c r="K123" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L123" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M123" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N123" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
       <c r="J124" s="36"/>
       <c r="K124" s="36"/>
       <c r="L124" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M124" s="36"/>
@@ -11457,11 +11457,11 @@
       <c r="E125" s="10"/>
       <c r="F125" s="11"/>
       <c r="L125" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N125" s="18">
-        <f t="shared" ref="N125:N163" si="26">M125+J125</f>
+        <f t="shared" ref="N125:N135" si="30">M125+J125</f>
         <v>0</v>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M126" s="16">
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="N126" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M127" s="16">
@@ -11549,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="N127" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11568,12 +11568,12 @@
       <c r="J128" s="8"/>
       <c r="K128" s="17"/>
       <c r="L128" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M128" s="16"/>
       <c r="N128" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M129" s="16">
@@ -11618,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="N129" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M130" s="16">
@@ -11663,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M131" s="16">
@@ -11708,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="N131" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11745,7 +11745,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M132" s="16">
@@ -11753,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="N132" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       <c r="J133" s="8"/>
       <c r="K133" s="17"/>
       <c r="L133" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M133" s="16"/>
       <c r="N133" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
         <v>8</v>
       </c>
       <c r="G134" s="13">
-        <f t="shared" ref="G134:G141" si="27">I134/(1+H134)</f>
+        <f t="shared" ref="G134:G141" si="31">I134/(1+H134)</f>
         <v>123.893805309735</v>
       </c>
       <c r="H134" s="15">
@@ -11812,19 +11812,19 @@
       </c>
       <c r="J134" s="8"/>
       <c r="K134" s="17">
-        <f t="shared" ref="K134:K158" si="28">J134*F134</f>
+        <f>J134*F134</f>
         <v>0</v>
       </c>
       <c r="L134" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M134" s="16">
-        <f t="shared" ref="M134:M158" si="29">J134*I134</f>
+        <f>J134*I134</f>
         <v>0</v>
       </c>
       <c r="N134" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
         <v>10.5</v>
       </c>
       <c r="G135" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>153.752212389381</v>
       </c>
       <c r="H135" s="15">
@@ -11859,19 +11859,19 @@
       </c>
       <c r="J135" s="8"/>
       <c r="K135" s="17">
-        <f t="shared" si="28"/>
+        <f>J135*F135</f>
         <v>0</v>
       </c>
       <c r="L135" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M135" s="16">
-        <f t="shared" si="29"/>
+        <f>J135*I135</f>
         <v>0</v>
       </c>
       <c r="N135" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
         <v>6</v>
       </c>
       <c r="G136" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>176.991150442478</v>
       </c>
       <c r="H136" s="15">
@@ -11906,19 +11906,19 @@
       </c>
       <c r="J136" s="8"/>
       <c r="K136" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="K136:K141" si="32">J136*F136</f>
         <v>0</v>
       </c>
       <c r="L136" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M136" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="M136:M141" si="33">J136*I136</f>
         <v>0</v>
       </c>
       <c r="N136" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="N136:N141" si="34">M136+J136</f>
         <v>0</v>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
         <v>4</v>
       </c>
       <c r="G137" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>123.893805309735</v>
       </c>
       <c r="H137" s="15">
@@ -11953,19 +11953,19 @@
       </c>
       <c r="J137" s="8"/>
       <c r="K137" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L137" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M137" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N137" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
         <v>8</v>
       </c>
       <c r="G138" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>230.088495575221</v>
       </c>
       <c r="H138" s="15">
@@ -12000,19 +12000,19 @@
       </c>
       <c r="J138" s="8"/>
       <c r="K138" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L138" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M138" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N138" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>8</v>
       </c>
       <c r="G139" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>115.929203539823</v>
       </c>
       <c r="H139" s="15">
@@ -12047,19 +12047,19 @@
       </c>
       <c r="J139" s="8"/>
       <c r="K139" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L139" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M139" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N139" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
         <v>6</v>
       </c>
       <c r="G140" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>88.495575221239</v>
       </c>
       <c r="H140" s="15">
@@ -12094,29 +12094,31 @@
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L140" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M140" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N140" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
-      <c r="A141" s="14"/>
-      <c r="B141" s="14" t="s">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" s="3" customFormat="1" spans="1:14">
+      <c r="A141" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B141" s="19" t="s">
         <v>267</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>268</v>
+        <v>101</v>
       </c>
       <c r="D141" s="13" t="s">
         <v>257</v>
@@ -12125,43 +12127,43 @@
         <v>258</v>
       </c>
       <c r="F141" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G141" s="13">
-        <f t="shared" si="27"/>
-        <v>129.203539823009</v>
+        <f>I141-1</f>
+        <v>107</v>
       </c>
       <c r="H141" s="15">
         <v>0.13</v>
       </c>
       <c r="I141" s="16">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L141" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M141" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N141" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="12"/>
-      <c r="B142" s="12" t="s">
+      <c r="A142" s="14"/>
+      <c r="B142" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>269</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="D142" s="13" t="s">
         <v>257</v>
@@ -12170,175 +12172,175 @@
         <v>258</v>
       </c>
       <c r="F142" s="7">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="G142" s="13">
-        <v>140</v>
+        <f>I142/(1+H142)</f>
+        <v>129.203539823009</v>
       </c>
       <c r="H142" s="15">
         <v>0.13</v>
       </c>
       <c r="I142" s="16">
-        <f>G142*(1+H142)</f>
-        <v>158.2</v>
+        <v>146</v>
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="K142:K159" si="35">J142*F142</f>
         <v>0</v>
       </c>
       <c r="L142" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M142" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="M142:M159" si="36">J142*I142</f>
         <v>0</v>
       </c>
       <c r="N142" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" s="3" customFormat="1" spans="1:14">
-      <c r="A143" s="26"/>
+        <f t="shared" ref="N142:N164" si="37">M142+J142</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
+      <c r="A143" s="12"/>
       <c r="B143" s="12" t="s">
         <v>270</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D143" s="13" t="s">
         <v>257</v>
       </c>
       <c r="E143" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F143" s="34">
-        <v>7.5</v>
+        <v>258</v>
+      </c>
+      <c r="F143" s="7">
+        <v>9.5</v>
       </c>
       <c r="G143" s="13">
-        <f>I143/(1+H143)</f>
-        <v>103.371681415929</v>
-      </c>
-      <c r="H143" s="35">
+        <v>140</v>
+      </c>
+      <c r="H143" s="15">
         <v>0.13</v>
       </c>
-      <c r="I143" s="37">
-        <v>116.81</v>
-      </c>
-      <c r="J143" s="34"/>
-      <c r="K143" s="38">
-        <f t="shared" si="28"/>
+      <c r="I143" s="16">
+        <f>G143*(1+H143)</f>
+        <v>158.2</v>
+      </c>
+      <c r="J143" s="8"/>
+      <c r="K143" s="17">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L143" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M143" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M143" s="16">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N143" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" s="3" customFormat="1" spans="1:14">
       <c r="A144" s="26"/>
-      <c r="B144" s="14" t="s">
+      <c r="B144" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C144" s="12" t="s">
-        <v>272</v>
+      <c r="C144" s="8" t="s">
+        <v>269</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="F144" s="34">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="G144" s="13">
         <f>I144/(1+H144)</f>
-        <v>132.743362831858</v>
+        <v>103.371681415929</v>
       </c>
       <c r="H144" s="35">
         <v>0.13</v>
       </c>
       <c r="I144" s="37">
-        <v>150</v>
+        <v>116.81</v>
       </c>
       <c r="J144" s="34"/>
       <c r="K144" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L144" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M144" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N144" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" s="3" customFormat="1" spans="1:15">
       <c r="A145" s="26"/>
       <c r="B145" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>96</v>
+        <v>272</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>273</v>
       </c>
       <c r="D145" s="13" t="s">
         <v>263</v>
       </c>
       <c r="E145" s="14" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="F145" s="34">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="G145" s="13">
-        <v>145</v>
+        <f>I145/(1+H145)</f>
+        <v>132.743362831858</v>
       </c>
       <c r="H145" s="35">
         <v>0.13</v>
       </c>
-      <c r="I145" s="16">
-        <f>G145*(1+H145)</f>
-        <v>163.85</v>
+      <c r="I145" s="37">
+        <v>150</v>
       </c>
       <c r="J145" s="34"/>
       <c r="K145" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L145" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M145" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N145" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" s="3" customFormat="1" spans="1:15">
       <c r="A146" s="26"/>
       <c r="B146" s="14" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>96</v>
@@ -12350,483 +12352,483 @@
         <v>119</v>
       </c>
       <c r="F146" s="34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G146" s="13">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="H146" s="35">
         <v>0.13</v>
       </c>
       <c r="I146" s="16">
         <f>G146*(1+H146)</f>
-        <v>114.13</v>
+        <v>163.85</v>
       </c>
       <c r="J146" s="34"/>
       <c r="K146" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L146" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M146" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N146" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" s="3" customFormat="1" spans="1:15">
       <c r="A147" s="26"/>
-      <c r="B147" s="12" t="s">
+      <c r="B147" s="14" t="s">
         <v>274</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E147" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F147" s="34">
-        <v>6</v>
-      </c>
-      <c r="G147" s="27">
-        <v>115</v>
+        <v>4</v>
+      </c>
+      <c r="G147" s="13">
+        <v>101</v>
       </c>
       <c r="H147" s="35">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I147" s="16">
         <f>G147*(1+H147)</f>
-        <v>124.2</v>
-      </c>
-      <c r="J147" s="8"/>
-      <c r="K147" s="17">
-        <f t="shared" si="28"/>
+        <v>114.13</v>
+      </c>
+      <c r="J147" s="34"/>
+      <c r="K147" s="38">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L147" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M147" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M147" s="37">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N147" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" s="3" customFormat="1" spans="1:15">
-      <c r="A148" s="14"/>
-      <c r="B148" s="14" t="s">
-        <v>262</v>
+      <c r="A148" s="26"/>
+      <c r="B148" s="12" t="s">
+        <v>275</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E148" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F148" s="7">
-        <v>4</v>
-      </c>
-      <c r="G148" s="13">
-        <f>I148/(1+H148)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H148" s="15">
-        <v>0.13</v>
+      <c r="F148" s="34">
+        <v>6</v>
+      </c>
+      <c r="G148" s="27">
+        <v>115</v>
+      </c>
+      <c r="H148" s="35">
+        <v>0.08</v>
       </c>
       <c r="I148" s="16">
-        <v>140</v>
+        <f>G148*(1+H148)</f>
+        <v>124.2</v>
       </c>
       <c r="J148" s="8"/>
       <c r="K148" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L148" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M148" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N148" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O148" s="2"/>
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="149" s="3" customFormat="1" spans="1:15">
-      <c r="A149" s="26"/>
-      <c r="B149" s="12" t="s">
-        <v>275</v>
+      <c r="A149" s="14"/>
+      <c r="B149" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>276</v>
+        <v>96</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E149" s="14"/>
-      <c r="F149" s="34">
-        <v>11</v>
-      </c>
-      <c r="G149" s="27">
-        <f>I149-1</f>
-        <v>177.5</v>
-      </c>
-      <c r="H149" s="35"/>
+        <v>263</v>
+      </c>
+      <c r="E149" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F149" s="7">
+        <v>4</v>
+      </c>
+      <c r="G149" s="13">
+        <f>I149/(1+H149)</f>
+        <v>123.893805309735</v>
+      </c>
+      <c r="H149" s="15">
+        <v>0.13</v>
+      </c>
       <c r="I149" s="16">
-        <v>178.5</v>
+        <v>140</v>
       </c>
       <c r="J149" s="8"/>
       <c r="K149" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L149" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M149" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N149" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="O149" s="2"/>
     </row>
     <row r="150" s="3" customFormat="1" spans="1:15">
       <c r="A150" s="26"/>
       <c r="B150" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D150" s="13" t="s">
         <v>278</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>279</v>
       </c>
       <c r="E150" s="14"/>
       <c r="F150" s="34">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G150" s="27">
         <f>I150-1</f>
-        <v>127.5</v>
+        <v>177.5</v>
       </c>
       <c r="H150" s="35"/>
       <c r="I150" s="16">
-        <v>128.5</v>
+        <v>178.5</v>
       </c>
       <c r="J150" s="8"/>
       <c r="K150" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L150" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M150" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N150" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="3" customFormat="1" spans="1:15">
-      <c r="A151" s="14"/>
-      <c r="B151" s="14" t="s">
-        <v>260</v>
+      <c r="A151" s="26"/>
+      <c r="B151" s="12" t="s">
+        <v>279</v>
       </c>
       <c r="C151" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D151" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="D151" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E151" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F151" s="7">
-        <v>6</v>
-      </c>
-      <c r="G151" s="13">
-        <f>I151/(1+H151)</f>
-        <v>176.991150442478</v>
-      </c>
-      <c r="H151" s="15">
-        <v>0.13</v>
-      </c>
+      <c r="E151" s="14"/>
+      <c r="F151" s="34">
+        <v>8</v>
+      </c>
+      <c r="G151" s="27">
+        <f>I151-1</f>
+        <v>127.5</v>
+      </c>
+      <c r="H151" s="35"/>
       <c r="I151" s="16">
-        <v>200</v>
+        <v>128.5</v>
       </c>
       <c r="J151" s="8"/>
       <c r="K151" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L151" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M151" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N151" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" s="3" customFormat="1" spans="1:15">
       <c r="A152" s="14"/>
       <c r="B152" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F152" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G152" s="13">
         <f>I152/(1+H152)</f>
-        <v>123.893805309735</v>
+        <v>176.991150442478</v>
       </c>
       <c r="H152" s="15">
         <v>0.13</v>
       </c>
       <c r="I152" s="16">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J152" s="8"/>
       <c r="K152" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L152" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M152" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N152" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
-      <c r="A153" s="26"/>
-      <c r="B153" s="12" t="s">
-        <v>274</v>
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" s="3" customFormat="1" spans="1:15">
+      <c r="A153" s="14"/>
+      <c r="B153" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F153" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G153" s="13">
-        <v>115</v>
+        <f>I153/(1+H153)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H153" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I153" s="16">
-        <f>G153*(1+H153)</f>
-        <v>124.2</v>
+        <v>140</v>
       </c>
       <c r="J153" s="8"/>
       <c r="K153" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L153" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M153" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N153" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" s="3" customFormat="1" spans="1:15">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
       <c r="A154" s="26"/>
-      <c r="B154" s="19" t="s">
+      <c r="B154" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C154" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C154" s="8" t="s">
-        <v>280</v>
-      </c>
       <c r="D154" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="F154" s="7">
         <v>6</v>
       </c>
       <c r="G154" s="13">
-        <f>I154-1</f>
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H154" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I154" s="16">
-        <v>108</v>
+        <f>G154*(1+H154)</f>
+        <v>124.2</v>
       </c>
       <c r="J154" s="8"/>
       <c r="K154" s="17">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L154" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M154" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N154" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" s="3" customFormat="1" spans="1:15">
       <c r="A155" s="26"/>
-      <c r="B155" s="12" t="s">
-        <v>270</v>
+      <c r="B155" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D155" s="13" t="s">
         <v>257</v>
       </c>
       <c r="E155" s="14" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="F155" s="7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G155" s="13">
         <f>I155-1</f>
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H155" s="15">
         <v>0.13</v>
       </c>
-      <c r="I155" s="39">
-        <v>135</v>
-      </c>
-      <c r="J155" s="34"/>
-      <c r="K155" s="38">
-        <f t="shared" si="28"/>
+      <c r="I155" s="16">
+        <v>108</v>
+      </c>
+      <c r="J155" s="8"/>
+      <c r="K155" s="17">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L155" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M155" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M155" s="16">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N155" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" s="3" customFormat="1" spans="1:15">
-      <c r="A156" s="12"/>
-      <c r="B156" s="19" t="s">
-        <v>269</v>
+      <c r="A156" s="26"/>
+      <c r="B156" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>101</v>
+        <v>281</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>257</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="F156" s="7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G156" s="13">
         <f>I156-1</f>
-        <v>150.2</v>
+        <v>134</v>
       </c>
       <c r="H156" s="15">
         <v>0.13</v>
       </c>
-      <c r="I156" s="16">
-        <v>151.2</v>
-      </c>
-      <c r="J156" s="8"/>
-      <c r="K156" s="17">
-        <f t="shared" si="28"/>
+      <c r="I156" s="39">
+        <v>135</v>
+      </c>
+      <c r="J156" s="34"/>
+      <c r="K156" s="38">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L156" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M156" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M156" s="37">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N156" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" s="3" customFormat="1" spans="1:15">
-      <c r="A157" s="26"/>
-      <c r="B157" s="12" t="s">
-        <v>282</v>
+      <c r="A157" s="12"/>
+      <c r="B157" s="19" t="s">
+        <v>270</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>101</v>
@@ -12835,43 +12837,43 @@
         <v>257</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="F157" s="7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G157" s="13">
         <f>I157-1</f>
-        <v>134</v>
+        <v>150.2</v>
       </c>
       <c r="H157" s="15">
         <v>0.13</v>
       </c>
       <c r="I157" s="16">
-        <v>135</v>
+        <v>151.2</v>
       </c>
       <c r="J157" s="8"/>
-      <c r="K157" s="38">
-        <f t="shared" si="28"/>
+      <c r="K157" s="17">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L157" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M157" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M157" s="16">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N157" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" s="3" customFormat="1" spans="1:15">
       <c r="A158" s="26"/>
       <c r="B158" s="12" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>101</v>
@@ -12883,129 +12885,130 @@
         <v>197</v>
       </c>
       <c r="F158" s="7">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G158" s="13">
         <f>I158-1</f>
-        <v>177.2</v>
+        <v>134</v>
       </c>
       <c r="H158" s="15">
         <v>0.13</v>
       </c>
       <c r="I158" s="16">
-        <v>178.2</v>
+        <v>135</v>
       </c>
       <c r="J158" s="8"/>
       <c r="K158" s="38">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L158" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M158" s="37">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N158" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" s="3" customFormat="1" spans="1:15">
       <c r="A159" s="26"/>
-      <c r="B159" s="26"/>
-      <c r="C159" s="26"/>
-      <c r="D159" s="26"/>
-      <c r="E159" s="26"/>
-      <c r="F159" s="34"/>
-      <c r="G159" s="27"/>
-      <c r="H159" s="35"/>
-      <c r="I159" s="16"/>
+      <c r="B159" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E159" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F159" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="G159" s="13">
+        <f>I159-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H159" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I159" s="16">
+        <v>178.2</v>
+      </c>
       <c r="J159" s="8"/>
-      <c r="K159" s="17"/>
+      <c r="K159" s="38">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="L159" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M159" s="16"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M159" s="37">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="N159" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" s="3" customFormat="1" spans="1:15">
       <c r="A160" s="26"/>
-      <c r="B160" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="C160" s="10"/>
-      <c r="D160" s="10"/>
-      <c r="E160" s="10"/>
-      <c r="F160" s="11"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="26"/>
+      <c r="D160" s="26"/>
+      <c r="E160" s="26"/>
+      <c r="F160" s="34"/>
       <c r="G160" s="27"/>
       <c r="H160" s="35"/>
       <c r="I160" s="16"/>
       <c r="J160" s="8"/>
       <c r="K160" s="17"/>
       <c r="L160" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M160" s="16"/>
       <c r="N160" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14">
-      <c r="B161" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D161" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E161" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F161" s="7">
-        <v>8</v>
-      </c>
-      <c r="G161" s="13">
-        <v>90</v>
-      </c>
-      <c r="H161" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I161" s="16">
-        <f>G161*(1+H161)</f>
-        <v>97.2</v>
-      </c>
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" s="3" customFormat="1" spans="1:14">
+      <c r="A161" s="26"/>
+      <c r="B161" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C161" s="10"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="10"/>
+      <c r="F161" s="11"/>
+      <c r="G161" s="27"/>
+      <c r="H161" s="35"/>
+      <c r="I161" s="16"/>
       <c r="J161" s="8"/>
-      <c r="K161" s="17">
-        <f>J161*F161</f>
-        <v>0</v>
-      </c>
+      <c r="K161" s="17"/>
       <c r="L161" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M161" s="16">
-        <f>J161*I161</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M161" s="16"/>
       <c r="N161" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="B162" s="40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>94</v>
@@ -13020,14 +13023,14 @@
         <v>8</v>
       </c>
       <c r="G162" s="13">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H162" s="15">
         <v>0.08</v>
       </c>
       <c r="I162" s="16">
         <f>G162*(1+H162)</f>
-        <v>99.36</v>
+        <v>97.2</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="17">
@@ -13035,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="17">
-        <f t="shared" ref="L162:L191" si="30">K162+J162/2</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M162" s="16">
@@ -13043,13 +13046,13 @@
         <v>0</v>
       </c>
       <c r="N162" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="B163" s="40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>94</v>
@@ -13061,17 +13064,17 @@
         <v>1000</v>
       </c>
       <c r="F163" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G163" s="13">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H163" s="15">
         <v>0.08</v>
       </c>
       <c r="I163" s="16">
         <f>G163*(1+H163)</f>
-        <v>93.96</v>
+        <v>99.36</v>
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="17">
@@ -13079,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="L163:L192" si="38">K163+J163/2</f>
         <v>0</v>
       </c>
       <c r="M163" s="16">
@@ -13087,99 +13090,99 @@
         <v>0</v>
       </c>
       <c r="N163" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:14">
-      <c r="B164" s="10" t="s">
+      <c r="B164" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E164" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F164" s="7">
+        <v>7</v>
+      </c>
+      <c r="G164" s="13">
+        <v>87</v>
+      </c>
+      <c r="H164" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I164" s="16">
+        <f>G164*(1+H164)</f>
+        <v>93.96</v>
+      </c>
+      <c r="J164" s="8"/>
+      <c r="K164" s="17">
+        <f>J164*F164</f>
+        <v>0</v>
+      </c>
+      <c r="L164" s="17">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="16">
+        <f>J164*I164</f>
+        <v>0</v>
+      </c>
+      <c r="N164" s="18">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14">
+      <c r="B165" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C164" s="10"/>
-      <c r="D164" s="10"/>
-      <c r="E164" s="10"/>
-      <c r="F164" s="11"/>
-      <c r="G164" s="13"/>
-      <c r="H164" s="15"/>
-      <c r="I164" s="16"/>
-      <c r="J164" s="8"/>
-      <c r="K164" s="17"/>
-      <c r="L164" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M164" s="16"/>
-      <c r="N164" s="18"/>
-    </row>
-    <row r="165" spans="1:14">
-      <c r="B165" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D165" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E165" s="41">
-        <v>300</v>
-      </c>
-      <c r="F165" s="7">
-        <v>4.65</v>
-      </c>
-      <c r="G165" s="13">
-        <v>61.5</v>
-      </c>
-      <c r="H165" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="I165" s="16">
-        <f>G165*(1+H165)</f>
-        <v>67.65</v>
-      </c>
+      <c r="C165" s="10"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="10"/>
+      <c r="F165" s="11"/>
+      <c r="G165" s="13"/>
+      <c r="H165" s="15"/>
+      <c r="I165" s="16"/>
       <c r="J165" s="8"/>
-      <c r="K165" s="17">
-        <f>J165*F165</f>
-        <v>0</v>
-      </c>
+      <c r="K165" s="17"/>
       <c r="L165" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M165" s="16">
-        <f>J165*I165</f>
-        <v>0</v>
-      </c>
-      <c r="N165" s="18">
-        <f t="shared" ref="N165:N191" si="31">M165+J165</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="16"/>
+      <c r="N165" s="18"/>
     </row>
     <row r="166" spans="1:14">
       <c r="B166" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E166" s="41">
         <v>300</v>
       </c>
       <c r="F166" s="7">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="G166" s="13">
-        <v>64.5</v>
+        <v>61.5</v>
       </c>
       <c r="H166" s="15">
         <v>0.1</v>
       </c>
       <c r="I166" s="16">
         <f>G166*(1+H166)</f>
-        <v>70.95</v>
+        <v>67.65</v>
       </c>
       <c r="J166" s="8"/>
       <c r="K166" s="17">
@@ -13187,7 +13190,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M166" s="16">
@@ -13195,36 +13198,35 @@
         <v>0</v>
       </c>
       <c r="N166" s="18">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" s="3" customFormat="1" spans="1:14">
-      <c r="A167" s="26"/>
-      <c r="B167" s="36" t="s">
-        <v>290</v>
+        <f t="shared" ref="N166:N192" si="39">M166+J166</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14">
+      <c r="B167" s="40" t="s">
+        <v>289</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E167" s="41">
         <v>300</v>
       </c>
       <c r="F167" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="G167" s="27">
-        <v>76.5</v>
-      </c>
-      <c r="H167" s="35">
+        <v>5.15</v>
+      </c>
+      <c r="G167" s="13">
+        <v>64.5</v>
+      </c>
+      <c r="H167" s="15">
         <v>0.1</v>
       </c>
       <c r="I167" s="16">
         <f>G167*(1+H167)</f>
-        <v>84.15</v>
+        <v>70.95</v>
       </c>
       <c r="J167" s="8"/>
       <c r="K167" s="17">
@@ -13232,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M167" s="16">
@@ -13240,36 +13242,36 @@
         <v>0</v>
       </c>
       <c r="N167" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" s="3" customFormat="1" spans="1:14">
       <c r="A168" s="26"/>
-      <c r="B168" s="2" t="s">
-        <v>291</v>
+      <c r="B168" s="36" t="s">
+        <v>290</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E168" s="41">
         <v>300</v>
       </c>
       <c r="F168" s="7">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="G168" s="27">
-        <v>94.5</v>
+        <v>76.5</v>
       </c>
       <c r="H168" s="35">
         <v>0.1</v>
       </c>
       <c r="I168" s="16">
         <f>G168*(1+H168)</f>
-        <v>103.95</v>
+        <v>84.15</v>
       </c>
       <c r="J168" s="8"/>
       <c r="K168" s="17">
@@ -13277,7 +13279,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M168" s="16">
@@ -13285,103 +13287,104 @@
         <v>0</v>
       </c>
       <c r="N168" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" s="3" customFormat="1" spans="1:14">
       <c r="A169" s="26"/>
-      <c r="B169" s="27"/>
-      <c r="C169" s="27"/>
-      <c r="D169" s="27"/>
-      <c r="E169" s="27"/>
-      <c r="F169" s="27"/>
-      <c r="G169" s="27"/>
-      <c r="H169" s="35"/>
-      <c r="I169" s="16"/>
+      <c r="B169" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E169" s="41">
+        <v>300</v>
+      </c>
+      <c r="F169" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="G169" s="27">
+        <v>94.5</v>
+      </c>
+      <c r="H169" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="I169" s="16">
+        <f>G169*(1+H169)</f>
+        <v>103.95</v>
+      </c>
       <c r="J169" s="8"/>
-      <c r="K169" s="17"/>
+      <c r="K169" s="17">
+        <f>J169*F169</f>
+        <v>0</v>
+      </c>
       <c r="L169" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M169" s="16"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M169" s="16">
+        <f>J169*I169</f>
+        <v>0</v>
+      </c>
       <c r="N169" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" s="3" customFormat="1" spans="1:14">
       <c r="A170" s="26"/>
-      <c r="B170" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C170" s="42"/>
-      <c r="D170" s="42"/>
-      <c r="E170" s="42"/>
-      <c r="F170" s="43"/>
+      <c r="B170" s="27"/>
+      <c r="C170" s="27"/>
+      <c r="D170" s="27"/>
+      <c r="E170" s="27"/>
+      <c r="F170" s="27"/>
       <c r="G170" s="27"/>
       <c r="H170" s="35"/>
       <c r="I170" s="16"/>
       <c r="J170" s="8"/>
       <c r="K170" s="17"/>
       <c r="L170" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M170" s="16"/>
       <c r="N170" s="18">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14">
-      <c r="B171" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D171" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E171" s="41">
-        <v>500</v>
-      </c>
-      <c r="F171" s="7">
-        <v>5</v>
-      </c>
-      <c r="G171" s="13">
-        <v>67.5</v>
-      </c>
-      <c r="H171" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I171" s="16">
-        <f t="shared" ref="I171:I191" si="32">G171*(1+H171)</f>
-        <v>72.9</v>
-      </c>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" s="3" customFormat="1" spans="1:14">
+      <c r="A171" s="26"/>
+      <c r="B171" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C171" s="42"/>
+      <c r="D171" s="42"/>
+      <c r="E171" s="42"/>
+      <c r="F171" s="43"/>
+      <c r="G171" s="27"/>
+      <c r="H171" s="35"/>
+      <c r="I171" s="16"/>
       <c r="J171" s="8"/>
-      <c r="K171" s="17">
-        <f t="shared" ref="K171:K191" si="33">J171*F171</f>
-        <v>0</v>
-      </c>
+      <c r="K171" s="17"/>
       <c r="L171" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M171" s="16">
-        <f t="shared" ref="M171:M191" si="34">J171*I171</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M171" s="16"/>
       <c r="N171" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="B172" s="40" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>94</v>
@@ -13393,39 +13396,39 @@
         <v>500</v>
       </c>
       <c r="F172" s="7">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="G172" s="13">
-        <v>79</v>
+        <v>67.5</v>
       </c>
       <c r="H172" s="15">
         <v>0.08</v>
       </c>
       <c r="I172" s="16">
-        <f t="shared" si="32"/>
-        <v>85.32</v>
+        <f t="shared" ref="I172:I192" si="40">G172*(1+H172)</f>
+        <v>72.9</v>
       </c>
       <c r="J172" s="8"/>
       <c r="K172" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="K172:K192" si="41">J172*F172</f>
         <v>0</v>
       </c>
       <c r="L172" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M172" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="M172:M192" si="42">J172*I172</f>
         <v>0</v>
       </c>
       <c r="N172" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:14">
-      <c r="B173" s="41" t="s">
-        <v>296</v>
+      <c r="B173" s="40" t="s">
+        <v>295</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>94</v>
@@ -13436,33 +13439,40 @@
       <c r="E173" s="41">
         <v>500</v>
       </c>
-      <c r="F173" s="7"/>
-      <c r="G173" s="13"/>
+      <c r="F173" s="7">
+        <v>6.2</v>
+      </c>
+      <c r="G173" s="13">
+        <v>79</v>
+      </c>
       <c r="H173" s="15">
         <v>0.08</v>
       </c>
-      <c r="I173" s="16"/>
+      <c r="I173" s="16">
+        <f t="shared" si="40"/>
+        <v>85.32</v>
+      </c>
       <c r="J173" s="8"/>
       <c r="K173" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L173" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M173" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N173" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:14">
-      <c r="B174" s="40" t="s">
-        <v>297</v>
+      <c r="B174" s="41" t="s">
+        <v>296</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>94</v>
@@ -13473,40 +13483,33 @@
       <c r="E174" s="41">
         <v>500</v>
       </c>
-      <c r="F174" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="G174" s="13">
-        <v>105</v>
-      </c>
+      <c r="F174" s="7"/>
+      <c r="G174" s="13"/>
       <c r="H174" s="15">
         <v>0.08</v>
       </c>
-      <c r="I174" s="16">
-        <f t="shared" si="32"/>
-        <v>113.4</v>
-      </c>
+      <c r="I174" s="16"/>
       <c r="J174" s="8"/>
       <c r="K174" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L174" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M174" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N174" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="B175" s="40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>94</v>
@@ -13518,39 +13521,39 @@
         <v>500</v>
       </c>
       <c r="F175" s="7">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G175" s="13">
-        <v>117.5</v>
+        <v>105</v>
       </c>
       <c r="H175" s="15">
         <v>0.08</v>
       </c>
       <c r="I175" s="16">
-        <f t="shared" si="32"/>
-        <v>126.9</v>
+        <f t="shared" si="40"/>
+        <v>113.4</v>
       </c>
       <c r="J175" s="8"/>
       <c r="K175" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L175" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M175" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N175" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:14">
-      <c r="B176" s="41" t="s">
-        <v>299</v>
+      <c r="B176" s="40" t="s">
+        <v>298</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>94</v>
@@ -13562,83 +13565,83 @@
         <v>500</v>
       </c>
       <c r="F176" s="7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G176" s="13">
-        <v>122.5</v>
+        <v>117.5</v>
       </c>
       <c r="H176" s="15">
         <v>0.08</v>
       </c>
       <c r="I176" s="16">
-        <f t="shared" si="32"/>
-        <v>132.3</v>
+        <f t="shared" si="40"/>
+        <v>126.9</v>
       </c>
       <c r="J176" s="8"/>
       <c r="K176" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L176" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M176" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N176" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="B177" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D177" s="41" t="s">
-        <v>301</v>
+      <c r="D177" s="13" t="s">
+        <v>294</v>
       </c>
       <c r="E177" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F177" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G177" s="13">
-        <v>100</v>
+        <v>122.5</v>
       </c>
       <c r="H177" s="15">
         <v>0.08</v>
       </c>
       <c r="I177" s="16">
-        <f t="shared" si="32"/>
-        <v>108</v>
+        <f t="shared" si="40"/>
+        <v>132.3</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L177" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M177" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N177" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:14">
-      <c r="B178" s="6" t="s">
-        <v>302</v>
+      <c r="B178" s="41" t="s">
+        <v>300</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>94</v>
@@ -13650,39 +13653,39 @@
         <v>5000</v>
       </c>
       <c r="F178" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G178" s="13">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="H178" s="15">
         <v>0.08</v>
       </c>
       <c r="I178" s="16">
-        <f t="shared" si="32"/>
-        <v>156.6</v>
+        <f t="shared" si="40"/>
+        <v>108</v>
       </c>
       <c r="J178" s="8"/>
       <c r="K178" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L178" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M178" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N178" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:14">
-      <c r="B179" s="41" t="s">
-        <v>303</v>
+      <c r="B179" s="6" t="s">
+        <v>302</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>94</v>
@@ -13694,40 +13697,39 @@
         <v>5000</v>
       </c>
       <c r="F179" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G179" s="13">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="H179" s="15">
         <v>0.08</v>
       </c>
       <c r="I179" s="16">
-        <f t="shared" si="32"/>
-        <v>145.8</v>
+        <f t="shared" si="40"/>
+        <v>156.6</v>
       </c>
       <c r="J179" s="8"/>
       <c r="K179" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L179" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M179" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N179" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:14">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6" t="s">
-        <v>304</v>
+      <c r="B180" s="41" t="s">
+        <v>303</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>94</v>
@@ -13739,39 +13741,40 @@
         <v>5000</v>
       </c>
       <c r="F180" s="7">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="G180" s="13">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="H180" s="15">
         <v>0.08</v>
       </c>
       <c r="I180" s="16">
-        <f t="shared" si="32"/>
-        <v>189</v>
+        <f t="shared" si="40"/>
+        <v>145.8</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L180" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M180" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N180" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:14">
-      <c r="B181" s="41" t="s">
-        <v>305</v>
+      <c r="A181" s="6"/>
+      <c r="B181" s="6" t="s">
+        <v>304</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>94</v>
@@ -13783,39 +13786,39 @@
         <v>5000</v>
       </c>
       <c r="F181" s="7">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="G181" s="13">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H181" s="15">
         <v>0.08</v>
       </c>
       <c r="I181" s="16">
-        <f t="shared" si="32"/>
-        <v>172.8</v>
+        <f t="shared" si="40"/>
+        <v>189</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L181" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M181" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N181" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:14">
-      <c r="B182" s="44" t="s">
-        <v>306</v>
+      <c r="B182" s="41" t="s">
+        <v>305</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>94</v>
@@ -13827,39 +13830,39 @@
         <v>5000</v>
       </c>
       <c r="F182" s="7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G182" s="13">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="H182" s="15">
         <v>0.08</v>
       </c>
       <c r="I182" s="16">
-        <f t="shared" si="32"/>
-        <v>205.2</v>
+        <f t="shared" si="40"/>
+        <v>172.8</v>
       </c>
       <c r="J182" s="8"/>
       <c r="K182" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L182" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M182" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N182" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:14">
-      <c r="B183" s="41" t="s">
-        <v>307</v>
+      <c r="B183" s="44" t="s">
+        <v>306</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>94</v>
@@ -13868,42 +13871,42 @@
         <v>301</v>
       </c>
       <c r="E183" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F183" s="7">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="G183" s="13">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="H183" s="15">
         <v>0.08</v>
       </c>
       <c r="I183" s="16">
-        <f t="shared" si="32"/>
-        <v>58.32</v>
+        <f t="shared" si="40"/>
+        <v>205.2</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L183" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M183" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N183" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:14">
-      <c r="B184" s="40" t="s">
-        <v>308</v>
+      <c r="B184" s="41" t="s">
+        <v>307</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>94</v>
@@ -13915,40 +13918,39 @@
         <v>1000</v>
       </c>
       <c r="F184" s="7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G184" s="13">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H184" s="15">
         <v>0.08</v>
       </c>
       <c r="I184" s="16">
-        <f t="shared" si="32"/>
-        <v>62.64</v>
+        <f t="shared" si="40"/>
+        <v>58.32</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L184" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M184" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N184" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:14">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6" t="s">
-        <v>309</v>
+      <c r="B185" s="40" t="s">
+        <v>308</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>94</v>
@@ -13960,39 +13962,40 @@
         <v>1000</v>
       </c>
       <c r="F185" s="7">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="G185" s="13">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H185" s="15">
         <v>0.08</v>
       </c>
       <c r="I185" s="16">
-        <f t="shared" si="32"/>
-        <v>68.04</v>
+        <f t="shared" si="40"/>
+        <v>62.64</v>
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L185" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M185" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N185" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:14">
-      <c r="B186" s="41" t="s">
-        <v>310</v>
+      <c r="A186" s="6"/>
+      <c r="B186" s="6" t="s">
+        <v>309</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>94</v>
@@ -14003,31 +14006,40 @@
       <c r="E186" s="41">
         <v>1000</v>
       </c>
-      <c r="F186" s="7"/>
-      <c r="G186" s="13"/>
-      <c r="H186" s="15"/>
-      <c r="I186" s="16"/>
+      <c r="F186" s="7">
+        <v>3.3</v>
+      </c>
+      <c r="G186" s="13">
+        <v>63</v>
+      </c>
+      <c r="H186" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I186" s="16">
+        <f t="shared" si="40"/>
+        <v>68.04</v>
+      </c>
       <c r="J186" s="8"/>
       <c r="K186" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L186" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M186" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N186" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="B187" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>94</v>
@@ -14044,63 +14056,54 @@
       <c r="I187" s="16"/>
       <c r="J187" s="8"/>
       <c r="K187" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L187" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M187" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N187" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:14">
-      <c r="B188" s="40" t="s">
-        <v>312</v>
+      <c r="B188" s="41" t="s">
+        <v>311</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D188" s="13" t="s">
-        <v>314</v>
+        <v>94</v>
+      </c>
+      <c r="D188" s="41" t="s">
+        <v>301</v>
       </c>
       <c r="E188" s="41">
-        <v>2000</v>
-      </c>
-      <c r="F188" s="7">
-        <v>5</v>
-      </c>
-      <c r="G188" s="13">
-        <v>140</v>
-      </c>
-      <c r="H188" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I188" s="16">
-        <f t="shared" si="32"/>
-        <v>151.2</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F188" s="7"/>
+      <c r="G188" s="13"/>
+      <c r="H188" s="15"/>
+      <c r="I188" s="16"/>
       <c r="J188" s="8"/>
       <c r="K188" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L188" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M188" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N188" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
@@ -14109,7 +14112,7 @@
         <v>312</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D189" s="13" t="s">
         <v>314</v>
@@ -14127,149 +14130,172 @@
         <v>0.08</v>
       </c>
       <c r="I189" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>151.2</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L189" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M189" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N189" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:14">
-      <c r="B190" s="41" t="s">
+      <c r="B190" s="40" t="s">
         <v>312</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>96</v>
+        <v>315</v>
       </c>
       <c r="D190" s="13" t="s">
         <v>314</v>
       </c>
       <c r="E190" s="41">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F190" s="7">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G190" s="13">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="H190" s="15">
         <v>0.08</v>
       </c>
       <c r="I190" s="16">
-        <f t="shared" si="32"/>
-        <v>75.6</v>
+        <f t="shared" si="40"/>
+        <v>151.2</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L190" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M190" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N190" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="B191" s="41" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D191" s="13" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="E191" s="41">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F191" s="7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G191" s="13">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H191" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I191" s="16">
-        <f t="shared" si="32"/>
-        <v>114.13</v>
+        <f t="shared" si="40"/>
+        <v>75.6</v>
       </c>
       <c r="J191" s="8"/>
       <c r="K191" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="L191" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M191" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N191" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:14">
-      <c r="F192" s="7"/>
-      <c r="G192" s="13"/>
-      <c r="H192" s="15"/>
-      <c r="J192" s="7" t="s">
-        <v>316</v>
-      </c>
+      <c r="B192" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E192" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F192" s="7">
+        <v>4</v>
+      </c>
+      <c r="G192" s="13">
+        <v>101</v>
+      </c>
+      <c r="H192" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I192" s="16">
+        <f t="shared" si="40"/>
+        <v>114.13</v>
+      </c>
+      <c r="J192" s="8"/>
       <c r="K192" s="17">
-        <f>SUM(J6:J190)</f>
-        <v>0</v>
-      </c>
-      <c r="L192" s="6" t="s">
-        <v>317</v>
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="L192" s="17">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M192" s="16">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="N192" s="18">
+        <f t="shared" si="39"/>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:13">
-      <c r="A193" s="45"/>
-      <c r="B193" s="45"/>
-      <c r="C193" s="45"/>
-      <c r="D193" s="45"/>
-      <c r="E193" s="45"/>
       <c r="F193" s="7"/>
       <c r="G193" s="13"/>
       <c r="H193" s="15"/>
-      <c r="I193" s="45"/>
-      <c r="J193" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="K193" s="7">
-        <f>SUM(K6:K190)</f>
+      <c r="J193" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="K193" s="17">
+        <f>SUM(J6:J191)</f>
         <v>0</v>
       </c>
       <c r="L193" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -14278,21 +14304,20 @@
       <c r="C194" s="45"/>
       <c r="D194" s="45"/>
       <c r="E194" s="45"/>
-      <c r="F194" s="45"/>
+      <c r="F194" s="7"/>
       <c r="G194" s="13"/>
       <c r="H194" s="15"/>
       <c r="I194" s="45"/>
       <c r="J194" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="K194" s="4">
-        <f>SUM(L:L)</f>
-        <v>0</v>
-      </c>
-      <c r="L194" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="K194" s="7">
+        <f>SUM(K6:K191)</f>
+        <v>0</v>
+      </c>
+      <c r="L194" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="M194" s="41"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="45"/>
@@ -14305,13 +14330,15 @@
       <c r="H195" s="15"/>
       <c r="I195" s="45"/>
       <c r="J195" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="K195" s="45">
-        <f>SUM(N5:N191)</f>
-        <v>0</v>
-      </c>
-      <c r="L195" s="45"/>
+        <v>320</v>
+      </c>
+      <c r="K195" s="4">
+        <f>SUM(L:L)</f>
+        <v>0</v>
+      </c>
+      <c r="L195" s="46" t="s">
+        <v>319</v>
+      </c>
       <c r="M195" s="41"/>
     </row>
     <row r="196" spans="1:13">
@@ -14324,8 +14351,13 @@
       <c r="G196" s="13"/>
       <c r="H196" s="15"/>
       <c r="I196" s="45"/>
-      <c r="J196" s="45"/>
-      <c r="K196" s="45"/>
+      <c r="J196" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="K196" s="45">
+        <f>SUM(N5:N192)</f>
+        <v>0</v>
+      </c>
       <c r="L196" s="45"/>
       <c r="M196" s="41"/>
     </row>
@@ -14351,7 +14383,7 @@
       <c r="D198" s="45"/>
       <c r="E198" s="45"/>
       <c r="F198" s="45"/>
-      <c r="G198" s="45"/>
+      <c r="G198" s="13"/>
       <c r="H198" s="15"/>
       <c r="I198" s="45"/>
       <c r="J198" s="45"/>
@@ -14386,9 +14418,7 @@
       <c r="I200" s="45"/>
       <c r="J200" s="45"/>
       <c r="K200" s="45"/>
-      <c r="L200" s="45" t="s">
-        <v>221</v>
-      </c>
+      <c r="L200" s="45"/>
       <c r="M200" s="41"/>
     </row>
     <row r="201" spans="1:13">
@@ -14399,11 +14429,13 @@
       <c r="E201" s="45"/>
       <c r="F201" s="45"/>
       <c r="G201" s="45"/>
-      <c r="H201" s="45"/>
+      <c r="H201" s="15"/>
       <c r="I201" s="45"/>
       <c r="J201" s="45"/>
       <c r="K201" s="45"/>
-      <c r="L201" s="45"/>
+      <c r="L201" s="45" t="s">
+        <v>221</v>
+      </c>
       <c r="M201" s="41"/>
     </row>
     <row r="202" spans="1:13">
@@ -14451,33 +14483,48 @@
       <c r="L204" s="45"/>
       <c r="M204" s="41"/>
     </row>
-    <row r="206" spans="1:13">
-      <c r="B206" s="6"/>
-      <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
-      <c r="E206" s="6"/>
-    </row>
-    <row r="208" spans="1:13">
-      <c r="J208" s="6"/>
+    <row r="205" spans="1:13">
+      <c r="A205" s="45"/>
+      <c r="B205" s="45"/>
+      <c r="C205" s="45"/>
+      <c r="D205" s="45"/>
+      <c r="E205" s="45"/>
+      <c r="F205" s="45"/>
+      <c r="G205" s="45"/>
+      <c r="H205" s="45"/>
+      <c r="I205" s="45"/>
+      <c r="J205" s="45"/>
+      <c r="K205" s="45"/>
+      <c r="L205" s="45"/>
+      <c r="M205" s="41"/>
+    </row>
+    <row r="207" spans="1:13">
+      <c r="B207" s="6"/>
+      <c r="C207" s="6"/>
+      <c r="D207" s="6"/>
+      <c r="E207" s="6"/>
     </row>
     <row r="209" spans="2:11">
-      <c r="K209" s="2" t="s">
+      <c r="J209" s="6"/>
+    </row>
+    <row r="210" spans="2:11">
+      <c r="K210" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="210" spans="2:11">
-      <c r="B210" s="6"/>
-      <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
-      <c r="E210" s="6"/>
-    </row>
-    <row r="223" spans="2:11">
-      <c r="E223" s="2" t="s">
+    <row r="211" spans="2:11">
+      <c r="B211" s="6"/>
+      <c r="C211" s="6"/>
+      <c r="D211" s="6"/>
+      <c r="E211" s="6"/>
+    </row>
+    <row r="224" spans="2:11">
+      <c r="E224" s="2" t="s">
         <v>221</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P195" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P196" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14496,7 +14543,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N191,工作表2!N6:N191&gt;0,"")</f>
+        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N192,工作表2!N6:N192&gt;0,"")</f>
         <v/>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -2694,7 +2694,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{180168D4-10D2-47BE-9C9D-5E3511E756DE}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{49295D35-08E6-4C46-BA06-FECC44474DE7}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2703,7 +2703,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{CB28540B-C89E-4051-8639-73313546CA54}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{5AD58371-CA77-47E9-808D-14B839EAA3F4}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -12921,7 +12921,7 @@
         <v>259</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>101</v>
+        <v>269</v>
       </c>
       <c r="D159" s="13" t="s">
         <v>257</v>

--- a/template.xlsx
+++ b/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="合同 " sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet name="工作表3" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$200</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'合同 '!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">发票!$A$1:$E$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">装箱单!$A$1:$L$36</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="326">
   <si>
     <t>销 售 合 同
 SALES CONTRACT</t>
@@ -602,6 +602,12 @@
     <t>Mx500</t>
   </si>
   <si>
+    <t>圆1200</t>
+  </si>
+  <si>
+    <t>50酱杯</t>
+  </si>
+  <si>
     <t>EP55</t>
   </si>
   <si>
@@ -728,6 +734,12 @@
     <t>河南海翔新材料科技有限公司</t>
   </si>
   <si>
+    <t>Ai6818黄</t>
+  </si>
+  <si>
+    <t>Ai55</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -875,6 +887,9 @@
     <t>6"甘蔗旦碟</t>
   </si>
   <si>
+    <t>浙江福昌环保科技有限公司</t>
+  </si>
+  <si>
     <t>7"甘蔗圓碟</t>
   </si>
   <si>
@@ -912,9 +927,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 紙餐具：飯盒蓋</t>
-  </si>
-  <si>
-    <t>浙江福昌环保科技有限公司</t>
   </si>
   <si>
     <t>9"甘蔗三格圓碟</t>
@@ -2694,7 +2706,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{49295D35-08E6-4C46-BA06-FECC44474DE7}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{3528275F-0746-488F-BF63-EBAD79B963D2}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2703,7 +2715,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{5AD58371-CA77-47E9-808D-14B839EAA3F4}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{79913256-A79F-4A51-9171-215E2F7C331A}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -6373,7 +6385,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P224"/>
+  <dimension ref="A1:P228"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.4" style="2" customWidth="1"/>
@@ -8391,7 +8403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1" spans="1:15">
+    <row r="49" ht="14.25" customHeight="1" spans="1:14">
       <c r="A49" s="12"/>
       <c r="B49" s="21" t="s">
         <v>171</v>
@@ -8436,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1" spans="1:15">
+    <row r="50" ht="14.25" customHeight="1" spans="1:14">
       <c r="A50" s="12"/>
       <c r="B50" s="21" t="s">
         <v>172</v>
@@ -8481,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1" spans="1:15">
+    <row r="51" ht="14.25" customHeight="1" spans="1:14">
       <c r="A51" s="12"/>
       <c r="B51" s="21" t="s">
         <v>173</v>
@@ -8499,7 +8511,7 @@
         <v>11</v>
       </c>
       <c r="G51" s="13">
-        <f>I51-1</f>
+        <f t="shared" ref="G51:G56" si="8">I51-1</f>
         <v>114</v>
       </c>
       <c r="H51" s="15">
@@ -8526,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1" spans="1:15">
+    <row r="52" ht="14.25" customHeight="1" spans="1:14">
       <c r="A52" s="12"/>
       <c r="B52" s="21" t="s">
         <v>174</v>
@@ -8542,7 +8554,7 @@
         <v>9.6</v>
       </c>
       <c r="G52" s="13">
-        <f>I52-1</f>
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
       <c r="H52" s="15">
@@ -8569,7 +8581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1" spans="1:15">
+    <row r="53" ht="14.25" customHeight="1" spans="1:14">
       <c r="A53" s="12"/>
       <c r="B53" s="20" t="s">
         <v>175</v>
@@ -8585,7 +8597,7 @@
         <v>10.62</v>
       </c>
       <c r="G53" s="13">
-        <f>I53-1</f>
+        <f t="shared" si="8"/>
         <v>131</v>
       </c>
       <c r="H53" s="15">
@@ -8612,7 +8624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1" spans="1:15">
+    <row r="54" ht="14.25" customHeight="1" spans="1:14">
       <c r="A54" s="12"/>
       <c r="B54" s="20" t="s">
         <v>176</v>
@@ -8628,7 +8640,7 @@
         <v>8.83</v>
       </c>
       <c r="G54" s="13">
-        <f>I54-1</f>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="H54" s="15">
@@ -8655,32 +8667,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1" spans="1:15">
+    <row r="55" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A55" s="12"/>
       <c r="B55" s="20" t="s">
         <v>177</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>127</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E55" s="20"/>
       <c r="F55" s="7">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="G55" s="13">
-        <f>I55/(1+H55)</f>
-        <v>81.7256637168142</v>
+        <f t="shared" si="8"/>
+        <v>144</v>
       </c>
       <c r="H55" s="15">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I55" s="16">
-        <v>92.35</v>
+        <v>145</v>
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="17">
@@ -8700,32 +8710,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1" spans="1:15">
+    <row r="56" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A56" s="12"/>
       <c r="B56" s="20" t="s">
         <v>178</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>166</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E56" s="20"/>
       <c r="F56" s="7">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="G56" s="13">
-        <f>I56/(1+H56)</f>
-        <v>77.2566371681416</v>
+        <f t="shared" si="8"/>
+        <v>84</v>
       </c>
       <c r="H56" s="15">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I56" s="16">
-        <v>87.3</v>
+        <v>85</v>
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="17">
@@ -8745,9 +8753,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1" spans="1:15">
+    <row r="57" ht="14.25" customHeight="1" spans="1:14">
       <c r="A57" s="12"/>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="20" t="s">
         <v>179</v>
       </c>
       <c r="C57" s="8" t="s">
@@ -8757,40 +8765,40 @@
         <v>136</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F57" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G57" s="13">
         <f>I57/(1+H57)</f>
-        <v>69.3362831858407</v>
+        <v>81.7256637168142</v>
       </c>
       <c r="H57" s="15">
         <v>0.13</v>
       </c>
       <c r="I57" s="16">
-        <v>78.35</v>
+        <v>92.35</v>
       </c>
       <c r="J57" s="8"/>
       <c r="K57" s="17">
-        <f t="shared" si="1"/>
+        <f>J57*F57</f>
         <v>0</v>
       </c>
       <c r="L57" s="17">
-        <f t="shared" si="2"/>
+        <f>K57+J57/2</f>
         <v>0</v>
       </c>
       <c r="M57" s="16">
-        <f t="shared" si="3"/>
+        <f>J57*I57</f>
         <v>0</v>
       </c>
       <c r="N57" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customHeight="1" spans="1:15">
+        <f>M57+J57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customHeight="1" spans="1:14">
       <c r="A58" s="12"/>
       <c r="B58" s="20" t="s">
         <v>180</v>
@@ -8805,195 +8813,195 @@
         <v>166</v>
       </c>
       <c r="F58" s="7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G58" s="13">
-        <v>94.09</v>
+        <f>I58/(1+H58)</f>
+        <v>77.2566371681416</v>
       </c>
       <c r="H58" s="15">
         <v>0.13</v>
       </c>
-      <c r="I58" s="23">
-        <f>G58+1</f>
+      <c r="I58" s="16">
+        <v>87.3</v>
+      </c>
+      <c r="J58" s="8"/>
+      <c r="K58" s="17">
+        <f>J58*F58</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="17">
+        <f>K58+J58/2</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="16">
+        <f>J58*I58</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="18">
+        <f>M58+J58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customHeight="1" spans="1:14">
+      <c r="A59" s="12"/>
+      <c r="B59" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F59" s="7">
+        <v>8</v>
+      </c>
+      <c r="G59" s="13">
+        <f>I59/(1+H59)</f>
+        <v>69.3362831858407</v>
+      </c>
+      <c r="H59" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I59" s="16">
+        <v>78.35</v>
+      </c>
+      <c r="J59" s="8"/>
+      <c r="K59" s="17">
+        <f>J59*F59</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="17">
+        <f>K59+J59/2</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="16">
+        <f>J59*I59</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="18">
+        <f>M59+J59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customHeight="1" spans="1:14">
+      <c r="A60" s="12"/>
+      <c r="B60" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F60" s="7">
+        <v>8.4</v>
+      </c>
+      <c r="G60" s="13">
+        <v>94.09</v>
+      </c>
+      <c r="H60" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I60" s="23">
+        <f>G60+1</f>
         <v>95.09</v>
       </c>
-      <c r="J58" s="24"/>
-      <c r="K58" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="16">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N58" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="J59" s="24"/>
-      <c r="K59" s="24"/>
-      <c r="L59" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="24"/>
-      <c r="N59" s="24"/>
-    </row>
-    <row r="60" spans="1:15">
-      <c r="A60" s="12"/>
-      <c r="B60" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
+      <c r="J60" s="24"/>
+      <c r="K60" s="17">
+        <f>J60*F60</f>
+        <v>0</v>
+      </c>
       <c r="L60" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-    </row>
-    <row r="61" spans="1:15">
+        <f>K60+J60/2</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="16">
+        <f>J60*I60</f>
+        <v>0</v>
+      </c>
+      <c r="N60" s="18">
+        <f>M60+J60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="12"/>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="17">
+        <f>K61+J61/2</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="12"/>
+      <c r="B62" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="17">
+        <f>K62+J62/2</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="12"/>
+      <c r="B63" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E61" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F61" s="7">
+      <c r="D63" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="F63" s="7">
         <v>8.5</v>
       </c>
-      <c r="G61" s="13">
+      <c r="G63" s="13">
         <f>9823.01/60</f>
         <v>163.716833333333</v>
       </c>
-      <c r="H61" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I61" s="16">
-        <f>G61*(1+H61)</f>
-        <v>185.000021666667</v>
-      </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="17">
-        <f>J61*F61</f>
-        <v>0</v>
-      </c>
-      <c r="L61" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="16">
-        <f>J61*I61</f>
-        <v>0</v>
-      </c>
-      <c r="N61" s="18">
-        <f>M61+J61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
-      <c r="A62" s="12"/>
-      <c r="B62" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E62" s="26">
-        <v>1000</v>
-      </c>
-      <c r="F62" s="7">
-        <v>18.2</v>
-      </c>
-      <c r="G62" s="13">
-        <f>I62/(1+H62)</f>
-        <v>336.283185840708</v>
-      </c>
-      <c r="H62" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I62" s="16">
-        <v>380</v>
-      </c>
-      <c r="J62" s="8"/>
-      <c r="K62" s="17">
-        <f>J62*F62</f>
-        <v>0</v>
-      </c>
-      <c r="L62" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M62" s="16">
-        <f>J62*I62</f>
-        <v>0</v>
-      </c>
-      <c r="N62" s="18">
-        <f>M62+J62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
-      <c r="A63" s="12"/>
-      <c r="B63" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E63" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="F63" s="7">
-        <v>9.25</v>
-      </c>
-      <c r="G63" s="13">
-        <f>I63/(1+H63)</f>
-        <v>141.592920353982</v>
-      </c>
       <c r="H63" s="15">
         <v>0.13</v>
       </c>
-      <c r="I63" s="13">
-        <v>160</v>
+      <c r="I63" s="16">
+        <f>G63*(1+H63)</f>
+        <v>185.000021666667</v>
       </c>
       <c r="J63" s="8"/>
       <c r="K63" s="17">
@@ -9001,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="17">
-        <f t="shared" si="2"/>
+        <f>K63+J63/2</f>
         <v>0</v>
       </c>
       <c r="M63" s="16">
@@ -9012,32 +9020,33 @@
         <f>M63+J63</f>
         <v>0</v>
       </c>
-      <c r="O63" s="13"/>
-    </row>
-    <row r="64" spans="1:15">
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" s="12"/>
       <c r="B64" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E64" s="26"/>
+        <v>186</v>
+      </c>
+      <c r="E64" s="26">
+        <v>1000</v>
+      </c>
       <c r="F64" s="7">
-        <v>13.5</v>
+        <v>18.2</v>
       </c>
       <c r="G64" s="13">
         <f>I64/(1+H64)</f>
-        <v>176.991150442478</v>
+        <v>336.283185840708</v>
       </c>
       <c r="H64" s="15">
         <v>0.13</v>
       </c>
-      <c r="I64" s="13">
-        <v>200</v>
+      <c r="I64" s="16">
+        <v>380</v>
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="17">
@@ -9045,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="17">
-        <f t="shared" si="2"/>
+        <f>K64+J64/2</f>
         <v>0</v>
       </c>
       <c r="M64" s="16">
@@ -9056,52 +9065,77 @@
         <f>M64+J64</f>
         <v>0</v>
       </c>
-      <c r="O64" s="13"/>
-    </row>
-    <row r="65" spans="1:14">
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="12"/>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E65" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="15"/>
+      <c r="F65" s="7">
+        <v>9.25</v>
+      </c>
+      <c r="G65" s="13">
+        <f>I65/(1+H65)</f>
+        <v>141.592920353982</v>
+      </c>
+      <c r="H65" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I65" s="13">
+        <v>160</v>
+      </c>
+      <c r="J65" s="8"/>
+      <c r="K65" s="17">
+        <f>J65*F65</f>
+        <v>0</v>
+      </c>
       <c r="L65" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="2"/>
-    </row>
-    <row r="66" spans="1:14">
+        <f>K65+J65/2</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="16">
+        <f>J65*I65</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="18">
+        <f>M65+J65</f>
+        <v>0</v>
+      </c>
+      <c r="O65" s="13"/>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="12"/>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="27" t="s">
         <v>191</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E66" s="26" t="s">
-        <v>185</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="E66" s="26"/>
       <c r="F66" s="7">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="G66" s="13">
-        <f>5575.22/60</f>
-        <v>92.9203333333333</v>
+        <f>I66/(1+H66)</f>
+        <v>176.991150442478</v>
       </c>
       <c r="H66" s="15">
         <v>0.13</v>
       </c>
-      <c r="I66" s="16">
-        <f>G66*(1+H66)</f>
-        <v>104.999976666667</v>
+      <c r="I66" s="13">
+        <v>200</v>
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="17">
@@ -9109,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="17">
-        <f t="shared" si="2"/>
+        <f>K66+J66/2</f>
         <v>0</v>
       </c>
       <c r="M66" s="16">
@@ -9117,81 +9151,55 @@
         <v>0</v>
       </c>
       <c r="N66" s="18">
-        <f t="shared" ref="N66:N93" si="8">M66+J66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <f>M66+J66</f>
+        <v>0</v>
+      </c>
+      <c r="O66" s="13"/>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" s="12"/>
-      <c r="B67" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" s="13" t="s">
+      <c r="B67" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E67" s="26">
-        <v>1000</v>
-      </c>
-      <c r="F67" s="7">
-        <v>7</v>
-      </c>
-      <c r="G67" s="13">
-        <f>I67/(1+H67)</f>
-        <v>230.088495575221</v>
-      </c>
-      <c r="H67" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I67" s="16">
-        <v>260</v>
-      </c>
-      <c r="J67" s="8"/>
-      <c r="K67" s="17">
-        <f>J67*F67</f>
-        <v>0</v>
-      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="15"/>
       <c r="L67" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="16">
-        <f>J67*I67</f>
-        <v>0</v>
-      </c>
-      <c r="N67" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <f>K67+J67/2</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="2"/>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="12"/>
       <c r="B68" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F68" s="7">
-        <v>9.25</v>
+        <v>2.4</v>
       </c>
       <c r="G68" s="13">
-        <f>I68/(1+H68)</f>
-        <v>141.592920353982</v>
+        <f>5575.22/60</f>
+        <v>92.9203333333333</v>
       </c>
       <c r="H68" s="15">
         <v>0.13</v>
       </c>
       <c r="I68" s="16">
-        <v>160</v>
+        <f>G68*(1+H68)</f>
+        <v>104.999976666667</v>
       </c>
       <c r="J68" s="8"/>
       <c r="K68" s="17">
@@ -9199,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="17">
-        <f t="shared" si="2"/>
+        <f>K68+J68/2</f>
         <v>0</v>
       </c>
       <c r="M68" s="16">
@@ -9207,11 +9215,11 @@
         <v>0</v>
       </c>
       <c r="N68" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <f t="shared" ref="N68:N95" si="9">M68+J68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="12"/>
       <c r="B69" s="27" t="s">
         <v>195</v>
@@ -9220,21 +9228,23 @@
         <v>95</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E69" s="26"/>
+        <v>194</v>
+      </c>
+      <c r="E69" s="26">
+        <v>1000</v>
+      </c>
       <c r="F69" s="7">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="G69" s="13">
         <f>I69/(1+H69)</f>
-        <v>141.592920353982</v>
+        <v>230.088495575221</v>
       </c>
       <c r="H69" s="15">
         <v>0.13</v>
       </c>
       <c r="I69" s="16">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="17">
@@ -9242,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="17">
-        <f t="shared" si="2"/>
+        <f>K69+J69/2</f>
         <v>0</v>
       </c>
       <c r="M69" s="16">
@@ -9250,128 +9260,126 @@
         <v>0</v>
       </c>
       <c r="N69" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="12"/>
-      <c r="B70" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="16"/>
+      <c r="B70" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F70" s="7">
+        <v>9.25</v>
+      </c>
+      <c r="G70" s="13">
+        <f>I70/(1+H70)</f>
+        <v>141.592920353982</v>
+      </c>
+      <c r="H70" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I70" s="16">
+        <v>160</v>
+      </c>
       <c r="J70" s="8"/>
-      <c r="K70" s="17"/>
+      <c r="K70" s="17">
+        <f>J70*F70</f>
+        <v>0</v>
+      </c>
       <c r="L70" s="17">
-        <f t="shared" ref="L70:L82" si="9">K70+J70/2</f>
-        <v>0</v>
-      </c>
-      <c r="M70" s="16"/>
+        <f>K70+J70/2</f>
+        <v>0</v>
+      </c>
+      <c r="M70" s="16">
+        <f>J70*I70</f>
+        <v>0</v>
+      </c>
       <c r="N70" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="12"/>
-      <c r="B71" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>91</v>
+      <c r="B71" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>197</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="E71" s="26"/>
       <c r="F71" s="7">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="G71" s="13">
-        <v>68</v>
+        <f>I71/(1+H71)</f>
+        <v>141.592920353982</v>
       </c>
       <c r="H71" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I71" s="16">
-        <f t="shared" ref="I71:I78" si="10">G71*(1+H71)</f>
-        <v>73.44</v>
+        <v>160</v>
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="17">
-        <f t="shared" ref="K71:K93" si="11">J71*F71</f>
+        <f>J71*F71</f>
         <v>0</v>
       </c>
       <c r="L71" s="17">
+        <f>K71+J71/2</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="16">
+        <f>J71*I71</f>
+        <v>0</v>
+      </c>
+      <c r="N71" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M71" s="16">
-        <f t="shared" ref="M71:M93" si="12">J71*I71</f>
-        <v>0</v>
-      </c>
-      <c r="N71" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="12"/>
-      <c r="B72" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F72" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="G72" s="13">
-        <v>74</v>
-      </c>
-      <c r="H72" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I72" s="16">
-        <f t="shared" si="10"/>
-        <v>79.92</v>
-      </c>
+      <c r="B72" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="16"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="17">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="K72" s="17"/>
       <c r="L72" s="17">
+        <f t="shared" ref="L72:L84" si="10">K72+J72/2</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="16"/>
+      <c r="N72" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M72" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N72" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:15">
       <c r="A73" s="12"/>
       <c r="B73" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>91</v>
@@ -9380,42 +9388,42 @@
         <v>136</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F73" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G73" s="13">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H73" s="15">
         <v>0.08</v>
       </c>
       <c r="I73" s="16">
-        <f t="shared" si="10"/>
-        <v>88.56</v>
+        <f t="shared" ref="I73:I80" si="11">G73*(1+H73)</f>
+        <v>73.44</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="K73:K95" si="12">J73*F73</f>
         <v>0</v>
       </c>
       <c r="L73" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="16">
+        <f t="shared" ref="M73:M95" si="13">J73*I73</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M73" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N73" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="12"/>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="19" t="s">
         <v>200</v>
       </c>
       <c r="C74" s="8" t="s">
@@ -9425,40 +9433,40 @@
         <v>136</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F74" s="7">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G74" s="13">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H74" s="15">
         <v>0.08</v>
       </c>
       <c r="I74" s="16">
-        <f t="shared" si="10"/>
-        <v>97.2</v>
+        <f t="shared" si="11"/>
+        <v>79.92</v>
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L74" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M74" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N74" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M74" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N74" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="12"/>
       <c r="B75" s="19" t="s">
         <v>201</v>
@@ -9470,40 +9478,40 @@
         <v>136</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="F75" s="7">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G75" s="13">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="H75" s="15">
         <v>0.08</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="10"/>
-        <v>65.88</v>
+        <f t="shared" si="11"/>
+        <v>88.56</v>
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L75" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N75" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M75" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N75" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" s="12"/>
       <c r="B76" s="12" t="s">
         <v>202</v>
@@ -9515,40 +9523,40 @@
         <v>136</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="F76" s="7">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="G76" s="13">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H76" s="15">
         <v>0.08</v>
       </c>
       <c r="I76" s="16">
-        <f t="shared" si="10"/>
-        <v>63.72</v>
+        <f t="shared" si="11"/>
+        <v>97.2</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L76" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N76" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M76" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77" s="12"/>
       <c r="B77" s="19" t="s">
         <v>203</v>
@@ -9572,31 +9580,31 @@
         <v>0.08</v>
       </c>
       <c r="I77" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>65.88</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L77" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M77" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="12"/>
-      <c r="B78" s="19">
-        <v>6828</v>
+      <c r="B78" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>91</v>
@@ -9617,159 +9625,159 @@
         <v>0.08</v>
       </c>
       <c r="I78" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>63.72</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L78" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M78" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N78" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M78" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N78" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" s="2" customFormat="1" spans="1:14">
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" s="12"/>
-      <c r="B79" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="C79" s="29" t="s">
+      <c r="B79" s="19" t="s">
         <v>205</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E79" s="30" t="s">
-        <v>129</v>
+      <c r="E79" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="F79" s="7">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="G79" s="13">
-        <f t="shared" ref="G79:G83" si="13">I79-1</f>
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="H79" s="15">
         <v>0.08</v>
       </c>
-      <c r="I79" s="13">
-        <v>90</v>
+      <c r="I79" s="16">
+        <f t="shared" si="11"/>
+        <v>65.88</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L79" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M79" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N79" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M79" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N79" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:14">
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80" s="12"/>
-      <c r="B80" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C80" s="29" t="s">
-        <v>205</v>
+      <c r="B80" s="19">
+        <v>6828</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E80" s="30" t="s">
+      <c r="E80" s="14" t="s">
         <v>127</v>
       </c>
       <c r="F80" s="7">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="G80" s="13">
-        <f t="shared" si="13"/>
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H80" s="15">
         <v>0.08</v>
       </c>
-      <c r="I80" s="13">
-        <v>70</v>
+      <c r="I80" s="16">
+        <f t="shared" si="11"/>
+        <v>63.72</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L80" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N80" s="18">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N80" s="18">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" spans="1:14">
       <c r="A81" s="12"/>
-      <c r="B81" s="31" t="s">
+      <c r="B81" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C81" s="29" t="s">
         <v>207</v>
-      </c>
-      <c r="C81" s="29" t="s">
-        <v>205</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E81" s="30" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="F81" s="7">
         <v>8.4</v>
       </c>
       <c r="G81" s="13">
-        <f t="shared" si="13"/>
-        <v>91</v>
+        <f t="shared" ref="G81:G85" si="14">I81-1</f>
+        <v>89</v>
       </c>
       <c r="H81" s="15">
         <v>0.08</v>
       </c>
       <c r="I81" s="13">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L81" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M81" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N81" s="18">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N81" s="18">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -9779,175 +9787,175 @@
         <v>208</v>
       </c>
       <c r="C82" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F82" s="7">
-        <v>10.4</v>
+        <v>6.3</v>
       </c>
       <c r="G82" s="13">
-        <f t="shared" si="13"/>
-        <v>76</v>
+        <f t="shared" si="14"/>
+        <v>69</v>
       </c>
       <c r="H82" s="15">
         <v>0.08</v>
       </c>
       <c r="I82" s="13">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L82" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M82" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N82" s="18">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N82" s="18">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" spans="1:14">
       <c r="A83" s="12"/>
-      <c r="B83" s="29" t="s">
+      <c r="B83" s="31" t="s">
         <v>209</v>
       </c>
       <c r="C83" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E83" s="30" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F83" s="7">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" si="13"/>
-        <v>89</v>
+        <f t="shared" si="14"/>
+        <v>91</v>
       </c>
       <c r="H83" s="15">
         <v>0.08</v>
       </c>
       <c r="I83" s="13">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J83" s="8"/>
-      <c r="K83" s="17"/>
-      <c r="L83" s="17"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="18"/>
+      <c r="K83" s="17">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L83" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M83" s="16">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N83" s="18">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="84" s="2" customFormat="1" spans="1:14">
       <c r="A84" s="12"/>
-      <c r="B84" s="31" t="s">
+      <c r="B84" s="29" t="s">
         <v>210</v>
       </c>
       <c r="C84" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E84" s="30" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F84" s="7">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G84" s="13">
-        <f t="shared" ref="G84:G89" si="14">I84-1</f>
-        <v>113</v>
+        <f t="shared" si="14"/>
+        <v>76</v>
       </c>
       <c r="H84" s="15">
         <v>0.08</v>
       </c>
       <c r="I84" s="13">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="17">
-        <f t="shared" ref="K84:K94" si="15">J84*F84</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L84" s="17">
-        <f t="shared" ref="L84:L94" si="16">K84+J84/2</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M84" s="16">
-        <f t="shared" ref="M84:M94" si="17">J84*I84</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N84" s="18">
-        <f t="shared" ref="N84:N94" si="18">M84+J84</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" spans="1:14">
       <c r="A85" s="12"/>
-      <c r="B85" s="31" t="s">
+      <c r="B85" s="29" t="s">
         <v>211</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E85" s="30" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="F85" s="7">
-        <v>7.2</v>
+        <v>11.4</v>
       </c>
       <c r="G85" s="13">
         <f t="shared" si="14"/>
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H85" s="15">
         <v>0.08</v>
       </c>
       <c r="I85" s="13">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J85" s="8"/>
-      <c r="K85" s="17">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L85" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="16">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="N85" s="18">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="K85" s="17"/>
+      <c r="L85" s="17"/>
+      <c r="M85" s="16"/>
+      <c r="N85" s="18"/>
     </row>
     <row r="86" s="2" customFormat="1" spans="1:14">
       <c r="A86" s="12"/>
-      <c r="B86" s="29" t="s">
-        <v>213</v>
+      <c r="B86" s="31" t="s">
+        <v>212</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>136</v>
@@ -9956,78 +9964,78 @@
         <v>129</v>
       </c>
       <c r="F86" s="7">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="G86" s="13">
-        <f t="shared" si="14"/>
-        <v>73.7</v>
+        <f t="shared" ref="G86:G91" si="15">I86-1</f>
+        <v>113</v>
       </c>
       <c r="H86" s="15">
         <v>0.08</v>
       </c>
       <c r="I86" s="13">
-        <v>74.7</v>
+        <v>114</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="K86:K98" si="16">J86*F86</f>
         <v>0</v>
       </c>
       <c r="L86" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="L86:L98" si="17">K86+J86/2</f>
         <v>0</v>
       </c>
       <c r="M86" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="M86:M98" si="18">J86*I86</f>
         <v>0</v>
       </c>
       <c r="N86" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="N86:N98" si="19">M86+J86</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" spans="1:14">
       <c r="A87" s="12"/>
-      <c r="B87" s="29" t="s">
-        <v>214</v>
+      <c r="B87" s="31" t="s">
+        <v>213</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="F87" s="7">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="G87" s="13">
-        <f t="shared" si="14"/>
-        <v>74.1</v>
+        <f t="shared" si="15"/>
+        <v>73</v>
       </c>
       <c r="H87" s="15">
         <v>0.08</v>
       </c>
       <c r="I87" s="13">
-        <v>75.1</v>
+        <v>74</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L87" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M87" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N87" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -10037,42 +10045,42 @@
         <v>215</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F88" s="7">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="G88" s="13">
-        <f t="shared" si="14"/>
-        <v>58.1</v>
+        <f t="shared" si="15"/>
+        <v>73.7</v>
       </c>
       <c r="H88" s="15">
         <v>0.08</v>
       </c>
       <c r="I88" s="13">
-        <v>59.1</v>
+        <v>74.7</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L88" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M88" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N88" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -10082,399 +10090,443 @@
         <v>216</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E89" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F89" s="7">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="G89" s="13">
-        <f t="shared" si="14"/>
-        <v>124</v>
+        <f t="shared" si="15"/>
+        <v>74.1</v>
       </c>
       <c r="H89" s="15">
         <v>0.08</v>
       </c>
       <c r="I89" s="13">
-        <v>125</v>
+        <v>75.1</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L89" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M89" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N89" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" spans="1:14">
       <c r="A90" s="12"/>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>218</v>
+      <c r="C90" s="29" t="s">
+        <v>207</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E90" s="12"/>
+      <c r="E90" s="30" t="s">
+        <v>127</v>
+      </c>
       <c r="F90" s="7">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G90" s="13">
-        <v>80</v>
+        <f t="shared" si="15"/>
+        <v>58.1</v>
       </c>
       <c r="H90" s="15">
         <v>0.08</v>
       </c>
       <c r="I90" s="13">
-        <v>81</v>
+        <v>59.1</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L90" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M90" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N90" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" spans="1:14">
       <c r="A91" s="12"/>
-      <c r="B91" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C91" s="12" t="s">
+      <c r="B91" s="29" t="s">
         <v>218</v>
+      </c>
+      <c r="C91" s="29" t="s">
+        <v>207</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E91" s="14" t="s">
-        <v>197</v>
+      <c r="E91" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="F91" s="7">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G91" s="13">
-        <v>68</v>
+        <f t="shared" si="15"/>
+        <v>124</v>
       </c>
       <c r="H91" s="15">
         <v>0.08</v>
       </c>
-      <c r="I91" s="16">
-        <f t="shared" ref="I91:I94" si="19">G91*(1+H91)</f>
-        <v>73.44</v>
+      <c r="I91" s="13">
+        <v>125</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L91" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M91" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N91" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" spans="1:14">
       <c r="A92" s="12"/>
-      <c r="B92" s="19" t="s">
-        <v>198</v>
+      <c r="B92" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E92" s="14" t="s">
-        <v>197</v>
-      </c>
+      <c r="E92" s="12"/>
       <c r="F92" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G92" s="13">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H92" s="15">
         <v>0.08</v>
       </c>
-      <c r="I92" s="16">
-        <f t="shared" si="19"/>
-        <v>79.92</v>
+      <c r="I92" s="13">
+        <v>81</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L92" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M92" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N92" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" s="2" customFormat="1" spans="1:14">
       <c r="A93" s="12"/>
       <c r="B93" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F93" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G93" s="13">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H93" s="15">
         <v>0.08</v>
       </c>
       <c r="I93" s="16">
-        <f t="shared" si="19"/>
-        <v>88.56</v>
+        <f t="shared" ref="I93:I96" si="20">G93*(1+H93)</f>
+        <v>73.44</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L93" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M93" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N93" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" s="2" customFormat="1" spans="1:14">
       <c r="A94" s="12"/>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="19" t="s">
         <v>200</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F94" s="7">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G94" s="13">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H94" s="15">
         <v>0.08</v>
       </c>
       <c r="I94" s="16">
-        <f t="shared" si="19"/>
-        <v>97.2</v>
+        <f t="shared" si="20"/>
+        <v>79.92</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L94" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="16">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N94" s="18">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" spans="1:14">
+      <c r="A95" s="12"/>
+      <c r="B95" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="G95" s="13">
+        <v>82</v>
+      </c>
+      <c r="H95" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I95" s="16">
+        <f t="shared" si="20"/>
+        <v>88.56</v>
+      </c>
+      <c r="J95" s="8"/>
+      <c r="K95" s="17">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M94" s="16">
+      <c r="L95" s="17">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="N94" s="18">
+      <c r="M95" s="16">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:14">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="12"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="J95" s="24"/>
-      <c r="K95" s="24"/>
-      <c r="L95" s="17">
-        <f t="shared" ref="L95:L98" si="20">K95+J95/2</f>
-        <v>0</v>
-      </c>
-      <c r="M95" s="24"/>
-      <c r="N95" s="24"/>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="N95" s="18">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" spans="1:14">
       <c r="A96" s="12"/>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C96" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="16"/>
-      <c r="J96" s="8" t="s">
+      <c r="D96" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F96" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="G96" s="13">
+        <v>90</v>
+      </c>
+      <c r="H96" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I96" s="16">
+        <f t="shared" si="20"/>
+        <v>97.2</v>
+      </c>
+      <c r="J96" s="8"/>
+      <c r="K96" s="17">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L96" s="17">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M96" s="16">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N96" s="18">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" spans="1:14">
+      <c r="A97" s="12"/>
+      <c r="B97" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="K96" s="17"/>
-      <c r="L96" s="17">
-        <v>0</v>
-      </c>
-      <c r="M96" s="16"/>
-      <c r="N96" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
-      <c r="A97" s="12"/>
-      <c r="B97" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>91</v>
+      <c r="C97" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>223</v>
+        <v>136</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="F97" s="7">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="G97" s="13">
-        <v>50.5</v>
+        <v>78</v>
       </c>
       <c r="H97" s="15">
         <v>0.08</v>
       </c>
       <c r="I97" s="16">
-        <f>G97*(1+H97)</f>
-        <v>54.54</v>
+        <v>79</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="17">
-        <f>J97*F97</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L97" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M97" s="16">
-        <f>J97*I97</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N97" s="18">
-        <f>M97+J97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" spans="1:14">
       <c r="A98" s="12"/>
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="29" t="s">
         <v>222</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>197</v>
+        <v>136</v>
+      </c>
+      <c r="E98" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="F98" s="7">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="G98" s="13">
-        <v>50.5</v>
+        <f>I98-1</f>
+        <v>69</v>
       </c>
       <c r="H98" s="15">
         <v>0.08</v>
       </c>
-      <c r="I98" s="16">
-        <f>G98*(1+H98)</f>
-        <v>54.54</v>
+      <c r="I98" s="13">
+        <v>70</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="17">
-        <f>J98*F98</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L98" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M98" s="16">
-        <f>J98*I98</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N98" s="18">
-        <f>M98+J98</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -10488,12 +10540,12 @@
       <c r="G99" s="13"/>
       <c r="H99" s="15"/>
       <c r="I99" s="23" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J99" s="24"/>
       <c r="K99" s="24"/>
       <c r="L99" s="17">
-        <f t="shared" ref="L99:L162" si="21">K99+J99/2</f>
+        <f t="shared" ref="L99:L102" si="21">K99+J99/2</f>
         <v>0</v>
       </c>
       <c r="M99" s="24"/>
@@ -10501,77 +10553,103 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="7"/>
+      <c r="B100" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="11"/>
       <c r="G100" s="13"/>
       <c r="H100" s="15"/>
       <c r="I100" s="16"/>
-      <c r="J100" s="8"/>
+      <c r="J100" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M100" s="16"/>
-      <c r="N100" s="18"/>
+      <c r="N100" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="12"/>
-      <c r="B101" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="16"/>
+      <c r="B101" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F101" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G101" s="13">
+        <v>50.5</v>
+      </c>
+      <c r="H101" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I101" s="16">
+        <f>G101*(1+H101)</f>
+        <v>54.54</v>
+      </c>
       <c r="J101" s="8"/>
-      <c r="K101" s="17"/>
+      <c r="K101" s="17">
+        <f>J101*F101</f>
+        <v>0</v>
+      </c>
       <c r="L101" s="17">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="M101" s="16"/>
+      <c r="M101" s="16">
+        <f>J101*I101</f>
+        <v>0</v>
+      </c>
       <c r="N101" s="18">
-        <f t="shared" ref="N101:N114" si="22">M101+J101</f>
+        <f>M101+J101</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="12"/>
       <c r="B102" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>91</v>
+        <v>226</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F102" s="7">
         <v>4.5</v>
       </c>
       <c r="G102" s="13">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="H102" s="15">
         <v>0.08</v>
       </c>
       <c r="I102" s="16">
-        <f t="shared" ref="I102:I114" si="23">G102*(1+H102)</f>
-        <v>55.08</v>
+        <f>G102*(1+H102)</f>
+        <v>54.54</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="17">
-        <f t="shared" ref="K102:K114" si="24">J102*F102</f>
+        <f>J102*F102</f>
         <v>0</v>
       </c>
       <c r="L102" s="17">
@@ -10579,146 +10657,75 @@
         <v>0</v>
       </c>
       <c r="M102" s="16">
-        <f t="shared" ref="M102:M114" si="25">J102*I102</f>
+        <f>J102*I102</f>
         <v>0</v>
       </c>
       <c r="N102" s="18">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="14" customHeight="1" spans="1:14">
+        <f>M102+J102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103" s="12"/>
-      <c r="B103" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F103" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G103" s="13">
-        <v>54</v>
-      </c>
-      <c r="H103" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I103" s="16">
-        <f t="shared" si="23"/>
-        <v>58.32</v>
-      </c>
-      <c r="J103" s="8"/>
-      <c r="K103" s="17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="15"/>
+      <c r="I103" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="J103" s="24"/>
+      <c r="K103" s="24"/>
       <c r="L103" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M103" s="16">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="N103" s="18">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L103:L166" si="22">K103+J103/2</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="24"/>
+      <c r="N103" s="24"/>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="12"/>
-      <c r="B104" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F104" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="G104" s="13">
-        <v>61</v>
-      </c>
-      <c r="H104" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I104" s="16">
-        <f t="shared" si="23"/>
-        <v>65.88</v>
-      </c>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="15"/>
+      <c r="I104" s="16"/>
       <c r="J104" s="8"/>
-      <c r="K104" s="17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
+      <c r="K104" s="17"/>
       <c r="L104" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="16">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="N104" s="18">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="M104" s="16"/>
+      <c r="N104" s="18"/>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="12"/>
-      <c r="B105" s="19" t="s">
+      <c r="B105" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="C105" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F105" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="G105" s="13">
-        <v>64</v>
-      </c>
-      <c r="H105" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I105" s="16">
-        <f t="shared" si="23"/>
-        <v>69.12</v>
-      </c>
+      <c r="C105" s="10"/>
+      <c r="D105" s="10"/>
+      <c r="E105" s="10"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="15"/>
+      <c r="I105" s="16"/>
       <c r="J105" s="8"/>
-      <c r="K105" s="17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
+      <c r="K105" s="17"/>
       <c r="L105" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="16">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="16"/>
       <c r="N105" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="N105:N118" si="23">M105+J105</f>
         <v>0</v>
       </c>
     </row>
@@ -10734,35 +10741,42 @@
         <v>126</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F106" s="7"/>
-      <c r="G106" s="13"/>
+        <v>199</v>
+      </c>
+      <c r="F106" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G106" s="13">
+        <v>51</v>
+      </c>
       <c r="H106" s="15">
         <v>0.08</v>
       </c>
-      <c r="I106" s="16"/>
+      <c r="I106" s="16">
+        <f t="shared" ref="I106:I118" si="24">G106*(1+H106)</f>
+        <v>55.08</v>
+      </c>
       <c r="J106" s="8"/>
       <c r="K106" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="K106:K118" si="25">J106*F106</f>
         <v>0</v>
       </c>
       <c r="L106" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M106" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="M106:M118" si="26">J106*I106</f>
         <v>0</v>
       </c>
       <c r="N106" s="18">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="14" customHeight="1" spans="1:14">
       <c r="A107" s="12"/>
-      <c r="B107" s="19" t="s">
+      <c r="B107" s="12" t="s">
         <v>230</v>
       </c>
       <c r="C107" s="8" t="s">
@@ -10772,42 +10786,42 @@
         <v>126</v>
       </c>
       <c r="E107" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F107" s="7">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="G107" s="13">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="H107" s="15">
         <v>0.08</v>
       </c>
       <c r="I107" s="16">
-        <f t="shared" si="23"/>
-        <v>74.52</v>
+        <f t="shared" si="24"/>
+        <v>58.32</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L107" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M107" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N107" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="12"/>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="19" t="s">
         <v>231</v>
       </c>
       <c r="C108" s="8" t="s">
@@ -10817,36 +10831,36 @@
         <v>126</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F108" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="G108" s="13">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H108" s="15">
         <v>0.08</v>
       </c>
       <c r="I108" s="16">
-        <f t="shared" si="23"/>
-        <v>77.76</v>
+        <f t="shared" si="24"/>
+        <v>65.88</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L108" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M108" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N108" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -10862,36 +10876,36 @@
         <v>126</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F109" s="7">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="G109" s="13">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="H109" s="15">
         <v>0.08</v>
       </c>
       <c r="I109" s="16">
-        <f t="shared" si="23"/>
-        <v>97.2</v>
+        <f t="shared" si="24"/>
+        <v>69.12</v>
       </c>
       <c r="J109" s="8"/>
       <c r="K109" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L109" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M109" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N109" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -10907,42 +10921,35 @@
         <v>126</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F110" s="7">
-        <v>8.5</v>
-      </c>
-      <c r="G110" s="13">
-        <v>93</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F110" s="7"/>
+      <c r="G110" s="13"/>
       <c r="H110" s="15">
         <v>0.08</v>
       </c>
-      <c r="I110" s="16">
+      <c r="I110" s="16"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="16">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="18">
         <f t="shared" si="23"/>
-        <v>100.44</v>
-      </c>
-      <c r="J110" s="32"/>
-      <c r="K110" s="17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="L110" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M110" s="16">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="N110" s="18">
-        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="12"/>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="19" t="s">
         <v>234</v>
       </c>
       <c r="C111" s="8" t="s">
@@ -10952,35 +10959,42 @@
         <v>126</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F111" s="7"/>
-      <c r="G111" s="13"/>
+        <v>199</v>
+      </c>
+      <c r="F111" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="G111" s="13">
+        <v>69</v>
+      </c>
       <c r="H111" s="15">
         <v>0.08</v>
       </c>
-      <c r="I111" s="16"/>
+      <c r="I111" s="16">
+        <f t="shared" si="24"/>
+        <v>74.52</v>
+      </c>
       <c r="J111" s="8"/>
       <c r="K111" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L111" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M111" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N111" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="12"/>
-      <c r="B112" s="19" t="s">
+      <c r="B112" s="12" t="s">
         <v>235</v>
       </c>
       <c r="C112" s="8" t="s">
@@ -10990,36 +11004,36 @@
         <v>126</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="F112" s="7">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="G112" s="13">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H112" s="15">
         <v>0.08</v>
       </c>
       <c r="I112" s="16">
-        <f t="shared" si="23"/>
-        <v>76.68</v>
+        <f t="shared" si="24"/>
+        <v>77.76</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L112" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M112" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N112" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -11035,42 +11049,42 @@
         <v>126</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="F113" s="7">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="G113" s="13">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H113" s="15">
         <v>0.08</v>
       </c>
       <c r="I113" s="16">
-        <f t="shared" si="23"/>
-        <v>79.92</v>
+        <f t="shared" si="24"/>
+        <v>97.2</v>
       </c>
       <c r="J113" s="8"/>
       <c r="K113" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L113" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M113" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N113" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="12"/>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="19" t="s">
         <v>237</v>
       </c>
       <c r="C114" s="8" t="s">
@@ -11080,274 +11094,271 @@
         <v>126</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F114" s="7"/>
-      <c r="G114" s="13"/>
+        <v>199</v>
+      </c>
+      <c r="F114" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="G114" s="13">
+        <v>93</v>
+      </c>
       <c r="H114" s="15">
         <v>0.08</v>
       </c>
-      <c r="I114" s="16"/>
-      <c r="J114" s="8"/>
+      <c r="I114" s="16">
+        <f t="shared" si="24"/>
+        <v>100.44</v>
+      </c>
+      <c r="J114" s="32"/>
       <c r="K114" s="17">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L114" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M114" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N114" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="12"/>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="12"/>
-      <c r="E115" s="12"/>
+      <c r="B115" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="F115" s="7"/>
       <c r="G115" s="13"/>
-      <c r="H115" s="15"/>
-      <c r="I115" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="J115" s="24"/>
-      <c r="K115" s="24"/>
+      <c r="H115" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I115" s="16"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="L115" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M115" s="24"/>
-      <c r="N115" s="24"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="16">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="N115" s="18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="12"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="13"/>
-      <c r="H116" s="15"/>
-      <c r="I116" s="16"/>
+      <c r="B116" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F116" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G116" s="13">
+        <v>71</v>
+      </c>
+      <c r="H116" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I116" s="16">
+        <f t="shared" si="24"/>
+        <v>76.68</v>
+      </c>
       <c r="J116" s="8"/>
-      <c r="K116" s="17"/>
+      <c r="K116" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="L116" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M116" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M116" s="16">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="N116" s="18">
-        <f t="shared" ref="N116:N123" si="26">M116+J116</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="12"/>
-      <c r="B117" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C117" s="10"/>
-      <c r="D117" s="10"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="13"/>
-      <c r="H117" s="15"/>
-      <c r="I117" s="16"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="17"/>
+      <c r="B117" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F117" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G117" s="13">
+        <v>74</v>
+      </c>
+      <c r="H117" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I117" s="16">
+        <f t="shared" si="24"/>
+        <v>79.92</v>
+      </c>
+      <c r="J117" s="8"/>
+      <c r="K117" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="L117" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M117" s="16">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="N117" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="12"/>
-      <c r="B118" s="19" t="s">
-        <v>239</v>
+      <c r="B118" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F118" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G118" s="13">
-        <v>31.5</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="F118" s="7"/>
+      <c r="G118" s="13"/>
       <c r="H118" s="15">
         <v>0.08</v>
       </c>
-      <c r="I118" s="16">
-        <f t="shared" ref="I118:I123" si="27">G118*(1+H118)</f>
-        <v>34.02</v>
-      </c>
+      <c r="I118" s="16"/>
       <c r="J118" s="8"/>
       <c r="K118" s="17">
-        <f t="shared" ref="K118:K123" si="28">J118*F118</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L118" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M118" s="16">
-        <f t="shared" ref="M118:M123" si="29">J118*I118</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="N118" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="12"/>
-      <c r="B119" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F119" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G119" s="13">
-        <v>42.5</v>
-      </c>
-      <c r="H119" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I119" s="16">
-        <f t="shared" si="27"/>
-        <v>45.9</v>
-      </c>
-      <c r="J119" s="8"/>
-      <c r="K119" s="17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="J119" s="24"/>
+      <c r="K119" s="24"/>
       <c r="L119" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="16">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="N119" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="24"/>
+      <c r="N119" s="24"/>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="12"/>
-      <c r="B120" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E120" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F120" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="G120" s="13">
-        <v>47</v>
-      </c>
-      <c r="H120" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I120" s="16">
+      <c r="F120" s="7"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="16"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="17"/>
+      <c r="L120" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="16"/>
+      <c r="N120" s="18">
+        <f t="shared" ref="N120:N127" si="27">M120+J120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" s="12"/>
+      <c r="B121" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C121" s="10"/>
+      <c r="D121" s="10"/>
+      <c r="E121" s="10"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="15"/>
+      <c r="I121" s="16"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="17"/>
+      <c r="L121" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="16"/>
+      <c r="N121" s="18">
         <f t="shared" si="27"/>
-        <v>50.76</v>
-      </c>
-      <c r="J120" s="4"/>
-      <c r="K120" s="17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="L120" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M120" s="16">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="N120" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="B121" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D121" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E121" s="12"/>
-      <c r="F121" s="7">
-        <v>4</v>
-      </c>
-      <c r="G121" s="13">
-        <v>52</v>
-      </c>
-      <c r="H121" s="33">
-        <v>0.095</v>
-      </c>
-      <c r="I121" s="16">
-        <f t="shared" si="27"/>
-        <v>56.94</v>
-      </c>
-      <c r="J121" s="4"/>
-      <c r="K121" s="17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="L121" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="16">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="N121" s="18">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:14">
-      <c r="B122" s="12" t="s">
+      <c r="A122" s="12"/>
+      <c r="B122" s="19" t="s">
         <v>243</v>
       </c>
       <c r="C122" s="8" t="s">
@@ -11356,40 +11367,42 @@
       <c r="D122" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E122" s="12"/>
+      <c r="E122" s="14" t="s">
+        <v>199</v>
+      </c>
       <c r="F122" s="7">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G122" s="13">
-        <v>34</v>
-      </c>
-      <c r="H122" s="33">
-        <v>0.095</v>
+        <v>31.5</v>
+      </c>
+      <c r="H122" s="15">
+        <v>0.08</v>
       </c>
       <c r="I122" s="16">
+        <f t="shared" ref="I122:I127" si="28">G122*(1+H122)</f>
+        <v>34.02</v>
+      </c>
+      <c r="J122" s="8"/>
+      <c r="K122" s="17">
+        <f t="shared" ref="K122:K127" si="29">J122*F122</f>
+        <v>0</v>
+      </c>
+      <c r="L122" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="16">
+        <f t="shared" ref="M122:M127" si="30">J122*I122</f>
+        <v>0</v>
+      </c>
+      <c r="N122" s="18">
         <f t="shared" si="27"/>
-        <v>37.23</v>
-      </c>
-      <c r="J122" s="4"/>
-      <c r="K122" s="17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="L122" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M122" s="16">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="N122" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" s="3" customFormat="1" spans="1:14">
-      <c r="A123" s="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="12"/>
       <c r="B123" s="19" t="s">
         <v>244</v>
       </c>
@@ -11399,255 +11412,272 @@
       <c r="D123" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E123" s="12"/>
-      <c r="F123" s="34">
-        <v>2.5</v>
-      </c>
-      <c r="G123" s="27">
-        <v>40.5</v>
-      </c>
-      <c r="H123" s="35">
-        <v>0.1</v>
+      <c r="E123" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F123" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="G123" s="13">
+        <v>42.5</v>
+      </c>
+      <c r="H123" s="15">
+        <v>0.08</v>
       </c>
       <c r="I123" s="16">
-        <f t="shared" si="27"/>
-        <v>44.55</v>
+        <f t="shared" si="28"/>
+        <v>45.9</v>
       </c>
       <c r="J123" s="8"/>
       <c r="K123" s="17">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L123" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="16">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="N123" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
+      <c r="A124" s="12"/>
+      <c r="B124" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F124" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="G124" s="13">
+        <v>47</v>
+      </c>
+      <c r="H124" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I124" s="16">
         <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="L123" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M123" s="16">
+        <v>50.76</v>
+      </c>
+      <c r="J124" s="4"/>
+      <c r="K124" s="17">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="N123" s="18">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
-      <c r="B124" s="12"/>
-      <c r="C124" s="12"/>
-      <c r="D124" s="12"/>
-      <c r="E124" s="12"/>
-      <c r="I124" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="J124" s="36"/>
-      <c r="K124" s="36"/>
       <c r="L124" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M124" s="36"/>
-      <c r="N124" s="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="16">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="N124" s="18">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="125" spans="1:14">
-      <c r="B125" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="C125" s="10"/>
-      <c r="D125" s="10"/>
-      <c r="E125" s="10"/>
-      <c r="F125" s="11"/>
+      <c r="B125" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E125" s="12"/>
+      <c r="F125" s="7">
+        <v>4</v>
+      </c>
+      <c r="G125" s="13">
+        <v>52</v>
+      </c>
+      <c r="H125" s="33">
+        <v>0.095</v>
+      </c>
+      <c r="I125" s="16">
+        <f t="shared" si="28"/>
+        <v>56.94</v>
+      </c>
+      <c r="J125" s="4"/>
+      <c r="K125" s="17">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="L125" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M125" s="16">
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="N125" s="18">
-        <f t="shared" ref="N125:N135" si="30">M125+J125</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:14">
-      <c r="A126" s="12"/>
-      <c r="B126" s="19" t="s">
-        <v>246</v>
+      <c r="B126" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>129</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="E126" s="12"/>
       <c r="F126" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G126" s="13">
-        <v>58</v>
-      </c>
-      <c r="H126" s="15">
-        <v>0.08</v>
+        <v>34</v>
+      </c>
+      <c r="H126" s="33">
+        <v>0.095</v>
       </c>
       <c r="I126" s="16">
-        <f>G126*(1+H126)</f>
-        <v>62.64</v>
-      </c>
-      <c r="J126" s="8"/>
+        <f t="shared" si="28"/>
+        <v>37.23</v>
+      </c>
+      <c r="J126" s="4"/>
       <c r="K126" s="17">
-        <f>J126*F126</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L126" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M126" s="16">
-        <f>J126*I126</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="N126" s="18">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14">
-      <c r="A127" s="12"/>
-      <c r="B127" s="12" t="s">
-        <v>247</v>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" s="3" customFormat="1" spans="1:14">
+      <c r="A127" s="26"/>
+      <c r="B127" s="19" t="s">
+        <v>248</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="E127" s="12"/>
-      <c r="F127" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="G127" s="13">
-        <v>75</v>
-      </c>
-      <c r="H127" s="15">
+      <c r="F127" s="34">
+        <v>2.5</v>
+      </c>
+      <c r="G127" s="27">
+        <v>40.5</v>
+      </c>
+      <c r="H127" s="35">
         <v>0.1</v>
       </c>
       <c r="I127" s="16">
-        <f>G127*(1+H127)</f>
-        <v>82.5</v>
+        <f t="shared" si="28"/>
+        <v>44.55</v>
       </c>
       <c r="J127" s="8"/>
       <c r="K127" s="17">
-        <f>J127*F127</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L127" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M127" s="16">
-        <f>J127*I127</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="N127" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:14">
-      <c r="A128" s="12"/>
-      <c r="B128" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="C128" s="10"/>
-      <c r="D128" s="10"/>
-      <c r="E128" s="10"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="13"/>
-      <c r="H128" s="15"/>
-      <c r="I128" s="16"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="17"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="12"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="I128" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="J128" s="36"/>
+      <c r="K128" s="36"/>
       <c r="L128" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M128" s="16"/>
-      <c r="N128" s="18">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="36"/>
+      <c r="N128" s="36"/>
     </row>
     <row r="129" spans="1:14">
-      <c r="A129" s="12"/>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C129" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E129" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F129" s="7">
-        <v>6</v>
-      </c>
-      <c r="G129" s="13">
-        <v>163.5</v>
-      </c>
-      <c r="H129" s="15">
-        <v>0.11</v>
-      </c>
-      <c r="I129" s="16">
-        <f>G129*(1+H129)</f>
-        <v>181.485</v>
-      </c>
-      <c r="J129" s="8"/>
-      <c r="K129" s="17">
-        <f>J129*F129</f>
-        <v>0</v>
-      </c>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="11"/>
       <c r="L129" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M129" s="16">
-        <f>J129*I129</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N129" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="N129:N139" si="31">M129+J129</f>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="12"/>
-      <c r="B130" s="4" t="s">
-        <v>251</v>
+      <c r="B130" s="19" t="s">
+        <v>250</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E130" s="4">
-        <v>1000</v>
+        <v>143</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="F130" s="7">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G130" s="13">
-        <v>159.1</v>
+        <v>58</v>
       </c>
       <c r="H130" s="15">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I130" s="16">
         <f>G130*(1+H130)</f>
-        <v>176.601</v>
+        <v>62.64</v>
       </c>
       <c r="J130" s="8"/>
       <c r="K130" s="17">
@@ -11655,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M130" s="16">
@@ -11663,36 +11693,34 @@
         <v>0</v>
       </c>
       <c r="N130" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="12"/>
-      <c r="B131" s="2" t="s">
-        <v>252</v>
+      <c r="B131" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E131" s="4">
-        <v>1000</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E131" s="12"/>
       <c r="F131" s="7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G131" s="13">
-        <v>124.7</v>
+        <v>75</v>
       </c>
       <c r="H131" s="15">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I131" s="16">
         <f>G131*(1+H131)</f>
-        <v>138.417</v>
+        <v>82.5</v>
       </c>
       <c r="J131" s="8"/>
       <c r="K131" s="17">
@@ -11700,7 +11728,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M131" s="16">
@@ -11708,107 +11736,105 @@
         <v>0</v>
       </c>
       <c r="N131" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="12"/>
-      <c r="B132" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E132" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F132" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G132" s="13">
-        <v>93.5</v>
-      </c>
-      <c r="H132" s="15">
-        <v>0.11</v>
-      </c>
-      <c r="I132" s="16">
-        <f>G132*(1+H132)</f>
-        <v>103.785</v>
-      </c>
+      <c r="B132" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="15"/>
+      <c r="I132" s="16"/>
       <c r="J132" s="8"/>
-      <c r="K132" s="17">
-        <f>J132*F132</f>
-        <v>0</v>
-      </c>
+      <c r="K132" s="17"/>
       <c r="L132" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M132" s="16">
-        <f>J132*I132</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="16"/>
       <c r="N132" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="12"/>
-      <c r="B133" s="10" t="s">
+      <c r="B133" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D133" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C133" s="10"/>
-      <c r="D133" s="10"/>
-      <c r="E133" s="10"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="13"/>
-      <c r="H133" s="15"/>
-      <c r="I133" s="16"/>
+      <c r="E133" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F133" s="7">
+        <v>6</v>
+      </c>
+      <c r="G133" s="13">
+        <v>163.5</v>
+      </c>
+      <c r="H133" s="15">
+        <v>0.11</v>
+      </c>
+      <c r="I133" s="16">
+        <f>G133*(1+H133)</f>
+        <v>181.485</v>
+      </c>
       <c r="J133" s="8"/>
-      <c r="K133" s="17"/>
+      <c r="K133" s="17">
+        <f>J133*F133</f>
+        <v>0</v>
+      </c>
       <c r="L133" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M133" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="16">
+        <f>J133*I133</f>
+        <v>0</v>
+      </c>
       <c r="N133" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="12"/>
+      <c r="B134" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B134" s="12" t="s">
-        <v>256</v>
-      </c>
       <c r="C134" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E134" s="14" t="s">
-        <v>258</v>
+        <v>254</v>
+      </c>
+      <c r="E134" s="4">
+        <v>1000</v>
       </c>
       <c r="F134" s="7">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="G134" s="13">
-        <f t="shared" ref="G134:G141" si="31">I134/(1+H134)</f>
-        <v>123.893805309735</v>
+        <v>159.1</v>
       </c>
       <c r="H134" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I134" s="16">
-        <v>140</v>
+        <f>G134*(1+H134)</f>
+        <v>176.601</v>
       </c>
       <c r="J134" s="8"/>
       <c r="K134" s="17">
@@ -11816,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M134" s="16">
@@ -11824,38 +11850,36 @@
         <v>0</v>
       </c>
       <c r="N134" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:14">
-      <c r="A135" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>259</v>
+      <c r="A135" s="12"/>
+      <c r="B135" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E135" s="14" t="s">
-        <v>197</v>
+        <v>254</v>
+      </c>
+      <c r="E135" s="4">
+        <v>1000</v>
       </c>
       <c r="F135" s="7">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="G135" s="13">
-        <f t="shared" si="31"/>
-        <v>153.752212389381</v>
+        <v>124.7</v>
       </c>
       <c r="H135" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I135" s="16">
-        <v>173.74</v>
+        <f>G135*(1+H135)</f>
+        <v>138.417</v>
       </c>
       <c r="J135" s="8"/>
       <c r="K135" s="17">
@@ -11863,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M135" s="16">
@@ -11871,110 +11895,85 @@
         <v>0</v>
       </c>
       <c r="N135" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:14">
-      <c r="A136" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B136" s="14" t="s">
-        <v>260</v>
+      <c r="A136" s="12"/>
+      <c r="B136" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>119</v>
+        <v>254</v>
+      </c>
+      <c r="E136" s="4">
+        <v>1000</v>
       </c>
       <c r="F136" s="7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G136" s="13">
-        <f t="shared" si="31"/>
-        <v>176.991150442478</v>
+        <v>93.5</v>
       </c>
       <c r="H136" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I136" s="16">
-        <v>200</v>
+        <f>G136*(1+H136)</f>
+        <v>103.785</v>
       </c>
       <c r="J136" s="8"/>
       <c r="K136" s="17">
-        <f t="shared" ref="K136:K141" si="32">J136*F136</f>
+        <f>J136*F136</f>
         <v>0</v>
       </c>
       <c r="L136" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M136" s="16">
-        <f t="shared" ref="M136:M141" si="33">J136*I136</f>
+        <f>J136*I136</f>
         <v>0</v>
       </c>
       <c r="N136" s="18">
-        <f t="shared" ref="N136:N141" si="34">M136+J136</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:14">
-      <c r="A137" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B137" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="E137" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F137" s="7">
-        <v>4</v>
-      </c>
-      <c r="G137" s="13">
+      <c r="A137" s="12"/>
+      <c r="B137" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C137" s="10"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="10"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="13"/>
+      <c r="H137" s="15"/>
+      <c r="I137" s="16"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="17"/>
+      <c r="L137" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M137" s="16"/>
+      <c r="N137" s="18">
         <f t="shared" si="31"/>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H137" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I137" s="16">
-        <v>140</v>
-      </c>
-      <c r="J137" s="8"/>
-      <c r="K137" s="17">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="L137" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M137" s="16">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N137" s="18">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>264</v>
+        <v>259</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>260</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>101</v>
@@ -11983,98 +11982,98 @@
         <v>261</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>119</v>
+        <v>262</v>
       </c>
       <c r="F138" s="7">
         <v>8</v>
       </c>
       <c r="G138" s="13">
-        <f t="shared" si="31"/>
-        <v>230.088495575221</v>
+        <f t="shared" ref="G138:G145" si="32">I138/(1+H138)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H138" s="15">
         <v>0.13</v>
       </c>
       <c r="I138" s="16">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="J138" s="8"/>
       <c r="K138" s="17">
-        <f t="shared" si="32"/>
+        <f>J138*F138</f>
         <v>0</v>
       </c>
       <c r="L138" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M138" s="16">
-        <f t="shared" si="33"/>
+        <f>J138*I138</f>
         <v>0</v>
       </c>
       <c r="N138" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="14" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F139" s="7">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G139" s="13">
-        <f t="shared" si="31"/>
-        <v>115.929203539823</v>
+        <f t="shared" si="32"/>
+        <v>153.752212389381</v>
       </c>
       <c r="H139" s="15">
         <v>0.13</v>
       </c>
       <c r="I139" s="16">
-        <v>131</v>
+        <v>173.74</v>
       </c>
       <c r="J139" s="8"/>
       <c r="K139" s="17">
-        <f t="shared" si="32"/>
+        <f>J139*F139</f>
         <v>0</v>
       </c>
       <c r="L139" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M139" s="16">
-        <f t="shared" si="33"/>
+        <f>J139*I139</f>
         <v>0</v>
       </c>
       <c r="N139" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="14" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E140" s="14" t="s">
         <v>119</v>
@@ -12083,578 +12082,593 @@
         <v>6</v>
       </c>
       <c r="G140" s="13">
-        <f t="shared" si="31"/>
-        <v>88.495575221239</v>
+        <f t="shared" si="32"/>
+        <v>176.991150442478</v>
       </c>
       <c r="H140" s="15">
         <v>0.13</v>
       </c>
       <c r="I140" s="16">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="K140:K145" si="33">J140*F140</f>
         <v>0</v>
       </c>
       <c r="L140" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M140" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="M140:M145" si="34">J140*I140</f>
         <v>0</v>
       </c>
       <c r="N140" s="18">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" s="3" customFormat="1" spans="1:14">
+        <f t="shared" ref="N140:N145" si="35">M140+J140</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B141" s="19" t="s">
-        <v>267</v>
+        <v>259</v>
+      </c>
+      <c r="B141" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="F141" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G141" s="13">
-        <f>I141-1</f>
-        <v>107</v>
+        <f t="shared" si="32"/>
+        <v>123.893805309735</v>
       </c>
       <c r="H141" s="15">
         <v>0.13</v>
       </c>
       <c r="I141" s="16">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L141" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M141" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N141" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="14"/>
+      <c r="A142" s="14" t="s">
+        <v>259</v>
+      </c>
       <c r="B142" s="14" t="s">
         <v>268</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>269</v>
+        <v>101</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="F142" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G142" s="13">
-        <f>I142/(1+H142)</f>
-        <v>129.203539823009</v>
+        <f t="shared" si="32"/>
+        <v>230.088495575221</v>
       </c>
       <c r="H142" s="15">
         <v>0.13</v>
       </c>
       <c r="I142" s="16">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="17">
-        <f t="shared" ref="K142:K159" si="35">J142*F142</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L142" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M142" s="16">
-        <f t="shared" ref="M142:M159" si="36">J142*I142</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N142" s="18">
-        <f t="shared" ref="N142:N164" si="37">M142+J142</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:14">
-      <c r="A143" s="12"/>
-      <c r="B143" s="12" t="s">
-        <v>270</v>
+      <c r="A143" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B143" s="14" t="s">
+        <v>269</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>269</v>
+        <v>101</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E143" s="14" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="F143" s="7">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="G143" s="13">
-        <v>140</v>
+        <f t="shared" si="32"/>
+        <v>115.929203539823</v>
       </c>
       <c r="H143" s="15">
         <v>0.13</v>
       </c>
       <c r="I143" s="16">
-        <f>G143*(1+H143)</f>
-        <v>158.2</v>
+        <v>131</v>
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="17">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M143" s="16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N143" s="18">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="L143" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M143" s="16">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="N143" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" s="3" customFormat="1" spans="1:14">
-      <c r="A144" s="26"/>
-      <c r="B144" s="12" t="s">
+    </row>
+    <row r="144" spans="1:14">
+      <c r="A144" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B144" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D144" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E144" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F144" s="7">
+        <v>6</v>
+      </c>
+      <c r="G144" s="13">
+        <f t="shared" si="32"/>
+        <v>88.495575221239</v>
+      </c>
+      <c r="H144" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I144" s="16">
+        <v>100</v>
+      </c>
+      <c r="J144" s="8"/>
+      <c r="K144" s="17">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="L144" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M144" s="16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N144" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" s="3" customFormat="1" spans="1:15">
+      <c r="A145" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B145" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="C144" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E144" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F144" s="34">
-        <v>7.5</v>
-      </c>
-      <c r="G144" s="13">
-        <f>I144/(1+H144)</f>
-        <v>103.371681415929</v>
-      </c>
-      <c r="H144" s="35">
+      <c r="C145" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E145" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F145" s="7">
+        <v>6</v>
+      </c>
+      <c r="G145" s="13">
+        <f>I145-1</f>
+        <v>107</v>
+      </c>
+      <c r="H145" s="15">
         <v>0.13</v>
       </c>
-      <c r="I144" s="37">
-        <v>116.81</v>
-      </c>
-      <c r="J144" s="34"/>
-      <c r="K144" s="38">
+      <c r="I145" s="16">
+        <v>108</v>
+      </c>
+      <c r="J145" s="8"/>
+      <c r="K145" s="17">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="L145" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M145" s="16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N145" s="18">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="L144" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M144" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="N144" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" s="3" customFormat="1" spans="1:15">
-      <c r="A145" s="26"/>
-      <c r="B145" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="C145" s="12" t="s">
+    </row>
+    <row r="146" spans="1:15">
+      <c r="A146" s="14"/>
+      <c r="B146" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="E145" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="F145" s="34">
-        <v>4.5</v>
-      </c>
-      <c r="G145" s="13">
-        <f>I145/(1+H145)</f>
-        <v>132.743362831858</v>
-      </c>
-      <c r="H145" s="35">
+      <c r="C146" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E146" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F146" s="7">
+        <v>7</v>
+      </c>
+      <c r="G146" s="13">
+        <f>I146/(1+H146)</f>
+        <v>129.203539823009</v>
+      </c>
+      <c r="H146" s="15">
         <v>0.13</v>
       </c>
-      <c r="I145" s="37">
-        <v>150</v>
-      </c>
-      <c r="J145" s="34"/>
-      <c r="K145" s="38">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="L145" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M145" s="37">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="N145" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" s="3" customFormat="1" spans="1:15">
-      <c r="A146" s="26"/>
-      <c r="B146" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="E146" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F146" s="34">
-        <v>6</v>
-      </c>
-      <c r="G146" s="13">
-        <v>145</v>
-      </c>
-      <c r="H146" s="35">
-        <v>0.13</v>
-      </c>
       <c r="I146" s="16">
-        <f>G146*(1+H146)</f>
-        <v>163.85</v>
-      </c>
-      <c r="J146" s="34"/>
-      <c r="K146" s="38">
-        <f t="shared" si="35"/>
+        <v>146</v>
+      </c>
+      <c r="J146" s="8"/>
+      <c r="K146" s="17">
+        <f t="shared" ref="K146:K163" si="36">J146*F146</f>
         <v>0</v>
       </c>
       <c r="L146" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M146" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M146" s="16">
+        <f t="shared" ref="M146:M163" si="37">J146*I146</f>
         <v>0</v>
       </c>
       <c r="N146" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" s="3" customFormat="1" spans="1:15">
-      <c r="A147" s="26"/>
-      <c r="B147" s="14" t="s">
+        <f t="shared" ref="N146:N168" si="38">M146+J146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="A147" s="12"/>
+      <c r="B147" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C147" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C147" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="D147" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E147" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F147" s="34">
-        <v>4</v>
+        <v>262</v>
+      </c>
+      <c r="F147" s="7">
+        <v>9.5</v>
       </c>
       <c r="G147" s="13">
-        <v>101</v>
-      </c>
-      <c r="H147" s="35">
+        <v>140</v>
+      </c>
+      <c r="H147" s="15">
         <v>0.13</v>
       </c>
       <c r="I147" s="16">
         <f>G147*(1+H147)</f>
-        <v>114.13</v>
-      </c>
-      <c r="J147" s="34"/>
-      <c r="K147" s="38">
-        <f t="shared" si="35"/>
+        <v>158.2</v>
+      </c>
+      <c r="J147" s="8"/>
+      <c r="K147" s="17">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L147" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M147" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M147" s="16">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N147" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" s="3" customFormat="1" spans="1:15">
       <c r="A148" s="26"/>
       <c r="B148" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="D148" s="13" t="s">
         <v>261</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="F148" s="34">
-        <v>6</v>
-      </c>
-      <c r="G148" s="27">
-        <v>115</v>
+        <v>7.5</v>
+      </c>
+      <c r="G148" s="13">
+        <f>I148/(1+H148)</f>
+        <v>103.371681415929</v>
       </c>
       <c r="H148" s="35">
-        <v>0.08</v>
-      </c>
-      <c r="I148" s="16">
-        <f>G148*(1+H148)</f>
-        <v>124.2</v>
-      </c>
-      <c r="J148" s="8"/>
-      <c r="K148" s="17">
-        <f t="shared" si="35"/>
+        <v>0.13</v>
+      </c>
+      <c r="I148" s="37">
+        <v>116.81</v>
+      </c>
+      <c r="J148" s="34"/>
+      <c r="K148" s="38">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L148" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M148" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M148" s="37">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N148" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="149" s="3" customFormat="1" spans="1:15">
-      <c r="A149" s="14"/>
+      <c r="A149" s="26"/>
       <c r="B149" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E149" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C149" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="E149" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F149" s="7">
-        <v>4</v>
+      <c r="F149" s="34">
+        <v>4.5</v>
       </c>
       <c r="G149" s="13">
         <f>I149/(1+H149)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H149" s="15">
+        <v>132.743362831858</v>
+      </c>
+      <c r="H149" s="35">
         <v>0.13</v>
       </c>
-      <c r="I149" s="16">
-        <v>140</v>
-      </c>
-      <c r="J149" s="8"/>
-      <c r="K149" s="17">
-        <f t="shared" si="35"/>
+      <c r="I149" s="37">
+        <v>150</v>
+      </c>
+      <c r="J149" s="34"/>
+      <c r="K149" s="38">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L149" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M149" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M149" s="37">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N149" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="O149" s="2"/>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="150" s="3" customFormat="1" spans="1:15">
       <c r="A150" s="26"/>
-      <c r="B150" s="12" t="s">
-        <v>276</v>
+      <c r="B150" s="14" t="s">
+        <v>264</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>277</v>
+        <v>96</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="E150" s="14"/>
+        <v>267</v>
+      </c>
+      <c r="E150" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="F150" s="34">
-        <v>11</v>
-      </c>
-      <c r="G150" s="27">
-        <f>I150-1</f>
-        <v>177.5</v>
-      </c>
-      <c r="H150" s="35"/>
+        <v>6</v>
+      </c>
+      <c r="G150" s="13">
+        <v>145</v>
+      </c>
+      <c r="H150" s="35">
+        <v>0.13</v>
+      </c>
       <c r="I150" s="16">
-        <v>178.5</v>
-      </c>
-      <c r="J150" s="8"/>
-      <c r="K150" s="17">
-        <f t="shared" si="35"/>
+        <f>G150*(1+H150)</f>
+        <v>163.85</v>
+      </c>
+      <c r="J150" s="34"/>
+      <c r="K150" s="38">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L150" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M150" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M150" s="37">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N150" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="3" customFormat="1" spans="1:15">
       <c r="A151" s="26"/>
-      <c r="B151" s="12" t="s">
+      <c r="B151" s="14" t="s">
         <v>279</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>277</v>
+        <v>96</v>
       </c>
       <c r="D151" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E151" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F151" s="34">
+        <v>4</v>
+      </c>
+      <c r="G151" s="13">
+        <v>101</v>
+      </c>
+      <c r="H151" s="35">
+        <v>0.13</v>
+      </c>
+      <c r="I151" s="16">
+        <f>G151*(1+H151)</f>
+        <v>114.13</v>
+      </c>
+      <c r="J151" s="34"/>
+      <c r="K151" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L151" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M151" s="37">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="N151" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" s="3" customFormat="1" spans="1:15">
+      <c r="A152" s="26"/>
+      <c r="B152" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="E151" s="14"/>
-      <c r="F151" s="34">
-        <v>8</v>
-      </c>
-      <c r="G151" s="27">
-        <f>I151-1</f>
-        <v>127.5</v>
-      </c>
-      <c r="H151" s="35"/>
-      <c r="I151" s="16">
-        <v>128.5</v>
-      </c>
-      <c r="J151" s="8"/>
-      <c r="K151" s="17">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="L151" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M151" s="16">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="N151" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" s="3" customFormat="1" spans="1:15">
-      <c r="A152" s="14"/>
-      <c r="B152" s="14" t="s">
-        <v>260</v>
-      </c>
       <c r="C152" s="8" t="s">
-        <v>281</v>
+        <v>96</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F152" s="7">
+      <c r="F152" s="34">
         <v>6</v>
       </c>
-      <c r="G152" s="13">
-        <f>I152/(1+H152)</f>
-        <v>176.991150442478</v>
-      </c>
-      <c r="H152" s="15">
-        <v>0.13</v>
+      <c r="G152" s="27">
+        <v>115</v>
+      </c>
+      <c r="H152" s="35">
+        <v>0.08</v>
       </c>
       <c r="I152" s="16">
-        <v>200</v>
+        <f>G152*(1+H152)</f>
+        <v>124.2</v>
       </c>
       <c r="J152" s="8"/>
       <c r="K152" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L152" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M152" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N152" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" s="3" customFormat="1" spans="1:15">
       <c r="A153" s="14"/>
       <c r="B153" s="14" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>281</v>
+        <v>96</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>119</v>
@@ -12674,471 +12688,489 @@
       </c>
       <c r="J153" s="8"/>
       <c r="K153" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L153" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M153" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N153" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O153" s="2"/>
+    </row>
+    <row r="154" s="3" customFormat="1" spans="1:15">
       <c r="A154" s="26"/>
       <c r="B154" s="12" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E154" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F154" s="7">
-        <v>6</v>
-      </c>
-      <c r="G154" s="13">
-        <v>115</v>
-      </c>
-      <c r="H154" s="15">
-        <v>0.08</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="E154" s="14"/>
+      <c r="F154" s="34">
+        <v>11</v>
+      </c>
+      <c r="G154" s="27">
+        <f>I154-1</f>
+        <v>177.5</v>
+      </c>
+      <c r="H154" s="35"/>
       <c r="I154" s="16">
-        <f>G154*(1+H154)</f>
-        <v>124.2</v>
+        <v>178.5</v>
       </c>
       <c r="J154" s="8"/>
       <c r="K154" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L154" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M154" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N154" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" s="3" customFormat="1" spans="1:15">
       <c r="A155" s="26"/>
-      <c r="B155" s="19" t="s">
-        <v>267</v>
+      <c r="B155" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E155" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="F155" s="7">
-        <v>6</v>
-      </c>
-      <c r="G155" s="13">
+        <v>285</v>
+      </c>
+      <c r="E155" s="14"/>
+      <c r="F155" s="34">
+        <v>8</v>
+      </c>
+      <c r="G155" s="27">
         <f>I155-1</f>
-        <v>107</v>
-      </c>
-      <c r="H155" s="15">
-        <v>0.13</v>
-      </c>
+        <v>127.5</v>
+      </c>
+      <c r="H155" s="35"/>
       <c r="I155" s="16">
-        <v>108</v>
+        <v>128.5</v>
       </c>
       <c r="J155" s="8"/>
       <c r="K155" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L155" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M155" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N155" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" s="3" customFormat="1" spans="1:15">
-      <c r="A156" s="26"/>
-      <c r="B156" s="12" t="s">
-        <v>271</v>
+      <c r="A156" s="14"/>
+      <c r="B156" s="14" t="s">
+        <v>264</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="F156" s="7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G156" s="13">
-        <f>I156-1</f>
-        <v>134</v>
+        <f>I156/(1+H156)</f>
+        <v>176.991150442478</v>
       </c>
       <c r="H156" s="15">
         <v>0.13</v>
       </c>
-      <c r="I156" s="39">
-        <v>135</v>
-      </c>
-      <c r="J156" s="34"/>
-      <c r="K156" s="38">
-        <f t="shared" si="35"/>
+      <c r="I156" s="16">
+        <v>200</v>
+      </c>
+      <c r="J156" s="8"/>
+      <c r="K156" s="17">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L156" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M156" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M156" s="16">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N156" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" s="3" customFormat="1" spans="1:15">
-      <c r="A157" s="12"/>
-      <c r="B157" s="19" t="s">
-        <v>270</v>
+      <c r="A157" s="14"/>
+      <c r="B157" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="F157" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G157" s="13">
-        <f>I157-1</f>
-        <v>150.2</v>
+        <f>I157/(1+H157)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H157" s="15">
         <v>0.13</v>
       </c>
       <c r="I157" s="16">
-        <v>151.2</v>
+        <v>140</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L157" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M157" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N157" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" s="3" customFormat="1" spans="1:15">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
       <c r="A158" s="26"/>
       <c r="B158" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="F158" s="7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G158" s="13">
-        <f>I158-1</f>
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="H158" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I158" s="16">
-        <v>135</v>
+        <f>G158*(1+H158)</f>
+        <v>124.2</v>
       </c>
       <c r="J158" s="8"/>
-      <c r="K158" s="38">
-        <f t="shared" si="35"/>
+      <c r="K158" s="17">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L158" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M158" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M158" s="16">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N158" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" s="3" customFormat="1" spans="1:15">
       <c r="A159" s="26"/>
-      <c r="B159" s="12" t="s">
-        <v>259</v>
+      <c r="B159" s="19" t="s">
+        <v>271</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E159" s="14" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="F159" s="7">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="G159" s="13">
         <f>I159-1</f>
-        <v>177.2</v>
+        <v>107</v>
       </c>
       <c r="H159" s="15">
         <v>0.13</v>
       </c>
       <c r="I159" s="16">
-        <v>178.2</v>
+        <v>108</v>
       </c>
       <c r="J159" s="8"/>
-      <c r="K159" s="38">
-        <f t="shared" si="35"/>
+      <c r="K159" s="17">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L159" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M159" s="37">
-        <f t="shared" si="36"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M159" s="16">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N159" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" s="3" customFormat="1" spans="1:15">
       <c r="A160" s="26"/>
-      <c r="B160" s="26"/>
-      <c r="C160" s="26"/>
-      <c r="D160" s="26"/>
-      <c r="E160" s="26"/>
-      <c r="F160" s="34"/>
-      <c r="G160" s="27"/>
-      <c r="H160" s="35"/>
-      <c r="I160" s="16"/>
-      <c r="J160" s="8"/>
-      <c r="K160" s="17"/>
+      <c r="B160" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E160" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F160" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="G160" s="13">
+        <f>I160-1</f>
+        <v>134</v>
+      </c>
+      <c r="H160" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I160" s="39">
+        <v>135</v>
+      </c>
+      <c r="J160" s="34"/>
+      <c r="K160" s="38">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
       <c r="L160" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M160" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M160" s="37">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="N160" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" s="3" customFormat="1" spans="1:14">
+      <c r="A161" s="12"/>
+      <c r="B161" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E161" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F161" s="7">
+        <v>8</v>
+      </c>
+      <c r="G161" s="13">
+        <f>I161-1</f>
+        <v>150.2</v>
+      </c>
+      <c r="H161" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I161" s="16">
+        <v>151.2</v>
+      </c>
+      <c r="J161" s="8"/>
+      <c r="K161" s="17">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L161" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M161" s="16">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="161" s="3" customFormat="1" spans="1:14">
-      <c r="A161" s="26"/>
-      <c r="B161" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="C161" s="10"/>
-      <c r="D161" s="10"/>
-      <c r="E161" s="10"/>
-      <c r="F161" s="11"/>
-      <c r="G161" s="27"/>
-      <c r="H161" s="35"/>
-      <c r="I161" s="16"/>
-      <c r="J161" s="8"/>
-      <c r="K161" s="17"/>
-      <c r="L161" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M161" s="16"/>
       <c r="N161" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14">
-      <c r="B162" s="40" t="s">
-        <v>284</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" s="3" customFormat="1" spans="1:14">
+      <c r="A162" s="26"/>
+      <c r="B162" s="12" t="s">
+        <v>286</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D162" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="E162" s="41">
-        <v>1000</v>
+      <c r="E162" s="14" t="s">
+        <v>199</v>
       </c>
       <c r="F162" s="7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G162" s="13">
-        <v>90</v>
+        <f>I162-1</f>
+        <v>134</v>
       </c>
       <c r="H162" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I162" s="16">
-        <f>G162*(1+H162)</f>
-        <v>97.2</v>
+        <v>135</v>
       </c>
       <c r="J162" s="8"/>
-      <c r="K162" s="17">
-        <f>J162*F162</f>
+      <c r="K162" s="38">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L162" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M162" s="16">
-        <f>J162*I162</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M162" s="37">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N162" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14">
-      <c r="B163" s="40" t="s">
-        <v>285</v>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" s="3" customFormat="1" spans="1:14">
+      <c r="A163" s="26"/>
+      <c r="B163" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D163" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="E163" s="41">
-        <v>1000</v>
+      <c r="E163" s="14" t="s">
+        <v>199</v>
       </c>
       <c r="F163" s="7">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G163" s="13">
-        <v>92</v>
+        <f>I163-1</f>
+        <v>177.2</v>
       </c>
       <c r="H163" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I163" s="16">
-        <f>G163*(1+H163)</f>
-        <v>99.36</v>
+        <v>178.2</v>
       </c>
       <c r="J163" s="8"/>
-      <c r="K163" s="17">
-        <f>J163*F163</f>
+      <c r="K163" s="38">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L163" s="17">
-        <f t="shared" ref="L163:L192" si="38">K163+J163/2</f>
-        <v>0</v>
-      </c>
-      <c r="M163" s="16">
-        <f>J163*I163</f>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M163" s="37">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N163" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14">
-      <c r="B164" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E164" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F164" s="7">
-        <v>7</v>
-      </c>
-      <c r="G164" s="13">
-        <v>87</v>
-      </c>
-      <c r="H164" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I164" s="16">
-        <f>G164*(1+H164)</f>
-        <v>93.96</v>
-      </c>
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" s="3" customFormat="1" spans="1:14">
+      <c r="A164" s="26"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="26"/>
+      <c r="D164" s="26"/>
+      <c r="E164" s="26"/>
+      <c r="F164" s="34"/>
+      <c r="G164" s="27"/>
+      <c r="H164" s="35"/>
+      <c r="I164" s="16"/>
       <c r="J164" s="8"/>
-      <c r="K164" s="17">
-        <f>J164*F164</f>
-        <v>0</v>
-      </c>
+      <c r="K164" s="17"/>
       <c r="L164" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="16"/>
+      <c r="N164" s="18">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="M164" s="16">
-        <f>J164*I164</f>
-        <v>0</v>
-      </c>
-      <c r="N164" s="18">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14">
+    </row>
+    <row r="165" s="3" customFormat="1" spans="1:14">
+      <c r="A165" s="26"/>
       <c r="B165" s="10" t="s">
         <v>287</v>
       </c>
@@ -13146,43 +13178,46 @@
       <c r="D165" s="10"/>
       <c r="E165" s="10"/>
       <c r="F165" s="11"/>
-      <c r="G165" s="13"/>
-      <c r="H165" s="15"/>
+      <c r="G165" s="27"/>
+      <c r="H165" s="35"/>
       <c r="I165" s="16"/>
       <c r="J165" s="8"/>
       <c r="K165" s="17"/>
       <c r="L165" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="16"/>
+      <c r="N165" s="18">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="M165" s="16"/>
-      <c r="N165" s="18"/>
     </row>
     <row r="166" spans="1:14">
       <c r="B166" s="40" t="s">
         <v>288</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="E166" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F166" s="7">
-        <v>4.65</v>
+        <v>8</v>
       </c>
       <c r="G166" s="13">
-        <v>61.5</v>
+        <v>90</v>
       </c>
       <c r="H166" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I166" s="16">
         <f>G166*(1+H166)</f>
-        <v>67.65</v>
+        <v>97.2</v>
       </c>
       <c r="J166" s="8"/>
       <c r="K166" s="17">
@@ -13190,7 +13225,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M166" s="16">
@@ -13198,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="N166" s="18">
-        <f t="shared" ref="N166:N192" si="39">M166+J166</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -13207,26 +13242,26 @@
         <v>289</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="E167" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F167" s="7">
-        <v>5.15</v>
+        <v>8</v>
       </c>
       <c r="G167" s="13">
-        <v>64.5</v>
+        <v>92</v>
       </c>
       <c r="H167" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I167" s="16">
         <f>G167*(1+H167)</f>
-        <v>70.95</v>
+        <v>99.36</v>
       </c>
       <c r="J167" s="8"/>
       <c r="K167" s="17">
@@ -13234,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="L167:L196" si="39">K167+J167/2</f>
         <v>0</v>
       </c>
       <c r="M167" s="16">
@@ -13242,36 +13277,35 @@
         <v>0</v>
       </c>
       <c r="N167" s="18">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" s="3" customFormat="1" spans="1:14">
-      <c r="A168" s="26"/>
-      <c r="B168" s="36" t="s">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14">
+      <c r="B168" s="40" t="s">
         <v>290</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="E168" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F168" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="G168" s="27">
-        <v>76.5</v>
-      </c>
-      <c r="H168" s="35">
-        <v>0.1</v>
+        <v>7</v>
+      </c>
+      <c r="G168" s="13">
+        <v>87</v>
+      </c>
+      <c r="H168" s="15">
+        <v>0.08</v>
       </c>
       <c r="I168" s="16">
         <f>G168*(1+H168)</f>
-        <v>84.15</v>
+        <v>93.96</v>
       </c>
       <c r="J168" s="8"/>
       <c r="K168" s="17">
@@ -13279,7 +13313,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M168" s="16">
@@ -13287,355 +13321,339 @@
         <v>0</v>
       </c>
       <c r="N168" s="18">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14">
+      <c r="B169" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="11"/>
+      <c r="G169" s="13"/>
+      <c r="H169" s="15"/>
+      <c r="I169" s="16"/>
+      <c r="J169" s="8"/>
+      <c r="K169" s="17"/>
+      <c r="L169" s="17">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="169" s="3" customFormat="1" spans="1:14">
-      <c r="A169" s="26"/>
-      <c r="B169" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C169" s="8" t="s">
+      <c r="M169" s="16"/>
+      <c r="N169" s="18"/>
+    </row>
+    <row r="170" spans="1:14">
+      <c r="B170" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C170" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="E169" s="41">
+      <c r="D170" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="E170" s="41">
         <v>300</v>
       </c>
-      <c r="F169" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="G169" s="27">
-        <v>94.5</v>
-      </c>
-      <c r="H169" s="35">
+      <c r="F170" s="7">
+        <v>4.65</v>
+      </c>
+      <c r="G170" s="13">
+        <v>61.5</v>
+      </c>
+      <c r="H170" s="15">
         <v>0.1</v>
       </c>
-      <c r="I169" s="16">
-        <f>G169*(1+H169)</f>
-        <v>103.95</v>
-      </c>
-      <c r="J169" s="8"/>
-      <c r="K169" s="17">
-        <f>J169*F169</f>
-        <v>0</v>
-      </c>
-      <c r="L169" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M169" s="16">
-        <f>J169*I169</f>
-        <v>0</v>
-      </c>
-      <c r="N169" s="18">
+      <c r="I170" s="16">
+        <f>G170*(1+H170)</f>
+        <v>67.65</v>
+      </c>
+      <c r="J170" s="8"/>
+      <c r="K170" s="17">
+        <f>J170*F170</f>
+        <v>0</v>
+      </c>
+      <c r="L170" s="17">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="170" s="3" customFormat="1" spans="1:14">
-      <c r="A170" s="26"/>
-      <c r="B170" s="27"/>
-      <c r="C170" s="27"/>
-      <c r="D170" s="27"/>
-      <c r="E170" s="27"/>
-      <c r="F170" s="27"/>
-      <c r="G170" s="27"/>
-      <c r="H170" s="35"/>
-      <c r="I170" s="16"/>
-      <c r="J170" s="8"/>
-      <c r="K170" s="17"/>
-      <c r="L170" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M170" s="16"/>
+      <c r="M170" s="16">
+        <f>J170*I170</f>
+        <v>0</v>
+      </c>
       <c r="N170" s="18">
+        <f t="shared" ref="N170:N196" si="40">M170+J170</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14">
+      <c r="B171" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="E171" s="41">
+        <v>300</v>
+      </c>
+      <c r="F171" s="7">
+        <v>5.15</v>
+      </c>
+      <c r="G171" s="13">
+        <v>64.5</v>
+      </c>
+      <c r="H171" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I171" s="16">
+        <f>G171*(1+H171)</f>
+        <v>70.95</v>
+      </c>
+      <c r="J171" s="8"/>
+      <c r="K171" s="17">
+        <f>J171*F171</f>
+        <v>0</v>
+      </c>
+      <c r="L171" s="17">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="171" s="3" customFormat="1" spans="1:14">
-      <c r="A171" s="26"/>
-      <c r="B171" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C171" s="42"/>
-      <c r="D171" s="42"/>
-      <c r="E171" s="42"/>
-      <c r="F171" s="43"/>
-      <c r="G171" s="27"/>
-      <c r="H171" s="35"/>
-      <c r="I171" s="16"/>
-      <c r="J171" s="8"/>
-      <c r="K171" s="17"/>
-      <c r="L171" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M171" s="16"/>
+      <c r="M171" s="16">
+        <f>J171*I171</f>
+        <v>0</v>
+      </c>
       <c r="N171" s="18">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14">
-      <c r="B172" s="40" t="s">
-        <v>293</v>
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" s="3" customFormat="1" spans="1:14">
+      <c r="A172" s="26"/>
+      <c r="B172" s="36" t="s">
+        <v>294</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="E172" s="41">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F172" s="7">
-        <v>5</v>
-      </c>
-      <c r="G172" s="13">
-        <v>67.5</v>
-      </c>
-      <c r="H172" s="15">
-        <v>0.08</v>
+        <v>5.9</v>
+      </c>
+      <c r="G172" s="27">
+        <v>76.5</v>
+      </c>
+      <c r="H172" s="35">
+        <v>0.1</v>
       </c>
       <c r="I172" s="16">
-        <f t="shared" ref="I172:I192" si="40">G172*(1+H172)</f>
-        <v>72.9</v>
+        <f>G172*(1+H172)</f>
+        <v>84.15</v>
       </c>
       <c r="J172" s="8"/>
       <c r="K172" s="17">
-        <f t="shared" ref="K172:K192" si="41">J172*F172</f>
+        <f>J172*F172</f>
         <v>0</v>
       </c>
       <c r="L172" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M172" s="16">
-        <f t="shared" ref="M172:M192" si="42">J172*I172</f>
+        <f>J172*I172</f>
         <v>0</v>
       </c>
       <c r="N172" s="18">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14">
-      <c r="B173" s="40" t="s">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" s="3" customFormat="1" spans="1:14">
+      <c r="A173" s="26"/>
+      <c r="B173" s="2" t="s">
         <v>295</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E173" s="41">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F173" s="7">
-        <v>6.2</v>
-      </c>
-      <c r="G173" s="13">
-        <v>79</v>
-      </c>
-      <c r="H173" s="15">
-        <v>0.08</v>
+        <v>4.7</v>
+      </c>
+      <c r="G173" s="27">
+        <v>94.5</v>
+      </c>
+      <c r="H173" s="35">
+        <v>0.1</v>
       </c>
       <c r="I173" s="16">
-        <f t="shared" si="40"/>
-        <v>85.32</v>
+        <f>G173*(1+H173)</f>
+        <v>103.95</v>
       </c>
       <c r="J173" s="8"/>
       <c r="K173" s="17">
-        <f t="shared" si="41"/>
+        <f>J173*F173</f>
         <v>0</v>
       </c>
       <c r="L173" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M173" s="16">
-        <f t="shared" si="42"/>
+        <f>J173*I173</f>
         <v>0</v>
       </c>
       <c r="N173" s="18">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14">
-      <c r="B174" s="41" t="s">
-        <v>296</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D174" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E174" s="41">
-        <v>500</v>
-      </c>
-      <c r="F174" s="7"/>
-      <c r="G174" s="13"/>
-      <c r="H174" s="15">
-        <v>0.08</v>
-      </c>
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" s="3" customFormat="1" spans="1:14">
+      <c r="A174" s="26"/>
+      <c r="B174" s="27"/>
+      <c r="C174" s="27"/>
+      <c r="D174" s="27"/>
+      <c r="E174" s="27"/>
+      <c r="F174" s="27"/>
+      <c r="G174" s="27"/>
+      <c r="H174" s="35"/>
       <c r="I174" s="16"/>
       <c r="J174" s="8"/>
-      <c r="K174" s="17">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
+      <c r="K174" s="17"/>
       <c r="L174" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M174" s="16">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M174" s="16"/>
       <c r="N174" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" s="3" customFormat="1" spans="1:14">
+      <c r="A175" s="26"/>
+      <c r="B175" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C175" s="42"/>
+      <c r="D175" s="42"/>
+      <c r="E175" s="42"/>
+      <c r="F175" s="43"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="35"/>
+      <c r="I175" s="16"/>
+      <c r="J175" s="8"/>
+      <c r="K175" s="17"/>
+      <c r="L175" s="17">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="B175" s="40" t="s">
-        <v>297</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D175" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E175" s="41">
-        <v>500</v>
-      </c>
-      <c r="F175" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="G175" s="13">
-        <v>105</v>
-      </c>
-      <c r="H175" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I175" s="16">
+      <c r="M175" s="16"/>
+      <c r="N175" s="18">
         <f t="shared" si="40"/>
-        <v>113.4</v>
-      </c>
-      <c r="J175" s="8"/>
-      <c r="K175" s="17">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L175" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M175" s="16">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="N175" s="18">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="B176" s="40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E176" s="41">
         <v>500</v>
       </c>
       <c r="F176" s="7">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="G176" s="13">
-        <v>117.5</v>
+        <v>67.5</v>
       </c>
       <c r="H176" s="15">
         <v>0.08</v>
       </c>
       <c r="I176" s="16">
-        <f t="shared" si="40"/>
-        <v>126.9</v>
+        <f t="shared" ref="I176:I196" si="41">G176*(1+H176)</f>
+        <v>72.9</v>
       </c>
       <c r="J176" s="8"/>
       <c r="K176" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="K176:K196" si="42">J176*F176</f>
         <v>0</v>
       </c>
       <c r="L176" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M176" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="M176:M196" si="43">J176*I176</f>
         <v>0</v>
       </c>
       <c r="N176" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:14">
-      <c r="B177" s="41" t="s">
+      <c r="B177" s="40" t="s">
         <v>299</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E177" s="41">
         <v>500</v>
       </c>
       <c r="F177" s="7">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="G177" s="13">
-        <v>122.5</v>
+        <v>79</v>
       </c>
       <c r="H177" s="15">
         <v>0.08</v>
       </c>
       <c r="I177" s="16">
-        <f t="shared" si="40"/>
-        <v>132.3</v>
+        <f t="shared" si="41"/>
+        <v>85.32</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L177" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M177" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N177" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -13646,261 +13664,253 @@
       <c r="C178" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D178" s="41" t="s">
-        <v>301</v>
+      <c r="D178" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="E178" s="41">
-        <v>5000</v>
-      </c>
-      <c r="F178" s="7">
-        <v>6</v>
-      </c>
-      <c r="G178" s="13">
-        <v>100</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="F178" s="7"/>
+      <c r="G178" s="13"/>
       <c r="H178" s="15">
         <v>0.08</v>
       </c>
-      <c r="I178" s="16">
-        <f t="shared" si="40"/>
-        <v>108</v>
-      </c>
+      <c r="I178" s="16"/>
       <c r="J178" s="8"/>
       <c r="K178" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L178" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M178" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N178" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:14">
-      <c r="B179" s="6" t="s">
-        <v>302</v>
+      <c r="B179" s="40" t="s">
+        <v>301</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D179" s="41" t="s">
-        <v>301</v>
+      <c r="D179" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="E179" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F179" s="7">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G179" s="13">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="H179" s="15">
         <v>0.08</v>
       </c>
       <c r="I179" s="16">
-        <f t="shared" si="40"/>
-        <v>156.6</v>
+        <f t="shared" si="41"/>
+        <v>113.4</v>
       </c>
       <c r="J179" s="8"/>
       <c r="K179" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L179" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M179" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N179" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:14">
-      <c r="B180" s="41" t="s">
-        <v>303</v>
+      <c r="B180" s="40" t="s">
+        <v>302</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D180" s="41" t="s">
-        <v>301</v>
+      <c r="D180" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="E180" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F180" s="7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G180" s="13">
-        <v>135</v>
+        <v>117.5</v>
       </c>
       <c r="H180" s="15">
         <v>0.08</v>
       </c>
       <c r="I180" s="16">
-        <f t="shared" si="40"/>
-        <v>145.8</v>
+        <f t="shared" si="41"/>
+        <v>126.9</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L180" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M180" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N180" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:14">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6" t="s">
-        <v>304</v>
+      <c r="B181" s="41" t="s">
+        <v>303</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D181" s="41" t="s">
-        <v>301</v>
+      <c r="D181" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="E181" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F181" s="7">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="G181" s="13">
-        <v>175</v>
+        <v>122.5</v>
       </c>
       <c r="H181" s="15">
         <v>0.08</v>
       </c>
       <c r="I181" s="16">
-        <f t="shared" si="40"/>
-        <v>189</v>
+        <f t="shared" si="41"/>
+        <v>132.3</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L181" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M181" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N181" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:14">
       <c r="B182" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D182" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E182" s="41">
         <v>5000</v>
       </c>
       <c r="F182" s="7">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="G182" s="13">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H182" s="15">
         <v>0.08</v>
       </c>
       <c r="I182" s="16">
-        <f t="shared" si="40"/>
-        <v>172.8</v>
+        <f t="shared" si="41"/>
+        <v>108</v>
       </c>
       <c r="J182" s="8"/>
       <c r="K182" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L182" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M182" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N182" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:14">
-      <c r="B183" s="44" t="s">
+      <c r="B183" s="6" t="s">
         <v>306</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D183" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E183" s="41">
         <v>5000</v>
       </c>
       <c r="F183" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G183" s="13">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="H183" s="15">
         <v>0.08</v>
       </c>
       <c r="I183" s="16">
-        <f t="shared" si="40"/>
-        <v>205.2</v>
+        <f t="shared" si="41"/>
+        <v>156.6</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L183" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M183" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N183" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -13912,163 +13922,172 @@
         <v>94</v>
       </c>
       <c r="D184" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E184" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F184" s="7">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G184" s="13">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="H184" s="15">
         <v>0.08</v>
       </c>
       <c r="I184" s="16">
-        <f t="shared" si="40"/>
-        <v>58.32</v>
+        <f t="shared" si="41"/>
+        <v>145.8</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L184" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M184" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N184" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:14">
-      <c r="B185" s="40" t="s">
+      <c r="A185" s="6"/>
+      <c r="B185" s="6" t="s">
         <v>308</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D185" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E185" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F185" s="7">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="G185" s="13">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="H185" s="15">
         <v>0.08</v>
       </c>
       <c r="I185" s="16">
-        <f t="shared" si="40"/>
-        <v>62.64</v>
+        <f t="shared" si="41"/>
+        <v>189</v>
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L185" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M185" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N185" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:14">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6" t="s">
+      <c r="B186" s="41" t="s">
         <v>309</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D186" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E186" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F186" s="7">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="G186" s="13">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="H186" s="15">
         <v>0.08</v>
       </c>
       <c r="I186" s="16">
-        <f t="shared" si="40"/>
-        <v>68.04</v>
+        <f t="shared" si="41"/>
+        <v>172.8</v>
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L186" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M186" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N186" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:14">
-      <c r="B187" s="41" t="s">
+      <c r="B187" s="44" t="s">
         <v>310</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D187" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E187" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F187" s="7"/>
-      <c r="G187" s="13"/>
-      <c r="H187" s="15"/>
-      <c r="I187" s="16"/>
+        <v>5000</v>
+      </c>
+      <c r="F187" s="7">
+        <v>10</v>
+      </c>
+      <c r="G187" s="13">
+        <v>190</v>
+      </c>
+      <c r="H187" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I187" s="16">
+        <f t="shared" si="41"/>
+        <v>205.2</v>
+      </c>
       <c r="J187" s="8"/>
       <c r="K187" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L187" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M187" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N187" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -14080,30 +14099,39 @@
         <v>94</v>
       </c>
       <c r="D188" s="41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E188" s="41">
         <v>1000</v>
       </c>
-      <c r="F188" s="7"/>
-      <c r="G188" s="13"/>
-      <c r="H188" s="15"/>
-      <c r="I188" s="16"/>
+      <c r="F188" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G188" s="13">
+        <v>54</v>
+      </c>
+      <c r="H188" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I188" s="16">
+        <f t="shared" si="41"/>
+        <v>58.32</v>
+      </c>
       <c r="J188" s="8"/>
       <c r="K188" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L188" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M188" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N188" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -14112,348 +14140,445 @@
         <v>312</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>314</v>
+        <v>94</v>
+      </c>
+      <c r="D189" s="41" t="s">
+        <v>305</v>
       </c>
       <c r="E189" s="41">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F189" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G189" s="13">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="H189" s="15">
         <v>0.08</v>
       </c>
       <c r="I189" s="16">
-        <f t="shared" si="40"/>
-        <v>151.2</v>
+        <f t="shared" si="41"/>
+        <v>62.64</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L189" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M189" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N189" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:14">
-      <c r="B190" s="40" t="s">
-        <v>312</v>
+      <c r="A190" s="6"/>
+      <c r="B190" s="6" t="s">
+        <v>313</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="D190" s="13" t="s">
-        <v>314</v>
+        <v>94</v>
+      </c>
+      <c r="D190" s="41" t="s">
+        <v>305</v>
       </c>
       <c r="E190" s="41">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F190" s="7">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="G190" s="13">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="H190" s="15">
         <v>0.08</v>
       </c>
       <c r="I190" s="16">
-        <f t="shared" si="40"/>
-        <v>151.2</v>
+        <f t="shared" si="41"/>
+        <v>68.04</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L190" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M190" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N190" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="B191" s="41" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D191" s="13" t="s">
-        <v>314</v>
+        <v>94</v>
+      </c>
+      <c r="D191" s="41" t="s">
+        <v>305</v>
       </c>
       <c r="E191" s="41">
         <v>1000</v>
       </c>
-      <c r="F191" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G191" s="13">
-        <v>70</v>
-      </c>
-      <c r="H191" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I191" s="16">
-        <f t="shared" si="40"/>
-        <v>75.6</v>
-      </c>
+      <c r="F191" s="7"/>
+      <c r="G191" s="13"/>
+      <c r="H191" s="15"/>
+      <c r="I191" s="16"/>
       <c r="J191" s="8"/>
       <c r="K191" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L191" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M191" s="16">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N191" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="B192" s="41" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D192" s="13" t="s">
-        <v>263</v>
+        <v>94</v>
+      </c>
+      <c r="D192" s="41" t="s">
+        <v>305</v>
       </c>
       <c r="E192" s="41">
-        <v>2000</v>
-      </c>
-      <c r="F192" s="7">
-        <v>4</v>
-      </c>
-      <c r="G192" s="13">
-        <v>101</v>
-      </c>
-      <c r="H192" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I192" s="16">
-        <f t="shared" si="40"/>
-        <v>114.13</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F192" s="7"/>
+      <c r="G192" s="13"/>
+      <c r="H192" s="15"/>
+      <c r="I192" s="16"/>
       <c r="J192" s="8"/>
       <c r="K192" s="17">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L192" s="17">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M192" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N192" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
+      <c r="B193" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="E193" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F193" s="7">
+        <v>5</v>
+      </c>
+      <c r="G193" s="13">
+        <v>140</v>
+      </c>
+      <c r="H193" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I193" s="16">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L192" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M192" s="16">
+        <v>151.2</v>
+      </c>
+      <c r="J193" s="8"/>
+      <c r="K193" s="17">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="N192" s="18">
+      <c r="L193" s="17">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:13">
-      <c r="F193" s="7"/>
-      <c r="G193" s="13"/>
-      <c r="H193" s="15"/>
-      <c r="J193" s="7" t="s">
+      <c r="M193" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N193" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
+      <c r="B194" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="K193" s="17">
-        <f>SUM(J6:J191)</f>
-        <v>0</v>
-      </c>
-      <c r="L193" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13">
-      <c r="A194" s="45"/>
-      <c r="B194" s="45"/>
-      <c r="C194" s="45"/>
-      <c r="D194" s="45"/>
-      <c r="E194" s="45"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="13"/>
-      <c r="H194" s="15"/>
-      <c r="I194" s="45"/>
-      <c r="J194" s="41" t="s">
+      <c r="C194" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D194" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="K194" s="7">
-        <f>SUM(K6:K191)</f>
-        <v>0</v>
-      </c>
-      <c r="L194" s="6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13">
-      <c r="A195" s="45"/>
-      <c r="B195" s="45"/>
-      <c r="C195" s="45"/>
-      <c r="D195" s="45"/>
-      <c r="E195" s="45"/>
-      <c r="F195" s="45"/>
-      <c r="G195" s="13"/>
-      <c r="H195" s="15"/>
-      <c r="I195" s="45"/>
-      <c r="J195" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="K195" s="4">
-        <f>SUM(L:L)</f>
-        <v>0</v>
-      </c>
-      <c r="L195" s="46" t="s">
-        <v>319</v>
-      </c>
-      <c r="M195" s="41"/>
-    </row>
-    <row r="196" spans="1:13">
-      <c r="A196" s="45"/>
-      <c r="B196" s="45"/>
-      <c r="C196" s="45"/>
-      <c r="D196" s="45"/>
-      <c r="E196" s="45"/>
-      <c r="F196" s="45"/>
-      <c r="G196" s="13"/>
-      <c r="H196" s="15"/>
-      <c r="I196" s="45"/>
-      <c r="J196" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="K196" s="45">
-        <f>SUM(N5:N192)</f>
-        <v>0</v>
-      </c>
-      <c r="L196" s="45"/>
-      <c r="M196" s="41"/>
-    </row>
-    <row r="197" spans="1:13">
-      <c r="A197" s="45"/>
-      <c r="B197" s="45"/>
-      <c r="C197" s="45"/>
-      <c r="D197" s="45"/>
-      <c r="E197" s="45"/>
-      <c r="F197" s="45"/>
+      <c r="E194" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F194" s="7">
+        <v>5</v>
+      </c>
+      <c r="G194" s="13">
+        <v>140</v>
+      </c>
+      <c r="H194" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I194" s="16">
+        <f t="shared" si="41"/>
+        <v>151.2</v>
+      </c>
+      <c r="J194" s="8"/>
+      <c r="K194" s="17">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L194" s="17">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M194" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N194" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14">
+      <c r="B195" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="E195" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F195" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G195" s="13">
+        <v>70</v>
+      </c>
+      <c r="H195" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I195" s="16">
+        <f t="shared" si="41"/>
+        <v>75.6</v>
+      </c>
+      <c r="J195" s="8"/>
+      <c r="K195" s="17">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L195" s="17">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M195" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N195" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14">
+      <c r="B196" s="41" t="s">
+        <v>279</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E196" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F196" s="7">
+        <v>4</v>
+      </c>
+      <c r="G196" s="13">
+        <v>101</v>
+      </c>
+      <c r="H196" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I196" s="16">
+        <f t="shared" si="41"/>
+        <v>114.13</v>
+      </c>
+      <c r="J196" s="8"/>
+      <c r="K196" s="17">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L196" s="17">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M196" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N196" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14">
+      <c r="F197" s="7"/>
       <c r="G197" s="13"/>
       <c r="H197" s="15"/>
-      <c r="I197" s="45"/>
-      <c r="J197" s="45"/>
-      <c r="K197" s="45"/>
-      <c r="L197" s="45"/>
-      <c r="M197" s="41"/>
-    </row>
-    <row r="198" spans="1:13">
+      <c r="J197" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="K197" s="17">
+        <f>SUM(J6:J195)</f>
+        <v>0</v>
+      </c>
+      <c r="L197" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14">
       <c r="A198" s="45"/>
       <c r="B198" s="45"/>
       <c r="C198" s="45"/>
       <c r="D198" s="45"/>
       <c r="E198" s="45"/>
-      <c r="F198" s="45"/>
+      <c r="F198" s="7"/>
       <c r="G198" s="13"/>
       <c r="H198" s="15"/>
       <c r="I198" s="45"/>
-      <c r="J198" s="45"/>
-      <c r="K198" s="45"/>
-      <c r="L198" s="45"/>
-      <c r="M198" s="41"/>
-    </row>
-    <row r="199" spans="1:13">
+      <c r="J198" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="K198" s="7">
+        <f>SUM(K6:K195)</f>
+        <v>0</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14">
       <c r="A199" s="45"/>
       <c r="B199" s="45"/>
       <c r="C199" s="45"/>
       <c r="D199" s="45"/>
       <c r="E199" s="45"/>
       <c r="F199" s="45"/>
-      <c r="G199" s="45"/>
+      <c r="G199" s="13"/>
       <c r="H199" s="15"/>
       <c r="I199" s="45"/>
-      <c r="J199" s="45"/>
-      <c r="K199" s="45"/>
-      <c r="L199" s="45"/>
+      <c r="J199" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="K199" s="4">
+        <f>SUM(L:L)</f>
+        <v>0</v>
+      </c>
+      <c r="L199" s="46" t="s">
+        <v>323</v>
+      </c>
       <c r="M199" s="41"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:14">
       <c r="A200" s="45"/>
       <c r="B200" s="45"/>
       <c r="C200" s="45"/>
       <c r="D200" s="45"/>
       <c r="E200" s="45"/>
       <c r="F200" s="45"/>
-      <c r="G200" s="45"/>
+      <c r="G200" s="13"/>
       <c r="H200" s="15"/>
       <c r="I200" s="45"/>
-      <c r="J200" s="45"/>
-      <c r="K200" s="45"/>
+      <c r="J200" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="K200" s="45">
+        <f>SUM(N5:N196)</f>
+        <v>0</v>
+      </c>
       <c r="L200" s="45"/>
       <c r="M200" s="41"/>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:14">
       <c r="A201" s="45"/>
       <c r="B201" s="45"/>
       <c r="C201" s="45"/>
       <c r="D201" s="45"/>
       <c r="E201" s="45"/>
       <c r="F201" s="45"/>
-      <c r="G201" s="45"/>
+      <c r="G201" s="13"/>
       <c r="H201" s="15"/>
       <c r="I201" s="45"/>
       <c r="J201" s="45"/>
       <c r="K201" s="45"/>
-      <c r="L201" s="45" t="s">
-        <v>221</v>
-      </c>
+      <c r="L201" s="45"/>
       <c r="M201" s="41"/>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:14">
       <c r="A202" s="45"/>
       <c r="B202" s="45"/>
       <c r="C202" s="45"/>
       <c r="D202" s="45"/>
       <c r="E202" s="45"/>
       <c r="F202" s="45"/>
-      <c r="G202" s="45"/>
-      <c r="H202" s="45"/>
+      <c r="G202" s="13"/>
+      <c r="H202" s="15"/>
       <c r="I202" s="45"/>
       <c r="J202" s="45"/>
       <c r="K202" s="45"/>
       <c r="L202" s="45"/>
       <c r="M202" s="41"/>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:14">
       <c r="A203" s="45"/>
       <c r="B203" s="45"/>
       <c r="C203" s="45"/>
@@ -14461,14 +14586,14 @@
       <c r="E203" s="45"/>
       <c r="F203" s="45"/>
       <c r="G203" s="45"/>
-      <c r="H203" s="45"/>
+      <c r="H203" s="15"/>
       <c r="I203" s="45"/>
       <c r="J203" s="45"/>
       <c r="K203" s="45"/>
       <c r="L203" s="45"/>
       <c r="M203" s="41"/>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:14">
       <c r="A204" s="45"/>
       <c r="B204" s="45"/>
       <c r="C204" s="45"/>
@@ -14476,14 +14601,14 @@
       <c r="E204" s="45"/>
       <c r="F204" s="45"/>
       <c r="G204" s="45"/>
-      <c r="H204" s="45"/>
+      <c r="H204" s="15"/>
       <c r="I204" s="45"/>
       <c r="J204" s="45"/>
       <c r="K204" s="45"/>
       <c r="L204" s="45"/>
       <c r="M204" s="41"/>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:14">
       <c r="A205" s="45"/>
       <c r="B205" s="45"/>
       <c r="C205" s="45"/>
@@ -14491,40 +14616,102 @@
       <c r="E205" s="45"/>
       <c r="F205" s="45"/>
       <c r="G205" s="45"/>
-      <c r="H205" s="45"/>
+      <c r="H205" s="15"/>
       <c r="I205" s="45"/>
       <c r="J205" s="45"/>
       <c r="K205" s="45"/>
-      <c r="L205" s="45"/>
+      <c r="L205" s="45" t="s">
+        <v>225</v>
+      </c>
       <c r="M205" s="41"/>
     </row>
-    <row r="207" spans="1:13">
-      <c r="B207" s="6"/>
-      <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
-      <c r="E207" s="6"/>
-    </row>
-    <row r="209" spans="2:11">
-      <c r="J209" s="6"/>
-    </row>
-    <row r="210" spans="2:11">
-      <c r="K210" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="211" spans="2:11">
+    <row r="206" spans="1:14">
+      <c r="A206" s="45"/>
+      <c r="B206" s="45"/>
+      <c r="C206" s="45"/>
+      <c r="D206" s="45"/>
+      <c r="E206" s="45"/>
+      <c r="F206" s="45"/>
+      <c r="G206" s="45"/>
+      <c r="H206" s="45"/>
+      <c r="I206" s="45"/>
+      <c r="J206" s="45"/>
+      <c r="K206" s="45"/>
+      <c r="L206" s="45"/>
+      <c r="M206" s="41"/>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" s="45"/>
+      <c r="B207" s="45"/>
+      <c r="C207" s="45"/>
+      <c r="D207" s="45"/>
+      <c r="E207" s="45"/>
+      <c r="F207" s="45"/>
+      <c r="G207" s="45"/>
+      <c r="H207" s="45"/>
+      <c r="I207" s="45"/>
+      <c r="J207" s="45"/>
+      <c r="K207" s="45"/>
+      <c r="L207" s="45"/>
+      <c r="M207" s="41"/>
+    </row>
+    <row r="208" spans="1:14">
+      <c r="A208" s="45"/>
+      <c r="B208" s="45"/>
+      <c r="C208" s="45"/>
+      <c r="D208" s="45"/>
+      <c r="E208" s="45"/>
+      <c r="F208" s="45"/>
+      <c r="G208" s="45"/>
+      <c r="H208" s="45"/>
+      <c r="I208" s="45"/>
+      <c r="J208" s="45"/>
+      <c r="K208" s="45"/>
+      <c r="L208" s="45"/>
+      <c r="M208" s="41"/>
+    </row>
+    <row r="209" spans="1:13">
+      <c r="A209" s="45"/>
+      <c r="B209" s="45"/>
+      <c r="C209" s="45"/>
+      <c r="D209" s="45"/>
+      <c r="E209" s="45"/>
+      <c r="F209" s="45"/>
+      <c r="G209" s="45"/>
+      <c r="H209" s="45"/>
+      <c r="I209" s="45"/>
+      <c r="J209" s="45"/>
+      <c r="K209" s="45"/>
+      <c r="L209" s="45"/>
+      <c r="M209" s="41"/>
+    </row>
+    <row r="211" spans="1:13">
       <c r="B211" s="6"/>
       <c r="C211" s="6"/>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
     </row>
-    <row r="224" spans="2:11">
-      <c r="E224" s="2" t="s">
-        <v>221</v>
+    <row r="213" spans="1:13">
+      <c r="J213" s="6"/>
+    </row>
+    <row r="214" spans="1:13">
+      <c r="K214" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13">
+      <c r="B215" s="6"/>
+      <c r="C215" s="6"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+    </row>
+    <row r="228" spans="5:5">
+      <c r="E228" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P196" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P200" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14543,7 +14730,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N192,工作表2!N6:N192&gt;0,"")</f>
+        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N196,工作表2!N6:N196&gt;0,"")</f>
         <v/>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="合同 " sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet name="工作表3" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$204</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'合同 '!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">发票!$A$1:$E$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">装箱单!$A$1:$L$36</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="330">
   <si>
     <t>销 售 合 同
 SALES CONTRACT</t>
@@ -647,6 +647,9 @@
     <t>L1紅黑三格</t>
   </si>
   <si>
+    <t>L4</t>
+  </si>
+  <si>
     <t>塑料餐盒蓋</t>
   </si>
   <si>
@@ -665,6 +668,9 @@
     <t>L1紅黑三格蓋</t>
   </si>
   <si>
+    <t>L4蓋</t>
+  </si>
+  <si>
     <t>H500</t>
   </si>
   <si>
@@ -738,6 +744,9 @@
   </si>
   <si>
     <t>Ai55</t>
+  </si>
+  <si>
+    <t>Ai500</t>
   </si>
   <si>
     <t>Total</t>
@@ -2709,7 +2718,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{7FC30F34-879C-4B6E-9339-B31E321A9363}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{0B789CF4-8B3E-4608-B422-5E76A67D6D76}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2718,7 +2727,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B88806DE-B3D7-4AD4-888F-837ED61B8C50}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{52EDBF2D-7F1D-4CC5-BEF0-B31EA26AF391}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -6388,7 +6397,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P229"/>
+  <dimension ref="A1:P232"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.4" style="2" customWidth="1"/>
@@ -9008,7 +9017,7 @@
       </c>
       <c r="J63" s="8"/>
       <c r="K63" s="17">
-        <f>J63*F63</f>
+        <f t="shared" ref="K63:K67" si="9">J63*F63</f>
         <v>0</v>
       </c>
       <c r="L63" s="17">
@@ -9016,11 +9025,11 @@
         <v>0</v>
       </c>
       <c r="M63" s="16">
-        <f>J63*I63</f>
+        <f t="shared" ref="M63:M67" si="10">J63*I63</f>
         <v>0</v>
       </c>
       <c r="N63" s="18">
-        <f>M63+J63</f>
+        <f t="shared" ref="N63:N67" si="11">M63+J63</f>
         <v>0</v>
       </c>
     </row>
@@ -9042,7 +9051,7 @@
         <v>18.2</v>
       </c>
       <c r="G64" s="13">
-        <f>I64/(1+H64)</f>
+        <f t="shared" ref="G64:G67" si="12">I64/(1+H64)</f>
         <v>336.283185840708</v>
       </c>
       <c r="H64" s="15">
@@ -9053,7 +9062,7 @@
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="17">
-        <f>J64*F64</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L64" s="17">
@@ -9061,11 +9070,11 @@
         <v>0</v>
       </c>
       <c r="M64" s="16">
-        <f>J64*I64</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N64" s="18">
-        <f>M64+J64</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -9087,7 +9096,7 @@
         <v>9.25</v>
       </c>
       <c r="G65" s="13">
-        <f>I65/(1+H65)</f>
+        <f t="shared" si="12"/>
         <v>141.592920353982</v>
       </c>
       <c r="H65" s="15">
@@ -9098,7 +9107,7 @@
       </c>
       <c r="J65" s="8"/>
       <c r="K65" s="17">
-        <f>J65*F65</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L65" s="17">
@@ -9106,11 +9115,11 @@
         <v>0</v>
       </c>
       <c r="M65" s="16">
-        <f>J65*I65</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N65" s="18">
-        <f>M65+J65</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O65" s="13"/>
@@ -9131,7 +9140,7 @@
         <v>13.5</v>
       </c>
       <c r="G66" s="13">
-        <f>I66/(1+H66)</f>
+        <f t="shared" si="12"/>
         <v>176.991150442478</v>
       </c>
       <c r="H66" s="15">
@@ -9142,7 +9151,7 @@
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="17">
-        <f>J66*F66</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L66" s="17">
@@ -9150,153 +9159,152 @@
         <v>0</v>
       </c>
       <c r="M66" s="16">
-        <f>J66*I66</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N66" s="18">
-        <f>M66+J66</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O66" s="13"/>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="12"/>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="15"/>
+      <c r="C67" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" s="26"/>
+      <c r="F67" s="7">
+        <v>12.15</v>
+      </c>
+      <c r="G67" s="13">
+        <f t="shared" si="12"/>
+        <v>233.628318584071</v>
+      </c>
+      <c r="H67" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I67" s="13">
+        <v>264</v>
+      </c>
+      <c r="J67" s="8"/>
+      <c r="K67" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="L67" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="2"/>
+        <f>K67+J67/2+0.3</f>
+        <v>0.3</v>
+      </c>
+      <c r="M67" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N67" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="13"/>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="12"/>
-      <c r="B68" s="25" t="s">
+      <c r="B68" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="15"/>
+      <c r="L68" s="17">
+        <f>K68+J68/2</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="2"/>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="12"/>
+      <c r="B69" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E68" s="26" t="s">
+      <c r="D69" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F69" s="7">
         <v>2.4</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G69" s="13">
         <f>5575.22/60</f>
         <v>92.9203333333333</v>
       </c>
-      <c r="H68" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I68" s="16">
-        <f>G68*(1+H68)</f>
-        <v>104.999976666667</v>
-      </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="17">
-        <f>J68*F68</f>
-        <v>0</v>
-      </c>
-      <c r="L68" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="16">
-        <f>J68*I68</f>
-        <v>0</v>
-      </c>
-      <c r="N68" s="18">
-        <f t="shared" ref="N68:N95" si="9">M68+J68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
-      <c r="A69" s="12"/>
-      <c r="B69" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E69" s="26">
-        <v>1000</v>
-      </c>
-      <c r="F69" s="7">
-        <v>7</v>
-      </c>
-      <c r="G69" s="13">
-        <f>I69/(1+H69)</f>
-        <v>230.088495575221</v>
-      </c>
       <c r="H69" s="15">
         <v>0.13</v>
       </c>
       <c r="I69" s="16">
-        <v>260</v>
+        <f>G69*(1+H69)</f>
+        <v>104.999976666667</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="17">
-        <f>J69*F69</f>
+        <f t="shared" ref="K69:K73" si="13">J69*F69</f>
         <v>0</v>
       </c>
       <c r="L69" s="17">
-        <f t="shared" si="2"/>
+        <f>K69+J69/2</f>
         <v>0</v>
       </c>
       <c r="M69" s="16">
-        <f>J69*I69</f>
+        <f t="shared" ref="M69:M73" si="14">J69*I69</f>
         <v>0</v>
       </c>
       <c r="N69" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="N69:N73" si="15">M69+J69</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="12"/>
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="27" t="s">
         <v>196</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E70" s="26" t="s">
-        <v>190</v>
+        <v>195</v>
+      </c>
+      <c r="E70" s="26">
+        <v>1000</v>
       </c>
       <c r="F70" s="7">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="G70" s="13">
-        <f>I70/(1+H70)</f>
-        <v>141.592920353982</v>
+        <f t="shared" ref="G70:G73" si="16">I70/(1+H70)</f>
+        <v>230.088495575221</v>
       </c>
       <c r="H70" s="15">
         <v>0.13</v>
       </c>
       <c r="I70" s="16">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="17">
-        <f>J70*F70</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L70" s="17">
@@ -9304,31 +9312,33 @@
         <v>0</v>
       </c>
       <c r="M70" s="16">
-        <f>J70*I70</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N70" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="12"/>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="25" t="s">
         <v>197</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E71" s="26"/>
+        <v>195</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>190</v>
+      </c>
       <c r="F71" s="7">
-        <v>5.2</v>
+        <v>9.25</v>
       </c>
       <c r="G71" s="13">
-        <f>I71/(1+H71)</f>
+        <f t="shared" si="16"/>
         <v>141.592920353982</v>
       </c>
       <c r="H71" s="15">
@@ -9339,140 +9349,136 @@
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="17">
-        <f>J71*F71</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L71" s="17">
-        <f>K71+J71/2</f>
+        <f t="shared" ref="L71:L73" si="17">K71+J71/2</f>
         <v>0</v>
       </c>
       <c r="M71" s="16">
-        <f>J71*I71</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N71" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="12"/>
-      <c r="B72" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="15"/>
-      <c r="I72" s="16"/>
+      <c r="B72" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" s="26"/>
+      <c r="F72" s="7">
+        <v>5.2</v>
+      </c>
+      <c r="G72" s="13">
+        <f t="shared" si="16"/>
+        <v>141.592920353982</v>
+      </c>
+      <c r="H72" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I72" s="16">
+        <v>160</v>
+      </c>
       <c r="J72" s="8"/>
-      <c r="K72" s="17"/>
+      <c r="K72" s="17">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="L72" s="17">
-        <f t="shared" ref="L72:L84" si="10">K72+J72/2</f>
-        <v>0</v>
-      </c>
-      <c r="M72" s="16"/>
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="N72" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="12"/>
-      <c r="B73" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>91</v>
+      <c r="B73" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>199</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="E73" s="26"/>
       <c r="F73" s="7">
-        <v>6.3</v>
+        <v>8.55</v>
       </c>
       <c r="G73" s="13">
-        <v>68</v>
+        <f t="shared" si="16"/>
+        <v>224.778761061947</v>
       </c>
       <c r="H73" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I73" s="16">
-        <f t="shared" ref="I73:I80" si="11">G73*(1+H73)</f>
-        <v>73.44</v>
+        <v>254</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="17">
-        <f t="shared" ref="K73:K95" si="12">J73*F73</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L73" s="17">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>K73+J73+0.15</f>
+        <v>0.15</v>
       </c>
       <c r="M73" s="16">
-        <f t="shared" ref="M73:M95" si="13">J73*I73</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N73" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="12"/>
-      <c r="B74" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F74" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="G74" s="13">
-        <v>74</v>
-      </c>
-      <c r="H74" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I74" s="16">
-        <f t="shared" si="11"/>
-        <v>79.92</v>
-      </c>
+      <c r="B74" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="16"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="17">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="K74" s="17"/>
       <c r="L74" s="17">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="16">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L74:L86" si="18">K74+J74/2</f>
+        <v>0</v>
+      </c>
+      <c r="M74" s="16"/>
       <c r="N74" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
+        <f t="shared" ref="N74:N97" si="19">M74+J74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="1:15">
       <c r="A75" s="12"/>
       <c r="B75" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>91</v>
@@ -9481,42 +9487,42 @@
         <v>136</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F75" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G75" s="13">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H75" s="15">
         <v>0.08</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="11"/>
-        <v>88.56</v>
+        <f t="shared" ref="I75:I82" si="20">G75*(1+H75)</f>
+        <v>73.44</v>
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="K75:K97" si="21">J75*F75</f>
         <v>0</v>
       </c>
       <c r="L75" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="M75:M97" si="22">J75*I75</f>
         <v>0</v>
       </c>
       <c r="N75" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="12"/>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="19" t="s">
         <v>202</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -9526,36 +9532,36 @@
         <v>136</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F76" s="7">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G76" s="13">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H76" s="15">
         <v>0.08</v>
       </c>
       <c r="I76" s="16">
-        <f t="shared" si="11"/>
-        <v>97.2</v>
+        <f t="shared" si="20"/>
+        <v>79.92</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L76" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M76" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N76" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -9571,36 +9577,36 @@
         <v>136</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="F77" s="7">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G77" s="13">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="H77" s="15">
         <v>0.08</v>
       </c>
       <c r="I77" s="16">
-        <f t="shared" si="11"/>
-        <v>65.88</v>
+        <f t="shared" si="20"/>
+        <v>88.56</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L77" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M77" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N77" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -9616,36 +9622,36 @@
         <v>136</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="F78" s="7">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="G78" s="13">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H78" s="15">
         <v>0.08</v>
       </c>
       <c r="I78" s="16">
-        <f t="shared" si="11"/>
-        <v>63.72</v>
+        <f t="shared" si="20"/>
+        <v>97.2</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L78" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M78" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N78" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -9673,31 +9679,31 @@
         <v>0.08</v>
       </c>
       <c r="I79" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>65.88</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L79" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M79" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N79" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="12"/>
-      <c r="B80" s="19">
-        <v>6828</v>
+      <c r="B80" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>91</v>
@@ -9718,159 +9724,159 @@
         <v>0.08</v>
       </c>
       <c r="I80" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v>63.72</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L80" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M80" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N80" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" s="2" customFormat="1" spans="1:14">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" s="12"/>
-      <c r="B81" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C81" s="29" t="s">
+      <c r="B81" s="19" t="s">
         <v>207</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E81" s="30" t="s">
-        <v>129</v>
+      <c r="E81" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="F81" s="7">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="G81" s="13">
-        <f t="shared" ref="G81:G85" si="14">I81-1</f>
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="H81" s="15">
         <v>0.08</v>
       </c>
-      <c r="I81" s="13">
-        <v>90</v>
+      <c r="I81" s="16">
+        <f t="shared" si="20"/>
+        <v>65.88</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L81" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M81" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N81" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" s="2" customFormat="1" spans="1:14">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" s="12"/>
-      <c r="B82" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C82" s="29" t="s">
-        <v>207</v>
+      <c r="B82" s="19">
+        <v>6828</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E82" s="30" t="s">
+      <c r="E82" s="14" t="s">
         <v>127</v>
       </c>
       <c r="F82" s="7">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="G82" s="13">
-        <f t="shared" si="14"/>
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H82" s="15">
         <v>0.08</v>
       </c>
-      <c r="I82" s="13">
-        <v>70</v>
+      <c r="I82" s="16">
+        <f t="shared" si="20"/>
+        <v>63.72</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L82" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M82" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N82" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" spans="1:14">
       <c r="A83" s="12"/>
-      <c r="B83" s="31" t="s">
+      <c r="B83" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" s="29" t="s">
         <v>209</v>
-      </c>
-      <c r="C83" s="29" t="s">
-        <v>207</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E83" s="30" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="F83" s="7">
         <v>8.4</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" si="14"/>
-        <v>91</v>
+        <f t="shared" ref="G83:G87" si="23">I83-1</f>
+        <v>89</v>
       </c>
       <c r="H83" s="15">
         <v>0.08</v>
       </c>
       <c r="I83" s="13">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L83" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M83" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N83" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -9880,175 +9886,175 @@
         <v>210</v>
       </c>
       <c r="C84" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E84" s="30" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F84" s="7">
-        <v>10.4</v>
+        <v>6.3</v>
       </c>
       <c r="G84" s="13">
-        <f t="shared" si="14"/>
-        <v>76</v>
+        <f t="shared" si="23"/>
+        <v>69</v>
       </c>
       <c r="H84" s="15">
         <v>0.08</v>
       </c>
       <c r="I84" s="13">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L84" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M84" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N84" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" spans="1:14">
       <c r="A85" s="12"/>
-      <c r="B85" s="29" t="s">
+      <c r="B85" s="31" t="s">
         <v>211</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E85" s="30" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F85" s="7">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="G85" s="13">
-        <f t="shared" si="14"/>
-        <v>89</v>
+        <f t="shared" si="23"/>
+        <v>91</v>
       </c>
       <c r="H85" s="15">
         <v>0.08</v>
       </c>
       <c r="I85" s="13">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J85" s="8"/>
-      <c r="K85" s="17"/>
-      <c r="L85" s="17"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="18"/>
+      <c r="K85" s="17">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="16">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="N85" s="18">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="86" s="2" customFormat="1" spans="1:14">
       <c r="A86" s="12"/>
-      <c r="B86" s="31" t="s">
+      <c r="B86" s="29" t="s">
         <v>212</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F86" s="7">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G86" s="13">
-        <f t="shared" ref="G86:G91" si="15">I86-1</f>
-        <v>113</v>
+        <f t="shared" si="23"/>
+        <v>76</v>
       </c>
       <c r="H86" s="15">
         <v>0.08</v>
       </c>
       <c r="I86" s="13">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="17">
-        <f t="shared" ref="K86:K98" si="16">J86*F86</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L86" s="17">
-        <f t="shared" ref="L86:L98" si="17">K86+J86/2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M86" s="16">
-        <f t="shared" ref="M86:M98" si="18">J86*I86</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N86" s="18">
-        <f t="shared" ref="N86:N98" si="19">M86+J86</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" spans="1:14">
       <c r="A87" s="12"/>
-      <c r="B87" s="31" t="s">
+      <c r="B87" s="29" t="s">
         <v>213</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="F87" s="7">
-        <v>7.2</v>
+        <v>11.4</v>
       </c>
       <c r="G87" s="13">
-        <f t="shared" si="15"/>
-        <v>73</v>
+        <f t="shared" si="23"/>
+        <v>89</v>
       </c>
       <c r="H87" s="15">
         <v>0.08</v>
       </c>
       <c r="I87" s="13">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J87" s="8"/>
-      <c r="K87" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="L87" s="17">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="16">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N87" s="18">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
+      <c r="K87" s="17"/>
+      <c r="L87" s="17"/>
+      <c r="M87" s="16"/>
+      <c r="N87" s="18"/>
     </row>
     <row r="88" s="2" customFormat="1" spans="1:14">
       <c r="A88" s="12"/>
-      <c r="B88" s="29" t="s">
-        <v>215</v>
+      <c r="B88" s="31" t="s">
+        <v>214</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>136</v>
@@ -10057,78 +10063,78 @@
         <v>129</v>
       </c>
       <c r="F88" s="7">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="G88" s="13">
-        <f t="shared" si="15"/>
-        <v>73.7</v>
+        <f t="shared" ref="G88:G93" si="24">I88-1</f>
+        <v>113</v>
       </c>
       <c r="H88" s="15">
         <v>0.08</v>
       </c>
       <c r="I88" s="13">
-        <v>74.7</v>
+        <v>114</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="K88:K101" si="25">J88*F88</f>
         <v>0</v>
       </c>
       <c r="L88" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="L88:L101" si="26">K88+J88/2</f>
         <v>0</v>
       </c>
       <c r="M88" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="M88:M101" si="27">J88*I88</f>
         <v>0</v>
       </c>
       <c r="N88" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="N88:N101" si="28">M88+J88</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" spans="1:14">
       <c r="A89" s="12"/>
-      <c r="B89" s="29" t="s">
-        <v>216</v>
+      <c r="B89" s="31" t="s">
+        <v>215</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E89" s="30" t="s">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="F89" s="7">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="G89" s="13">
-        <f t="shared" si="15"/>
-        <v>74.1</v>
+        <f t="shared" si="24"/>
+        <v>73</v>
       </c>
       <c r="H89" s="15">
         <v>0.08</v>
       </c>
       <c r="I89" s="13">
-        <v>75.1</v>
+        <v>74</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L89" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M89" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N89" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
@@ -10138,42 +10144,42 @@
         <v>217</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E90" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F90" s="7">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="G90" s="13">
-        <f t="shared" si="15"/>
-        <v>58.1</v>
+        <f t="shared" si="24"/>
+        <v>73.7</v>
       </c>
       <c r="H90" s="15">
         <v>0.08</v>
       </c>
       <c r="I90" s="13">
-        <v>59.1</v>
+        <v>74.7</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L90" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M90" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N90" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
@@ -10183,687 +10189,687 @@
         <v>218</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E91" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F91" s="7">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="G91" s="13">
-        <f t="shared" si="15"/>
-        <v>124</v>
+        <f t="shared" si="24"/>
+        <v>74.1</v>
       </c>
       <c r="H91" s="15">
         <v>0.08</v>
       </c>
       <c r="I91" s="13">
-        <v>125</v>
+        <v>75.1</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L91" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M91" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N91" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" spans="1:14">
       <c r="A92" s="12"/>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>220</v>
+      <c r="C92" s="29" t="s">
+        <v>209</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E92" s="12"/>
+      <c r="E92" s="30" t="s">
+        <v>127</v>
+      </c>
       <c r="F92" s="7">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G92" s="13">
-        <v>80</v>
+        <f t="shared" si="24"/>
+        <v>58.1</v>
       </c>
       <c r="H92" s="15">
         <v>0.08</v>
       </c>
       <c r="I92" s="13">
-        <v>81</v>
+        <v>59.1</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L92" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M92" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N92" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" s="2" customFormat="1" spans="1:14">
       <c r="A93" s="12"/>
-      <c r="B93" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C93" s="12" t="s">
+      <c r="B93" s="29" t="s">
         <v>220</v>
+      </c>
+      <c r="C93" s="29" t="s">
+        <v>209</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E93" s="14" t="s">
-        <v>199</v>
+      <c r="E93" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="F93" s="7">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G93" s="13">
-        <v>68</v>
+        <f t="shared" si="24"/>
+        <v>124</v>
       </c>
       <c r="H93" s="15">
         <v>0.08</v>
       </c>
-      <c r="I93" s="16">
-        <f t="shared" ref="I93:I96" si="20">G93*(1+H93)</f>
-        <v>73.44</v>
+      <c r="I93" s="13">
+        <v>125</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L93" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M93" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N93" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" s="2" customFormat="1" spans="1:14">
       <c r="A94" s="12"/>
-      <c r="B94" s="19" t="s">
-        <v>200</v>
+      <c r="B94" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E94" s="14" t="s">
-        <v>199</v>
-      </c>
+      <c r="E94" s="12"/>
       <c r="F94" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G94" s="13">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H94" s="15">
         <v>0.08</v>
       </c>
-      <c r="I94" s="16">
-        <f t="shared" si="20"/>
-        <v>79.92</v>
+      <c r="I94" s="13">
+        <v>81</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L94" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M94" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N94" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" spans="1:14">
       <c r="A95" s="12"/>
       <c r="B95" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F95" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G95" s="13">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H95" s="15">
         <v>0.08</v>
       </c>
       <c r="I95" s="16">
-        <f t="shared" si="20"/>
-        <v>88.56</v>
+        <f t="shared" ref="I95:I98" si="29">G95*(1+H95)</f>
+        <v>73.44</v>
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L95" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M95" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N95" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" spans="1:14">
       <c r="A96" s="12"/>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="19" t="s">
         <v>202</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F96" s="7">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G96" s="13">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H96" s="15">
         <v>0.08</v>
       </c>
       <c r="I96" s="16">
-        <f t="shared" si="20"/>
-        <v>97.2</v>
+        <f t="shared" si="29"/>
+        <v>79.92</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L96" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M96" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N96" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" spans="1:14">
       <c r="A97" s="12"/>
-      <c r="B97" s="12" t="s">
-        <v>221</v>
+      <c r="B97" s="19" t="s">
+        <v>203</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="F97" s="7">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G97" s="13">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H97" s="15">
         <v>0.08</v>
       </c>
       <c r="I97" s="16">
-        <v>79</v>
+        <f t="shared" si="29"/>
+        <v>88.56</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L97" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M97" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N97" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" spans="1:14">
       <c r="A98" s="12"/>
-      <c r="B98" s="29" t="s">
+      <c r="B98" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C98" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E98" s="30" t="s">
-        <v>127</v>
+      <c r="E98" s="14" t="s">
+        <v>201</v>
       </c>
       <c r="F98" s="7">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="G98" s="13">
-        <f>I98-1</f>
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="H98" s="15">
         <v>0.08</v>
       </c>
-      <c r="I98" s="13">
-        <v>70</v>
+      <c r="I98" s="16">
+        <f t="shared" si="29"/>
+        <v>97.2</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L98" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M98" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N98" s="18">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" s="2" customFormat="1" spans="1:14">
       <c r="A99" s="12"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="15"/>
-      <c r="I99" s="23" t="s">
+      <c r="B99" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="J99" s="24"/>
-      <c r="K99" s="24"/>
+      <c r="C99" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F99" s="7">
+        <v>9</v>
+      </c>
+      <c r="G99" s="13">
+        <v>78</v>
+      </c>
+      <c r="H99" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I99" s="16">
+        <v>79</v>
+      </c>
+      <c r="J99" s="8"/>
+      <c r="K99" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="L99" s="17">
-        <f t="shared" ref="L99:L102" si="21">K99+J99/2</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="24"/>
-      <c r="N99" s="24"/>
-    </row>
-    <row r="100" spans="1:14">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="16">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="N99" s="18">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" spans="1:14">
       <c r="A100" s="12"/>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="15"/>
-      <c r="I100" s="16"/>
-      <c r="J100" s="8" t="s">
+      <c r="C100" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E100" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F100" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="G100" s="13">
+        <f>I100-1</f>
+        <v>69</v>
+      </c>
+      <c r="H100" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I100" s="13">
+        <v>70</v>
+      </c>
+      <c r="J100" s="8"/>
+      <c r="K100" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L100" s="17">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="16">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="N100" s="18">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" spans="1:14">
+      <c r="A101" s="12"/>
+      <c r="B101" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="K100" s="17"/>
-      <c r="L100" s="17">
-        <v>0</v>
-      </c>
-      <c r="M100" s="16"/>
-      <c r="N100" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
-      <c r="A101" s="12"/>
-      <c r="B101" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>91</v>
+      <c r="C101" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>199</v>
+        <v>136</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F101" s="7">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="G101" s="13">
-        <v>50.5</v>
+        <f>I101-1</f>
+        <v>58</v>
       </c>
       <c r="H101" s="15">
         <v>0.08</v>
       </c>
-      <c r="I101" s="16">
-        <f>G101*(1+H101)</f>
-        <v>54.54</v>
+      <c r="I101" s="13">
+        <v>59</v>
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="17">
-        <f>J101*F101</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L101" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M101" s="16">
-        <f>J101*I101</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N101" s="18">
-        <f>M101+J101</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="12"/>
-      <c r="B102" s="19" t="s">
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="15"/>
+      <c r="I102" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="C102" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F102" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G102" s="13">
-        <v>50.5</v>
-      </c>
-      <c r="H102" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I102" s="16">
-        <f>G102*(1+H102)</f>
-        <v>54.54</v>
-      </c>
-      <c r="J102" s="8"/>
-      <c r="K102" s="17">
-        <f>J102*F102</f>
-        <v>0</v>
-      </c>
+      <c r="J102" s="24"/>
+      <c r="K102" s="24"/>
       <c r="L102" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="16">
-        <f>J102*I102</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="18">
-        <f>M102+J102</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L102:L105" si="30">K102+J102/2</f>
+        <v>0</v>
+      </c>
+      <c r="M102" s="24"/>
+      <c r="N102" s="24"/>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="12"/>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="12"/>
-      <c r="E103" s="12"/>
-      <c r="F103" s="7"/>
+      <c r="B103" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C103" s="10"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10"/>
+      <c r="F103" s="11"/>
       <c r="G103" s="13"/>
       <c r="H103" s="15"/>
-      <c r="I103" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="J103" s="24"/>
-      <c r="K103" s="24"/>
+      <c r="I103" s="16"/>
+      <c r="J103" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="K103" s="17"/>
       <c r="L103" s="17">
-        <f t="shared" ref="L103:L166" si="22">K103+J103/2</f>
-        <v>0</v>
-      </c>
-      <c r="M103" s="24"/>
-      <c r="N103" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="16"/>
+      <c r="N103" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="12"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="13"/>
-      <c r="H104" s="15"/>
-      <c r="I104" s="16"/>
+      <c r="B104" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F104" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G104" s="13">
+        <v>50.5</v>
+      </c>
+      <c r="H104" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I104" s="16">
+        <f>G104*(1+H104)</f>
+        <v>54.54</v>
+      </c>
       <c r="J104" s="8"/>
-      <c r="K104" s="17"/>
+      <c r="K104" s="17">
+        <f>J104*F104</f>
+        <v>0</v>
+      </c>
       <c r="L104" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="16"/>
-      <c r="N104" s="18"/>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M104" s="16">
+        <f>J104*I104</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="18">
+        <f>M104+J104</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="12"/>
-      <c r="B105" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="15"/>
-      <c r="I105" s="16"/>
+      <c r="B105" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F105" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G105" s="13">
+        <v>50.5</v>
+      </c>
+      <c r="H105" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I105" s="16">
+        <f>G105*(1+H105)</f>
+        <v>54.54</v>
+      </c>
       <c r="J105" s="8"/>
-      <c r="K105" s="17"/>
+      <c r="K105" s="17">
+        <f>J105*F105</f>
+        <v>0</v>
+      </c>
       <c r="L105" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="16"/>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="16">
+        <f>J105*I105</f>
+        <v>0</v>
+      </c>
       <c r="N105" s="18">
-        <f t="shared" ref="N105:N118" si="23">M105+J105</f>
+        <f>M105+J105</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="12"/>
-      <c r="B106" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E106" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F106" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G106" s="13">
-        <v>51</v>
-      </c>
-      <c r="H106" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I106" s="16">
-        <f t="shared" ref="I106:I118" si="24">G106*(1+H106)</f>
-        <v>55.08</v>
-      </c>
-      <c r="J106" s="8"/>
-      <c r="K106" s="17">
-        <f t="shared" ref="K106:K118" si="25">J106*F106</f>
-        <v>0</v>
-      </c>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="13"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="J106" s="24"/>
+      <c r="K106" s="24"/>
       <c r="L106" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M106" s="16">
-        <f t="shared" ref="M106:M118" si="26">J106*I106</f>
-        <v>0</v>
-      </c>
-      <c r="N106" s="18">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="14" customHeight="1" spans="1:14">
+        <f t="shared" ref="L106:L169" si="31">K106+J106/2</f>
+        <v>0</v>
+      </c>
+      <c r="M106" s="24"/>
+      <c r="N106" s="24"/>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" s="12"/>
-      <c r="B107" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E107" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F107" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G107" s="13">
-        <v>54</v>
-      </c>
-      <c r="H107" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I107" s="16">
-        <f t="shared" si="24"/>
-        <v>58.32</v>
-      </c>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="15"/>
+      <c r="I107" s="16"/>
       <c r="J107" s="8"/>
-      <c r="K107" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
+      <c r="K107" s="17"/>
       <c r="L107" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="N107" s="18">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="16"/>
+      <c r="N107" s="18"/>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="12"/>
-      <c r="B108" s="19" t="s">
+      <c r="B108" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C108" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E108" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F108" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="G108" s="13">
-        <v>61</v>
-      </c>
-      <c r="H108" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I108" s="16">
-        <f t="shared" si="24"/>
-        <v>65.88</v>
-      </c>
+      <c r="C108" s="10"/>
+      <c r="D108" s="10"/>
+      <c r="E108" s="10"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="15"/>
+      <c r="I108" s="16"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
+      <c r="K108" s="17"/>
       <c r="L108" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M108" s="16"/>
       <c r="N108" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="N108:N121" si="32">M108+J108</f>
         <v>0</v>
       </c>
     </row>
@@ -10879,42 +10885,42 @@
         <v>126</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F109" s="7">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="G109" s="13">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H109" s="15">
         <v>0.08</v>
       </c>
       <c r="I109" s="16">
-        <f t="shared" si="24"/>
-        <v>69.12</v>
+        <f t="shared" ref="I109:I121" si="33">G109*(1+H109)</f>
+        <v>55.08</v>
       </c>
       <c r="J109" s="8"/>
       <c r="K109" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="K109:K121" si="34">J109*F109</f>
         <v>0</v>
       </c>
       <c r="L109" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M109" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="M109:M121" si="35">J109*I109</f>
         <v>0</v>
       </c>
       <c r="N109" s="18">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" ht="14" customHeight="1" spans="1:14">
       <c r="A110" s="12"/>
-      <c r="B110" s="19" t="s">
+      <c r="B110" s="12" t="s">
         <v>233</v>
       </c>
       <c r="C110" s="8" t="s">
@@ -10924,29 +10930,36 @@
         <v>126</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F110" s="7"/>
-      <c r="G110" s="13"/>
+        <v>201</v>
+      </c>
+      <c r="F110" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G110" s="13">
+        <v>54</v>
+      </c>
       <c r="H110" s="15">
         <v>0.08</v>
       </c>
-      <c r="I110" s="16"/>
+      <c r="I110" s="16">
+        <f t="shared" si="33"/>
+        <v>58.32</v>
+      </c>
       <c r="J110" s="8"/>
       <c r="K110" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L110" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M110" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N110" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -10962,42 +10975,42 @@
         <v>126</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F111" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="G111" s="13">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H111" s="15">
         <v>0.08</v>
       </c>
       <c r="I111" s="16">
-        <f t="shared" si="24"/>
-        <v>74.52</v>
+        <f t="shared" si="33"/>
+        <v>65.88</v>
       </c>
       <c r="J111" s="8"/>
       <c r="K111" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L111" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M111" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N111" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="12"/>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="19" t="s">
         <v>235</v>
       </c>
       <c r="C112" s="8" t="s">
@@ -11007,36 +11020,36 @@
         <v>126</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F112" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="G112" s="13">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H112" s="15">
         <v>0.08</v>
       </c>
       <c r="I112" s="16">
-        <f t="shared" si="24"/>
-        <v>77.76</v>
+        <f t="shared" si="33"/>
+        <v>69.12</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L112" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M112" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N112" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -11052,36 +11065,29 @@
         <v>126</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F113" s="7">
-        <v>8.5</v>
-      </c>
-      <c r="G113" s="13">
-        <v>90</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="F113" s="7"/>
+      <c r="G113" s="13"/>
       <c r="H113" s="15">
         <v>0.08</v>
       </c>
-      <c r="I113" s="16">
-        <f t="shared" si="24"/>
-        <v>97.2</v>
-      </c>
+      <c r="I113" s="16"/>
       <c r="J113" s="8"/>
       <c r="K113" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L113" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M113" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N113" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -11097,36 +11103,36 @@
         <v>126</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F114" s="7">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G114" s="13">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H114" s="15">
         <v>0.08</v>
       </c>
       <c r="I114" s="16">
-        <f t="shared" si="24"/>
-        <v>100.44</v>
-      </c>
-      <c r="J114" s="32"/>
+        <f t="shared" si="33"/>
+        <v>74.52</v>
+      </c>
+      <c r="J114" s="8"/>
       <c r="K114" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L114" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M114" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N114" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -11142,29 +11148,36 @@
         <v>126</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F115" s="7"/>
-      <c r="G115" s="13"/>
+        <v>201</v>
+      </c>
+      <c r="F115" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="G115" s="13">
+        <v>72</v>
+      </c>
       <c r="H115" s="15">
         <v>0.08</v>
       </c>
-      <c r="I115" s="16"/>
+      <c r="I115" s="16">
+        <f t="shared" si="33"/>
+        <v>77.76</v>
+      </c>
       <c r="J115" s="8"/>
       <c r="K115" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L115" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M115" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N115" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -11180,36 +11193,36 @@
         <v>126</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="F116" s="7">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="G116" s="13">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H116" s="15">
         <v>0.08</v>
       </c>
       <c r="I116" s="16">
-        <f t="shared" si="24"/>
-        <v>76.68</v>
+        <f t="shared" si="33"/>
+        <v>97.2</v>
       </c>
       <c r="J116" s="8"/>
       <c r="K116" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L116" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M116" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N116" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -11225,36 +11238,36 @@
         <v>126</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="F117" s="7">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="G117" s="13">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H117" s="15">
         <v>0.08</v>
       </c>
       <c r="I117" s="16">
-        <f t="shared" si="24"/>
-        <v>79.92</v>
-      </c>
-      <c r="J117" s="8"/>
+        <f t="shared" si="33"/>
+        <v>100.44</v>
+      </c>
+      <c r="J117" s="32"/>
       <c r="K117" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L117" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M117" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N117" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -11280,221 +11293,215 @@
       <c r="I118" s="16"/>
       <c r="J118" s="8"/>
       <c r="K118" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L118" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M118" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N118" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="12"/>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12"/>
-      <c r="E119" s="12"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="15"/>
-      <c r="I119" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="J119" s="24"/>
-      <c r="K119" s="24"/>
+      <c r="B119" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E119" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F119" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G119" s="13">
+        <v>71</v>
+      </c>
+      <c r="H119" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I119" s="16">
+        <f t="shared" si="33"/>
+        <v>76.68</v>
+      </c>
+      <c r="J119" s="8"/>
+      <c r="K119" s="17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
       <c r="L119" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="24"/>
-      <c r="N119" s="24"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="N119" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="12"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="15"/>
-      <c r="I120" s="16"/>
+      <c r="B120" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E120" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F120" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G120" s="13">
+        <v>74</v>
+      </c>
+      <c r="H120" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I120" s="16">
+        <f t="shared" si="33"/>
+        <v>79.92</v>
+      </c>
       <c r="J120" s="8"/>
-      <c r="K120" s="17"/>
+      <c r="K120" s="17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
       <c r="L120" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M120" s="16"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="N120" s="18">
-        <f t="shared" ref="N120:N127" si="27">M120+J120</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="12"/>
-      <c r="B121" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="C121" s="10"/>
-      <c r="D121" s="10"/>
-      <c r="E121" s="10"/>
-      <c r="F121" s="11"/>
+      <c r="B121" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F121" s="7"/>
       <c r="G121" s="13"/>
-      <c r="H121" s="15"/>
+      <c r="H121" s="15">
+        <v>0.08</v>
+      </c>
       <c r="I121" s="16"/>
-      <c r="J121" s="4"/>
-      <c r="K121" s="17"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
       <c r="L121" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="16"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="N121" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="12"/>
-      <c r="B122" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E122" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F122" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G122" s="13">
-        <v>31.5</v>
-      </c>
-      <c r="H122" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I122" s="16">
-        <f t="shared" ref="I122:I127" si="28">G122*(1+H122)</f>
-        <v>34.02</v>
-      </c>
-      <c r="J122" s="8"/>
-      <c r="K122" s="17">
-        <f t="shared" ref="K122:K127" si="29">J122*F122</f>
-        <v>0</v>
-      </c>
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="15"/>
+      <c r="I122" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="J122" s="24"/>
+      <c r="K122" s="24"/>
       <c r="L122" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M122" s="16">
-        <f t="shared" ref="M122:M127" si="30">J122*I122</f>
-        <v>0</v>
-      </c>
-      <c r="N122" s="18">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="24"/>
+      <c r="N122" s="24"/>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="12"/>
-      <c r="B123" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D123" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F123" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G123" s="13">
-        <v>42.5</v>
-      </c>
-      <c r="H123" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I123" s="16">
-        <f t="shared" si="28"/>
-        <v>45.9</v>
-      </c>
+      <c r="F123" s="7"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="15"/>
+      <c r="I123" s="16"/>
       <c r="J123" s="8"/>
-      <c r="K123" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
+      <c r="K123" s="17"/>
       <c r="L123" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M123" s="16">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="16"/>
       <c r="N123" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="N123:N130" si="36">M123+J123</f>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="12"/>
-      <c r="B124" s="19" t="s">
+      <c r="B124" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="C124" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F124" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="G124" s="13">
-        <v>47</v>
-      </c>
-      <c r="H124" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I124" s="16">
-        <f t="shared" si="28"/>
-        <v>50.76</v>
-      </c>
+      <c r="C124" s="10"/>
+      <c r="D124" s="10"/>
+      <c r="E124" s="10"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="15"/>
+      <c r="I124" s="16"/>
       <c r="J124" s="4"/>
-      <c r="K124" s="17">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
+      <c r="K124" s="17"/>
       <c r="L124" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M124" s="16">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="16"/>
       <c r="N124" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:14">
+      <c r="A125" s="12"/>
       <c r="B125" s="19" t="s">
         <v>246</v>
       </c>
@@ -11504,40 +11511,43 @@
       <c r="D125" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E125" s="12"/>
+      <c r="E125" s="14" t="s">
+        <v>201</v>
+      </c>
       <c r="F125" s="7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G125" s="13">
-        <v>52</v>
-      </c>
-      <c r="H125" s="33">
-        <v>0.095</v>
+        <v>31.5</v>
+      </c>
+      <c r="H125" s="15">
+        <v>0.08</v>
       </c>
       <c r="I125" s="16">
-        <f t="shared" si="28"/>
-        <v>56.94</v>
-      </c>
-      <c r="J125" s="4"/>
+        <f t="shared" ref="I125:I130" si="37">G125*(1+H125)</f>
+        <v>34.02</v>
+      </c>
+      <c r="J125" s="8"/>
       <c r="K125" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="K125:K130" si="38">J125*F125</f>
         <v>0</v>
       </c>
       <c r="L125" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M125" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="M125:M130" si="39">J125*I125</f>
         <v>0</v>
       </c>
       <c r="N125" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:14">
-      <c r="B126" s="12" t="s">
+      <c r="A126" s="12"/>
+      <c r="B126" s="19" t="s">
         <v>247</v>
       </c>
       <c r="C126" s="8" t="s">
@@ -11546,40 +11556,42 @@
       <c r="D126" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E126" s="12"/>
+      <c r="E126" s="14" t="s">
+        <v>201</v>
+      </c>
       <c r="F126" s="7">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G126" s="13">
-        <v>34</v>
-      </c>
-      <c r="H126" s="33">
-        <v>0.095</v>
+        <v>42.5</v>
+      </c>
+      <c r="H126" s="15">
+        <v>0.08</v>
       </c>
       <c r="I126" s="16">
-        <f t="shared" si="28"/>
-        <v>37.23</v>
-      </c>
-      <c r="J126" s="4"/>
+        <f t="shared" si="37"/>
+        <v>45.9</v>
+      </c>
+      <c r="J126" s="8"/>
       <c r="K126" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L126" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M126" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N126" s="18">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" s="3" customFormat="1" spans="1:14">
-      <c r="A127" s="26"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
+      <c r="A127" s="12"/>
       <c r="B127" s="19" t="s">
         <v>248</v>
       </c>
@@ -11589,162 +11601,185 @@
       <c r="D127" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E127" s="12"/>
-      <c r="F127" s="34">
-        <v>2.5</v>
-      </c>
-      <c r="G127" s="27">
-        <v>40.5</v>
-      </c>
-      <c r="H127" s="35">
-        <v>0.1</v>
+      <c r="E127" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F127" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="G127" s="13">
+        <v>47</v>
+      </c>
+      <c r="H127" s="15">
+        <v>0.08</v>
       </c>
       <c r="I127" s="16">
-        <f t="shared" si="28"/>
-        <v>44.55</v>
-      </c>
-      <c r="J127" s="8"/>
+        <f t="shared" si="37"/>
+        <v>50.76</v>
+      </c>
+      <c r="J127" s="4"/>
       <c r="K127" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L127" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M127" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N127" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:14">
-      <c r="B128" s="12"/>
-      <c r="C128" s="12"/>
-      <c r="D128" s="12"/>
+      <c r="B128" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>123</v>
+      </c>
       <c r="E128" s="12"/>
-      <c r="I128" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="J128" s="36"/>
-      <c r="K128" s="36"/>
+      <c r="F128" s="7">
+        <v>4</v>
+      </c>
+      <c r="G128" s="13">
+        <v>52</v>
+      </c>
+      <c r="H128" s="33">
+        <v>0.095</v>
+      </c>
+      <c r="I128" s="16">
+        <f t="shared" si="37"/>
+        <v>56.94</v>
+      </c>
+      <c r="J128" s="4"/>
+      <c r="K128" s="17">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="L128" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M128" s="36"/>
-      <c r="N128" s="36"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="16">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="N128" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="129" spans="1:14">
-      <c r="B129" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C129" s="10"/>
-      <c r="D129" s="10"/>
-      <c r="E129" s="10"/>
-      <c r="F129" s="11"/>
+      <c r="B129" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E129" s="12"/>
+      <c r="F129" s="7">
+        <v>3</v>
+      </c>
+      <c r="G129" s="13">
+        <v>34</v>
+      </c>
+      <c r="H129" s="33">
+        <v>0.095</v>
+      </c>
+      <c r="I129" s="16">
+        <f t="shared" si="37"/>
+        <v>37.23</v>
+      </c>
+      <c r="J129" s="4"/>
+      <c r="K129" s="17">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="L129" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M129" s="16">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N129" s="18">
-        <f t="shared" ref="N129:N139" si="31">M129+J129</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14">
-      <c r="A130" s="12"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" s="3" customFormat="1" spans="1:14">
+      <c r="A130" s="26"/>
       <c r="B130" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E130" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F130" s="7">
-        <v>4</v>
-      </c>
-      <c r="G130" s="13">
-        <v>58</v>
-      </c>
-      <c r="H130" s="15">
-        <v>0.08</v>
+        <v>123</v>
+      </c>
+      <c r="E130" s="12"/>
+      <c r="F130" s="34">
+        <v>2.5</v>
+      </c>
+      <c r="G130" s="27">
+        <v>40.5</v>
+      </c>
+      <c r="H130" s="35">
+        <v>0.1</v>
       </c>
       <c r="I130" s="16">
-        <f>G130*(1+H130)</f>
-        <v>62.64</v>
+        <f t="shared" si="37"/>
+        <v>44.55</v>
       </c>
       <c r="J130" s="8"/>
       <c r="K130" s="17">
-        <f>J130*F130</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L130" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M130" s="16">
-        <f>J130*I130</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N130" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
+      <c r="B131" s="12"/>
+      <c r="C131" s="12"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+      <c r="I131" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="J131" s="36"/>
+      <c r="K131" s="36"/>
+      <c r="L131" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:14">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E131" s="12"/>
-      <c r="F131" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="G131" s="13">
-        <v>75</v>
-      </c>
-      <c r="H131" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="I131" s="16">
-        <f>G131*(1+H131)</f>
-        <v>82.5</v>
-      </c>
-      <c r="J131" s="8"/>
-      <c r="K131" s="17">
-        <f>J131*F131</f>
-        <v>0</v>
-      </c>
-      <c r="L131" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M131" s="16">
-        <f>J131*I131</f>
-        <v>0</v>
-      </c>
-      <c r="N131" s="18">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
+      <c r="M131" s="36"/>
+      <c r="N131" s="36"/>
     </row>
     <row r="132" spans="1:14">
-      <c r="A132" s="12"/>
       <c r="B132" s="10" t="s">
         <v>252</v>
       </c>
@@ -11752,47 +11787,41 @@
       <c r="D132" s="10"/>
       <c r="E132" s="10"/>
       <c r="F132" s="11"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="15"/>
-      <c r="I132" s="16"/>
-      <c r="J132" s="8"/>
-      <c r="K132" s="17"/>
       <c r="L132" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M132" s="16"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="N132" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="N132:N142" si="40">M132+J132</f>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="12"/>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="19" t="s">
         <v>253</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E133" s="4">
-        <v>1000</v>
+        <v>143</v>
+      </c>
+      <c r="E133" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="F133" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G133" s="13">
-        <v>163.5</v>
+        <v>58</v>
       </c>
       <c r="H133" s="15">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I133" s="16">
         <f>G133*(1+H133)</f>
-        <v>181.485</v>
+        <v>62.64</v>
       </c>
       <c r="J133" s="8"/>
       <c r="K133" s="17">
@@ -11800,7 +11829,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M133" s="16">
@@ -11808,36 +11837,34 @@
         <v>0</v>
       </c>
       <c r="N133" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="12"/>
-      <c r="B134" s="4" t="s">
-        <v>255</v>
+      <c r="B134" s="12" t="s">
+        <v>254</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E134" s="4">
-        <v>1000</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E134" s="12"/>
       <c r="F134" s="7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G134" s="13">
-        <v>159.1</v>
+        <v>75</v>
       </c>
       <c r="H134" s="15">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I134" s="16">
         <f>G134*(1+H134)</f>
-        <v>176.601</v>
+        <v>82.5</v>
       </c>
       <c r="J134" s="8"/>
       <c r="K134" s="17">
@@ -11845,7 +11872,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M134" s="16">
@@ -11853,81 +11880,60 @@
         <v>0</v>
       </c>
       <c r="N134" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="12"/>
-      <c r="B135" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E135" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F135" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G135" s="13">
-        <v>124.7</v>
-      </c>
-      <c r="H135" s="15">
-        <v>0.11</v>
-      </c>
-      <c r="I135" s="16">
-        <f>G135*(1+H135)</f>
-        <v>138.417</v>
-      </c>
+      <c r="B135" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C135" s="10"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="15"/>
+      <c r="I135" s="16"/>
       <c r="J135" s="8"/>
-      <c r="K135" s="17">
-        <f>J135*F135</f>
-        <v>0</v>
-      </c>
+      <c r="K135" s="17"/>
       <c r="L135" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M135" s="16">
-        <f>J135*I135</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M135" s="16"/>
       <c r="N135" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="12"/>
-      <c r="B136" s="4" t="s">
-        <v>257</v>
+      <c r="B136" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E136" s="4">
         <v>1000</v>
       </c>
       <c r="F136" s="7">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G136" s="13">
-        <v>93.5</v>
+        <v>163.5</v>
       </c>
       <c r="H136" s="15">
         <v>0.11</v>
       </c>
       <c r="I136" s="16">
         <f>G136*(1+H136)</f>
-        <v>103.785</v>
+        <v>181.485</v>
       </c>
       <c r="J136" s="8"/>
       <c r="K136" s="17">
@@ -11935,7 +11941,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M136" s="16">
@@ -11943,62 +11949,81 @@
         <v>0</v>
       </c>
       <c r="N136" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="12"/>
-      <c r="B137" s="10" t="s">
+      <c r="B137" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C137" s="10"/>
-      <c r="D137" s="10"/>
-      <c r="E137" s="10"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="13"/>
-      <c r="H137" s="15"/>
-      <c r="I137" s="16"/>
+      <c r="C137" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E137" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F137" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="G137" s="13">
+        <v>159.1</v>
+      </c>
+      <c r="H137" s="15">
+        <v>0.11</v>
+      </c>
+      <c r="I137" s="16">
+        <f>G137*(1+H137)</f>
+        <v>176.601</v>
+      </c>
       <c r="J137" s="8"/>
-      <c r="K137" s="17"/>
+      <c r="K137" s="17">
+        <f>J137*F137</f>
+        <v>0</v>
+      </c>
       <c r="L137" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M137" s="16"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M137" s="16">
+        <f>J137*I137</f>
+        <v>0</v>
+      </c>
       <c r="N137" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:14">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="12"/>
+      <c r="B138" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B138" s="12" t="s">
-        <v>260</v>
-      </c>
       <c r="C138" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
+      </c>
+      <c r="E138" s="4">
+        <v>1000</v>
       </c>
       <c r="F138" s="7">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="G138" s="13">
-        <f t="shared" ref="G138:G145" si="32">I138/(1+H138)</f>
-        <v>123.893805309735</v>
+        <v>124.7</v>
       </c>
       <c r="H138" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I138" s="16">
-        <v>140</v>
+        <f>G138*(1+H138)</f>
+        <v>138.417</v>
       </c>
       <c r="J138" s="8"/>
       <c r="K138" s="17">
@@ -12006,7 +12031,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M138" s="16">
@@ -12014,38 +12039,36 @@
         <v>0</v>
       </c>
       <c r="N138" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:14">
-      <c r="A139" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B139" s="14" t="s">
-        <v>263</v>
+      <c r="A139" s="12"/>
+      <c r="B139" s="4" t="s">
+        <v>260</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>199</v>
+        <v>257</v>
+      </c>
+      <c r="E139" s="4">
+        <v>1000</v>
       </c>
       <c r="F139" s="7">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="G139" s="13">
-        <f t="shared" si="32"/>
-        <v>153.752212389381</v>
+        <v>93.5</v>
       </c>
       <c r="H139" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I139" s="16">
-        <v>173.74</v>
+        <f>G139*(1+H139)</f>
+        <v>103.785</v>
       </c>
       <c r="J139" s="8"/>
       <c r="K139" s="17">
@@ -12053,7 +12076,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M139" s="16">
@@ -12061,78 +12084,55 @@
         <v>0</v>
       </c>
       <c r="N139" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
+      <c r="A140" s="12"/>
+      <c r="B140" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="13"/>
+      <c r="H140" s="15"/>
+      <c r="I140" s="16"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="17"/>
+      <c r="L140" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:14">
-      <c r="A140" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B140" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E140" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F140" s="7">
-        <v>6</v>
-      </c>
-      <c r="G140" s="13">
-        <f t="shared" si="32"/>
-        <v>176.991150442478</v>
-      </c>
-      <c r="H140" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I140" s="16">
-        <v>200</v>
-      </c>
-      <c r="J140" s="8"/>
-      <c r="K140" s="17">
-        <f t="shared" ref="K140:K145" si="33">J140*F140</f>
-        <v>0</v>
-      </c>
-      <c r="L140" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M140" s="16">
-        <f t="shared" ref="M140:M145" si="34">J140*I140</f>
-        <v>0</v>
-      </c>
+      <c r="M140" s="16"/>
       <c r="N140" s="18">
-        <f t="shared" ref="N140:N145" si="35">M140+J140</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B141" s="14" t="s">
-        <v>266</v>
+        <v>262</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>119</v>
+        <v>265</v>
       </c>
       <c r="F141" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G141" s="13">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="G141:G148" si="41">I141/(1+H141)</f>
         <v>123.893805309735</v>
       </c>
       <c r="H141" s="15">
@@ -12143,1281 +12143,1314 @@
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="17">
-        <f t="shared" si="33"/>
+        <f>J141*F141</f>
         <v>0</v>
       </c>
       <c r="L141" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M141" s="16">
-        <f t="shared" si="34"/>
+        <f>J141*I141</f>
         <v>0</v>
       </c>
       <c r="N141" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="F142" s="7">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G142" s="13">
-        <f t="shared" si="32"/>
-        <v>230.088495575221</v>
+        <f t="shared" si="41"/>
+        <v>153.752212389381</v>
       </c>
       <c r="H142" s="15">
         <v>0.13</v>
       </c>
       <c r="I142" s="16">
-        <v>260</v>
+        <v>173.74</v>
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="17">
-        <f t="shared" si="33"/>
+        <f>J142*F142</f>
         <v>0</v>
       </c>
       <c r="L142" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M142" s="16">
-        <f t="shared" si="34"/>
+        <f>J142*I142</f>
         <v>0</v>
       </c>
       <c r="N142" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E143" s="14" t="s">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="F143" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G143" s="13">
-        <f t="shared" si="32"/>
-        <v>115.929203539823</v>
+        <f t="shared" si="41"/>
+        <v>176.991150442478</v>
       </c>
       <c r="H143" s="15">
         <v>0.13</v>
       </c>
       <c r="I143" s="16">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="K143:K148" si="42">J143*F143</f>
         <v>0</v>
       </c>
       <c r="L143" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M143" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="M143:M148" si="43">J143*I143</f>
         <v>0</v>
       </c>
       <c r="N143" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="N143:N148" si="44">M143+J143</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E144" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F144" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G144" s="13">
-        <f t="shared" si="32"/>
-        <v>88.495575221239</v>
+        <f t="shared" si="41"/>
+        <v>123.893805309735</v>
       </c>
       <c r="H144" s="15">
         <v>0.13</v>
       </c>
       <c r="I144" s="16">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J144" s="8"/>
       <c r="K144" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L144" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M144" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N144" s="18">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" s="3" customFormat="1" spans="1:15">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
       <c r="A145" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B145" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="B145" s="14" t="s">
         <v>271</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>272</v>
+        <v>101</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E145" s="14" t="s">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="F145" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G145" s="13">
-        <f>I145-1</f>
-        <v>107</v>
+        <f t="shared" si="41"/>
+        <v>230.088495575221</v>
       </c>
       <c r="H145" s="15">
         <v>0.13</v>
       </c>
       <c r="I145" s="16">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="J145" s="8"/>
       <c r="K145" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L145" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M145" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N145" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:15">
-      <c r="A146" s="14"/>
+      <c r="A146" s="14" t="s">
+        <v>262</v>
+      </c>
       <c r="B146" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E146" s="14" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="F146" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G146" s="13">
-        <f>I146/(1+H146)</f>
-        <v>129.203539823009</v>
+        <f t="shared" si="41"/>
+        <v>115.929203539823</v>
       </c>
       <c r="H146" s="15">
         <v>0.13</v>
       </c>
       <c r="I146" s="16">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="J146" s="8"/>
       <c r="K146" s="17">
-        <f t="shared" ref="K146:K149" si="36">J146*F146</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L146" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M146" s="16">
-        <f t="shared" ref="M146:M149" si="37">J146*I146</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N146" s="18">
-        <f t="shared" ref="N146:N149" si="38">M146+J146</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:15">
-      <c r="A147" s="12"/>
-      <c r="B147" s="12" t="s">
-        <v>275</v>
+      <c r="A147" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B147" s="14" t="s">
+        <v>273</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E147" s="14" t="s">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="F147" s="7">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G147" s="13">
-        <v>140</v>
+        <f t="shared" si="41"/>
+        <v>88.495575221239</v>
       </c>
       <c r="H147" s="15">
         <v>0.13</v>
       </c>
       <c r="I147" s="16">
-        <f>G147*(1+H147)</f>
-        <v>158.2</v>
+        <v>100</v>
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="17">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L147" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M147" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N147" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" s="3" customFormat="1" spans="1:15">
-      <c r="A148" s="26"/>
-      <c r="B148" s="12" t="s">
+      <c r="A148" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E148" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F148" s="7">
+        <v>6</v>
+      </c>
+      <c r="G148" s="13">
+        <f>I148-1</f>
+        <v>107</v>
+      </c>
+      <c r="H148" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I148" s="16">
+        <v>108</v>
+      </c>
+      <c r="J148" s="8"/>
+      <c r="K148" s="17">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L148" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M148" s="16">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N148" s="18">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149" s="14"/>
+      <c r="B149" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C148" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E148" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F148" s="34">
-        <v>7.5</v>
-      </c>
-      <c r="G148" s="13">
-        <f>I148/(1+H148)</f>
-        <v>103.371681415929</v>
-      </c>
-      <c r="H148" s="35">
-        <v>0.13</v>
-      </c>
-      <c r="I148" s="37">
-        <v>116.81</v>
-      </c>
-      <c r="J148" s="34"/>
-      <c r="K148" s="38">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="L148" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M148" s="37">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N148" s="18">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" s="3" customFormat="1" spans="1:15">
-      <c r="A149" s="26"/>
-      <c r="B149" s="12" t="s">
+      <c r="C149" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="C149" s="8" t="s">
-        <v>274</v>
-      </c>
       <c r="D149" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E149" s="14" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="F149" s="7">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="G149" s="13">
-        <f>I149-1</f>
-        <v>177.2</v>
+        <f>I149/(1+H149)</f>
+        <v>129.203539823009</v>
       </c>
       <c r="H149" s="15">
         <v>0.13</v>
       </c>
       <c r="I149" s="16">
-        <v>178.2</v>
+        <v>146</v>
       </c>
       <c r="J149" s="8"/>
-      <c r="K149" s="38">
-        <f t="shared" si="36"/>
+      <c r="K149" s="17">
+        <f t="shared" ref="K149:K152" si="45">J149*F149</f>
         <v>0</v>
       </c>
       <c r="L149" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M149" s="37">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M149" s="16">
+        <f t="shared" ref="M149:M152" si="46">J149*I149</f>
         <v>0</v>
       </c>
       <c r="N149" s="18">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" s="3" customFormat="1" ht="11" customHeight="1" spans="1:15">
-      <c r="A150" s="26"/>
-      <c r="B150" s="14" t="s">
+        <f t="shared" ref="N149:N152" si="47">M149+J149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
+      <c r="A150" s="12"/>
+      <c r="B150" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C150" s="12" t="s">
-        <v>279</v>
+      <c r="C150" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="F150" s="34">
-        <v>4.5</v>
+        <v>265</v>
+      </c>
+      <c r="F150" s="7">
+        <v>9.5</v>
       </c>
       <c r="G150" s="13">
-        <f>I150/(1+H150)</f>
-        <v>132.743362831858</v>
-      </c>
-      <c r="H150" s="35">
+        <v>140</v>
+      </c>
+      <c r="H150" s="15">
         <v>0.13</v>
       </c>
-      <c r="I150" s="37">
-        <v>150</v>
-      </c>
-      <c r="J150" s="34"/>
-      <c r="K150" s="38">
-        <f t="shared" ref="K150:K164" si="39">J150*F150</f>
+      <c r="I150" s="16">
+        <f>G150*(1+H150)</f>
+        <v>158.2</v>
+      </c>
+      <c r="J150" s="8"/>
+      <c r="K150" s="17">
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L150" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M150" s="37">
-        <f t="shared" ref="M150:M164" si="40">J150*I150</f>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M150" s="16">
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="N150" s="18">
-        <f t="shared" ref="N150:N169" si="41">M150+J150</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="3" customFormat="1" spans="1:15">
       <c r="A151" s="26"/>
-      <c r="B151" s="14" t="s">
+      <c r="B151" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D151" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="C151" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>267</v>
-      </c>
       <c r="E151" s="14" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="F151" s="34">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G151" s="13">
-        <v>145</v>
+        <f>I151/(1+H151)</f>
+        <v>103.371681415929</v>
       </c>
       <c r="H151" s="35">
         <v>0.13</v>
       </c>
-      <c r="I151" s="16">
-        <f>G151*(1+H151)</f>
-        <v>163.85</v>
+      <c r="I151" s="37">
+        <v>116.81</v>
       </c>
       <c r="J151" s="34"/>
       <c r="K151" s="38">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L151" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M151" s="37">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="N151" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" s="3" customFormat="1" spans="1:15">
       <c r="A152" s="26"/>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="12" t="s">
         <v>280</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="D152" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E152" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F152" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="G152" s="13">
+        <f>I152-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H152" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I152" s="16">
+        <v>178.2</v>
+      </c>
+      <c r="J152" s="8"/>
+      <c r="K152" s="38">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="L152" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M152" s="37">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="N152" s="18">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" s="3" customFormat="1" ht="11" customHeight="1" spans="1:15">
+      <c r="A153" s="26"/>
+      <c r="B153" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E153" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F153" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="G153" s="13">
+        <f>I153/(1+H153)</f>
+        <v>132.743362831858</v>
+      </c>
+      <c r="H153" s="35">
+        <v>0.13</v>
+      </c>
+      <c r="I153" s="37">
+        <v>150</v>
+      </c>
+      <c r="J153" s="34"/>
+      <c r="K153" s="38">
+        <f t="shared" ref="K153:K167" si="48">J153*F153</f>
+        <v>0</v>
+      </c>
+      <c r="L153" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M153" s="37">
+        <f t="shared" ref="M153:M167" si="49">J153*I153</f>
+        <v>0</v>
+      </c>
+      <c r="N153" s="18">
+        <f t="shared" ref="N153:N172" si="50">M153+J153</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" s="3" customFormat="1" spans="1:15">
+      <c r="A154" s="26"/>
+      <c r="B154" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="E152" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F152" s="34">
-        <v>4</v>
-      </c>
-      <c r="G152" s="13">
-        <v>101</v>
-      </c>
-      <c r="H152" s="35">
-        <v>0.13</v>
-      </c>
-      <c r="I152" s="16">
-        <f>G152*(1+H152)</f>
-        <v>114.13</v>
-      </c>
-      <c r="J152" s="34"/>
-      <c r="K152" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="L152" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M152" s="37">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="N152" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" s="3" customFormat="1" spans="1:15">
-      <c r="A153" s="26"/>
-      <c r="B153" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D153" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E153" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F153" s="34">
-        <v>4</v>
-      </c>
-      <c r="G153" s="27">
-        <v>115</v>
-      </c>
-      <c r="H153" s="35">
-        <v>0.08</v>
-      </c>
-      <c r="I153" s="16">
-        <f>G153*(1+H153)</f>
-        <v>124.2</v>
-      </c>
-      <c r="J153" s="8"/>
-      <c r="K153" s="17">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="L153" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M153" s="16">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="N153" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" s="3" customFormat="1" spans="1:15">
-      <c r="A154" s="14"/>
-      <c r="B154" s="14" t="s">
-        <v>266</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E154" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F154" s="7">
-        <v>4</v>
+      <c r="F154" s="34">
+        <v>6</v>
       </c>
       <c r="G154" s="13">
-        <f>I154/(1+H154)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H154" s="15">
+        <v>145</v>
+      </c>
+      <c r="H154" s="35">
         <v>0.13</v>
       </c>
       <c r="I154" s="16">
-        <v>140</v>
-      </c>
-      <c r="J154" s="8"/>
-      <c r="K154" s="17">
-        <f t="shared" si="39"/>
+        <f>G154*(1+H154)</f>
+        <v>163.85</v>
+      </c>
+      <c r="J154" s="34"/>
+      <c r="K154" s="38">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L154" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M154" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M154" s="37">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N154" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="O154" s="2"/>
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="155" s="3" customFormat="1" spans="1:15">
       <c r="A155" s="26"/>
-      <c r="B155" s="12" t="s">
-        <v>282</v>
+      <c r="B155" s="14" t="s">
+        <v>283</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>283</v>
+        <v>96</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="E155" s="14"/>
+        <v>270</v>
+      </c>
+      <c r="E155" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="F155" s="34">
-        <v>11</v>
-      </c>
-      <c r="G155" s="27">
-        <f>I155-1</f>
-        <v>177.5</v>
-      </c>
-      <c r="H155" s="35"/>
+        <v>4</v>
+      </c>
+      <c r="G155" s="13">
+        <v>101</v>
+      </c>
+      <c r="H155" s="35">
+        <v>0.13</v>
+      </c>
       <c r="I155" s="16">
-        <v>178.5</v>
-      </c>
-      <c r="J155" s="8"/>
-      <c r="K155" s="17">
-        <f t="shared" si="39"/>
+        <f>G155*(1+H155)</f>
+        <v>114.13</v>
+      </c>
+      <c r="J155" s="34"/>
+      <c r="K155" s="38">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L155" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M155" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M155" s="37">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N155" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" s="3" customFormat="1" spans="1:15">
       <c r="A156" s="26"/>
       <c r="B156" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>283</v>
+        <v>96</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="E156" s="14"/>
+        <v>268</v>
+      </c>
+      <c r="E156" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="F156" s="34">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G156" s="27">
-        <f>I156-1</f>
-        <v>127.5</v>
-      </c>
-      <c r="H156" s="35"/>
+        <v>115</v>
+      </c>
+      <c r="H156" s="35">
+        <v>0.08</v>
+      </c>
       <c r="I156" s="16">
-        <v>128.5</v>
+        <f>G156*(1+H156)</f>
+        <v>124.2</v>
       </c>
       <c r="J156" s="8"/>
       <c r="K156" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L156" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M156" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N156" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" s="3" customFormat="1" spans="1:15">
       <c r="A157" s="14"/>
       <c r="B157" s="14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>272</v>
+        <v>96</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F157" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G157" s="13">
         <f>I157/(1+H157)</f>
-        <v>176.991150442478</v>
+        <v>123.893805309735</v>
       </c>
       <c r="H157" s="15">
         <v>0.13</v>
       </c>
       <c r="I157" s="16">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L157" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M157" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N157" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="O157" s="2"/>
     </row>
     <row r="158" s="3" customFormat="1" spans="1:15">
-      <c r="A158" s="14"/>
-      <c r="B158" s="14" t="s">
-        <v>266</v>
+      <c r="A158" s="26"/>
+      <c r="B158" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="E158" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F158" s="7">
-        <v>4</v>
-      </c>
-      <c r="G158" s="13">
-        <f>I158/(1+H158)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H158" s="15">
-        <v>0.13</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="E158" s="14"/>
+      <c r="F158" s="34">
+        <v>11</v>
+      </c>
+      <c r="G158" s="27">
+        <f>I158-1</f>
+        <v>177.5</v>
+      </c>
+      <c r="H158" s="35"/>
       <c r="I158" s="16">
-        <v>140</v>
+        <v>178.5</v>
       </c>
       <c r="J158" s="8"/>
       <c r="K158" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L158" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M158" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N158" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" s="3" customFormat="1" ht="13" customHeight="1" spans="1:15">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" s="3" customFormat="1" spans="1:15">
       <c r="A159" s="26"/>
       <c r="B159" s="12" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E159" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F159" s="7">
-        <v>4</v>
-      </c>
-      <c r="G159" s="13">
-        <v>115</v>
-      </c>
-      <c r="H159" s="15">
-        <v>0.08</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="E159" s="14"/>
+      <c r="F159" s="34">
+        <v>8</v>
+      </c>
+      <c r="G159" s="27">
+        <f>I159-1</f>
+        <v>127.5</v>
+      </c>
+      <c r="H159" s="35"/>
       <c r="I159" s="16">
-        <f>G159*(1+H159)</f>
-        <v>124.2</v>
+        <v>128.5</v>
       </c>
       <c r="J159" s="8"/>
       <c r="K159" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L159" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M159" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N159" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" s="3" customFormat="1" spans="1:15">
-      <c r="A160" s="26"/>
-      <c r="B160" s="19" t="s">
-        <v>271</v>
+      <c r="A160" s="14"/>
+      <c r="B160" s="14" t="s">
+        <v>267</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E160" s="14" t="s">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="F160" s="7">
         <v>6</v>
       </c>
       <c r="G160" s="13">
-        <f>I160-1</f>
-        <v>107</v>
+        <f>I160/(1+H160)</f>
+        <v>176.991150442478</v>
       </c>
       <c r="H160" s="15">
         <v>0.13</v>
       </c>
       <c r="I160" s="16">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="J160" s="8"/>
       <c r="K160" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L160" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M160" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N160" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="161" s="3" customFormat="1" spans="1:14">
-      <c r="A161" s="26"/>
-      <c r="B161" s="12" t="s">
-        <v>276</v>
+      <c r="A161" s="14"/>
+      <c r="B161" s="14" t="s">
+        <v>269</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D161" s="13" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E161" s="14" t="s">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="F161" s="7">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G161" s="13">
-        <f>I161-1</f>
-        <v>134</v>
+        <f>I161/(1+H161)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H161" s="15">
         <v>0.13</v>
       </c>
-      <c r="I161" s="39">
-        <v>135</v>
-      </c>
-      <c r="J161" s="34"/>
-      <c r="K161" s="38">
-        <f t="shared" si="39"/>
+      <c r="I161" s="16">
+        <v>140</v>
+      </c>
+      <c r="J161" s="8"/>
+      <c r="K161" s="17">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L161" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M161" s="37">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M161" s="16">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N161" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" s="3" customFormat="1" spans="1:14">
-      <c r="A162" s="12"/>
-      <c r="B162" s="19" t="s">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" s="3" customFormat="1" ht="13" customHeight="1" spans="1:14">
+      <c r="A162" s="26"/>
+      <c r="B162" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C162" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="C162" s="8" t="s">
-        <v>101</v>
-      </c>
       <c r="D162" s="13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E162" s="14" t="s">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="F162" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G162" s="13">
-        <f>I162-1</f>
-        <v>150.2</v>
+        <v>115</v>
       </c>
       <c r="H162" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I162" s="16">
-        <v>151.2</v>
+        <f>G162*(1+H162)</f>
+        <v>124.2</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="17">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L162" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M162" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N162" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" s="3" customFormat="1" spans="1:14">
       <c r="A163" s="26"/>
-      <c r="B163" s="12" t="s">
-        <v>287</v>
+      <c r="B163" s="19" t="s">
+        <v>274</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="D163" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E163" s="14" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="F163" s="7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G163" s="13">
         <f>I163-1</f>
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H163" s="15">
         <v>0.13</v>
       </c>
       <c r="I163" s="16">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="J163" s="8"/>
-      <c r="K163" s="38">
-        <f t="shared" si="39"/>
+      <c r="K163" s="17">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L163" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M163" s="37">
-        <f t="shared" si="40"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M163" s="16">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N163" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" s="3" customFormat="1" spans="1:14">
       <c r="A164" s="26"/>
       <c r="B164" s="12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="D164" s="13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E164" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F164" s="7">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G164" s="13">
         <f>I164-1</f>
-        <v>177.2</v>
+        <v>134</v>
       </c>
       <c r="H164" s="15">
         <v>0.13</v>
       </c>
-      <c r="I164" s="16">
-        <v>178.2</v>
-      </c>
-      <c r="J164" s="8"/>
+      <c r="I164" s="39">
+        <v>135</v>
+      </c>
+      <c r="J164" s="34"/>
       <c r="K164" s="38">
-        <f t="shared" si="39"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L164" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M164" s="37">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N164" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="165" s="3" customFormat="1" spans="1:14">
-      <c r="A165" s="26"/>
-      <c r="B165" s="26"/>
-      <c r="C165" s="26"/>
-      <c r="D165" s="26"/>
-      <c r="E165" s="26"/>
-      <c r="F165" s="34"/>
-      <c r="G165" s="27"/>
-      <c r="H165" s="35"/>
-      <c r="I165" s="16"/>
+      <c r="A165" s="12"/>
+      <c r="B165" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D165" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E165" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F165" s="7">
+        <v>8</v>
+      </c>
+      <c r="G165" s="13">
+        <f>I165-1</f>
+        <v>150.2</v>
+      </c>
+      <c r="H165" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I165" s="16">
+        <v>151.2</v>
+      </c>
       <c r="J165" s="8"/>
-      <c r="K165" s="17"/>
+      <c r="K165" s="17">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="L165" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M165" s="16"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="16">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="N165" s="18">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="166" s="3" customFormat="1" spans="1:14">
       <c r="A166" s="26"/>
-      <c r="B166" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C166" s="10"/>
-      <c r="D166" s="10"/>
-      <c r="E166" s="10"/>
-      <c r="F166" s="11"/>
-      <c r="G166" s="27"/>
-      <c r="H166" s="35"/>
-      <c r="I166" s="16"/>
+      <c r="B166" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E166" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F166" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="G166" s="13">
+        <f>I166-1</f>
+        <v>134</v>
+      </c>
+      <c r="H166" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I166" s="16">
+        <v>135</v>
+      </c>
       <c r="J166" s="8"/>
-      <c r="K166" s="17"/>
+      <c r="K166" s="38">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="L166" s="17">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M166" s="16"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M166" s="37">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="N166" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14">
-      <c r="B167" s="40" t="s">
-        <v>289</v>
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" s="3" customFormat="1" spans="1:14">
+      <c r="A167" s="26"/>
+      <c r="B167" s="12" t="s">
+        <v>280</v>
       </c>
       <c r="C167" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D167" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E167" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F167" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="G167" s="13">
+        <f>I167-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H167" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I167" s="16">
+        <v>178.2</v>
+      </c>
+      <c r="J167" s="8"/>
+      <c r="K167" s="38">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="L167" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M167" s="37">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="N167" s="18">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" s="3" customFormat="1" spans="1:14">
+      <c r="A168" s="26"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="26"/>
+      <c r="D168" s="26"/>
+      <c r="E168" s="26"/>
+      <c r="F168" s="34"/>
+      <c r="G168" s="27"/>
+      <c r="H168" s="35"/>
+      <c r="I168" s="16"/>
+      <c r="J168" s="8"/>
+      <c r="K168" s="17"/>
+      <c r="L168" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M168" s="16"/>
+      <c r="N168" s="18">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" s="3" customFormat="1" spans="1:14">
+      <c r="A169" s="26"/>
+      <c r="B169" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="11"/>
+      <c r="G169" s="27"/>
+      <c r="H169" s="35"/>
+      <c r="I169" s="16"/>
+      <c r="J169" s="8"/>
+      <c r="K169" s="17"/>
+      <c r="L169" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M169" s="16"/>
+      <c r="N169" s="18">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14">
+      <c r="B170" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C170" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E167" s="41">
+      <c r="D170" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E170" s="41">
         <v>1000</v>
       </c>
-      <c r="F167" s="7">
+      <c r="F170" s="7">
         <v>8</v>
       </c>
-      <c r="G167" s="13">
+      <c r="G170" s="13">
         <v>90</v>
       </c>
-      <c r="H167" s="15">
+      <c r="H170" s="15">
         <v>0.08</v>
       </c>
-      <c r="I167" s="16">
-        <f>G167*(1+H167)</f>
+      <c r="I170" s="16">
+        <f>G170*(1+H170)</f>
         <v>97.2</v>
       </c>
-      <c r="J167" s="8"/>
-      <c r="K167" s="17">
-        <f>J167*F167</f>
-        <v>0</v>
-      </c>
-      <c r="L167" s="17">
-        <f>K167+J167/2</f>
-        <v>0</v>
-      </c>
-      <c r="M167" s="16">
-        <f>J167*I167</f>
-        <v>0</v>
-      </c>
-      <c r="N167" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14">
-      <c r="B168" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E168" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F168" s="7">
-        <v>8</v>
-      </c>
-      <c r="G168" s="13">
-        <v>92</v>
-      </c>
-      <c r="H168" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I168" s="16">
-        <f>G168*(1+H168)</f>
-        <v>99.36</v>
-      </c>
-      <c r="J168" s="8"/>
-      <c r="K168" s="17">
-        <f>J168*F168</f>
-        <v>0</v>
-      </c>
-      <c r="L168" s="17">
-        <f t="shared" ref="L168:L197" si="42">K168+J168/2</f>
-        <v>0</v>
-      </c>
-      <c r="M168" s="16">
-        <f>J168*I168</f>
-        <v>0</v>
-      </c>
-      <c r="N168" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14">
-      <c r="B169" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E169" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F169" s="7">
-        <v>7</v>
-      </c>
-      <c r="G169" s="13">
-        <v>87</v>
-      </c>
-      <c r="H169" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I169" s="16">
-        <f>G169*(1+H169)</f>
-        <v>93.96</v>
-      </c>
-      <c r="J169" s="8"/>
-      <c r="K169" s="17">
-        <f>J169*F169</f>
-        <v>0</v>
-      </c>
-      <c r="L169" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M169" s="16">
-        <f>J169*I169</f>
-        <v>0</v>
-      </c>
-      <c r="N169" s="18">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14">
-      <c r="B170" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C170" s="10"/>
-      <c r="D170" s="10"/>
-      <c r="E170" s="10"/>
-      <c r="F170" s="11"/>
-      <c r="G170" s="13"/>
-      <c r="H170" s="15"/>
-      <c r="I170" s="16"/>
       <c r="J170" s="8"/>
-      <c r="K170" s="17"/>
+      <c r="K170" s="17">
+        <f>J170*F170</f>
+        <v>0</v>
+      </c>
       <c r="L170" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M170" s="16"/>
-      <c r="N170" s="18"/>
+        <f>K170+J170/2</f>
+        <v>0</v>
+      </c>
+      <c r="M170" s="16">
+        <f>J170*I170</f>
+        <v>0</v>
+      </c>
+      <c r="N170" s="18">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="171" spans="1:14">
       <c r="B171" s="40" t="s">
         <v>293</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D171" s="13" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E171" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F171" s="7">
-        <v>4.65</v>
+        <v>8</v>
       </c>
       <c r="G171" s="13">
-        <v>61.5</v>
+        <v>92</v>
       </c>
       <c r="H171" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I171" s="16">
         <f>G171*(1+H171)</f>
-        <v>67.65</v>
+        <v>99.36</v>
       </c>
       <c r="J171" s="8"/>
       <c r="K171" s="17">
@@ -13425,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="L171:L200" si="51">K171+J171/2</f>
         <v>0</v>
       </c>
       <c r="M171" s="16">
@@ -13433,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="N171" s="18">
-        <f t="shared" ref="N171:N197" si="43">M171+J171</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
@@ -13442,26 +13475,26 @@
         <v>294</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E172" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F172" s="7">
-        <v>5.15</v>
+        <v>7</v>
       </c>
       <c r="G172" s="13">
-        <v>64.5</v>
+        <v>87</v>
       </c>
       <c r="H172" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I172" s="16">
         <f>G172*(1+H172)</f>
-        <v>70.95</v>
+        <v>93.96</v>
       </c>
       <c r="J172" s="8"/>
       <c r="K172" s="17">
@@ -13469,7 +13502,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M172" s="16">
@@ -13477,81 +13510,55 @@
         <v>0</v>
       </c>
       <c r="N172" s="18">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" s="3" customFormat="1" spans="1:14">
-      <c r="A173" s="26"/>
-      <c r="B173" s="36" t="s">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
+      <c r="B173" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C173" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D173" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="E173" s="41">
-        <v>300</v>
-      </c>
-      <c r="F173" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="G173" s="27">
-        <v>76.5</v>
-      </c>
-      <c r="H173" s="35">
-        <v>0.1</v>
-      </c>
-      <c r="I173" s="16">
-        <f>G173*(1+H173)</f>
-        <v>84.15</v>
-      </c>
+      <c r="C173" s="10"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="11"/>
+      <c r="G173" s="13"/>
+      <c r="H173" s="15"/>
+      <c r="I173" s="16"/>
       <c r="J173" s="8"/>
-      <c r="K173" s="17">
-        <f>J173*F173</f>
-        <v>0</v>
-      </c>
+      <c r="K173" s="17"/>
       <c r="L173" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M173" s="16">
-        <f>J173*I173</f>
-        <v>0</v>
-      </c>
-      <c r="N173" s="18">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" s="3" customFormat="1" spans="1:14">
-      <c r="A174" s="26"/>
-      <c r="B174" s="2" t="s">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M173" s="16"/>
+      <c r="N173" s="18"/>
+    </row>
+    <row r="174" spans="1:14">
+      <c r="B174" s="40" t="s">
         <v>296</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E174" s="41">
         <v>300</v>
       </c>
       <c r="F174" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="G174" s="27">
-        <v>94.5</v>
-      </c>
-      <c r="H174" s="35">
+        <v>4.65</v>
+      </c>
+      <c r="G174" s="13">
+        <v>61.5</v>
+      </c>
+      <c r="H174" s="15">
         <v>0.1</v>
       </c>
       <c r="I174" s="16">
         <f>G174*(1+H174)</f>
-        <v>103.95</v>
+        <v>67.65</v>
       </c>
       <c r="J174" s="8"/>
       <c r="K174" s="17">
@@ -13559,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M174" s="16">
@@ -13567,222 +13574,231 @@
         <v>0</v>
       </c>
       <c r="N174" s="18">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" s="3" customFormat="1" spans="1:14">
-      <c r="A175" s="26"/>
-      <c r="B175" s="27"/>
-      <c r="C175" s="27"/>
-      <c r="D175" s="27"/>
-      <c r="E175" s="27"/>
-      <c r="F175" s="27"/>
-      <c r="G175" s="27"/>
-      <c r="H175" s="35"/>
-      <c r="I175" s="16"/>
+        <f t="shared" ref="N174:N200" si="52">M174+J174</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="B175" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="E175" s="41">
+        <v>300</v>
+      </c>
+      <c r="F175" s="7">
+        <v>5.15</v>
+      </c>
+      <c r="G175" s="13">
+        <v>64.5</v>
+      </c>
+      <c r="H175" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I175" s="16">
+        <f>G175*(1+H175)</f>
+        <v>70.95</v>
+      </c>
       <c r="J175" s="8"/>
-      <c r="K175" s="17"/>
+      <c r="K175" s="17">
+        <f>J175*F175</f>
+        <v>0</v>
+      </c>
       <c r="L175" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M175" s="16"/>
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M175" s="16">
+        <f>J175*I175</f>
+        <v>0</v>
+      </c>
       <c r="N175" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" s="3" customFormat="1" spans="1:14">
       <c r="A176" s="26"/>
-      <c r="B176" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="C176" s="42"/>
-      <c r="D176" s="42"/>
-      <c r="E176" s="42"/>
-      <c r="F176" s="43"/>
-      <c r="G176" s="27"/>
-      <c r="H176" s="35"/>
-      <c r="I176" s="16"/>
+      <c r="B176" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="E176" s="41">
+        <v>300</v>
+      </c>
+      <c r="F176" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="G176" s="27">
+        <v>76.5</v>
+      </c>
+      <c r="H176" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="I176" s="16">
+        <f>G176*(1+H176)</f>
+        <v>84.15</v>
+      </c>
       <c r="J176" s="8"/>
-      <c r="K176" s="17"/>
+      <c r="K176" s="17">
+        <f>J176*F176</f>
+        <v>0</v>
+      </c>
       <c r="L176" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M176" s="16"/>
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M176" s="16">
+        <f>J176*I176</f>
+        <v>0</v>
+      </c>
       <c r="N176" s="18">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
-      <c r="B177" s="40" t="s">
-        <v>298</v>
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" s="3" customFormat="1" spans="1:14">
+      <c r="A177" s="26"/>
+      <c r="B177" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E177" s="41">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F177" s="7">
-        <v>5</v>
-      </c>
-      <c r="G177" s="13">
-        <v>67.5</v>
-      </c>
-      <c r="H177" s="15">
-        <v>0.08</v>
+        <v>4.7</v>
+      </c>
+      <c r="G177" s="27">
+        <v>94.5</v>
+      </c>
+      <c r="H177" s="35">
+        <v>0.1</v>
       </c>
       <c r="I177" s="16">
-        <f t="shared" ref="I177:I197" si="44">G177*(1+H177)</f>
-        <v>72.9</v>
+        <f>G177*(1+H177)</f>
+        <v>103.95</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="17">
-        <f t="shared" ref="K177:K197" si="45">J177*F177</f>
+        <f>J177*F177</f>
         <v>0</v>
       </c>
       <c r="L177" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M177" s="16">
-        <f t="shared" ref="M177:M197" si="46">J177*I177</f>
+        <f>J177*I177</f>
         <v>0</v>
       </c>
       <c r="N177" s="18">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14">
-      <c r="B178" s="40" t="s">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" s="3" customFormat="1" spans="1:14">
+      <c r="A178" s="26"/>
+      <c r="B178" s="27"/>
+      <c r="C178" s="27"/>
+      <c r="D178" s="27"/>
+      <c r="E178" s="27"/>
+      <c r="F178" s="27"/>
+      <c r="G178" s="27"/>
+      <c r="H178" s="35"/>
+      <c r="I178" s="16"/>
+      <c r="J178" s="8"/>
+      <c r="K178" s="17"/>
+      <c r="L178" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M178" s="16"/>
+      <c r="N178" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" s="3" customFormat="1" spans="1:14">
+      <c r="A179" s="26"/>
+      <c r="B179" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C178" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="E178" s="41">
-        <v>500</v>
-      </c>
-      <c r="F178" s="7">
-        <v>6.2</v>
-      </c>
-      <c r="G178" s="13">
-        <v>79</v>
-      </c>
-      <c r="H178" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I178" s="16">
-        <f t="shared" si="44"/>
-        <v>85.32</v>
-      </c>
-      <c r="J178" s="8"/>
-      <c r="K178" s="17">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L178" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M178" s="16">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="N178" s="18">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14">
-      <c r="B179" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D179" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="E179" s="41">
-        <v>500</v>
-      </c>
-      <c r="F179" s="7"/>
-      <c r="G179" s="13"/>
-      <c r="H179" s="15">
-        <v>0.08</v>
-      </c>
+      <c r="C179" s="42"/>
+      <c r="D179" s="42"/>
+      <c r="E179" s="42"/>
+      <c r="F179" s="43"/>
+      <c r="G179" s="27"/>
+      <c r="H179" s="35"/>
       <c r="I179" s="16"/>
       <c r="J179" s="8"/>
-      <c r="K179" s="17">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
+      <c r="K179" s="17"/>
       <c r="L179" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M179" s="16">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M179" s="16"/>
       <c r="N179" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="B180" s="40" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D180" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E180" s="41">
         <v>500</v>
       </c>
       <c r="F180" s="7">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G180" s="13">
-        <v>105</v>
+        <v>67.5</v>
       </c>
       <c r="H180" s="15">
         <v>0.08</v>
       </c>
       <c r="I180" s="16">
-        <f t="shared" si="44"/>
-        <v>113.4</v>
+        <f t="shared" ref="I180:I200" si="53">G180*(1+H180)</f>
+        <v>72.9</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="K180:K200" si="54">J180*F180</f>
         <v>0</v>
       </c>
       <c r="L180" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M180" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="M180:M200" si="55">J180*I180</f>
         <v>0</v>
       </c>
       <c r="N180" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
@@ -13794,39 +13810,39 @@
         <v>94</v>
       </c>
       <c r="D181" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E181" s="41">
         <v>500</v>
       </c>
       <c r="F181" s="7">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="G181" s="13">
-        <v>117.5</v>
+        <v>79</v>
       </c>
       <c r="H181" s="15">
         <v>0.08</v>
       </c>
       <c r="I181" s="16">
-        <f t="shared" si="44"/>
-        <v>126.9</v>
+        <f t="shared" si="53"/>
+        <v>85.32</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L181" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M181" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N181" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
@@ -13838,437 +13854,429 @@
         <v>94</v>
       </c>
       <c r="D182" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E182" s="41">
         <v>500</v>
       </c>
-      <c r="F182" s="7">
-        <v>8</v>
-      </c>
-      <c r="G182" s="13">
-        <v>122.5</v>
-      </c>
+      <c r="F182" s="7"/>
+      <c r="G182" s="13"/>
       <c r="H182" s="15">
         <v>0.08</v>
       </c>
-      <c r="I182" s="16">
-        <f t="shared" si="44"/>
-        <v>132.3</v>
-      </c>
+      <c r="I182" s="16"/>
       <c r="J182" s="8"/>
       <c r="K182" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L182" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M182" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N182" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:14">
-      <c r="B183" s="41" t="s">
+      <c r="B183" s="40" t="s">
         <v>305</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D183" s="41" t="s">
-        <v>306</v>
+      <c r="D183" s="13" t="s">
+        <v>302</v>
       </c>
       <c r="E183" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F183" s="7">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G183" s="13">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H183" s="15">
         <v>0.08</v>
       </c>
       <c r="I183" s="16">
-        <f t="shared" si="44"/>
-        <v>108</v>
+        <f t="shared" si="53"/>
+        <v>113.4</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L183" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M183" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N183" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:14">
-      <c r="B184" s="6" t="s">
-        <v>307</v>
+      <c r="B184" s="40" t="s">
+        <v>306</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D184" s="41" t="s">
-        <v>306</v>
+      <c r="D184" s="13" t="s">
+        <v>302</v>
       </c>
       <c r="E184" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F184" s="7">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G184" s="13">
-        <v>145</v>
+        <v>117.5</v>
       </c>
       <c r="H184" s="15">
         <v>0.08</v>
       </c>
       <c r="I184" s="16">
-        <f t="shared" si="44"/>
-        <v>156.6</v>
+        <f t="shared" si="53"/>
+        <v>126.9</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L184" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M184" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N184" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="B185" s="41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D185" s="41" t="s">
-        <v>306</v>
+      <c r="D185" s="13" t="s">
+        <v>302</v>
       </c>
       <c r="E185" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F185" s="7">
         <v>8</v>
       </c>
       <c r="G185" s="13">
-        <v>135</v>
+        <v>122.5</v>
       </c>
       <c r="H185" s="15">
         <v>0.08</v>
       </c>
       <c r="I185" s="16">
-        <f t="shared" si="44"/>
-        <v>145.8</v>
+        <f t="shared" si="53"/>
+        <v>132.3</v>
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L185" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M185" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N185" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:14">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6" t="s">
-        <v>309</v>
+      <c r="B186" s="41" t="s">
+        <v>308</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D186" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E186" s="41">
         <v>5000</v>
       </c>
       <c r="F186" s="7">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="G186" s="13">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="H186" s="15">
         <v>0.08</v>
       </c>
       <c r="I186" s="16">
-        <f t="shared" si="44"/>
-        <v>189</v>
+        <f t="shared" si="53"/>
+        <v>108</v>
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L186" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M186" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N186" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:14">
-      <c r="B187" s="41" t="s">
+      <c r="B187" s="6" t="s">
         <v>310</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D187" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E187" s="41">
         <v>5000</v>
       </c>
       <c r="F187" s="7">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="G187" s="13">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H187" s="15">
         <v>0.08</v>
       </c>
       <c r="I187" s="16">
-        <f t="shared" si="44"/>
-        <v>172.8</v>
+        <f t="shared" si="53"/>
+        <v>156.6</v>
       </c>
       <c r="J187" s="8"/>
       <c r="K187" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L187" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M187" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N187" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:14">
-      <c r="B188" s="44" t="s">
+      <c r="B188" s="41" t="s">
         <v>311</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D188" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E188" s="41">
         <v>5000</v>
       </c>
       <c r="F188" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G188" s="13">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="H188" s="15">
         <v>0.08</v>
       </c>
       <c r="I188" s="16">
-        <f t="shared" si="44"/>
-        <v>205.2</v>
+        <f t="shared" si="53"/>
+        <v>145.8</v>
       </c>
       <c r="J188" s="8"/>
       <c r="K188" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L188" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M188" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N188" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:14">
-      <c r="B189" s="41" t="s">
+      <c r="A189" s="6"/>
+      <c r="B189" s="6" t="s">
         <v>312</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D189" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E189" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F189" s="7">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="G189" s="13">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="H189" s="15">
         <v>0.08</v>
       </c>
       <c r="I189" s="16">
-        <f t="shared" si="44"/>
-        <v>58.32</v>
+        <f t="shared" si="53"/>
+        <v>189</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L189" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M189" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N189" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:14">
-      <c r="B190" s="40" t="s">
+      <c r="B190" s="41" t="s">
         <v>313</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D190" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E190" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F190" s="7">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="G190" s="13">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="H190" s="15">
         <v>0.08</v>
       </c>
       <c r="I190" s="16">
-        <f t="shared" si="44"/>
-        <v>62.64</v>
+        <f t="shared" si="53"/>
+        <v>172.8</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L190" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M190" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N190" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:14">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6" t="s">
+      <c r="B191" s="44" t="s">
         <v>314</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D191" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E191" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F191" s="7">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="G191" s="13">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="H191" s="15">
         <v>0.08</v>
       </c>
       <c r="I191" s="16">
-        <f t="shared" si="44"/>
-        <v>68.04</v>
+        <f t="shared" si="53"/>
+        <v>205.2</v>
       </c>
       <c r="J191" s="8"/>
       <c r="K191" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L191" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M191" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N191" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
@@ -14280,321 +14288,391 @@
         <v>94</v>
       </c>
       <c r="D192" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E192" s="41">
         <v>1000</v>
       </c>
-      <c r="F192" s="7"/>
-      <c r="G192" s="13"/>
-      <c r="H192" s="15"/>
-      <c r="I192" s="16"/>
+      <c r="F192" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G192" s="13">
+        <v>54</v>
+      </c>
+      <c r="H192" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I192" s="16">
+        <f t="shared" si="53"/>
+        <v>58.32</v>
+      </c>
       <c r="J192" s="8"/>
       <c r="K192" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L192" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M192" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N192" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:14">
-      <c r="B193" s="41" t="s">
+      <c r="B193" s="40" t="s">
         <v>316</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D193" s="41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E193" s="41">
         <v>1000</v>
       </c>
-      <c r="F193" s="7"/>
-      <c r="G193" s="13"/>
-      <c r="H193" s="15"/>
-      <c r="I193" s="16"/>
+      <c r="F193" s="7">
+        <v>4</v>
+      </c>
+      <c r="G193" s="13">
+        <v>58</v>
+      </c>
+      <c r="H193" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I193" s="16">
+        <f t="shared" si="53"/>
+        <v>62.64</v>
+      </c>
       <c r="J193" s="8"/>
       <c r="K193" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L193" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M193" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N193" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:14">
-      <c r="B194" s="40" t="s">
+      <c r="A194" s="6"/>
+      <c r="B194" s="6" t="s">
         <v>317</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="D194" s="13" t="s">
-        <v>319</v>
+        <v>94</v>
+      </c>
+      <c r="D194" s="41" t="s">
+        <v>309</v>
       </c>
       <c r="E194" s="41">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F194" s="7">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="G194" s="13">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="H194" s="15">
         <v>0.08</v>
       </c>
       <c r="I194" s="16">
-        <f t="shared" si="44"/>
-        <v>151.2</v>
+        <f t="shared" si="53"/>
+        <v>68.04</v>
       </c>
       <c r="J194" s="8"/>
       <c r="K194" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L194" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M194" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N194" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:14">
-      <c r="B195" s="40" t="s">
-        <v>317</v>
+      <c r="B195" s="41" t="s">
+        <v>318</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="D195" s="13" t="s">
-        <v>319</v>
+        <v>94</v>
+      </c>
+      <c r="D195" s="41" t="s">
+        <v>309</v>
       </c>
       <c r="E195" s="41">
-        <v>2000</v>
-      </c>
-      <c r="F195" s="7">
-        <v>5</v>
-      </c>
-      <c r="G195" s="13">
-        <v>140</v>
-      </c>
-      <c r="H195" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I195" s="16">
-        <f t="shared" si="44"/>
-        <v>151.2</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F195" s="7"/>
+      <c r="G195" s="13"/>
+      <c r="H195" s="15"/>
+      <c r="I195" s="16"/>
       <c r="J195" s="8"/>
       <c r="K195" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L195" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M195" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N195" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:14">
       <c r="B196" s="41" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D196" s="13" t="s">
-        <v>319</v>
+        <v>94</v>
+      </c>
+      <c r="D196" s="41" t="s">
+        <v>309</v>
       </c>
       <c r="E196" s="41">
         <v>1000</v>
       </c>
-      <c r="F196" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G196" s="13">
-        <v>70</v>
-      </c>
-      <c r="H196" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I196" s="16">
-        <f t="shared" si="44"/>
-        <v>75.6</v>
-      </c>
+      <c r="F196" s="7"/>
+      <c r="G196" s="13"/>
+      <c r="H196" s="15"/>
+      <c r="I196" s="16"/>
       <c r="J196" s="8"/>
       <c r="K196" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L196" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M196" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N196" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:14">
-      <c r="B197" s="41" t="s">
-        <v>280</v>
+      <c r="B197" s="40" t="s">
+        <v>320</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>96</v>
+        <v>321</v>
       </c>
       <c r="D197" s="13" t="s">
-        <v>267</v>
+        <v>322</v>
       </c>
       <c r="E197" s="41">
         <v>2000</v>
       </c>
       <c r="F197" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G197" s="13">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="H197" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I197" s="16">
-        <f t="shared" si="44"/>
-        <v>114.13</v>
+        <f t="shared" si="53"/>
+        <v>151.2</v>
       </c>
       <c r="J197" s="8"/>
       <c r="K197" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L197" s="17">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M197" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N197" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:14">
-      <c r="F198" s="7"/>
-      <c r="G198" s="13"/>
-      <c r="H198" s="15"/>
-      <c r="J198" s="7" t="s">
-        <v>321</v>
-      </c>
+      <c r="B198" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="E198" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F198" s="7">
+        <v>5</v>
+      </c>
+      <c r="G198" s="13">
+        <v>140</v>
+      </c>
+      <c r="H198" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I198" s="16">
+        <f t="shared" si="53"/>
+        <v>151.2</v>
+      </c>
+      <c r="J198" s="8"/>
       <c r="K198" s="17">
-        <f>SUM(J6:J196)</f>
-        <v>0</v>
-      </c>
-      <c r="L198" s="6" t="s">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L198" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M198" s="16">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N198" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14">
+      <c r="B199" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D199" s="13" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="199" spans="1:14">
-      <c r="A199" s="45"/>
-      <c r="B199" s="45"/>
-      <c r="C199" s="45"/>
-      <c r="D199" s="45"/>
-      <c r="E199" s="45"/>
-      <c r="F199" s="7"/>
-      <c r="G199" s="13"/>
-      <c r="H199" s="15"/>
-      <c r="I199" s="45"/>
-      <c r="J199" s="41" t="s">
-        <v>323</v>
-      </c>
-      <c r="K199" s="7">
-        <f>SUM(K6:K196)</f>
-        <v>0</v>
-      </c>
-      <c r="L199" s="6" t="s">
-        <v>324</v>
+      <c r="E199" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F199" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G199" s="13">
+        <v>70</v>
+      </c>
+      <c r="H199" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I199" s="16">
+        <f t="shared" si="53"/>
+        <v>75.6</v>
+      </c>
+      <c r="J199" s="8"/>
+      <c r="K199" s="17">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L199" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M199" s="16">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N199" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:14">
-      <c r="A200" s="45"/>
-      <c r="B200" s="45"/>
-      <c r="C200" s="45"/>
-      <c r="D200" s="45"/>
-      <c r="E200" s="45"/>
-      <c r="F200" s="45"/>
-      <c r="G200" s="13"/>
-      <c r="H200" s="15"/>
-      <c r="I200" s="45"/>
-      <c r="J200" s="41" t="s">
-        <v>325</v>
-      </c>
-      <c r="K200" s="4">
-        <f>SUM(L:L)</f>
-        <v>0</v>
-      </c>
-      <c r="L200" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="M200" s="41"/>
+      <c r="B200" s="41" t="s">
+        <v>283</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D200" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E200" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F200" s="7">
+        <v>4</v>
+      </c>
+      <c r="G200" s="13">
+        <v>101</v>
+      </c>
+      <c r="H200" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I200" s="16">
+        <f t="shared" si="53"/>
+        <v>114.13</v>
+      </c>
+      <c r="J200" s="8"/>
+      <c r="K200" s="17">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L200" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M200" s="16">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N200" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="201" spans="1:14">
-      <c r="A201" s="45"/>
-      <c r="B201" s="45"/>
-      <c r="C201" s="45"/>
-      <c r="D201" s="45"/>
-      <c r="E201" s="45"/>
-      <c r="F201" s="45"/>
+      <c r="F201" s="7"/>
       <c r="G201" s="13"/>
       <c r="H201" s="15"/>
-      <c r="I201" s="45"/>
-      <c r="J201" s="41" t="s">
-        <v>326</v>
-      </c>
-      <c r="K201" s="45">
-        <f>SUM(N5:N197)</f>
-        <v>0</v>
-      </c>
-      <c r="L201" s="45"/>
-      <c r="M201" s="41"/>
+      <c r="J201" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="K201" s="17">
+        <f>SUM(J6:J199)</f>
+        <v>0</v>
+      </c>
+      <c r="L201" s="6" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="45"/>
@@ -14602,14 +14680,20 @@
       <c r="C202" s="45"/>
       <c r="D202" s="45"/>
       <c r="E202" s="45"/>
-      <c r="F202" s="45"/>
+      <c r="F202" s="7"/>
       <c r="G202" s="13"/>
       <c r="H202" s="15"/>
       <c r="I202" s="45"/>
-      <c r="J202" s="45"/>
-      <c r="K202" s="45"/>
-      <c r="L202" s="45"/>
-      <c r="M202" s="41"/>
+      <c r="J202" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="K202" s="7">
+        <f>SUM(K6:K199)</f>
+        <v>0</v>
+      </c>
+      <c r="L202" s="6" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="45"/>
@@ -14621,9 +14705,16 @@
       <c r="G203" s="13"/>
       <c r="H203" s="15"/>
       <c r="I203" s="45"/>
-      <c r="J203" s="45"/>
-      <c r="K203" s="45"/>
-      <c r="L203" s="45"/>
+      <c r="J203" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="K203" s="4">
+        <f>SUM(L:L)</f>
+        <v>0.45</v>
+      </c>
+      <c r="L203" s="46" t="s">
+        <v>327</v>
+      </c>
       <c r="M203" s="41"/>
     </row>
     <row r="204" spans="1:14">
@@ -14633,11 +14724,16 @@
       <c r="D204" s="45"/>
       <c r="E204" s="45"/>
       <c r="F204" s="45"/>
-      <c r="G204" s="45"/>
+      <c r="G204" s="13"/>
       <c r="H204" s="15"/>
       <c r="I204" s="45"/>
-      <c r="J204" s="45"/>
-      <c r="K204" s="45"/>
+      <c r="J204" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="K204" s="45">
+        <f>SUM(N5:N200)</f>
+        <v>0</v>
+      </c>
       <c r="L204" s="45"/>
       <c r="M204" s="41"/>
     </row>
@@ -14648,7 +14744,7 @@
       <c r="D205" s="45"/>
       <c r="E205" s="45"/>
       <c r="F205" s="45"/>
-      <c r="G205" s="45"/>
+      <c r="G205" s="13"/>
       <c r="H205" s="15"/>
       <c r="I205" s="45"/>
       <c r="J205" s="45"/>
@@ -14663,14 +14759,12 @@
       <c r="D206" s="45"/>
       <c r="E206" s="45"/>
       <c r="F206" s="45"/>
-      <c r="G206" s="45"/>
+      <c r="G206" s="13"/>
       <c r="H206" s="15"/>
       <c r="I206" s="45"/>
       <c r="J206" s="45"/>
       <c r="K206" s="45"/>
-      <c r="L206" s="45" t="s">
-        <v>225</v>
-      </c>
+      <c r="L206" s="45"/>
       <c r="M206" s="41"/>
     </row>
     <row r="207" spans="1:14">
@@ -14681,7 +14775,7 @@
       <c r="E207" s="45"/>
       <c r="F207" s="45"/>
       <c r="G207" s="45"/>
-      <c r="H207" s="45"/>
+      <c r="H207" s="15"/>
       <c r="I207" s="45"/>
       <c r="J207" s="45"/>
       <c r="K207" s="45"/>
@@ -14696,7 +14790,7 @@
       <c r="E208" s="45"/>
       <c r="F208" s="45"/>
       <c r="G208" s="45"/>
-      <c r="H208" s="45"/>
+      <c r="H208" s="15"/>
       <c r="I208" s="45"/>
       <c r="J208" s="45"/>
       <c r="K208" s="45"/>
@@ -14711,11 +14805,13 @@
       <c r="E209" s="45"/>
       <c r="F209" s="45"/>
       <c r="G209" s="45"/>
-      <c r="H209" s="45"/>
+      <c r="H209" s="15"/>
       <c r="I209" s="45"/>
       <c r="J209" s="45"/>
       <c r="K209" s="45"/>
-      <c r="L209" s="45"/>
+      <c r="L209" s="45" t="s">
+        <v>228</v>
+      </c>
       <c r="M209" s="41"/>
     </row>
     <row r="210" spans="1:13">
@@ -14733,33 +14829,78 @@
       <c r="L210" s="45"/>
       <c r="M210" s="41"/>
     </row>
+    <row r="211" spans="1:13">
+      <c r="A211" s="45"/>
+      <c r="B211" s="45"/>
+      <c r="C211" s="45"/>
+      <c r="D211" s="45"/>
+      <c r="E211" s="45"/>
+      <c r="F211" s="45"/>
+      <c r="G211" s="45"/>
+      <c r="H211" s="45"/>
+      <c r="I211" s="45"/>
+      <c r="J211" s="45"/>
+      <c r="K211" s="45"/>
+      <c r="L211" s="45"/>
+      <c r="M211" s="41"/>
+    </row>
     <row r="212" spans="1:13">
-      <c r="B212" s="6"/>
-      <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
-      <c r="E212" s="6"/>
-    </row>
-    <row r="214" spans="1:13">
-      <c r="J214" s="6"/>
+      <c r="A212" s="45"/>
+      <c r="B212" s="45"/>
+      <c r="C212" s="45"/>
+      <c r="D212" s="45"/>
+      <c r="E212" s="45"/>
+      <c r="F212" s="45"/>
+      <c r="G212" s="45"/>
+      <c r="H212" s="45"/>
+      <c r="I212" s="45"/>
+      <c r="J212" s="45"/>
+      <c r="K212" s="45"/>
+      <c r="L212" s="45"/>
+      <c r="M212" s="41"/>
+    </row>
+    <row r="213" spans="1:13">
+      <c r="A213" s="45"/>
+      <c r="B213" s="45"/>
+      <c r="C213" s="45"/>
+      <c r="D213" s="45"/>
+      <c r="E213" s="45"/>
+      <c r="F213" s="45"/>
+      <c r="G213" s="45"/>
+      <c r="H213" s="45"/>
+      <c r="I213" s="45"/>
+      <c r="J213" s="45"/>
+      <c r="K213" s="45"/>
+      <c r="L213" s="45"/>
+      <c r="M213" s="41"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="K215" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13">
-      <c r="B216" s="6"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="6"/>
-    </row>
-    <row r="229" spans="5:5">
-      <c r="E229" s="2" t="s">
-        <v>225</v>
+      <c r="B215" s="6"/>
+      <c r="C215" s="6"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+    </row>
+    <row r="217" spans="1:13">
+      <c r="J217" s="6"/>
+    </row>
+    <row r="218" spans="1:13">
+      <c r="K218" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13">
+      <c r="B219" s="6"/>
+      <c r="C219" s="6"/>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
+    </row>
+    <row r="232" spans="5:5">
+      <c r="E232" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P201" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P204" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14778,7 +14919,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N197,工作表2!N6:N197&gt;0,"")</f>
+        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N200,工作表2!N6:N200&gt;0,"")</f>
         <v/>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="合同 " sheetId="1" r:id="rId1"/>
@@ -2718,7 +2718,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{0B789CF4-8B3E-4608-B422-5E76A67D6D76}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{B75626F1-A762-4DEA-A24B-C5A8C5C24DB7}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2727,7 +2727,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{52EDBF2D-7F1D-4CC5-BEF0-B31EA26AF391}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{85DE178B-79C5-4C58-A87E-8F4335D7B177}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -9466,7 +9466,7 @@
       <c r="J74" s="8"/>
       <c r="K74" s="17"/>
       <c r="L74" s="17">
-        <f t="shared" ref="L74:L86" si="18">K74+J74/2</f>
+        <f t="shared" ref="L74:L87" si="18">K74+J74/2</f>
         <v>0</v>
       </c>
       <c r="M74" s="16"/>
@@ -10043,10 +10043,22 @@
         <v>90</v>
       </c>
       <c r="J87" s="8"/>
-      <c r="K87" s="17"/>
-      <c r="L87" s="17"/>
-      <c r="M87" s="16"/>
-      <c r="N87" s="18"/>
+      <c r="K87" s="17">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="L87" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M87" s="16">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="N87" s="18">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="88" s="2" customFormat="1" spans="1:14">
       <c r="A88" s="12"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="合同 " sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet name="工作表3" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$207</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'合同 '!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">发票!$A$1:$E$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">装箱单!$A$1:$L$36</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="333">
   <si>
     <t>销 售 合 同
 SALES CONTRACT</t>
@@ -600,6 +600,15 @@
   </si>
   <si>
     <t>Mx500</t>
+  </si>
+  <si>
+    <t>圆1500</t>
+  </si>
+  <si>
+    <t>六角碗1000ml</t>
+  </si>
+  <si>
+    <t>750椭圆形</t>
   </si>
   <si>
     <t>圆1200</t>
@@ -2718,7 +2727,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{B75626F1-A762-4DEA-A24B-C5A8C5C24DB7}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{FD6121AB-B835-4EC6-A86B-A78C84A887FC}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2727,7 +2736,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{85DE178B-79C5-4C58-A87E-8F4335D7B177}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{2B8A42B1-4339-4762-BA4C-17189445C9A7}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -6397,7 +6406,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P232"/>
+  <dimension ref="A1:P235"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.4" style="2" customWidth="1"/>
@@ -6522,7 +6531,7 @@
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="17">
-        <f t="shared" ref="K6:K60" si="1">J6*F6</f>
+        <f t="shared" ref="K6:K63" si="1">J6*F6</f>
         <v>0</v>
       </c>
       <c r="L6" s="17">
@@ -6530,11 +6539,11 @@
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f t="shared" ref="M6:M60" si="3">J6*I6</f>
+        <f t="shared" ref="M6:M63" si="3">J6*I6</f>
         <v>0</v>
       </c>
       <c r="N6" s="18">
-        <f t="shared" ref="N6:N60" si="4">M6+J6</f>
+        <f t="shared" ref="N6:N63" si="4">M6+J6</f>
         <v>0</v>
       </c>
     </row>
@@ -8523,7 +8532,7 @@
         <v>11</v>
       </c>
       <c r="G51" s="13">
-        <f t="shared" ref="G51:G56" si="8">I51-1</f>
+        <f t="shared" ref="G51:G59" si="8">I51-1</f>
         <v>114</v>
       </c>
       <c r="H51" s="15">
@@ -8692,17 +8701,17 @@
       </c>
       <c r="E55" s="20"/>
       <c r="F55" s="7">
-        <v>10.6</v>
+        <v>13.5</v>
       </c>
       <c r="G55" s="13">
         <f t="shared" si="8"/>
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="H55" s="15">
         <v>0.06</v>
       </c>
       <c r="I55" s="16">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="17">
@@ -8731,21 +8740,21 @@
         <v>97</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E56" s="20"/>
       <c r="F56" s="7">
-        <v>6.25</v>
+        <v>13.5</v>
       </c>
       <c r="G56" s="13">
         <f t="shared" si="8"/>
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H56" s="15">
         <v>0.06</v>
       </c>
       <c r="I56" s="16">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="17">
@@ -8765,32 +8774,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1" spans="1:14">
+    <row r="57" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A57" s="12"/>
       <c r="B57" s="20" t="s">
         <v>179</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>127</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E57" s="20"/>
       <c r="F57" s="7">
-        <v>9</v>
+        <v>17.2</v>
       </c>
       <c r="G57" s="13">
-        <f>I57/(1+H57)</f>
-        <v>81.7256637168142</v>
+        <f t="shared" si="8"/>
+        <v>130</v>
       </c>
       <c r="H57" s="15">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I57" s="16">
-        <v>92.35</v>
+        <v>131</v>
       </c>
       <c r="J57" s="8"/>
       <c r="K57" s="17">
@@ -8810,32 +8817,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1" spans="1:14">
+    <row r="58" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A58" s="12"/>
       <c r="B58" s="20" t="s">
         <v>180</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>166</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E58" s="20"/>
       <c r="F58" s="7">
-        <v>8</v>
+        <v>10.6</v>
       </c>
       <c r="G58" s="13">
-        <f>I58/(1+H58)</f>
-        <v>77.2566371681416</v>
+        <f t="shared" si="8"/>
+        <v>144</v>
       </c>
       <c r="H58" s="15">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I58" s="16">
-        <v>87.3</v>
+        <v>145</v>
       </c>
       <c r="J58" s="8"/>
       <c r="K58" s="17">
@@ -8855,32 +8860,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="14.25" customHeight="1" spans="1:14">
+    <row r="59" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A59" s="12"/>
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="20" t="s">
         <v>181</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>166</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E59" s="20"/>
       <c r="F59" s="7">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="G59" s="13">
-        <f>I59/(1+H59)</f>
-        <v>69.3362831858407</v>
+        <f t="shared" si="8"/>
+        <v>84</v>
       </c>
       <c r="H59" s="15">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I59" s="16">
-        <v>78.35</v>
+        <v>85</v>
       </c>
       <c r="J59" s="8"/>
       <c r="K59" s="17">
@@ -8912,22 +8915,22 @@
         <v>136</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F60" s="7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="G60" s="13">
-        <v>94.09</v>
+        <f>I60/(1+H60)</f>
+        <v>81.7256637168142</v>
       </c>
       <c r="H60" s="15">
         <v>0.13</v>
       </c>
-      <c r="I60" s="23">
-        <f>G60+1</f>
-        <v>95.09</v>
-      </c>
-      <c r="J60" s="24"/>
+      <c r="I60" s="16">
+        <v>92.35</v>
+      </c>
+      <c r="J60" s="8"/>
       <c r="K60" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -8945,213 +8948,214 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" ht="14.25" customHeight="1" spans="1:14">
       <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="23" t="s">
+      <c r="B61" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
+      <c r="C61" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F61" s="7">
+        <v>8</v>
+      </c>
+      <c r="G61" s="13">
+        <f>I61/(1+H61)</f>
+        <v>77.2566371681416</v>
+      </c>
+      <c r="H61" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I61" s="16">
+        <v>87.3</v>
+      </c>
+      <c r="J61" s="8"/>
+      <c r="K61" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L61" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="M61" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" customHeight="1" spans="1:14">
       <c r="A62" s="12"/>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
+      <c r="C62" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" s="7">
+        <v>8</v>
+      </c>
+      <c r="G62" s="13">
+        <f>I62/(1+H62)</f>
+        <v>69.3362831858407</v>
+      </c>
+      <c r="H62" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I62" s="16">
+        <v>78.35</v>
+      </c>
+      <c r="J62" s="8"/>
+      <c r="K62" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L62" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M62" s="15"/>
-      <c r="N62" s="15"/>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="M62" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25" customHeight="1" spans="1:14">
       <c r="A63" s="12"/>
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" s="7">
+        <v>8.4</v>
+      </c>
+      <c r="G63" s="13">
+        <v>94.09</v>
+      </c>
+      <c r="H63" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I63" s="23">
+        <f>G63+1</f>
+        <v>95.09</v>
+      </c>
+      <c r="J63" s="24"/>
+      <c r="K63" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L63" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N63" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M64" s="24"/>
+      <c r="N64" s="24"/>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="12"/>
+      <c r="B65" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="12"/>
+      <c r="B66" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E63" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="F63" s="7">
+      <c r="D66" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F66" s="7">
         <v>8.5</v>
       </c>
-      <c r="G63" s="13">
+      <c r="G66" s="13">
         <f>9823.01/60</f>
         <v>163.716833333333</v>
       </c>
-      <c r="H63" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I63" s="16">
-        <f>G63*(1+H63)</f>
-        <v>185.000021666667</v>
-      </c>
-      <c r="J63" s="8"/>
-      <c r="K63" s="17">
-        <f t="shared" ref="K63:K67" si="9">J63*F63</f>
-        <v>0</v>
-      </c>
-      <c r="L63" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M63" s="16">
-        <f t="shared" ref="M63:M67" si="10">J63*I63</f>
-        <v>0</v>
-      </c>
-      <c r="N63" s="18">
-        <f t="shared" ref="N63:N67" si="11">M63+J63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="12"/>
-      <c r="B64" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E64" s="26">
-        <v>1000</v>
-      </c>
-      <c r="F64" s="7">
-        <v>18.2</v>
-      </c>
-      <c r="G64" s="13">
-        <f t="shared" ref="G64:G67" si="12">I64/(1+H64)</f>
-        <v>336.283185840708</v>
-      </c>
-      <c r="H64" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I64" s="16">
-        <v>380</v>
-      </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="17">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M64" s="16">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N64" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
-      <c r="A65" s="12"/>
-      <c r="B65" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E65" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F65" s="7">
-        <v>9.25</v>
-      </c>
-      <c r="G65" s="13">
-        <f t="shared" si="12"/>
-        <v>141.592920353982</v>
-      </c>
-      <c r="H65" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I65" s="13">
-        <v>160</v>
-      </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="17">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L65" s="17">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="16">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N65" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O65" s="13"/>
-    </row>
-    <row r="66" spans="1:15">
-      <c r="A66" s="12"/>
-      <c r="B66" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E66" s="26"/>
-      <c r="F66" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="G66" s="13">
-        <f t="shared" si="12"/>
-        <v>176.991150442478</v>
-      </c>
       <c r="H66" s="15">
         <v>0.13</v>
       </c>
-      <c r="I66" s="13">
-        <v>200</v>
+      <c r="I66" s="16">
+        <f>G66*(1+H66)</f>
+        <v>185.000021666667</v>
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="K66:K70" si="9">J66*F66</f>
         <v>0</v>
       </c>
       <c r="L66" s="17">
@@ -9159,39 +9163,40 @@
         <v>0</v>
       </c>
       <c r="M66" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="M66:M70" si="10">J66*I66</f>
         <v>0</v>
       </c>
       <c r="N66" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O66" s="13"/>
+        <f t="shared" ref="N66:N70" si="11">M66+J66</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="12"/>
       <c r="B67" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="26"/>
+        <v>189</v>
+      </c>
+      <c r="E67" s="26">
+        <v>1000</v>
+      </c>
       <c r="F67" s="7">
-        <v>12.15</v>
+        <v>18.2</v>
       </c>
       <c r="G67" s="13">
-        <f t="shared" si="12"/>
-        <v>233.628318584071</v>
+        <f t="shared" ref="G67:G70" si="12">I67/(1+H67)</f>
+        <v>336.283185840708</v>
       </c>
       <c r="H67" s="15">
         <v>0.13</v>
       </c>
-      <c r="I67" s="13">
-        <v>264</v>
+      <c r="I67" s="16">
+        <v>380</v>
       </c>
       <c r="J67" s="8"/>
       <c r="K67" s="17">
@@ -9199,8 +9204,8 @@
         <v>0</v>
       </c>
       <c r="L67" s="17">
-        <f>K67+J67/2+0.3</f>
-        <v>0.3</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="M67" s="16">
         <f t="shared" si="10"/>
@@ -9210,201 +9215,201 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O67" s="13"/>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="12"/>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E68" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="15"/>
+      <c r="F68" s="7">
+        <v>9.25</v>
+      </c>
+      <c r="G68" s="13">
+        <f t="shared" si="12"/>
+        <v>141.592920353982</v>
+      </c>
+      <c r="H68" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I68" s="13">
+        <v>160</v>
+      </c>
+      <c r="J68" s="8"/>
+      <c r="K68" s="17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="L68" s="17">
-        <f>K68+J68/2</f>
-        <v>0</v>
-      </c>
-      <c r="M68" s="2"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="13"/>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="12"/>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="27" t="s">
         <v>194</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E69" s="26" t="s">
-        <v>187</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="E69" s="26"/>
       <c r="F69" s="7">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="G69" s="13">
-        <f>5575.22/60</f>
-        <v>92.9203333333333</v>
+        <f t="shared" si="12"/>
+        <v>176.991150442478</v>
       </c>
       <c r="H69" s="15">
         <v>0.13</v>
       </c>
-      <c r="I69" s="16">
-        <f>G69*(1+H69)</f>
-        <v>104.999976666667</v>
+      <c r="I69" s="13">
+        <v>200</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="17">
-        <f t="shared" ref="K69:K73" si="13">J69*F69</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L69" s="17">
-        <f>K69+J69/2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M69" s="16">
-        <f t="shared" ref="M69:M73" si="14">J69*I69</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N69" s="18">
-        <f t="shared" ref="N69:N73" si="15">M69+J69</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="13"/>
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="12"/>
       <c r="B70" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E70" s="26">
-        <v>1000</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="E70" s="26"/>
       <c r="F70" s="7">
-        <v>7</v>
+        <v>12.15</v>
       </c>
       <c r="G70" s="13">
-        <f t="shared" ref="G70:G73" si="16">I70/(1+H70)</f>
-        <v>230.088495575221</v>
+        <f t="shared" si="12"/>
+        <v>233.628318584071</v>
       </c>
       <c r="H70" s="15">
         <v>0.13</v>
       </c>
-      <c r="I70" s="16">
-        <v>260</v>
+      <c r="I70" s="13">
+        <v>264</v>
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L70" s="17">
-        <f>K70+J70/2</f>
-        <v>0</v>
+        <f>K70+J70/2+0.3</f>
+        <v>0.3</v>
       </c>
       <c r="M70" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N70" s="18">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O70" s="13"/>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="12"/>
-      <c r="B71" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E71" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F71" s="7">
-        <v>9.25</v>
-      </c>
-      <c r="G71" s="13">
-        <f t="shared" si="16"/>
-        <v>141.592920353982</v>
-      </c>
-      <c r="H71" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I71" s="16">
-        <v>160</v>
-      </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="17">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+      <c r="B71" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="15"/>
       <c r="L71" s="17">
-        <f t="shared" ref="L71:L73" si="17">K71+J71/2</f>
-        <v>0</v>
-      </c>
-      <c r="M71" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="18">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
+        <f>K71+J71/2</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="2"/>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="12"/>
-      <c r="B72" s="27" t="s">
-        <v>198</v>
+      <c r="B72" s="25" t="s">
+        <v>197</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>95</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E72" s="26"/>
+        <v>198</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>190</v>
+      </c>
       <c r="F72" s="7">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="G72" s="13">
-        <f t="shared" si="16"/>
-        <v>141.592920353982</v>
+        <f>5575.22/60</f>
+        <v>92.9203333333333</v>
       </c>
       <c r="H72" s="15">
         <v>0.13</v>
       </c>
       <c r="I72" s="16">
-        <v>160</v>
+        <f>G72*(1+H72)</f>
+        <v>104.999976666667</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="K72:K76" si="13">J72*F72</f>
         <v>0</v>
       </c>
       <c r="L72" s="17">
-        <f t="shared" si="17"/>
+        <f>K72+J72/2</f>
         <v>0</v>
       </c>
       <c r="M72" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="M72:M76" si="14">J72*I72</f>
         <v>0</v>
       </c>
       <c r="N72" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="N72:N76" si="15">M72+J72</f>
         <v>0</v>
       </c>
     </row>
@@ -9417,21 +9422,23 @@
         <v>95</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E73" s="26"/>
+        <v>198</v>
+      </c>
+      <c r="E73" s="26">
+        <v>1000</v>
+      </c>
       <c r="F73" s="7">
-        <v>8.55</v>
+        <v>7</v>
       </c>
       <c r="G73" s="13">
-        <f t="shared" si="16"/>
-        <v>224.778761061947</v>
+        <f t="shared" ref="G73:G76" si="16">I73/(1+H73)</f>
+        <v>230.088495575221</v>
       </c>
       <c r="H73" s="15">
         <v>0.13</v>
       </c>
       <c r="I73" s="16">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="17">
@@ -9439,8 +9446,8 @@
         <v>0</v>
       </c>
       <c r="L73" s="17">
-        <f>K73+J73+0.15</f>
-        <v>0.15</v>
+        <f>K73+J73/2</f>
+        <v>0</v>
       </c>
       <c r="M73" s="16">
         <f t="shared" si="14"/>
@@ -9453,167 +9460,163 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="12"/>
-      <c r="B74" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="16"/>
+      <c r="B74" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="F74" s="7">
+        <v>9.25</v>
+      </c>
+      <c r="G74" s="13">
+        <f t="shared" si="16"/>
+        <v>141.592920353982</v>
+      </c>
+      <c r="H74" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I74" s="16">
+        <v>160</v>
+      </c>
       <c r="J74" s="8"/>
-      <c r="K74" s="17"/>
+      <c r="K74" s="17">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="L74" s="17">
-        <f t="shared" ref="L74:L87" si="18">K74+J74/2</f>
-        <v>0</v>
-      </c>
-      <c r="M74" s="16"/>
+        <f t="shared" ref="L74:L76" si="17">K74+J74/2</f>
+        <v>0</v>
+      </c>
+      <c r="M74" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="N74" s="18">
-        <f t="shared" ref="N74:N97" si="19">M74+J74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:15">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="12"/>
-      <c r="B75" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>91</v>
+      <c r="B75" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>201</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="E75" s="26"/>
       <c r="F75" s="7">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="G75" s="13">
-        <v>68</v>
+        <f t="shared" si="16"/>
+        <v>141.592920353982</v>
       </c>
       <c r="H75" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" ref="I75:I82" si="20">G75*(1+H75)</f>
-        <v>73.44</v>
+        <v>160</v>
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="17">
-        <f t="shared" ref="K75:K97" si="21">J75*F75</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L75" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" ref="M75:M97" si="22">J75*I75</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N75" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="12"/>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>91</v>
+      <c r="C76" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E76" s="14" t="s">
-        <v>201</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="E76" s="26"/>
       <c r="F76" s="7">
-        <v>7.5</v>
+        <v>8.55</v>
       </c>
       <c r="G76" s="13">
-        <v>74</v>
+        <f t="shared" si="16"/>
+        <v>224.778761061947</v>
       </c>
       <c r="H76" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I76" s="16">
-        <f t="shared" si="20"/>
-        <v>79.92</v>
+        <v>254</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L76" s="17">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>K76+J76+0.15</f>
+        <v>0.15</v>
       </c>
       <c r="M76" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N76" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="12"/>
-      <c r="B77" s="19" t="s">
+      <c r="B77" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17">
+        <f t="shared" ref="L77:L90" si="18">K77+J77/2</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="16"/>
+      <c r="N77" s="18">
+        <f t="shared" ref="N77:N100" si="19">M77+J77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" spans="1:15">
+      <c r="A78" s="12"/>
+      <c r="B78" s="19" t="s">
         <v>203</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F77" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="G77" s="13">
-        <v>82</v>
-      </c>
-      <c r="H77" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I77" s="16">
-        <f t="shared" si="20"/>
-        <v>88.56</v>
-      </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="17">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="16">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="18">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12" t="s">
-        <v>204</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>91</v>
@@ -9622,24 +9625,24 @@
         <v>136</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F78" s="7">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="G78" s="13">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="H78" s="15">
         <v>0.08</v>
       </c>
       <c r="I78" s="16">
-        <f t="shared" si="20"/>
-        <v>97.2</v>
+        <f t="shared" ref="I78:I85" si="20">G78*(1+H78)</f>
+        <v>73.44</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="K78:K100" si="21">J78*F78</f>
         <v>0</v>
       </c>
       <c r="L78" s="17">
@@ -9647,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="M78:M100" si="22">J78*I78</f>
         <v>0</v>
       </c>
       <c r="N78" s="18">
@@ -9667,20 +9670,20 @@
         <v>136</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="F79" s="7">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G79" s="13">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H79" s="15">
         <v>0.08</v>
       </c>
       <c r="I79" s="16">
         <f t="shared" si="20"/>
-        <v>65.88</v>
+        <v>79.92</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="17">
@@ -9702,7 +9705,7 @@
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="12"/>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="19" t="s">
         <v>206</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -9712,20 +9715,20 @@
         <v>136</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="F80" s="7">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G80" s="13">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H80" s="15">
         <v>0.08</v>
       </c>
       <c r="I80" s="16">
         <f t="shared" si="20"/>
-        <v>63.72</v>
+        <v>88.56</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="17">
@@ -9747,7 +9750,7 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="12"/>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="12" t="s">
         <v>207</v>
       </c>
       <c r="C81" s="8" t="s">
@@ -9757,20 +9760,20 @@
         <v>136</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="F81" s="7">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="G81" s="13">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H81" s="15">
         <v>0.08</v>
       </c>
       <c r="I81" s="16">
         <f t="shared" si="20"/>
-        <v>65.88</v>
+        <v>97.2</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="17">
@@ -9792,8 +9795,8 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="12"/>
-      <c r="B82" s="19">
-        <v>6828</v>
+      <c r="B82" s="19" t="s">
+        <v>208</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>91</v>
@@ -9808,14 +9811,14 @@
         <v>5.5</v>
       </c>
       <c r="G82" s="13">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H82" s="15">
         <v>0.08</v>
       </c>
       <c r="I82" s="16">
         <f t="shared" si="20"/>
-        <v>63.72</v>
+        <v>65.88</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="17">
@@ -9835,32 +9838,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" s="2" customFormat="1" spans="1:14">
+    <row r="83" spans="1:14">
       <c r="A83" s="12"/>
-      <c r="B83" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C83" s="29" t="s">
+      <c r="B83" s="12" t="s">
         <v>209</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E83" s="30" t="s">
-        <v>129</v>
+      <c r="E83" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="F83" s="7">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="G83" s="13">
-        <f t="shared" ref="G83:G87" si="23">I83-1</f>
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H83" s="15">
         <v>0.08</v>
       </c>
-      <c r="I83" s="13">
-        <v>90</v>
+      <c r="I83" s="16">
+        <f t="shared" si="20"/>
+        <v>63.72</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="17">
@@ -9880,32 +9883,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" s="2" customFormat="1" spans="1:14">
+    <row r="84" spans="1:14">
       <c r="A84" s="12"/>
-      <c r="B84" s="29" t="s">
+      <c r="B84" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="29" t="s">
-        <v>209</v>
+      <c r="C84" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E84" s="14" t="s">
         <v>127</v>
       </c>
       <c r="F84" s="7">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="G84" s="13">
-        <f t="shared" si="23"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H84" s="15">
         <v>0.08</v>
       </c>
-      <c r="I84" s="13">
-        <v>70</v>
+      <c r="I84" s="16">
+        <f t="shared" si="20"/>
+        <v>65.88</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="17">
@@ -9925,32 +9928,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" s="2" customFormat="1" spans="1:14">
+    <row r="85" spans="1:14">
       <c r="A85" s="12"/>
-      <c r="B85" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="C85" s="29" t="s">
-        <v>209</v>
+      <c r="B85" s="19">
+        <v>6828</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E85" s="30" t="s">
-        <v>166</v>
+      <c r="E85" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="F85" s="7">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="G85" s="13">
-        <f t="shared" si="23"/>
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="H85" s="15">
         <v>0.08</v>
       </c>
-      <c r="I85" s="13">
-        <v>92</v>
+      <c r="I85" s="16">
+        <f t="shared" si="20"/>
+        <v>63.72</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="17">
@@ -9973,29 +9976,29 @@
     <row r="86" s="2" customFormat="1" spans="1:14">
       <c r="A86" s="12"/>
       <c r="B86" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C86" s="29" t="s">
         <v>212</v>
-      </c>
-      <c r="C86" s="29" t="s">
-        <v>209</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="F86" s="7">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="G86" s="13">
-        <f t="shared" si="23"/>
-        <v>76</v>
+        <f t="shared" ref="G86:G90" si="23">I86-1</f>
+        <v>89</v>
       </c>
       <c r="H86" s="15">
         <v>0.08</v>
       </c>
       <c r="I86" s="13">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="17">
@@ -10021,26 +10024,26 @@
         <v>213</v>
       </c>
       <c r="C87" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F87" s="7">
-        <v>11.4</v>
+        <v>6.3</v>
       </c>
       <c r="G87" s="13">
         <f t="shared" si="23"/>
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H87" s="15">
         <v>0.08</v>
       </c>
       <c r="I87" s="13">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="17">
@@ -10066,97 +10069,97 @@
         <v>214</v>
       </c>
       <c r="C88" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F88" s="7">
-        <v>10.2</v>
+        <v>8.4</v>
       </c>
       <c r="G88" s="13">
-        <f t="shared" ref="G88:G93" si="24">I88-1</f>
-        <v>113</v>
+        <f t="shared" si="23"/>
+        <v>91</v>
       </c>
       <c r="H88" s="15">
         <v>0.08</v>
       </c>
       <c r="I88" s="13">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="17">
-        <f t="shared" ref="K88:K101" si="25">J88*F88</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L88" s="17">
-        <f t="shared" ref="L88:L101" si="26">K88+J88/2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M88" s="16">
-        <f t="shared" ref="M88:M101" si="27">J88*I88</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N88" s="18">
-        <f t="shared" ref="N88:N101" si="28">M88+J88</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" spans="1:14">
       <c r="A89" s="12"/>
-      <c r="B89" s="31" t="s">
+      <c r="B89" s="29" t="s">
         <v>215</v>
       </c>
       <c r="C89" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E89" s="30" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="F89" s="7">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="G89" s="13">
-        <f t="shared" si="24"/>
-        <v>73</v>
+        <f t="shared" si="23"/>
+        <v>76</v>
       </c>
       <c r="H89" s="15">
         <v>0.08</v>
       </c>
       <c r="I89" s="13">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L89" s="17">
-        <f t="shared" si="26"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M89" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N89" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" spans="1:14">
       <c r="A90" s="12"/>
       <c r="B90" s="29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C90" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>136</v>
@@ -10165,43 +10168,43 @@
         <v>129</v>
       </c>
       <c r="F90" s="7">
-        <v>6.9</v>
+        <v>11.4</v>
       </c>
       <c r="G90" s="13">
-        <f t="shared" si="24"/>
-        <v>73.7</v>
+        <f t="shared" si="23"/>
+        <v>89</v>
       </c>
       <c r="H90" s="15">
         <v>0.08</v>
       </c>
       <c r="I90" s="13">
-        <v>74.7</v>
+        <v>90</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L90" s="17">
-        <f t="shared" si="26"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M90" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N90" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" spans="1:14">
       <c r="A91" s="12"/>
-      <c r="B91" s="29" t="s">
-        <v>218</v>
+      <c r="B91" s="31" t="s">
+        <v>217</v>
       </c>
       <c r="C91" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>136</v>
@@ -10210,62 +10213,62 @@
         <v>129</v>
       </c>
       <c r="F91" s="7">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="G91" s="13">
-        <f t="shared" si="24"/>
-        <v>74.1</v>
+        <f t="shared" ref="G91:G96" si="24">I91-1</f>
+        <v>113</v>
       </c>
       <c r="H91" s="15">
         <v>0.08</v>
       </c>
       <c r="I91" s="13">
-        <v>75.1</v>
+        <v>114</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="K91:K104" si="25">J91*F91</f>
         <v>0</v>
       </c>
       <c r="L91" s="17">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="L91:L104" si="26">K91+J91/2</f>
         <v>0</v>
       </c>
       <c r="M91" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="M91:M104" si="27">J91*I91</f>
         <v>0</v>
       </c>
       <c r="N91" s="18">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="N91:N104" si="28">M91+J91</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" spans="1:14">
       <c r="A92" s="12"/>
-      <c r="B92" s="29" t="s">
-        <v>219</v>
+      <c r="B92" s="31" t="s">
+        <v>218</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E92" s="30" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="F92" s="7">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="G92" s="13">
         <f t="shared" si="24"/>
-        <v>58.1</v>
+        <v>73</v>
       </c>
       <c r="H92" s="15">
         <v>0.08</v>
       </c>
       <c r="I92" s="13">
-        <v>59.1</v>
+        <v>74</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="17">
@@ -10291,26 +10294,26 @@
         <v>220</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E93" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F93" s="7">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="G93" s="13">
         <f t="shared" si="24"/>
-        <v>124</v>
+        <v>73.7</v>
       </c>
       <c r="H93" s="15">
         <v>0.08</v>
       </c>
       <c r="I93" s="13">
-        <v>125</v>
+        <v>74.7</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="17">
@@ -10332,27 +10335,30 @@
     </row>
     <row r="94" s="2" customFormat="1" spans="1:14">
       <c r="A94" s="12"/>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="C94" s="12" t="s">
-        <v>222</v>
+      <c r="C94" s="29" t="s">
+        <v>212</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E94" s="12"/>
+      <c r="E94" s="30" t="s">
+        <v>129</v>
+      </c>
       <c r="F94" s="7">
-        <v>6.3</v>
+        <v>9.9</v>
       </c>
       <c r="G94" s="13">
-        <v>80</v>
+        <f t="shared" si="24"/>
+        <v>74.1</v>
       </c>
       <c r="H94" s="15">
         <v>0.08</v>
       </c>
       <c r="I94" s="13">
-        <v>81</v>
+        <v>75.1</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="17">
@@ -10374,30 +10380,30 @@
     </row>
     <row r="95" s="2" customFormat="1" spans="1:14">
       <c r="A95" s="12"/>
-      <c r="B95" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C95" s="12" t="s">
+      <c r="B95" s="29" t="s">
         <v>222</v>
+      </c>
+      <c r="C95" s="29" t="s">
+        <v>212</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E95" s="14" t="s">
-        <v>201</v>
+      <c r="E95" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="F95" s="7">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G95" s="13">
-        <v>68</v>
+        <f t="shared" si="24"/>
+        <v>58.1</v>
       </c>
       <c r="H95" s="15">
         <v>0.08</v>
       </c>
-      <c r="I95" s="16">
-        <f t="shared" ref="I95:I98" si="29">G95*(1+H95)</f>
-        <v>73.44</v>
+      <c r="I95" s="13">
+        <v>59.1</v>
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="17">
@@ -10419,30 +10425,30 @@
     </row>
     <row r="96" s="2" customFormat="1" spans="1:14">
       <c r="A96" s="12"/>
-      <c r="B96" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>222</v>
+      <c r="B96" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="29" t="s">
+        <v>212</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E96" s="14" t="s">
-        <v>201</v>
+      <c r="E96" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="F96" s="7">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="G96" s="13">
-        <v>74</v>
+        <f t="shared" si="24"/>
+        <v>124</v>
       </c>
       <c r="H96" s="15">
         <v>0.08</v>
       </c>
-      <c r="I96" s="16">
-        <f t="shared" si="29"/>
-        <v>79.92</v>
+      <c r="I96" s="13">
+        <v>125</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="17">
@@ -10464,30 +10470,27 @@
     </row>
     <row r="97" s="2" customFormat="1" spans="1:14">
       <c r="A97" s="12"/>
-      <c r="B97" s="19" t="s">
-        <v>203</v>
+      <c r="B97" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E97" s="14" t="s">
-        <v>201</v>
-      </c>
+      <c r="E97" s="12"/>
       <c r="F97" s="7">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G97" s="13">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H97" s="15">
         <v>0.08</v>
       </c>
-      <c r="I97" s="16">
-        <f t="shared" si="29"/>
-        <v>88.56</v>
+      <c r="I97" s="13">
+        <v>81</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="17">
@@ -10509,30 +10512,30 @@
     </row>
     <row r="98" s="2" customFormat="1" spans="1:14">
       <c r="A98" s="12"/>
-      <c r="B98" s="12" t="s">
-        <v>204</v>
+      <c r="B98" s="19" t="s">
+        <v>203</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F98" s="7">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="G98" s="13">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="H98" s="15">
         <v>0.08</v>
       </c>
       <c r="I98" s="16">
-        <f t="shared" si="29"/>
-        <v>97.2</v>
+        <f t="shared" ref="I98:I101" si="29">G98*(1+H98)</f>
+        <v>73.44</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="17">
@@ -10554,29 +10557,30 @@
     </row>
     <row r="99" s="2" customFormat="1" spans="1:14">
       <c r="A99" s="12"/>
-      <c r="B99" s="12" t="s">
-        <v>223</v>
+      <c r="B99" s="19" t="s">
+        <v>205</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="F99" s="7">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G99" s="13">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H99" s="15">
         <v>0.08</v>
       </c>
       <c r="I99" s="16">
-        <v>79</v>
+        <f t="shared" si="29"/>
+        <v>79.92</v>
       </c>
       <c r="J99" s="8"/>
       <c r="K99" s="17">
@@ -10598,30 +10602,30 @@
     </row>
     <row r="100" s="2" customFormat="1" spans="1:14">
       <c r="A100" s="12"/>
-      <c r="B100" s="29" t="s">
-        <v>224</v>
+      <c r="B100" s="19" t="s">
+        <v>206</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E100" s="30" t="s">
-        <v>127</v>
+      <c r="E100" s="14" t="s">
+        <v>204</v>
       </c>
       <c r="F100" s="7">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="G100" s="13">
-        <f>I100-1</f>
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H100" s="15">
         <v>0.08</v>
       </c>
-      <c r="I100" s="13">
-        <v>70</v>
+      <c r="I100" s="16">
+        <f t="shared" si="29"/>
+        <v>88.56</v>
       </c>
       <c r="J100" s="8"/>
       <c r="K100" s="17">
@@ -10643,30 +10647,30 @@
     </row>
     <row r="101" s="2" customFormat="1" spans="1:14">
       <c r="A101" s="12"/>
-      <c r="B101" s="29" t="s">
+      <c r="B101" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C101" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E101" s="30" t="s">
-        <v>129</v>
+      <c r="E101" s="14" t="s">
+        <v>204</v>
       </c>
       <c r="F101" s="7">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="G101" s="13">
-        <f>I101-1</f>
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="H101" s="15">
         <v>0.08</v>
       </c>
-      <c r="I101" s="13">
-        <v>59</v>
+      <c r="I101" s="16">
+        <f t="shared" si="29"/>
+        <v>97.2</v>
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="17">
@@ -10686,337 +10690,336 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" s="2" customFormat="1" spans="1:14">
       <c r="A102" s="12"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="15"/>
-      <c r="I102" s="23" t="s">
+      <c r="B102" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="J102" s="24"/>
-      <c r="K102" s="24"/>
+      <c r="C102" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F102" s="7">
+        <v>9</v>
+      </c>
+      <c r="G102" s="13">
+        <v>78</v>
+      </c>
+      <c r="H102" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I102" s="16">
+        <v>79</v>
+      </c>
+      <c r="J102" s="8"/>
+      <c r="K102" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="L102" s="17">
-        <f t="shared" ref="L102:L105" si="30">K102+J102/2</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="24"/>
-      <c r="N102" s="24"/>
-    </row>
-    <row r="103" spans="1:14">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="16">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="N102" s="18">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="1:14">
       <c r="A103" s="12"/>
-      <c r="B103" s="10" t="s">
+      <c r="B103" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-      <c r="E103" s="10"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="15"/>
-      <c r="I103" s="16"/>
-      <c r="J103" s="8" t="s">
+      <c r="C103" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F103" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="G103" s="13">
+        <f>I103-1</f>
+        <v>69</v>
+      </c>
+      <c r="H103" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I103" s="13">
+        <v>70</v>
+      </c>
+      <c r="J103" s="8"/>
+      <c r="K103" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L103" s="17">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="16">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="N103" s="18">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" spans="1:14">
+      <c r="A104" s="12"/>
+      <c r="B104" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="K103" s="17"/>
-      <c r="L103" s="17">
-        <v>0</v>
-      </c>
-      <c r="M103" s="16"/>
-      <c r="N103" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
-      <c r="A104" s="12"/>
-      <c r="B104" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>91</v>
+      <c r="C104" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E104" s="14" t="s">
-        <v>201</v>
+        <v>136</v>
+      </c>
+      <c r="E104" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="F104" s="7">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="G104" s="13">
-        <v>50.5</v>
+        <f>I104-1</f>
+        <v>58</v>
       </c>
       <c r="H104" s="15">
         <v>0.08</v>
       </c>
-      <c r="I104" s="16">
-        <f>G104*(1+H104)</f>
-        <v>54.54</v>
+      <c r="I104" s="13">
+        <v>59</v>
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="17">
-        <f>J104*F104</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L104" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="M104" s="16">
-        <f>J104*I104</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N104" s="18">
-        <f>M104+J104</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="12"/>
-      <c r="B105" s="19" t="s">
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="15"/>
+      <c r="I105" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F105" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G105" s="13">
-        <v>50.5</v>
-      </c>
-      <c r="H105" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I105" s="16">
-        <f>G105*(1+H105)</f>
-        <v>54.54</v>
-      </c>
-      <c r="J105" s="8"/>
-      <c r="K105" s="17">
-        <f>J105*F105</f>
-        <v>0</v>
-      </c>
+      <c r="J105" s="24"/>
+      <c r="K105" s="24"/>
       <c r="L105" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="16">
-        <f>J105*I105</f>
-        <v>0</v>
-      </c>
-      <c r="N105" s="18">
-        <f>M105+J105</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L105:L108" si="30">K105+J105/2</f>
+        <v>0</v>
+      </c>
+      <c r="M105" s="24"/>
+      <c r="N105" s="24"/>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="12"/>
-      <c r="E106" s="12"/>
-      <c r="F106" s="7"/>
+      <c r="B106" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C106" s="10"/>
+      <c r="D106" s="10"/>
+      <c r="E106" s="10"/>
+      <c r="F106" s="11"/>
       <c r="G106" s="13"/>
       <c r="H106" s="15"/>
-      <c r="I106" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="J106" s="24"/>
-      <c r="K106" s="24"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="K106" s="17"/>
       <c r="L106" s="17">
-        <f t="shared" ref="L106:L169" si="31">K106+J106/2</f>
-        <v>0</v>
-      </c>
-      <c r="M106" s="24"/>
-      <c r="N106" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="16"/>
+      <c r="N106" s="18">
+        <v>0</v>
+      </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="12"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="12"/>
-      <c r="E107" s="12"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="15"/>
-      <c r="I107" s="16"/>
+      <c r="B107" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F107" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G107" s="13">
+        <v>50.5</v>
+      </c>
+      <c r="H107" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I107" s="16">
+        <f>G107*(1+H107)</f>
+        <v>54.54</v>
+      </c>
       <c r="J107" s="8"/>
-      <c r="K107" s="17"/>
+      <c r="K107" s="17">
+        <f>J107*F107</f>
+        <v>0</v>
+      </c>
       <c r="L107" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="16"/>
-      <c r="N107" s="18"/>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="16">
+        <f>J107*I107</f>
+        <v>0</v>
+      </c>
+      <c r="N107" s="18">
+        <f>M107+J107</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="12"/>
-      <c r="B108" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="15"/>
-      <c r="I108" s="16"/>
+      <c r="B108" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F108" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G108" s="13">
+        <v>50.5</v>
+      </c>
+      <c r="H108" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I108" s="16">
+        <f>G108*(1+H108)</f>
+        <v>54.54</v>
+      </c>
       <c r="J108" s="8"/>
-      <c r="K108" s="17"/>
+      <c r="K108" s="17">
+        <f>J108*F108</f>
+        <v>0</v>
+      </c>
       <c r="L108" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="16"/>
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M108" s="16">
+        <f>J108*I108</f>
+        <v>0</v>
+      </c>
       <c r="N108" s="18">
-        <f t="shared" ref="N108:N121" si="32">M108+J108</f>
+        <f>M108+J108</f>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="12"/>
-      <c r="B109" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F109" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G109" s="13">
-        <v>51</v>
-      </c>
-      <c r="H109" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I109" s="16">
-        <f t="shared" ref="I109:I121" si="33">G109*(1+H109)</f>
-        <v>55.08</v>
-      </c>
-      <c r="J109" s="8"/>
-      <c r="K109" s="17">
-        <f t="shared" ref="K109:K121" si="34">J109*F109</f>
-        <v>0</v>
-      </c>
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="13"/>
+      <c r="H109" s="15"/>
+      <c r="I109" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="J109" s="24"/>
+      <c r="K109" s="24"/>
       <c r="L109" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="16">
-        <f t="shared" ref="M109:M121" si="35">J109*I109</f>
-        <v>0</v>
-      </c>
-      <c r="N109" s="18">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" ht="14" customHeight="1" spans="1:14">
+        <f t="shared" ref="L109:L172" si="31">K109+J109/2</f>
+        <v>0</v>
+      </c>
+      <c r="M109" s="24"/>
+      <c r="N109" s="24"/>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110" s="12"/>
-      <c r="B110" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E110" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F110" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G110" s="13">
-        <v>54</v>
-      </c>
-      <c r="H110" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I110" s="16">
-        <f t="shared" si="33"/>
-        <v>58.32</v>
-      </c>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="16"/>
       <c r="J110" s="8"/>
-      <c r="K110" s="17">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
+      <c r="K110" s="17"/>
       <c r="L110" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M110" s="16">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N110" s="18">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
+      <c r="M110" s="16"/>
+      <c r="N110" s="18"/>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="12"/>
-      <c r="B111" s="19" t="s">
+      <c r="B111" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F111" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="G111" s="13">
-        <v>61</v>
-      </c>
-      <c r="H111" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I111" s="16">
-        <f t="shared" si="33"/>
-        <v>65.88</v>
-      </c>
+      <c r="C111" s="10"/>
+      <c r="D111" s="10"/>
+      <c r="E111" s="10"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="15"/>
+      <c r="I111" s="16"/>
       <c r="J111" s="8"/>
-      <c r="K111" s="17">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
+      <c r="K111" s="17"/>
       <c r="L111" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M111" s="16">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
+      <c r="M111" s="16"/>
       <c r="N111" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="N111:N124" si="32">M111+J111</f>
         <v>0</v>
       </c>
     </row>
@@ -11032,24 +11035,24 @@
         <v>126</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F112" s="7">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="G112" s="13">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H112" s="15">
         <v>0.08</v>
       </c>
       <c r="I112" s="16">
-        <f t="shared" si="33"/>
-        <v>69.12</v>
+        <f t="shared" ref="I112:I124" si="33">G112*(1+H112)</f>
+        <v>55.08</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="K112:K124" si="34">J112*F112</f>
         <v>0</v>
       </c>
       <c r="L112" s="17">
@@ -11057,7 +11060,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="M112:M124" si="35">J112*I112</f>
         <v>0</v>
       </c>
       <c r="N112" s="18">
@@ -11065,9 +11068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" ht="14" customHeight="1" spans="1:14">
       <c r="A113" s="12"/>
-      <c r="B113" s="19" t="s">
+      <c r="B113" s="12" t="s">
         <v>236</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -11077,14 +11080,21 @@
         <v>126</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F113" s="7"/>
-      <c r="G113" s="13"/>
+        <v>204</v>
+      </c>
+      <c r="F113" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="G113" s="13">
+        <v>54</v>
+      </c>
       <c r="H113" s="15">
         <v>0.08</v>
       </c>
-      <c r="I113" s="16"/>
+      <c r="I113" s="16">
+        <f t="shared" si="33"/>
+        <v>58.32</v>
+      </c>
       <c r="J113" s="8"/>
       <c r="K113" s="17">
         <f t="shared" si="34"/>
@@ -11115,20 +11125,20 @@
         <v>126</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F114" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="G114" s="13">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H114" s="15">
         <v>0.08</v>
       </c>
       <c r="I114" s="16">
         <f t="shared" si="33"/>
-        <v>74.52</v>
+        <v>65.88</v>
       </c>
       <c r="J114" s="8"/>
       <c r="K114" s="17">
@@ -11150,7 +11160,7 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="12"/>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="19" t="s">
         <v>238</v>
       </c>
       <c r="C115" s="8" t="s">
@@ -11160,20 +11170,20 @@
         <v>126</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F115" s="7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="G115" s="13">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H115" s="15">
         <v>0.08</v>
       </c>
       <c r="I115" s="16">
         <f t="shared" si="33"/>
-        <v>77.76</v>
+        <v>69.12</v>
       </c>
       <c r="J115" s="8"/>
       <c r="K115" s="17">
@@ -11205,21 +11215,14 @@
         <v>126</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F116" s="7">
-        <v>8.5</v>
-      </c>
-      <c r="G116" s="13">
-        <v>90</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F116" s="7"/>
+      <c r="G116" s="13"/>
       <c r="H116" s="15">
         <v>0.08</v>
       </c>
-      <c r="I116" s="16">
-        <f t="shared" si="33"/>
-        <v>97.2</v>
-      </c>
+      <c r="I116" s="16"/>
       <c r="J116" s="8"/>
       <c r="K116" s="17">
         <f t="shared" si="34"/>
@@ -11250,22 +11253,22 @@
         <v>126</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F117" s="7">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G117" s="13">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H117" s="15">
         <v>0.08</v>
       </c>
       <c r="I117" s="16">
         <f t="shared" si="33"/>
-        <v>100.44</v>
-      </c>
-      <c r="J117" s="32"/>
+        <v>74.52</v>
+      </c>
+      <c r="J117" s="8"/>
       <c r="K117" s="17">
         <f t="shared" si="34"/>
         <v>0</v>
@@ -11295,14 +11298,21 @@
         <v>126</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F118" s="7"/>
-      <c r="G118" s="13"/>
+        <v>204</v>
+      </c>
+      <c r="F118" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="G118" s="13">
+        <v>72</v>
+      </c>
       <c r="H118" s="15">
         <v>0.08</v>
       </c>
-      <c r="I118" s="16"/>
+      <c r="I118" s="16">
+        <f t="shared" si="33"/>
+        <v>77.76</v>
+      </c>
       <c r="J118" s="8"/>
       <c r="K118" s="17">
         <f t="shared" si="34"/>
@@ -11333,20 +11343,20 @@
         <v>126</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="F119" s="7">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="G119" s="13">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H119" s="15">
         <v>0.08</v>
       </c>
       <c r="I119" s="16">
         <f t="shared" si="33"/>
-        <v>76.68</v>
+        <v>97.2</v>
       </c>
       <c r="J119" s="8"/>
       <c r="K119" s="17">
@@ -11378,22 +11388,22 @@
         <v>126</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="F120" s="7">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="G120" s="13">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H120" s="15">
         <v>0.08</v>
       </c>
       <c r="I120" s="16">
         <f t="shared" si="33"/>
-        <v>79.92</v>
-      </c>
-      <c r="J120" s="8"/>
+        <v>100.44</v>
+      </c>
+      <c r="J120" s="32"/>
       <c r="K120" s="17">
         <f t="shared" si="34"/>
         <v>0</v>
@@ -11451,393 +11461,442 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="12"/>
-      <c r="B122" s="12"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="12"/>
-      <c r="E122" s="12"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="15"/>
-      <c r="I122" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="J122" s="24"/>
-      <c r="K122" s="24"/>
+      <c r="B122" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F122" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G122" s="13">
+        <v>71</v>
+      </c>
+      <c r="H122" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I122" s="16">
+        <f t="shared" si="33"/>
+        <v>76.68</v>
+      </c>
+      <c r="J122" s="8"/>
+      <c r="K122" s="17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
       <c r="L122" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M122" s="24"/>
-      <c r="N122" s="24"/>
+      <c r="M122" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="N122" s="18">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="12"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="15"/>
-      <c r="I123" s="16"/>
+      <c r="B123" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F123" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="G123" s="13">
+        <v>74</v>
+      </c>
+      <c r="H123" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I123" s="16">
+        <f t="shared" si="33"/>
+        <v>79.92</v>
+      </c>
       <c r="J123" s="8"/>
-      <c r="K123" s="17"/>
+      <c r="K123" s="17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
       <c r="L123" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M123" s="16"/>
+      <c r="M123" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="N123" s="18">
-        <f t="shared" ref="N123:N130" si="36">M123+J123</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="12"/>
-      <c r="B124" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="11"/>
+      <c r="B124" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F124" s="7"/>
       <c r="G124" s="13"/>
-      <c r="H124" s="15"/>
+      <c r="H124" s="15">
+        <v>0.08</v>
+      </c>
       <c r="I124" s="16"/>
-      <c r="J124" s="4"/>
-      <c r="K124" s="17"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
       <c r="L124" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M124" s="16"/>
+      <c r="M124" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="N124" s="18">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="12"/>
-      <c r="B125" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F125" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G125" s="13">
-        <v>31.5</v>
-      </c>
-      <c r="H125" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I125" s="16">
-        <f t="shared" ref="I125:I130" si="37">G125*(1+H125)</f>
-        <v>34.02</v>
-      </c>
-      <c r="J125" s="8"/>
-      <c r="K125" s="17">
-        <f t="shared" ref="K125:K130" si="38">J125*F125</f>
-        <v>0</v>
-      </c>
+      <c r="B125" s="12"/>
+      <c r="C125" s="12"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="15"/>
+      <c r="I125" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="J125" s="24"/>
+      <c r="K125" s="24"/>
       <c r="L125" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M125" s="16">
-        <f t="shared" ref="M125:M130" si="39">J125*I125</f>
-        <v>0</v>
-      </c>
-      <c r="N125" s="18">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
+      <c r="M125" s="24"/>
+      <c r="N125" s="24"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="12"/>
-      <c r="B126" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="C126" s="8" t="s">
+      <c r="F126" s="7"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="15"/>
+      <c r="I126" s="16"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="17"/>
+      <c r="L126" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="16"/>
+      <c r="N126" s="18">
+        <f t="shared" ref="N126:N133" si="36">M126+J126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
+      <c r="A127" s="12"/>
+      <c r="B127" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="15"/>
+      <c r="I127" s="16"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="17"/>
+      <c r="L127" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="16"/>
+      <c r="N127" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
+      <c r="A128" s="12"/>
+      <c r="B128" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D128" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E126" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F126" s="7">
+      <c r="E128" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F128" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G128" s="13">
+        <v>31.5</v>
+      </c>
+      <c r="H128" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I128" s="16">
+        <f t="shared" ref="I128:I133" si="37">G128*(1+H128)</f>
+        <v>34.02</v>
+      </c>
+      <c r="J128" s="8"/>
+      <c r="K128" s="17">
+        <f t="shared" ref="K128:K133" si="38">J128*F128</f>
+        <v>0</v>
+      </c>
+      <c r="L128" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="16">
+        <f t="shared" ref="M128:M133" si="39">J128*I128</f>
+        <v>0</v>
+      </c>
+      <c r="N128" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="12"/>
+      <c r="B129" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F129" s="7">
         <v>3.5</v>
       </c>
-      <c r="G126" s="13">
+      <c r="G129" s="13">
         <v>42.5</v>
       </c>
-      <c r="H126" s="15">
+      <c r="H129" s="15">
         <v>0.08</v>
       </c>
-      <c r="I126" s="16">
+      <c r="I129" s="16">
         <f t="shared" si="37"/>
         <v>45.9</v>
       </c>
-      <c r="J126" s="8"/>
-      <c r="K126" s="17">
+      <c r="J129" s="8"/>
+      <c r="K129" s="17">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="L126" s="17">
+      <c r="L129" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M126" s="16">
+      <c r="M129" s="16">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N126" s="18">
+      <c r="N129" s="18">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
-      <c r="A127" s="12"/>
-      <c r="B127" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="C127" s="8" t="s">
+    <row r="130" spans="1:14">
+      <c r="A130" s="12"/>
+      <c r="B130" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D127" s="13" t="s">
+      <c r="D130" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E127" s="14" t="s">
+      <c r="E130" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F130" s="7">
         <v>3.9</v>
       </c>
-      <c r="G127" s="13">
+      <c r="G130" s="13">
         <v>47</v>
       </c>
-      <c r="H127" s="15">
+      <c r="H130" s="15">
         <v>0.08</v>
       </c>
-      <c r="I127" s="16">
+      <c r="I130" s="16">
         <f t="shared" si="37"/>
         <v>50.76</v>
       </c>
-      <c r="J127" s="4"/>
-      <c r="K127" s="17">
+      <c r="J130" s="4"/>
+      <c r="K130" s="17">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="L127" s="17">
+      <c r="L130" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M127" s="16">
+      <c r="M130" s="16">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N127" s="18">
+      <c r="N130" s="18">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
-      <c r="B128" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="C128" s="8" t="s">
+    <row r="131" spans="1:14">
+      <c r="B131" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C131" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D131" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E128" s="12"/>
-      <c r="F128" s="7">
+      <c r="E131" s="12"/>
+      <c r="F131" s="7">
         <v>4</v>
       </c>
-      <c r="G128" s="13">
+      <c r="G131" s="13">
         <v>52</v>
       </c>
-      <c r="H128" s="33">
+      <c r="H131" s="33">
         <v>0.095</v>
       </c>
-      <c r="I128" s="16">
+      <c r="I131" s="16">
         <f t="shared" si="37"/>
         <v>56.94</v>
       </c>
-      <c r="J128" s="4"/>
-      <c r="K128" s="17">
+      <c r="J131" s="4"/>
+      <c r="K131" s="17">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="L128" s="17">
+      <c r="L131" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M128" s="16">
+      <c r="M131" s="16">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N128" s="18">
+      <c r="N131" s="18">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
-      <c r="B129" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C129" s="8" t="s">
+    <row r="132" spans="1:14">
+      <c r="B132" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D132" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E129" s="12"/>
-      <c r="F129" s="7">
+      <c r="E132" s="12"/>
+      <c r="F132" s="7">
         <v>3</v>
       </c>
-      <c r="G129" s="13">
+      <c r="G132" s="13">
         <v>34</v>
       </c>
-      <c r="H129" s="33">
+      <c r="H132" s="33">
         <v>0.095</v>
       </c>
-      <c r="I129" s="16">
+      <c r="I132" s="16">
         <f t="shared" si="37"/>
         <v>37.23</v>
       </c>
-      <c r="J129" s="4"/>
-      <c r="K129" s="17">
+      <c r="J132" s="4"/>
+      <c r="K132" s="17">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="L129" s="17">
+      <c r="L132" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M129" s="16">
+      <c r="M132" s="16">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N129" s="18">
+      <c r="N132" s="18">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
-    <row r="130" s="3" customFormat="1" spans="1:14">
-      <c r="A130" s="26"/>
-      <c r="B130" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="C130" s="8" t="s">
+    <row r="133" s="3" customFormat="1" spans="1:14">
+      <c r="A133" s="26"/>
+      <c r="B133" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C133" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D133" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E130" s="12"/>
-      <c r="F130" s="34">
+      <c r="E133" s="12"/>
+      <c r="F133" s="34">
         <v>2.5</v>
       </c>
-      <c r="G130" s="27">
+      <c r="G133" s="27">
         <v>40.5</v>
       </c>
-      <c r="H130" s="35">
+      <c r="H133" s="35">
         <v>0.1</v>
       </c>
-      <c r="I130" s="16">
+      <c r="I133" s="16">
         <f t="shared" si="37"/>
         <v>44.55</v>
       </c>
-      <c r="J130" s="8"/>
-      <c r="K130" s="17">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="L130" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M130" s="16">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="N130" s="18">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14">
-      <c r="B131" s="12"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12"/>
-      <c r="E131" s="12"/>
-      <c r="I131" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="J131" s="36"/>
-      <c r="K131" s="36"/>
-      <c r="L131" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M131" s="36"/>
-      <c r="N131" s="36"/>
-    </row>
-    <row r="132" spans="1:14">
-      <c r="B132" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C132" s="10"/>
-      <c r="D132" s="10"/>
-      <c r="E132" s="10"/>
-      <c r="F132" s="11"/>
-      <c r="L132" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="N132" s="18">
-        <f t="shared" ref="N132:N142" si="40">M132+J132</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14">
-      <c r="A133" s="12"/>
-      <c r="B133" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F133" s="7">
-        <v>4</v>
-      </c>
-      <c r="G133" s="13">
-        <v>58</v>
-      </c>
-      <c r="H133" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I133" s="16">
-        <f>G133*(1+H133)</f>
-        <v>62.64</v>
-      </c>
       <c r="J133" s="8"/>
       <c r="K133" s="17">
-        <f>J133*F133</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L133" s="17">
@@ -11845,59 +11904,32 @@
         <v>0</v>
       </c>
       <c r="M133" s="16">
-        <f>J133*I133</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N133" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D134" s="13" t="s">
-        <v>143</v>
-      </c>
+      <c r="B134" s="12"/>
+      <c r="C134" s="12"/>
+      <c r="D134" s="12"/>
       <c r="E134" s="12"/>
-      <c r="F134" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="G134" s="13">
-        <v>75</v>
-      </c>
-      <c r="H134" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="I134" s="16">
-        <f>G134*(1+H134)</f>
-        <v>82.5</v>
-      </c>
-      <c r="J134" s="8"/>
-      <c r="K134" s="17">
-        <f>J134*F134</f>
-        <v>0</v>
-      </c>
+      <c r="I134" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="J134" s="36"/>
+      <c r="K134" s="36"/>
       <c r="L134" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M134" s="16">
-        <f>J134*I134</f>
-        <v>0</v>
-      </c>
-      <c r="N134" s="18">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
+      <c r="M134" s="36"/>
+      <c r="N134" s="36"/>
     </row>
     <row r="135" spans="1:14">
-      <c r="A135" s="12"/>
       <c r="B135" s="10" t="s">
         <v>255</v>
       </c>
@@ -11905,47 +11937,41 @@
       <c r="D135" s="10"/>
       <c r="E135" s="10"/>
       <c r="F135" s="11"/>
-      <c r="G135" s="13"/>
-      <c r="H135" s="15"/>
-      <c r="I135" s="16"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="17"/>
       <c r="L135" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M135" s="16"/>
       <c r="N135" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="N135:N145" si="40">M135+J135</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="12"/>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="19" t="s">
         <v>256</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E136" s="4">
-        <v>1000</v>
+        <v>143</v>
+      </c>
+      <c r="E136" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="F136" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G136" s="13">
-        <v>163.5</v>
+        <v>58</v>
       </c>
       <c r="H136" s="15">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I136" s="16">
         <f>G136*(1+H136)</f>
-        <v>181.485</v>
+        <v>62.64</v>
       </c>
       <c r="J136" s="8"/>
       <c r="K136" s="17">
@@ -11967,30 +11993,28 @@
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="12"/>
-      <c r="B137" s="4" t="s">
-        <v>258</v>
+      <c r="B137" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E137" s="4">
-        <v>1000</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="E137" s="12"/>
       <c r="F137" s="7">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G137" s="13">
-        <v>159.1</v>
+        <v>75</v>
       </c>
       <c r="H137" s="15">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I137" s="16">
         <f>G137*(1+H137)</f>
-        <v>176.601</v>
+        <v>82.5</v>
       </c>
       <c r="J137" s="8"/>
       <c r="K137" s="17">
@@ -12012,44 +12036,23 @@
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="12"/>
-      <c r="B138" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E138" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F138" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G138" s="13">
-        <v>124.7</v>
-      </c>
-      <c r="H138" s="15">
-        <v>0.11</v>
-      </c>
-      <c r="I138" s="16">
-        <f>G138*(1+H138)</f>
-        <v>138.417</v>
-      </c>
+      <c r="B138" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C138" s="10"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="13"/>
+      <c r="H138" s="15"/>
+      <c r="I138" s="16"/>
       <c r="J138" s="8"/>
-      <c r="K138" s="17">
-        <f>J138*F138</f>
-        <v>0</v>
-      </c>
+      <c r="K138" s="17"/>
       <c r="L138" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M138" s="16">
-        <f>J138*I138</f>
-        <v>0</v>
-      </c>
+      <c r="M138" s="16"/>
       <c r="N138" s="18">
         <f t="shared" si="40"/>
         <v>0</v>
@@ -12057,30 +12060,30 @@
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="12"/>
-      <c r="B139" s="4" t="s">
-        <v>260</v>
+      <c r="B139" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E139" s="4">
         <v>1000</v>
       </c>
       <c r="F139" s="7">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G139" s="13">
-        <v>93.5</v>
+        <v>163.5</v>
       </c>
       <c r="H139" s="15">
         <v>0.11</v>
       </c>
       <c r="I139" s="16">
         <f>G139*(1+H139)</f>
-        <v>103.785</v>
+        <v>181.485</v>
       </c>
       <c r="J139" s="8"/>
       <c r="K139" s="17">
@@ -12102,56 +12105,75 @@
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="12"/>
-      <c r="B140" s="10" t="s">
+      <c r="B140" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C140" s="10"/>
-      <c r="D140" s="10"/>
-      <c r="E140" s="10"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="13"/>
-      <c r="H140" s="15"/>
-      <c r="I140" s="16"/>
+      <c r="C140" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E140" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F140" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="G140" s="13">
+        <v>159.1</v>
+      </c>
+      <c r="H140" s="15">
+        <v>0.11</v>
+      </c>
+      <c r="I140" s="16">
+        <f>G140*(1+H140)</f>
+        <v>176.601</v>
+      </c>
       <c r="J140" s="8"/>
-      <c r="K140" s="17"/>
+      <c r="K140" s="17">
+        <f>J140*F140</f>
+        <v>0</v>
+      </c>
       <c r="L140" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M140" s="16"/>
+      <c r="M140" s="16">
+        <f>J140*I140</f>
+        <v>0</v>
+      </c>
       <c r="N140" s="18">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:14">
-      <c r="A141" s="14" t="s">
+      <c r="A141" s="12"/>
+      <c r="B141" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B141" s="12" t="s">
-        <v>263</v>
-      </c>
       <c r="C141" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E141" s="14" t="s">
-        <v>265</v>
+        <v>260</v>
+      </c>
+      <c r="E141" s="4">
+        <v>1000</v>
       </c>
       <c r="F141" s="7">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="G141" s="13">
-        <f t="shared" ref="G141:G148" si="41">I141/(1+H141)</f>
-        <v>123.893805309735</v>
+        <v>124.7</v>
       </c>
       <c r="H141" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I141" s="16">
-        <v>140</v>
+        <f>G141*(1+H141)</f>
+        <v>138.417</v>
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="17">
@@ -12172,33 +12194,31 @@
       </c>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B142" s="14" t="s">
-        <v>266</v>
+      <c r="A142" s="12"/>
+      <c r="B142" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E142" s="14" t="s">
-        <v>201</v>
+        <v>260</v>
+      </c>
+      <c r="E142" s="4">
+        <v>1000</v>
       </c>
       <c r="F142" s="7">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="G142" s="13">
-        <f t="shared" si="41"/>
-        <v>153.752212389381</v>
+        <v>93.5</v>
       </c>
       <c r="H142" s="15">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I142" s="16">
-        <v>173.74</v>
+        <f>G142*(1+H142)</f>
+        <v>103.785</v>
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="17">
@@ -12219,221 +12239,198 @@
       </c>
     </row>
     <row r="143" spans="1:14">
-      <c r="A143" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B143" s="14" t="s">
+      <c r="A143" s="12"/>
+      <c r="B143" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="13"/>
+      <c r="H143" s="15"/>
+      <c r="I143" s="16"/>
+      <c r="J143" s="8"/>
+      <c r="K143" s="17"/>
+      <c r="L143" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M143" s="16"/>
+      <c r="N143" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
+      <c r="A144" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D144" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="E144" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="F144" s="7">
+        <v>8</v>
+      </c>
+      <c r="G144" s="13">
+        <f t="shared" ref="G144:G151" si="41">I144/(1+H144)</f>
+        <v>123.893805309735</v>
+      </c>
+      <c r="H144" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I144" s="16">
+        <v>140</v>
+      </c>
+      <c r="J144" s="8"/>
+      <c r="K144" s="17">
+        <f>J144*F144</f>
+        <v>0</v>
+      </c>
+      <c r="L144" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M144" s="16">
+        <f>J144*I144</f>
+        <v>0</v>
+      </c>
+      <c r="N144" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C145" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D143" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E143" s="14" t="s">
+      <c r="D145" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E145" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F145" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="G145" s="13">
+        <f t="shared" si="41"/>
+        <v>153.752212389381</v>
+      </c>
+      <c r="H145" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I145" s="16">
+        <v>173.74</v>
+      </c>
+      <c r="J145" s="8"/>
+      <c r="K145" s="17">
+        <f>J145*F145</f>
+        <v>0</v>
+      </c>
+      <c r="L145" s="17">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M145" s="16">
+        <f>J145*I145</f>
+        <v>0</v>
+      </c>
+      <c r="N145" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
+      <c r="A146" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="E146" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F143" s="7">
+      <c r="F146" s="7">
         <v>6</v>
       </c>
-      <c r="G143" s="13">
+      <c r="G146" s="13">
         <f t="shared" si="41"/>
         <v>176.991150442478</v>
       </c>
-      <c r="H143" s="15">
+      <c r="H146" s="15">
         <v>0.13</v>
       </c>
-      <c r="I143" s="16">
+      <c r="I146" s="16">
         <v>200</v>
       </c>
-      <c r="J143" s="8"/>
-      <c r="K143" s="17">
-        <f t="shared" ref="K143:K148" si="42">J143*F143</f>
-        <v>0</v>
-      </c>
-      <c r="L143" s="17">
+      <c r="J146" s="8"/>
+      <c r="K146" s="17">
+        <f t="shared" ref="K146:K151" si="42">J146*F146</f>
+        <v>0</v>
+      </c>
+      <c r="L146" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M143" s="16">
-        <f t="shared" ref="M143:M148" si="43">J143*I143</f>
-        <v>0</v>
-      </c>
-      <c r="N143" s="18">
-        <f t="shared" ref="N143:N148" si="44">M143+J143</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14">
-      <c r="A144" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B144" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C144" s="8" t="s">
+      <c r="M146" s="16">
+        <f t="shared" ref="M146:M151" si="43">J146*I146</f>
+        <v>0</v>
+      </c>
+      <c r="N146" s="18">
+        <f t="shared" ref="N146:N151" si="44">M146+J146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="A147" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B147" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="C147" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D144" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="E144" s="14" t="s">
+      <c r="D147" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E147" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F147" s="7">
         <v>4</v>
       </c>
-      <c r="G144" s="13">
+      <c r="G147" s="13">
         <f t="shared" si="41"/>
         <v>123.893805309735</v>
       </c>
-      <c r="H144" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I144" s="16">
-        <v>140</v>
-      </c>
-      <c r="J144" s="8"/>
-      <c r="K144" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="L144" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M144" s="16">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N144" s="18">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15">
-      <c r="A145" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B145" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E145" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F145" s="7">
-        <v>8</v>
-      </c>
-      <c r="G145" s="13">
-        <f t="shared" si="41"/>
-        <v>230.088495575221</v>
-      </c>
-      <c r="H145" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I145" s="16">
-        <v>260</v>
-      </c>
-      <c r="J145" s="8"/>
-      <c r="K145" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="L145" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M145" s="16">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N145" s="18">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15">
-      <c r="A146" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B146" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E146" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F146" s="7">
-        <v>8</v>
-      </c>
-      <c r="G146" s="13">
-        <f t="shared" si="41"/>
-        <v>115.929203539823</v>
-      </c>
-      <c r="H146" s="15">
-        <v>0.13</v>
-      </c>
-      <c r="I146" s="16">
-        <v>131</v>
-      </c>
-      <c r="J146" s="8"/>
-      <c r="K146" s="17">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="L146" s="17">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="M146" s="16">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N146" s="18">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15">
-      <c r="A147" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B147" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="E147" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F147" s="7">
-        <v>6</v>
-      </c>
-      <c r="G147" s="13">
-        <f t="shared" si="41"/>
-        <v>88.495575221239</v>
-      </c>
       <c r="H147" s="15">
         <v>0.13</v>
       </c>
       <c r="I147" s="16">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="17">
@@ -12453,34 +12450,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" s="3" customFormat="1" spans="1:15">
+    <row r="148" spans="1:15">
       <c r="A148" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B148" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B148" s="14" t="s">
         <v>274</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>275</v>
+        <v>101</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>265</v>
+        <v>119</v>
       </c>
       <c r="F148" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G148" s="13">
-        <f>I148-1</f>
-        <v>107</v>
+        <f t="shared" si="41"/>
+        <v>230.088495575221</v>
       </c>
       <c r="H148" s="15">
         <v>0.13</v>
       </c>
       <c r="I148" s="16">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="J148" s="8"/>
       <c r="K148" s="17">
@@ -12501,35 +12498,37 @@
       </c>
     </row>
     <row r="149" spans="1:15">
-      <c r="A149" s="14"/>
+      <c r="A149" s="14" t="s">
+        <v>265</v>
+      </c>
       <c r="B149" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>277</v>
+        <v>101</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E149" s="14" t="s">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="F149" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G149" s="13">
-        <f>I149/(1+H149)</f>
-        <v>129.203539823009</v>
+        <f t="shared" si="41"/>
+        <v>115.929203539823</v>
       </c>
       <c r="H149" s="15">
         <v>0.13</v>
       </c>
       <c r="I149" s="16">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="J149" s="8"/>
       <c r="K149" s="17">
-        <f t="shared" ref="K149:K152" si="45">J149*F149</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L149" s="17">
@@ -12537,44 +12536,46 @@
         <v>0</v>
       </c>
       <c r="M149" s="16">
-        <f t="shared" ref="M149:M152" si="46">J149*I149</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N149" s="18">
-        <f t="shared" ref="N149:N152" si="47">M149+J149</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:15">
-      <c r="A150" s="12"/>
-      <c r="B150" s="12" t="s">
-        <v>278</v>
+      <c r="A150" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B150" s="14" t="s">
+        <v>276</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>277</v>
+        <v>101</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>265</v>
+        <v>119</v>
       </c>
       <c r="F150" s="7">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G150" s="13">
-        <v>140</v>
+        <f t="shared" si="41"/>
+        <v>88.495575221239</v>
       </c>
       <c r="H150" s="15">
         <v>0.13</v>
       </c>
       <c r="I150" s="16">
-        <f>G150*(1+H150)</f>
-        <v>158.2</v>
+        <v>100</v>
       </c>
       <c r="J150" s="8"/>
       <c r="K150" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L150" s="17">
@@ -12582,179 +12583,181 @@
         <v>0</v>
       </c>
       <c r="M150" s="16">
-        <f t="shared" si="46"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N150" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" s="3" customFormat="1" spans="1:15">
-      <c r="A151" s="26"/>
-      <c r="B151" s="12" t="s">
-        <v>279</v>
+      <c r="A151" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>277</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E151" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F151" s="34">
-        <v>7.5</v>
+        <v>268</v>
+      </c>
+      <c r="F151" s="7">
+        <v>6</v>
       </c>
       <c r="G151" s="13">
-        <f>I151/(1+H151)</f>
-        <v>103.371681415929</v>
-      </c>
-      <c r="H151" s="35">
+        <f>I151-1</f>
+        <v>107</v>
+      </c>
+      <c r="H151" s="15">
         <v>0.13</v>
       </c>
-      <c r="I151" s="37">
-        <v>116.81</v>
-      </c>
-      <c r="J151" s="34"/>
-      <c r="K151" s="38">
-        <f t="shared" si="45"/>
+      <c r="I151" s="16">
+        <v>108</v>
+      </c>
+      <c r="J151" s="8"/>
+      <c r="K151" s="17">
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L151" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M151" s="37">
-        <f t="shared" si="46"/>
+      <c r="M151" s="16">
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N151" s="18">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" s="3" customFormat="1" spans="1:15">
-      <c r="A152" s="26"/>
-      <c r="B152" s="12" t="s">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
+      <c r="A152" s="14"/>
+      <c r="B152" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C152" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C152" s="8" t="s">
-        <v>277</v>
-      </c>
       <c r="D152" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="F152" s="7">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="G152" s="13">
-        <f>I152-1</f>
-        <v>177.2</v>
+        <f>I152/(1+H152)</f>
+        <v>129.203539823009</v>
       </c>
       <c r="H152" s="15">
         <v>0.13</v>
       </c>
       <c r="I152" s="16">
-        <v>178.2</v>
+        <v>146</v>
       </c>
       <c r="J152" s="8"/>
-      <c r="K152" s="38">
-        <f t="shared" si="45"/>
+      <c r="K152" s="17">
+        <f t="shared" ref="K152:K155" si="45">J152*F152</f>
         <v>0</v>
       </c>
       <c r="L152" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M152" s="37">
-        <f t="shared" si="46"/>
+      <c r="M152" s="16">
+        <f t="shared" ref="M152:M155" si="46">J152*I152</f>
         <v>0</v>
       </c>
       <c r="N152" s="18">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" s="3" customFormat="1" ht="11" customHeight="1" spans="1:15">
-      <c r="A153" s="26"/>
-      <c r="B153" s="14" t="s">
+        <f t="shared" ref="N152:N155" si="47">M152+J152</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153" s="12"/>
+      <c r="B153" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="C153" s="12" t="s">
-        <v>282</v>
+      <c r="C153" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="F153" s="34">
-        <v>4.5</v>
+        <v>268</v>
+      </c>
+      <c r="F153" s="7">
+        <v>9.5</v>
       </c>
       <c r="G153" s="13">
-        <f>I153/(1+H153)</f>
-        <v>132.743362831858</v>
-      </c>
-      <c r="H153" s="35">
+        <v>140</v>
+      </c>
+      <c r="H153" s="15">
         <v>0.13</v>
       </c>
-      <c r="I153" s="37">
-        <v>150</v>
-      </c>
-      <c r="J153" s="34"/>
-      <c r="K153" s="38">
-        <f t="shared" ref="K153:K167" si="48">J153*F153</f>
+      <c r="I153" s="16">
+        <f>G153*(1+H153)</f>
+        <v>158.2</v>
+      </c>
+      <c r="J153" s="8"/>
+      <c r="K153" s="17">
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L153" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M153" s="37">
-        <f t="shared" ref="M153:M167" si="49">J153*I153</f>
+      <c r="M153" s="16">
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="N153" s="18">
-        <f t="shared" ref="N153:N172" si="50">M153+J153</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" s="3" customFormat="1" spans="1:15">
       <c r="A154" s="26"/>
-      <c r="B154" s="14" t="s">
+      <c r="B154" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D154" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C154" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>270</v>
-      </c>
       <c r="E154" s="14" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="F154" s="34">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G154" s="13">
-        <v>145</v>
+        <f>I154/(1+H154)</f>
+        <v>103.371681415929</v>
       </c>
       <c r="H154" s="35">
         <v>0.13</v>
       </c>
-      <c r="I154" s="16">
-        <f>G154*(1+H154)</f>
-        <v>163.85</v>
+      <c r="I154" s="37">
+        <v>116.81</v>
       </c>
       <c r="J154" s="34"/>
       <c r="K154" s="38">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L154" s="17">
@@ -12762,44 +12765,44 @@
         <v>0</v>
       </c>
       <c r="M154" s="37">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="N154" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" s="3" customFormat="1" spans="1:15">
       <c r="A155" s="26"/>
-      <c r="B155" s="14" t="s">
+      <c r="B155" s="12" t="s">
         <v>283</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>96</v>
+        <v>280</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E155" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F155" s="34">
-        <v>4</v>
+        <v>204</v>
+      </c>
+      <c r="F155" s="7">
+        <v>10.5</v>
       </c>
       <c r="G155" s="13">
-        <v>101</v>
-      </c>
-      <c r="H155" s="35">
+        <f>I155-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H155" s="15">
         <v>0.13</v>
       </c>
       <c r="I155" s="16">
-        <f>G155*(1+H155)</f>
-        <v>114.13</v>
-      </c>
-      <c r="J155" s="34"/>
+        <v>178.2</v>
+      </c>
+      <c r="J155" s="8"/>
       <c r="K155" s="38">
-        <f t="shared" si="48"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L155" s="17">
@@ -12807,88 +12810,88 @@
         <v>0</v>
       </c>
       <c r="M155" s="37">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="N155" s="18">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" s="3" customFormat="1" spans="1:15">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" s="3" customFormat="1" ht="11" customHeight="1" spans="1:15">
       <c r="A156" s="26"/>
-      <c r="B156" s="12" t="s">
+      <c r="B156" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="C156" s="8" t="s">
-        <v>96</v>
+      <c r="C156" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="D156" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E156" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E156" s="14" t="s">
-        <v>119</v>
-      </c>
       <c r="F156" s="34">
-        <v>4</v>
-      </c>
-      <c r="G156" s="27">
-        <v>115</v>
+        <v>4.5</v>
+      </c>
+      <c r="G156" s="13">
+        <f>I156/(1+H156)</f>
+        <v>132.743362831858</v>
       </c>
       <c r="H156" s="35">
-        <v>0.08</v>
-      </c>
-      <c r="I156" s="16">
-        <f>G156*(1+H156)</f>
-        <v>124.2</v>
-      </c>
-      <c r="J156" s="8"/>
-      <c r="K156" s="17">
-        <f t="shared" si="48"/>
+        <v>0.13</v>
+      </c>
+      <c r="I156" s="37">
+        <v>150</v>
+      </c>
+      <c r="J156" s="34"/>
+      <c r="K156" s="38">
+        <f t="shared" ref="K156:K170" si="48">J156*F156</f>
         <v>0</v>
       </c>
       <c r="L156" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M156" s="16">
-        <f t="shared" si="49"/>
+      <c r="M156" s="37">
+        <f t="shared" ref="M156:M170" si="49">J156*I156</f>
         <v>0</v>
       </c>
       <c r="N156" s="18">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="N156:N175" si="50">M156+J156</f>
         <v>0</v>
       </c>
     </row>
     <row r="157" s="3" customFormat="1" spans="1:15">
-      <c r="A157" s="14"/>
+      <c r="A157" s="26"/>
       <c r="B157" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F157" s="7">
-        <v>4</v>
+      <c r="F157" s="34">
+        <v>6</v>
       </c>
       <c r="G157" s="13">
-        <f>I157/(1+H157)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H157" s="15">
+        <v>145</v>
+      </c>
+      <c r="H157" s="35">
         <v>0.13</v>
       </c>
       <c r="I157" s="16">
-        <v>140</v>
-      </c>
-      <c r="J157" s="8"/>
-      <c r="K157" s="17">
+        <f>G157*(1+H157)</f>
+        <v>163.85</v>
+      </c>
+      <c r="J157" s="34"/>
+      <c r="K157" s="38">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -12896,7 +12899,7 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M157" s="16">
+      <c r="M157" s="37">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
@@ -12904,33 +12907,36 @@
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="O157" s="2"/>
     </row>
     <row r="158" s="3" customFormat="1" spans="1:15">
       <c r="A158" s="26"/>
-      <c r="B158" s="12" t="s">
-        <v>285</v>
+      <c r="B158" s="14" t="s">
+        <v>286</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>286</v>
+        <v>96</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="E158" s="14"/>
+        <v>273</v>
+      </c>
+      <c r="E158" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="F158" s="34">
-        <v>11</v>
-      </c>
-      <c r="G158" s="27">
-        <f>I158-1</f>
-        <v>177.5</v>
-      </c>
-      <c r="H158" s="35"/>
+        <v>4</v>
+      </c>
+      <c r="G158" s="13">
+        <v>101</v>
+      </c>
+      <c r="H158" s="35">
+        <v>0.13</v>
+      </c>
       <c r="I158" s="16">
-        <v>178.5</v>
-      </c>
-      <c r="J158" s="8"/>
-      <c r="K158" s="17">
+        <f>G158*(1+H158)</f>
+        <v>114.13</v>
+      </c>
+      <c r="J158" s="34"/>
+      <c r="K158" s="38">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -12938,7 +12944,7 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M158" s="16">
+      <c r="M158" s="37">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
@@ -12950,25 +12956,29 @@
     <row r="159" s="3" customFormat="1" spans="1:15">
       <c r="A159" s="26"/>
       <c r="B159" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>286</v>
+        <v>96</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="E159" s="14"/>
+        <v>271</v>
+      </c>
+      <c r="E159" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="F159" s="34">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G159" s="27">
-        <f>I159-1</f>
-        <v>127.5</v>
-      </c>
-      <c r="H159" s="35"/>
+        <v>115</v>
+      </c>
+      <c r="H159" s="35">
+        <v>0.08</v>
+      </c>
       <c r="I159" s="16">
-        <v>128.5</v>
+        <f>G159*(1+H159)</f>
+        <v>124.2</v>
       </c>
       <c r="J159" s="8"/>
       <c r="K159" s="17">
@@ -12991,29 +13001,29 @@
     <row r="160" s="3" customFormat="1" spans="1:15">
       <c r="A160" s="14"/>
       <c r="B160" s="14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>275</v>
+        <v>96</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E160" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F160" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G160" s="13">
         <f>I160/(1+H160)</f>
-        <v>176.991150442478</v>
+        <v>123.893805309735</v>
       </c>
       <c r="H160" s="15">
         <v>0.13</v>
       </c>
       <c r="I160" s="16">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="J160" s="8"/>
       <c r="K160" s="17">
@@ -13032,33 +13042,30 @@
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
+      <c r="O160" s="2"/>
     </row>
     <row r="161" s="3" customFormat="1" spans="1:14">
-      <c r="A161" s="14"/>
-      <c r="B161" s="14" t="s">
-        <v>269</v>
+      <c r="A161" s="26"/>
+      <c r="B161" s="12" t="s">
+        <v>288</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="D161" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="E161" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F161" s="7">
-        <v>4</v>
-      </c>
-      <c r="G161" s="13">
-        <f>I161/(1+H161)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H161" s="15">
-        <v>0.13</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="E161" s="14"/>
+      <c r="F161" s="34">
+        <v>11</v>
+      </c>
+      <c r="G161" s="27">
+        <f>I161-1</f>
+        <v>177.5</v>
+      </c>
+      <c r="H161" s="35"/>
       <c r="I161" s="16">
-        <v>140</v>
+        <v>178.5</v>
       </c>
       <c r="J161" s="8"/>
       <c r="K161" s="17">
@@ -13078,32 +13085,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" s="3" customFormat="1" ht="13" customHeight="1" spans="1:14">
+    <row r="162" s="3" customFormat="1" spans="1:14">
       <c r="A162" s="26"/>
       <c r="B162" s="12" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E162" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F162" s="7">
-        <v>4</v>
-      </c>
-      <c r="G162" s="13">
-        <v>115</v>
-      </c>
-      <c r="H162" s="15">
-        <v>0.08</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="E162" s="14"/>
+      <c r="F162" s="34">
+        <v>8</v>
+      </c>
+      <c r="G162" s="27">
+        <f>I162-1</f>
+        <v>127.5</v>
+      </c>
+      <c r="H162" s="35"/>
       <c r="I162" s="16">
-        <f>G162*(1+H162)</f>
-        <v>124.2</v>
+        <v>128.5</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="17">
@@ -13124,31 +13127,31 @@
       </c>
     </row>
     <row r="163" s="3" customFormat="1" spans="1:14">
-      <c r="A163" s="26"/>
-      <c r="B163" s="19" t="s">
-        <v>274</v>
+      <c r="A163" s="14"/>
+      <c r="B163" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D163" s="13" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E163" s="14" t="s">
-        <v>265</v>
+        <v>119</v>
       </c>
       <c r="F163" s="7">
         <v>6</v>
       </c>
       <c r="G163" s="13">
-        <f>I163-1</f>
-        <v>107</v>
+        <f>I163/(1+H163)</f>
+        <v>176.991150442478</v>
       </c>
       <c r="H163" s="15">
         <v>0.13</v>
       </c>
       <c r="I163" s="16">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="17">
@@ -13169,34 +13172,34 @@
       </c>
     </row>
     <row r="164" s="3" customFormat="1" spans="1:14">
-      <c r="A164" s="26"/>
-      <c r="B164" s="12" t="s">
-        <v>279</v>
+      <c r="A164" s="14"/>
+      <c r="B164" s="14" t="s">
+        <v>272</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D164" s="13" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="E164" s="14" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="F164" s="7">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G164" s="13">
-        <f>I164-1</f>
-        <v>134</v>
+        <f>I164/(1+H164)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H164" s="15">
         <v>0.13</v>
       </c>
-      <c r="I164" s="39">
-        <v>135</v>
-      </c>
-      <c r="J164" s="34"/>
-      <c r="K164" s="38">
+      <c r="I164" s="16">
+        <v>140</v>
+      </c>
+      <c r="J164" s="8"/>
+      <c r="K164" s="17">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -13204,7 +13207,7 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M164" s="37">
+      <c r="M164" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
@@ -13213,32 +13216,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" s="3" customFormat="1" spans="1:14">
-      <c r="A165" s="12"/>
-      <c r="B165" s="19" t="s">
+    <row r="165" s="3" customFormat="1" ht="13" customHeight="1" spans="1:14">
+      <c r="A165" s="26"/>
+      <c r="B165" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C165" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C165" s="8" t="s">
-        <v>101</v>
-      </c>
       <c r="D165" s="13" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E165" s="14" t="s">
-        <v>265</v>
+        <v>119</v>
       </c>
       <c r="F165" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G165" s="13">
-        <f>I165-1</f>
-        <v>150.2</v>
+        <v>115</v>
       </c>
       <c r="H165" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I165" s="16">
-        <v>151.2</v>
+        <f>G165*(1+H165)</f>
+        <v>124.2</v>
       </c>
       <c r="J165" s="8"/>
       <c r="K165" s="17">
@@ -13260,33 +13263,33 @@
     </row>
     <row r="166" s="3" customFormat="1" spans="1:14">
       <c r="A166" s="26"/>
-      <c r="B166" s="12" t="s">
-        <v>290</v>
+      <c r="B166" s="19" t="s">
+        <v>277</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E166" s="14" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="F166" s="7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G166" s="13">
         <f>I166-1</f>
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H166" s="15">
         <v>0.13</v>
       </c>
       <c r="I166" s="16">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="J166" s="8"/>
-      <c r="K166" s="38">
+      <c r="K166" s="17">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -13294,7 +13297,7 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M166" s="37">
+      <c r="M166" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
@@ -13306,31 +13309,31 @@
     <row r="167" s="3" customFormat="1" spans="1:14">
       <c r="A167" s="26"/>
       <c r="B167" s="12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="D167" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E167" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F167" s="7">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G167" s="13">
         <f>I167-1</f>
-        <v>177.2</v>
+        <v>134</v>
       </c>
       <c r="H167" s="15">
         <v>0.13</v>
       </c>
-      <c r="I167" s="16">
-        <v>178.2</v>
-      </c>
-      <c r="J167" s="8"/>
+      <c r="I167" s="39">
+        <v>135</v>
+      </c>
+      <c r="J167" s="34"/>
       <c r="K167" s="38">
         <f t="shared" si="48"/>
         <v>0</v>
@@ -13349,22 +13352,45 @@
       </c>
     </row>
     <row r="168" s="3" customFormat="1" spans="1:14">
-      <c r="A168" s="26"/>
-      <c r="B168" s="26"/>
-      <c r="C168" s="26"/>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
-      <c r="F168" s="34"/>
-      <c r="G168" s="27"/>
-      <c r="H168" s="35"/>
-      <c r="I168" s="16"/>
+      <c r="A168" s="12"/>
+      <c r="B168" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E168" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="F168" s="7">
+        <v>8</v>
+      </c>
+      <c r="G168" s="13">
+        <f>I168-1</f>
+        <v>150.2</v>
+      </c>
+      <c r="H168" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I168" s="16">
+        <v>151.2</v>
+      </c>
       <c r="J168" s="8"/>
-      <c r="K168" s="17"/>
+      <c r="K168" s="17">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="L168" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M168" s="16"/>
+      <c r="M168" s="16">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="N168" s="18">
         <f t="shared" si="50"/>
         <v>0</v>
@@ -13372,65 +13398,87 @@
     </row>
     <row r="169" s="3" customFormat="1" spans="1:14">
       <c r="A169" s="26"/>
-      <c r="B169" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C169" s="10"/>
-      <c r="D169" s="10"/>
-      <c r="E169" s="10"/>
-      <c r="F169" s="11"/>
-      <c r="G169" s="27"/>
-      <c r="H169" s="35"/>
-      <c r="I169" s="16"/>
+      <c r="B169" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E169" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F169" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="G169" s="13">
+        <f>I169-1</f>
+        <v>134</v>
+      </c>
+      <c r="H169" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I169" s="16">
+        <v>135</v>
+      </c>
       <c r="J169" s="8"/>
-      <c r="K169" s="17"/>
+      <c r="K169" s="38">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="L169" s="17">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M169" s="16"/>
+      <c r="M169" s="37">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="N169" s="18">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
-      <c r="B170" s="40" t="s">
-        <v>292</v>
+    <row r="170" s="3" customFormat="1" spans="1:14">
+      <c r="A170" s="26"/>
+      <c r="B170" s="12" t="s">
+        <v>283</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E170" s="41">
-        <v>1000</v>
+        <v>267</v>
+      </c>
+      <c r="E170" s="14" t="s">
+        <v>204</v>
       </c>
       <c r="F170" s="7">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G170" s="13">
-        <v>90</v>
+        <f>I170-1</f>
+        <v>177.2</v>
       </c>
       <c r="H170" s="15">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I170" s="16">
-        <f>G170*(1+H170)</f>
-        <v>97.2</v>
+        <v>178.2</v>
       </c>
       <c r="J170" s="8"/>
-      <c r="K170" s="17">
-        <f>J170*F170</f>
+      <c r="K170" s="38">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="L170" s="17">
-        <f>K170+J170/2</f>
-        <v>0</v>
-      </c>
-      <c r="M170" s="16">
-        <f>J170*I170</f>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M170" s="37">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N170" s="18">
@@ -13438,139 +13486,121 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
-      <c r="B171" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D171" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E171" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F171" s="7">
-        <v>8</v>
-      </c>
-      <c r="G171" s="13">
-        <v>92</v>
-      </c>
-      <c r="H171" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I171" s="16">
-        <f>G171*(1+H171)</f>
-        <v>99.36</v>
-      </c>
+    <row r="171" s="3" customFormat="1" spans="1:14">
+      <c r="A171" s="26"/>
+      <c r="B171" s="26"/>
+      <c r="C171" s="26"/>
+      <c r="D171" s="26"/>
+      <c r="E171" s="26"/>
+      <c r="F171" s="34"/>
+      <c r="G171" s="27"/>
+      <c r="H171" s="35"/>
+      <c r="I171" s="16"/>
       <c r="J171" s="8"/>
-      <c r="K171" s="17">
-        <f>J171*F171</f>
-        <v>0</v>
-      </c>
+      <c r="K171" s="17"/>
       <c r="L171" s="17">
-        <f t="shared" ref="L171:L200" si="51">K171+J171/2</f>
-        <v>0</v>
-      </c>
-      <c r="M171" s="16">
-        <f>J171*I171</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M171" s="16"/>
       <c r="N171" s="18">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
-      <c r="B172" s="40" t="s">
+    <row r="172" s="3" customFormat="1" spans="1:14">
+      <c r="A172" s="26"/>
+      <c r="B172" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="C172" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E172" s="41">
-        <v>1000</v>
-      </c>
-      <c r="F172" s="7">
-        <v>7</v>
-      </c>
-      <c r="G172" s="13">
-        <v>87</v>
-      </c>
-      <c r="H172" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I172" s="16">
-        <f>G172*(1+H172)</f>
-        <v>93.96</v>
-      </c>
+      <c r="C172" s="10"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="11"/>
+      <c r="G172" s="27"/>
+      <c r="H172" s="35"/>
+      <c r="I172" s="16"/>
       <c r="J172" s="8"/>
-      <c r="K172" s="17">
-        <f>J172*F172</f>
-        <v>0</v>
-      </c>
+      <c r="K172" s="17"/>
       <c r="L172" s="17">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="M172" s="16">
-        <f>J172*I172</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M172" s="16"/>
       <c r="N172" s="18">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:14">
-      <c r="B173" s="10" t="s">
+      <c r="B173" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="C173" s="10"/>
-      <c r="D173" s="10"/>
-      <c r="E173" s="10"/>
-      <c r="F173" s="11"/>
-      <c r="G173" s="13"/>
-      <c r="H173" s="15"/>
-      <c r="I173" s="16"/>
+      <c r="C173" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="E173" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F173" s="7">
+        <v>8</v>
+      </c>
+      <c r="G173" s="13">
+        <v>90</v>
+      </c>
+      <c r="H173" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I173" s="16">
+        <f>G173*(1+H173)</f>
+        <v>97.2</v>
+      </c>
       <c r="J173" s="8"/>
-      <c r="K173" s="17"/>
+      <c r="K173" s="17">
+        <f>J173*F173</f>
+        <v>0</v>
+      </c>
       <c r="L173" s="17">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="M173" s="16"/>
-      <c r="N173" s="18"/>
+        <f>K173+J173/2</f>
+        <v>0</v>
+      </c>
+      <c r="M173" s="16">
+        <f>J173*I173</f>
+        <v>0</v>
+      </c>
+      <c r="N173" s="18">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="174" spans="1:14">
       <c r="B174" s="40" t="s">
         <v>296</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D174" s="13" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E174" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F174" s="7">
-        <v>4.65</v>
+        <v>8</v>
       </c>
       <c r="G174" s="13">
-        <v>61.5</v>
+        <v>92</v>
       </c>
       <c r="H174" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I174" s="16">
         <f>G174*(1+H174)</f>
-        <v>67.65</v>
+        <v>99.36</v>
       </c>
       <c r="J174" s="8"/>
       <c r="K174" s="17">
@@ -13578,7 +13608,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="17">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="L174:L203" si="51">K174+J174/2</f>
         <v>0</v>
       </c>
       <c r="M174" s="16">
@@ -13586,7 +13616,7 @@
         <v>0</v>
       </c>
       <c r="N174" s="18">
-        <f t="shared" ref="N174:N200" si="52">M174+J174</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
@@ -13595,26 +13625,26 @@
         <v>297</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E175" s="41">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F175" s="7">
-        <v>5.15</v>
+        <v>7</v>
       </c>
       <c r="G175" s="13">
-        <v>64.5</v>
+        <v>87</v>
       </c>
       <c r="H175" s="15">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I175" s="16">
         <f>G175*(1+H175)</f>
-        <v>70.95</v>
+        <v>93.96</v>
       </c>
       <c r="J175" s="8"/>
       <c r="K175" s="17">
@@ -13630,81 +13660,55 @@
         <v>0</v>
       </c>
       <c r="N175" s="18">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" s="3" customFormat="1" spans="1:14">
-      <c r="A176" s="26"/>
-      <c r="B176" s="36" t="s">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
+      <c r="B176" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C176" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D176" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="E176" s="41">
-        <v>300</v>
-      </c>
-      <c r="F176" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="G176" s="27">
-        <v>76.5</v>
-      </c>
-      <c r="H176" s="35">
-        <v>0.1</v>
-      </c>
-      <c r="I176" s="16">
-        <f>G176*(1+H176)</f>
-        <v>84.15</v>
-      </c>
+      <c r="C176" s="10"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="10"/>
+      <c r="F176" s="11"/>
+      <c r="G176" s="13"/>
+      <c r="H176" s="15"/>
+      <c r="I176" s="16"/>
       <c r="J176" s="8"/>
-      <c r="K176" s="17">
-        <f>J176*F176</f>
-        <v>0</v>
-      </c>
+      <c r="K176" s="17"/>
       <c r="L176" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M176" s="16">
-        <f>J176*I176</f>
-        <v>0</v>
-      </c>
-      <c r="N176" s="18">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" s="3" customFormat="1" spans="1:14">
-      <c r="A177" s="26"/>
-      <c r="B177" s="2" t="s">
+      <c r="M176" s="16"/>
+      <c r="N176" s="18"/>
+    </row>
+    <row r="177" spans="1:14">
+      <c r="B177" s="40" t="s">
         <v>299</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E177" s="41">
         <v>300</v>
       </c>
       <c r="F177" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="G177" s="27">
-        <v>94.5</v>
-      </c>
-      <c r="H177" s="35">
+        <v>4.65</v>
+      </c>
+      <c r="G177" s="13">
+        <v>61.5</v>
+      </c>
+      <c r="H177" s="15">
         <v>0.1</v>
       </c>
       <c r="I177" s="16">
         <f>G177*(1+H177)</f>
-        <v>103.95</v>
+        <v>67.65</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="17">
@@ -13720,27 +13724,49 @@
         <v>0</v>
       </c>
       <c r="N177" s="18">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" s="3" customFormat="1" spans="1:14">
-      <c r="A178" s="26"/>
-      <c r="B178" s="27"/>
-      <c r="C178" s="27"/>
-      <c r="D178" s="27"/>
-      <c r="E178" s="27"/>
-      <c r="F178" s="27"/>
-      <c r="G178" s="27"/>
-      <c r="H178" s="35"/>
-      <c r="I178" s="16"/>
+        <f t="shared" ref="N177:N203" si="52">M177+J177</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14">
+      <c r="B178" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E178" s="41">
+        <v>300</v>
+      </c>
+      <c r="F178" s="7">
+        <v>5.15</v>
+      </c>
+      <c r="G178" s="13">
+        <v>64.5</v>
+      </c>
+      <c r="H178" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="I178" s="16">
+        <f>G178*(1+H178)</f>
+        <v>70.95</v>
+      </c>
       <c r="J178" s="8"/>
-      <c r="K178" s="17"/>
+      <c r="K178" s="17">
+        <f>J178*F178</f>
+        <v>0</v>
+      </c>
       <c r="L178" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M178" s="16"/>
+      <c r="M178" s="16">
+        <f>J178*I178</f>
+        <v>0</v>
+      </c>
       <c r="N178" s="18">
         <f t="shared" si="52"/>
         <v>0</v>
@@ -13748,57 +13774,79 @@
     </row>
     <row r="179" s="3" customFormat="1" spans="1:14">
       <c r="A179" s="26"/>
-      <c r="B179" s="10" t="s">
+      <c r="B179" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D179" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E179" s="41">
         <v>300</v>
       </c>
-      <c r="C179" s="42"/>
-      <c r="D179" s="42"/>
-      <c r="E179" s="42"/>
-      <c r="F179" s="43"/>
-      <c r="G179" s="27"/>
-      <c r="H179" s="35"/>
-      <c r="I179" s="16"/>
+      <c r="F179" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="G179" s="27">
+        <v>76.5</v>
+      </c>
+      <c r="H179" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="I179" s="16">
+        <f>G179*(1+H179)</f>
+        <v>84.15</v>
+      </c>
       <c r="J179" s="8"/>
-      <c r="K179" s="17"/>
+      <c r="K179" s="17">
+        <f>J179*F179</f>
+        <v>0</v>
+      </c>
       <c r="L179" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M179" s="16"/>
+      <c r="M179" s="16">
+        <f>J179*I179</f>
+        <v>0</v>
+      </c>
       <c r="N179" s="18">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
-      <c r="B180" s="40" t="s">
-        <v>301</v>
+    <row r="180" s="3" customFormat="1" spans="1:14">
+      <c r="A180" s="26"/>
+      <c r="B180" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D180" s="13" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E180" s="41">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F180" s="7">
-        <v>5</v>
-      </c>
-      <c r="G180" s="13">
-        <v>67.5</v>
-      </c>
-      <c r="H180" s="15">
-        <v>0.08</v>
+        <v>4.7</v>
+      </c>
+      <c r="G180" s="27">
+        <v>94.5</v>
+      </c>
+      <c r="H180" s="35">
+        <v>0.1</v>
       </c>
       <c r="I180" s="16">
-        <f t="shared" ref="I180:I200" si="53">G180*(1+H180)</f>
-        <v>72.9</v>
+        <f>G180*(1+H180)</f>
+        <v>103.95</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="17">
-        <f t="shared" ref="K180:K200" si="54">J180*F180</f>
+        <f>J180*F180</f>
         <v>0</v>
       </c>
       <c r="L180" s="17">
@@ -13806,7 +13854,7 @@
         <v>0</v>
       </c>
       <c r="M180" s="16">
-        <f t="shared" ref="M180:M200" si="55">J180*I180</f>
+        <f>J180*I180</f>
         <v>0</v>
       </c>
       <c r="N180" s="18">
@@ -13814,82 +13862,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
-      <c r="B181" s="40" t="s">
-        <v>303</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D181" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="E181" s="41">
-        <v>500</v>
-      </c>
-      <c r="F181" s="7">
-        <v>6.2</v>
-      </c>
-      <c r="G181" s="13">
-        <v>79</v>
-      </c>
-      <c r="H181" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I181" s="16">
-        <f t="shared" si="53"/>
-        <v>85.32</v>
-      </c>
+    <row r="181" s="3" customFormat="1" spans="1:14">
+      <c r="A181" s="26"/>
+      <c r="B181" s="27"/>
+      <c r="C181" s="27"/>
+      <c r="D181" s="27"/>
+      <c r="E181" s="27"/>
+      <c r="F181" s="27"/>
+      <c r="G181" s="27"/>
+      <c r="H181" s="35"/>
+      <c r="I181" s="16"/>
       <c r="J181" s="8"/>
-      <c r="K181" s="17">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
+      <c r="K181" s="17"/>
       <c r="L181" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M181" s="16">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
+      <c r="M181" s="16"/>
       <c r="N181" s="18">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
-      <c r="B182" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D182" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="E182" s="41">
-        <v>500</v>
-      </c>
-      <c r="F182" s="7"/>
-      <c r="G182" s="13"/>
-      <c r="H182" s="15">
-        <v>0.08</v>
-      </c>
+    <row r="182" s="3" customFormat="1" spans="1:14">
+      <c r="A182" s="26"/>
+      <c r="B182" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C182" s="42"/>
+      <c r="D182" s="42"/>
+      <c r="E182" s="42"/>
+      <c r="F182" s="43"/>
+      <c r="G182" s="27"/>
+      <c r="H182" s="35"/>
       <c r="I182" s="16"/>
       <c r="J182" s="8"/>
-      <c r="K182" s="17">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
+      <c r="K182" s="17"/>
       <c r="L182" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="M182" s="16">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
+      <c r="M182" s="16"/>
       <c r="N182" s="18">
         <f t="shared" si="52"/>
         <v>0</v>
@@ -13897,33 +13910,33 @@
     </row>
     <row r="183" spans="1:14">
       <c r="B183" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D183" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E183" s="41">
         <v>500</v>
       </c>
       <c r="F183" s="7">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G183" s="13">
-        <v>105</v>
+        <v>67.5</v>
       </c>
       <c r="H183" s="15">
         <v>0.08</v>
       </c>
       <c r="I183" s="16">
-        <f t="shared" si="53"/>
-        <v>113.4</v>
+        <f t="shared" ref="I183:I203" si="53">G183*(1+H183)</f>
+        <v>72.9</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="17">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="K183:K203" si="54">J183*F183</f>
         <v>0</v>
       </c>
       <c r="L183" s="17">
@@ -13931,7 +13944,7 @@
         <v>0</v>
       </c>
       <c r="M183" s="16">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="M183:M203" si="55">J183*I183</f>
         <v>0</v>
       </c>
       <c r="N183" s="18">
@@ -13947,23 +13960,23 @@
         <v>94</v>
       </c>
       <c r="D184" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E184" s="41">
         <v>500</v>
       </c>
       <c r="F184" s="7">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="G184" s="13">
-        <v>117.5</v>
+        <v>79</v>
       </c>
       <c r="H184" s="15">
         <v>0.08</v>
       </c>
       <c r="I184" s="16">
         <f t="shared" si="53"/>
-        <v>126.9</v>
+        <v>85.32</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="17">
@@ -13991,24 +14004,17 @@
         <v>94</v>
       </c>
       <c r="D185" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E185" s="41">
         <v>500</v>
       </c>
-      <c r="F185" s="7">
-        <v>8</v>
-      </c>
-      <c r="G185" s="13">
-        <v>122.5</v>
-      </c>
+      <c r="F185" s="7"/>
+      <c r="G185" s="13"/>
       <c r="H185" s="15">
         <v>0.08</v>
       </c>
-      <c r="I185" s="16">
-        <f t="shared" si="53"/>
-        <v>132.3</v>
-      </c>
+      <c r="I185" s="16"/>
       <c r="J185" s="8"/>
       <c r="K185" s="17">
         <f t="shared" si="54"/>
@@ -14028,30 +14034,30 @@
       </c>
     </row>
     <row r="186" spans="1:14">
-      <c r="B186" s="41" t="s">
+      <c r="B186" s="40" t="s">
         <v>308</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D186" s="41" t="s">
-        <v>309</v>
+      <c r="D186" s="13" t="s">
+        <v>305</v>
       </c>
       <c r="E186" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F186" s="7">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G186" s="13">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H186" s="15">
         <v>0.08</v>
       </c>
       <c r="I186" s="16">
         <f t="shared" si="53"/>
-        <v>108</v>
+        <v>113.4</v>
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="17">
@@ -14072,30 +14078,30 @@
       </c>
     </row>
     <row r="187" spans="1:14">
-      <c r="B187" s="6" t="s">
-        <v>310</v>
+      <c r="B187" s="40" t="s">
+        <v>309</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D187" s="41" t="s">
-        <v>309</v>
+      <c r="D187" s="13" t="s">
+        <v>305</v>
       </c>
       <c r="E187" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F187" s="7">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G187" s="13">
-        <v>145</v>
+        <v>117.5</v>
       </c>
       <c r="H187" s="15">
         <v>0.08</v>
       </c>
       <c r="I187" s="16">
         <f t="shared" si="53"/>
-        <v>156.6</v>
+        <v>126.9</v>
       </c>
       <c r="J187" s="8"/>
       <c r="K187" s="17">
@@ -14117,29 +14123,29 @@
     </row>
     <row r="188" spans="1:14">
       <c r="B188" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D188" s="41" t="s">
-        <v>309</v>
+      <c r="D188" s="13" t="s">
+        <v>305</v>
       </c>
       <c r="E188" s="41">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F188" s="7">
         <v>8</v>
       </c>
       <c r="G188" s="13">
-        <v>135</v>
+        <v>122.5</v>
       </c>
       <c r="H188" s="15">
         <v>0.08</v>
       </c>
       <c r="I188" s="16">
         <f t="shared" si="53"/>
-        <v>145.8</v>
+        <v>132.3</v>
       </c>
       <c r="J188" s="8"/>
       <c r="K188" s="17">
@@ -14160,31 +14166,30 @@
       </c>
     </row>
     <row r="189" spans="1:14">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6" t="s">
-        <v>312</v>
+      <c r="B189" s="41" t="s">
+        <v>311</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D189" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E189" s="41">
         <v>5000</v>
       </c>
       <c r="F189" s="7">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="G189" s="13">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="H189" s="15">
         <v>0.08</v>
       </c>
       <c r="I189" s="16">
         <f t="shared" si="53"/>
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="17">
@@ -14205,30 +14210,30 @@
       </c>
     </row>
     <row r="190" spans="1:14">
-      <c r="B190" s="41" t="s">
+      <c r="B190" s="6" t="s">
         <v>313</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D190" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E190" s="41">
         <v>5000</v>
       </c>
       <c r="F190" s="7">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="G190" s="13">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H190" s="15">
         <v>0.08</v>
       </c>
       <c r="I190" s="16">
         <f t="shared" si="53"/>
-        <v>172.8</v>
+        <v>156.6</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="17">
@@ -14249,30 +14254,30 @@
       </c>
     </row>
     <row r="191" spans="1:14">
-      <c r="B191" s="44" t="s">
+      <c r="B191" s="41" t="s">
         <v>314</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D191" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E191" s="41">
         <v>5000</v>
       </c>
       <c r="F191" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G191" s="13">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="H191" s="15">
         <v>0.08</v>
       </c>
       <c r="I191" s="16">
         <f t="shared" si="53"/>
-        <v>205.2</v>
+        <v>145.8</v>
       </c>
       <c r="J191" s="8"/>
       <c r="K191" s="17">
@@ -14293,30 +14298,31 @@
       </c>
     </row>
     <row r="192" spans="1:14">
-      <c r="B192" s="41" t="s">
+      <c r="A192" s="6"/>
+      <c r="B192" s="6" t="s">
         <v>315</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D192" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E192" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F192" s="7">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="G192" s="13">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="H192" s="15">
         <v>0.08</v>
       </c>
       <c r="I192" s="16">
         <f t="shared" si="53"/>
-        <v>58.32</v>
+        <v>189</v>
       </c>
       <c r="J192" s="8"/>
       <c r="K192" s="17">
@@ -14337,30 +14343,30 @@
       </c>
     </row>
     <row r="193" spans="1:14">
-      <c r="B193" s="40" t="s">
+      <c r="B193" s="41" t="s">
         <v>316</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D193" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E193" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F193" s="7">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="G193" s="13">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="H193" s="15">
         <v>0.08</v>
       </c>
       <c r="I193" s="16">
         <f t="shared" si="53"/>
-        <v>62.64</v>
+        <v>172.8</v>
       </c>
       <c r="J193" s="8"/>
       <c r="K193" s="17">
@@ -14381,31 +14387,30 @@
       </c>
     </row>
     <row r="194" spans="1:14">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6" t="s">
+      <c r="B194" s="44" t="s">
         <v>317</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D194" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E194" s="41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F194" s="7">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="G194" s="13">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="H194" s="15">
         <v>0.08</v>
       </c>
       <c r="I194" s="16">
         <f t="shared" si="53"/>
-        <v>68.04</v>
+        <v>205.2</v>
       </c>
       <c r="J194" s="8"/>
       <c r="K194" s="17">
@@ -14433,15 +14438,24 @@
         <v>94</v>
       </c>
       <c r="D195" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E195" s="41">
         <v>1000</v>
       </c>
-      <c r="F195" s="7"/>
-      <c r="G195" s="13"/>
-      <c r="H195" s="15"/>
-      <c r="I195" s="16"/>
+      <c r="F195" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G195" s="13">
+        <v>54</v>
+      </c>
+      <c r="H195" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I195" s="16">
+        <f t="shared" si="53"/>
+        <v>58.32</v>
+      </c>
       <c r="J195" s="8"/>
       <c r="K195" s="17">
         <f t="shared" si="54"/>
@@ -14461,22 +14475,31 @@
       </c>
     </row>
     <row r="196" spans="1:14">
-      <c r="B196" s="41" t="s">
+      <c r="B196" s="40" t="s">
         <v>319</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>94</v>
       </c>
       <c r="D196" s="41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E196" s="41">
         <v>1000</v>
       </c>
-      <c r="F196" s="7"/>
-      <c r="G196" s="13"/>
-      <c r="H196" s="15"/>
-      <c r="I196" s="16"/>
+      <c r="F196" s="7">
+        <v>4</v>
+      </c>
+      <c r="G196" s="13">
+        <v>58</v>
+      </c>
+      <c r="H196" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I196" s="16">
+        <f t="shared" si="53"/>
+        <v>62.64</v>
+      </c>
       <c r="J196" s="8"/>
       <c r="K196" s="17">
         <f t="shared" si="54"/>
@@ -14496,30 +14519,31 @@
       </c>
     </row>
     <row r="197" spans="1:14">
-      <c r="B197" s="40" t="s">
+      <c r="A197" s="6"/>
+      <c r="B197" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D197" s="13" t="s">
-        <v>322</v>
+        <v>94</v>
+      </c>
+      <c r="D197" s="41" t="s">
+        <v>312</v>
       </c>
       <c r="E197" s="41">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F197" s="7">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="G197" s="13">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="H197" s="15">
         <v>0.08</v>
       </c>
       <c r="I197" s="16">
         <f t="shared" si="53"/>
-        <v>151.2</v>
+        <v>68.04</v>
       </c>
       <c r="J197" s="8"/>
       <c r="K197" s="17">
@@ -14540,31 +14564,22 @@
       </c>
     </row>
     <row r="198" spans="1:14">
-      <c r="B198" s="40" t="s">
-        <v>320</v>
+      <c r="B198" s="41" t="s">
+        <v>321</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D198" s="13" t="s">
-        <v>322</v>
+        <v>94</v>
+      </c>
+      <c r="D198" s="41" t="s">
+        <v>312</v>
       </c>
       <c r="E198" s="41">
-        <v>2000</v>
-      </c>
-      <c r="F198" s="7">
-        <v>5</v>
-      </c>
-      <c r="G198" s="13">
-        <v>140</v>
-      </c>
-      <c r="H198" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I198" s="16">
-        <f t="shared" si="53"/>
-        <v>151.2</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F198" s="7"/>
+      <c r="G198" s="13"/>
+      <c r="H198" s="15"/>
+      <c r="I198" s="16"/>
       <c r="J198" s="8"/>
       <c r="K198" s="17">
         <f t="shared" si="54"/>
@@ -14585,30 +14600,21 @@
     </row>
     <row r="199" spans="1:14">
       <c r="B199" s="41" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D199" s="13" t="s">
-        <v>322</v>
+        <v>94</v>
+      </c>
+      <c r="D199" s="41" t="s">
+        <v>312</v>
       </c>
       <c r="E199" s="41">
         <v>1000</v>
       </c>
-      <c r="F199" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G199" s="13">
-        <v>70</v>
-      </c>
-      <c r="H199" s="15">
-        <v>0.08</v>
-      </c>
-      <c r="I199" s="16">
-        <f t="shared" si="53"/>
-        <v>75.6</v>
-      </c>
+      <c r="F199" s="7"/>
+      <c r="G199" s="13"/>
+      <c r="H199" s="15"/>
+      <c r="I199" s="16"/>
       <c r="J199" s="8"/>
       <c r="K199" s="17">
         <f t="shared" si="54"/>
@@ -14628,30 +14634,30 @@
       </c>
     </row>
     <row r="200" spans="1:14">
-      <c r="B200" s="41" t="s">
-        <v>283</v>
+      <c r="B200" s="40" t="s">
+        <v>323</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="D200" s="13" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="E200" s="41">
         <v>2000</v>
       </c>
       <c r="F200" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G200" s="13">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="H200" s="15">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I200" s="16">
         <f t="shared" si="53"/>
-        <v>114.13</v>
+        <v>151.2</v>
       </c>
       <c r="J200" s="8"/>
       <c r="K200" s="17">
@@ -14672,82 +14678,151 @@
       </c>
     </row>
     <row r="201" spans="1:14">
-      <c r="F201" s="7"/>
-      <c r="G201" s="13"/>
-      <c r="H201" s="15"/>
-      <c r="J201" s="7" t="s">
-        <v>324</v>
-      </c>
+      <c r="B201" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="E201" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F201" s="7">
+        <v>5</v>
+      </c>
+      <c r="G201" s="13">
+        <v>140</v>
+      </c>
+      <c r="H201" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I201" s="16">
+        <f t="shared" si="53"/>
+        <v>151.2</v>
+      </c>
+      <c r="J201" s="8"/>
       <c r="K201" s="17">
-        <f>SUM(J6:J199)</f>
-        <v>0</v>
-      </c>
-      <c r="L201" s="6" t="s">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L201" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M201" s="16">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N201" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14">
+      <c r="B202" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="C202" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D202" s="13" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="202" spans="1:14">
-      <c r="A202" s="45"/>
-      <c r="B202" s="45"/>
-      <c r="C202" s="45"/>
-      <c r="D202" s="45"/>
-      <c r="E202" s="45"/>
-      <c r="F202" s="7"/>
-      <c r="G202" s="13"/>
-      <c r="H202" s="15"/>
-      <c r="I202" s="45"/>
-      <c r="J202" s="41" t="s">
-        <v>326</v>
-      </c>
-      <c r="K202" s="7">
-        <f>SUM(K6:K199)</f>
-        <v>0</v>
-      </c>
-      <c r="L202" s="6" t="s">
-        <v>327</v>
+      <c r="E202" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F202" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="G202" s="13">
+        <v>70</v>
+      </c>
+      <c r="H202" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="I202" s="16">
+        <f t="shared" si="53"/>
+        <v>75.6</v>
+      </c>
+      <c r="J202" s="8"/>
+      <c r="K202" s="17">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L202" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M202" s="16">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N202" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:14">
-      <c r="A203" s="45"/>
-      <c r="B203" s="45"/>
-      <c r="C203" s="45"/>
-      <c r="D203" s="45"/>
-      <c r="E203" s="45"/>
-      <c r="F203" s="45"/>
-      <c r="G203" s="13"/>
-      <c r="H203" s="15"/>
-      <c r="I203" s="45"/>
-      <c r="J203" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="K203" s="4">
-        <f>SUM(L:L)</f>
-        <v>0.45</v>
-      </c>
-      <c r="L203" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="M203" s="41"/>
+      <c r="B203" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D203" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E203" s="41">
+        <v>2000</v>
+      </c>
+      <c r="F203" s="7">
+        <v>4</v>
+      </c>
+      <c r="G203" s="13">
+        <v>101</v>
+      </c>
+      <c r="H203" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="I203" s="16">
+        <f t="shared" si="53"/>
+        <v>114.13</v>
+      </c>
+      <c r="J203" s="8"/>
+      <c r="K203" s="17">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="L203" s="17">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="M203" s="16">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N203" s="18">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="204" spans="1:14">
-      <c r="A204" s="45"/>
-      <c r="B204" s="45"/>
-      <c r="C204" s="45"/>
-      <c r="D204" s="45"/>
-      <c r="E204" s="45"/>
-      <c r="F204" s="45"/>
+      <c r="F204" s="7"/>
       <c r="G204" s="13"/>
       <c r="H204" s="15"/>
-      <c r="I204" s="45"/>
-      <c r="J204" s="41" t="s">
-        <v>329</v>
-      </c>
-      <c r="K204" s="45">
-        <f>SUM(N5:N200)</f>
-        <v>0</v>
-      </c>
-      <c r="L204" s="45"/>
-      <c r="M204" s="41"/>
+      <c r="J204" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="K204" s="17">
+        <f>SUM(J6:J202)</f>
+        <v>0</v>
+      </c>
+      <c r="L204" s="6" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="45"/>
@@ -14755,14 +14830,20 @@
       <c r="C205" s="45"/>
       <c r="D205" s="45"/>
       <c r="E205" s="45"/>
-      <c r="F205" s="45"/>
+      <c r="F205" s="7"/>
       <c r="G205" s="13"/>
       <c r="H205" s="15"/>
       <c r="I205" s="45"/>
-      <c r="J205" s="45"/>
-      <c r="K205" s="45"/>
-      <c r="L205" s="45"/>
-      <c r="M205" s="41"/>
+      <c r="J205" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="K205" s="7">
+        <f>SUM(K6:K202)</f>
+        <v>0</v>
+      </c>
+      <c r="L205" s="6" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="45"/>
@@ -14774,9 +14855,16 @@
       <c r="G206" s="13"/>
       <c r="H206" s="15"/>
       <c r="I206" s="45"/>
-      <c r="J206" s="45"/>
-      <c r="K206" s="45"/>
-      <c r="L206" s="45"/>
+      <c r="J206" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="K206" s="4">
+        <f>SUM(L:L)</f>
+        <v>0.45</v>
+      </c>
+      <c r="L206" s="46" t="s">
+        <v>330</v>
+      </c>
       <c r="M206" s="41"/>
     </row>
     <row r="207" spans="1:14">
@@ -14786,11 +14874,16 @@
       <c r="D207" s="45"/>
       <c r="E207" s="45"/>
       <c r="F207" s="45"/>
-      <c r="G207" s="45"/>
+      <c r="G207" s="13"/>
       <c r="H207" s="15"/>
       <c r="I207" s="45"/>
-      <c r="J207" s="45"/>
-      <c r="K207" s="45"/>
+      <c r="J207" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="K207" s="45">
+        <f>SUM(N5:N203)</f>
+        <v>0</v>
+      </c>
       <c r="L207" s="45"/>
       <c r="M207" s="41"/>
     </row>
@@ -14801,7 +14894,7 @@
       <c r="D208" s="45"/>
       <c r="E208" s="45"/>
       <c r="F208" s="45"/>
-      <c r="G208" s="45"/>
+      <c r="G208" s="13"/>
       <c r="H208" s="15"/>
       <c r="I208" s="45"/>
       <c r="J208" s="45"/>
@@ -14816,14 +14909,12 @@
       <c r="D209" s="45"/>
       <c r="E209" s="45"/>
       <c r="F209" s="45"/>
-      <c r="G209" s="45"/>
+      <c r="G209" s="13"/>
       <c r="H209" s="15"/>
       <c r="I209" s="45"/>
       <c r="J209" s="45"/>
       <c r="K209" s="45"/>
-      <c r="L209" s="45" t="s">
-        <v>228</v>
-      </c>
+      <c r="L209" s="45"/>
       <c r="M209" s="41"/>
     </row>
     <row r="210" spans="1:13">
@@ -14834,7 +14925,7 @@
       <c r="E210" s="45"/>
       <c r="F210" s="45"/>
       <c r="G210" s="45"/>
-      <c r="H210" s="45"/>
+      <c r="H210" s="15"/>
       <c r="I210" s="45"/>
       <c r="J210" s="45"/>
       <c r="K210" s="45"/>
@@ -14849,7 +14940,7 @@
       <c r="E211" s="45"/>
       <c r="F211" s="45"/>
       <c r="G211" s="45"/>
-      <c r="H211" s="45"/>
+      <c r="H211" s="15"/>
       <c r="I211" s="45"/>
       <c r="J211" s="45"/>
       <c r="K211" s="45"/>
@@ -14864,11 +14955,13 @@
       <c r="E212" s="45"/>
       <c r="F212" s="45"/>
       <c r="G212" s="45"/>
-      <c r="H212" s="45"/>
+      <c r="H212" s="15"/>
       <c r="I212" s="45"/>
       <c r="J212" s="45"/>
       <c r="K212" s="45"/>
-      <c r="L212" s="45"/>
+      <c r="L212" s="45" t="s">
+        <v>231</v>
+      </c>
       <c r="M212" s="41"/>
     </row>
     <row r="213" spans="1:13">
@@ -14886,33 +14979,78 @@
       <c r="L213" s="45"/>
       <c r="M213" s="41"/>
     </row>
+    <row r="214" spans="1:13">
+      <c r="A214" s="45"/>
+      <c r="B214" s="45"/>
+      <c r="C214" s="45"/>
+      <c r="D214" s="45"/>
+      <c r="E214" s="45"/>
+      <c r="F214" s="45"/>
+      <c r="G214" s="45"/>
+      <c r="H214" s="45"/>
+      <c r="I214" s="45"/>
+      <c r="J214" s="45"/>
+      <c r="K214" s="45"/>
+      <c r="L214" s="45"/>
+      <c r="M214" s="41"/>
+    </row>
     <row r="215" spans="1:13">
-      <c r="B215" s="6"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
-      <c r="E215" s="6"/>
-    </row>
-    <row r="217" spans="1:13">
-      <c r="J217" s="6"/>
+      <c r="A215" s="45"/>
+      <c r="B215" s="45"/>
+      <c r="C215" s="45"/>
+      <c r="D215" s="45"/>
+      <c r="E215" s="45"/>
+      <c r="F215" s="45"/>
+      <c r="G215" s="45"/>
+      <c r="H215" s="45"/>
+      <c r="I215" s="45"/>
+      <c r="J215" s="45"/>
+      <c r="K215" s="45"/>
+      <c r="L215" s="45"/>
+      <c r="M215" s="41"/>
+    </row>
+    <row r="216" spans="1:13">
+      <c r="A216" s="45"/>
+      <c r="B216" s="45"/>
+      <c r="C216" s="45"/>
+      <c r="D216" s="45"/>
+      <c r="E216" s="45"/>
+      <c r="F216" s="45"/>
+      <c r="G216" s="45"/>
+      <c r="H216" s="45"/>
+      <c r="I216" s="45"/>
+      <c r="J216" s="45"/>
+      <c r="K216" s="45"/>
+      <c r="L216" s="45"/>
+      <c r="M216" s="41"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="K218" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13">
-      <c r="B219" s="6"/>
-      <c r="C219" s="6"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="6"/>
-    </row>
-    <row r="232" spans="5:5">
-      <c r="E232" s="2" t="s">
-        <v>228</v>
+      <c r="B218" s="6"/>
+      <c r="C218" s="6"/>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
+    </row>
+    <row r="220" spans="1:13">
+      <c r="J220" s="6"/>
+    </row>
+    <row r="221" spans="1:13">
+      <c r="K221" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13">
+      <c r="B222" s="6"/>
+      <c r="C222" s="6"/>
+      <c r="D222" s="6"/>
+      <c r="E222" s="6"/>
+    </row>
+    <row r="235" spans="5:5">
+      <c r="E235" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P204" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P207" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14931,7 +15069,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N200,工作表2!N6:N200&gt;0,"")</f>
+        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N203,工作表2!N6:N203&gt;0,"")</f>
         <v/>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -16,7 +16,7 @@
     <sheet name="工作表3" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">工作表2!$A$4:$P$217</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'合同 '!$A$1:$G$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">发票!$A$1:$E$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">装箱单!$A$1:$L$36</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="348">
   <si>
     <t>销 售 合 同
 SALES CONTRACT</t>
@@ -615,6 +615,12 @@
   </si>
   <si>
     <t>50酱杯</t>
+  </si>
+  <si>
+    <t>500注塑磨砂杯</t>
+  </si>
+  <si>
+    <t>東莞伟利兴</t>
   </si>
   <si>
     <t>EP55</t>
@@ -2789,7 +2795,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{85F5A38D-9082-452A-8924-0B48EA48E6AC}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{5FC2D8F0-A7BE-4B51-9CFF-49827AA34F66}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2798,7 +2804,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{87539BF8-8DE9-4670-9980-0C64610D1865}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{037E7845-33B3-45D1-93F7-44279F07FDC8}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -6468,7 +6474,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P244"/>
+  <dimension ref="A1:P245"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="19.4" style="2" customWidth="1"/>
@@ -8594,7 +8600,7 @@
         <v>11</v>
       </c>
       <c r="G51" s="14">
-        <f t="shared" ref="G51:G59" si="8">I51-1</f>
+        <f t="shared" ref="G51:G60" si="8">I51-1</f>
         <v>114</v>
       </c>
       <c r="H51" s="16">
@@ -8965,32 +8971,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" ht="14.25" customHeight="1" spans="1:14">
+    <row r="60" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:14">
       <c r="A60" s="13"/>
       <c r="B60" s="21" t="s">
         <v>182</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>127</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E60" s="21"/>
       <c r="F60" s="8">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G60" s="14">
-        <f>I60/(1+H60)</f>
-        <v>81.7256637168142</v>
+        <f t="shared" si="8"/>
+        <v>141.58</v>
       </c>
       <c r="H60" s="16">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I60" s="17">
-        <v>92.35</v>
+        <v>142.58</v>
       </c>
       <c r="J60" s="9"/>
       <c r="K60" s="18">
@@ -9013,7 +9017,7 @@
     <row r="61" ht="14.25" customHeight="1" spans="1:14">
       <c r="A61" s="13"/>
       <c r="B61" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>102</v>
@@ -9022,43 +9026,43 @@
         <v>136</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F61" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G61" s="14">
         <f>I61/(1+H61)</f>
-        <v>77.2566371681416</v>
+        <v>81.7256637168142</v>
       </c>
       <c r="H61" s="16">
         <v>0.13</v>
       </c>
       <c r="I61" s="17">
-        <v>87.3</v>
+        <v>92.35</v>
       </c>
       <c r="J61" s="9"/>
       <c r="K61" s="18">
-        <f t="shared" si="1"/>
+        <f>J61*F61</f>
         <v>0</v>
       </c>
       <c r="L61" s="18">
-        <f t="shared" si="2"/>
+        <f>K61+J61/2</f>
         <v>0</v>
       </c>
       <c r="M61" s="17">
-        <f t="shared" si="3"/>
+        <f>J61*I61</f>
         <v>0</v>
       </c>
       <c r="N61" s="19">
-        <f t="shared" si="4"/>
+        <f>M61+J61</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1" spans="1:14">
       <c r="A62" s="13"/>
-      <c r="B62" s="23" t="s">
-        <v>184</v>
+      <c r="B62" s="21" t="s">
+        <v>185</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>102</v>
@@ -9074,36 +9078,36 @@
       </c>
       <c r="G62" s="14">
         <f>I62/(1+H62)</f>
-        <v>69.3362831858407</v>
+        <v>77.2566371681416</v>
       </c>
       <c r="H62" s="16">
         <v>0.13</v>
       </c>
       <c r="I62" s="17">
-        <v>78.35</v>
+        <v>87.3</v>
       </c>
       <c r="J62" s="9"/>
       <c r="K62" s="18">
-        <f t="shared" si="1"/>
+        <f>J62*F62</f>
         <v>0</v>
       </c>
       <c r="L62" s="18">
-        <f t="shared" si="2"/>
+        <f>K62+J62/2</f>
         <v>0</v>
       </c>
       <c r="M62" s="17">
-        <f t="shared" si="3"/>
+        <f>J62*I62</f>
         <v>0</v>
       </c>
       <c r="N62" s="19">
-        <f t="shared" si="4"/>
+        <f>M62+J62</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1" spans="1:14">
       <c r="A63" s="13"/>
-      <c r="B63" s="21" t="s">
-        <v>185</v>
+      <c r="B63" s="23" t="s">
+        <v>186</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>102</v>
@@ -9115,195 +9119,195 @@
         <v>166</v>
       </c>
       <c r="F63" s="8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G63" s="14">
-        <v>94.09</v>
+        <f>I63/(1+H63)</f>
+        <v>69.3362831858407</v>
       </c>
       <c r="H63" s="16">
         <v>0.13</v>
       </c>
-      <c r="I63" s="24">
-        <f>G63+1</f>
+      <c r="I63" s="17">
+        <v>78.35</v>
+      </c>
+      <c r="J63" s="9"/>
+      <c r="K63" s="18">
+        <f>J63*F63</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="18">
+        <f>K63+J63/2</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="17">
+        <f>J63*I63</f>
+        <v>0</v>
+      </c>
+      <c r="N63" s="19">
+        <f>M63+J63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="14.25" customHeight="1" spans="1:14">
+      <c r="A64" s="13"/>
+      <c r="B64" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" s="8">
+        <v>8.4</v>
+      </c>
+      <c r="G64" s="14">
+        <v>94.09</v>
+      </c>
+      <c r="H64" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="I64" s="24">
+        <f>G64+1</f>
         <v>95.09</v>
       </c>
-      <c r="J63" s="25"/>
-      <c r="K63" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L63" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M63" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N63" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="24" t="s">
-        <v>186</v>
-      </c>
       <c r="J64" s="25"/>
-      <c r="K64" s="25"/>
+      <c r="K64" s="18">
+        <f>J64*F64</f>
+        <v>0</v>
+      </c>
       <c r="L64" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
+        <f>K64+J64/2</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="17">
+        <f>J64*I64</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="19">
+        <f>M64+J64</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="13"/>
-      <c r="B65" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="12"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="8"/>
       <c r="G65" s="14"/>
       <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="16"/>
+      <c r="I65" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J65" s="25"/>
+      <c r="K65" s="25"/>
       <c r="L65" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="16"/>
-      <c r="N65" s="16"/>
+        <f>K65+J65/2</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="25"/>
+      <c r="N65" s="25"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="13"/>
-      <c r="B66" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="C66" s="8" t="s">
+      <c r="B66" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="18">
+        <f>K66+J66/2</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="16"/>
+      <c r="N66" s="16"/>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="13"/>
+      <c r="B67" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D66" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E66" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="F66" s="8">
+      <c r="D67" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F67" s="8">
         <v>8.5</v>
       </c>
-      <c r="G66" s="14">
+      <c r="G67" s="14">
         <f>9823.01/60</f>
         <v>163.716833333333</v>
       </c>
-      <c r="H66" s="16">
-        <v>0.13</v>
-      </c>
-      <c r="I66" s="17">
-        <f>G66*(1+H66)</f>
-        <v>185.000021666667</v>
-      </c>
-      <c r="J66" s="9"/>
-      <c r="K66" s="18">
-        <f t="shared" ref="K66:K72" si="9">J66*F66</f>
-        <v>0</v>
-      </c>
-      <c r="L66" s="18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M66" s="17">
-        <f t="shared" ref="M66:M72" si="10">J66*I66</f>
-        <v>0</v>
-      </c>
-      <c r="N66" s="19">
-        <f t="shared" ref="N66:N72" si="11">M66+J66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
-      <c r="A67" s="13"/>
-      <c r="B67" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E67" s="27">
-        <v>1000</v>
-      </c>
-      <c r="F67" s="8">
-        <v>18.2</v>
-      </c>
-      <c r="G67" s="14">
-        <f>I67/(1+H67)</f>
-        <v>336.283185840708</v>
-      </c>
       <c r="H67" s="16">
         <v>0.13</v>
       </c>
       <c r="I67" s="17">
-        <v>380</v>
+        <f>G67*(1+H67)</f>
+        <v>185.000021666667</v>
       </c>
       <c r="J67" s="9"/>
       <c r="K67" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="K67:K73" si="9">J67*F67</f>
         <v>0</v>
       </c>
       <c r="L67" s="18">
-        <f t="shared" si="2"/>
+        <f>K67+J67/2</f>
         <v>0</v>
       </c>
       <c r="M67" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="M67:M73" si="10">J67*I67</f>
         <v>0</v>
       </c>
       <c r="N67" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="N67:N73" si="11">M67+J67</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="13"/>
       <c r="B68" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E68" s="27" t="s">
-        <v>193</v>
+        <v>191</v>
+      </c>
+      <c r="E68" s="27">
+        <v>1000</v>
       </c>
       <c r="F68" s="8">
-        <v>9.25</v>
+        <v>18.2</v>
       </c>
       <c r="G68" s="14">
         <f>I68/(1+H68)</f>
-        <v>141.592920353982</v>
+        <v>336.283185840708</v>
       </c>
       <c r="H68" s="16">
         <v>0.13</v>
       </c>
-      <c r="I68" s="14">
-        <v>160</v>
+      <c r="I68" s="17">
+        <v>380</v>
       </c>
       <c r="J68" s="9"/>
       <c r="K68" s="18">
@@ -9311,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="18">
-        <f t="shared" si="2"/>
+        <f>K68+J68/2</f>
         <v>0</v>
       </c>
       <c r="M68" s="17">
@@ -9322,7 +9326,6 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="13"/>
@@ -9333,21 +9336,23 @@
         <v>95</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E69" s="27"/>
+        <v>191</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>195</v>
+      </c>
       <c r="F69" s="8">
-        <v>13.5</v>
+        <v>9.25</v>
       </c>
       <c r="G69" s="14">
         <f>I69/(1+H69)</f>
-        <v>176.991150442478</v>
+        <v>141.592920353982</v>
       </c>
       <c r="H69" s="16">
         <v>0.13</v>
       </c>
       <c r="I69" s="14">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="J69" s="9"/>
       <c r="K69" s="18">
@@ -9355,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="18">
-        <f t="shared" si="2"/>
+        <f>K69+J69/2</f>
         <v>0</v>
       </c>
       <c r="M69" s="17">
@@ -9371,27 +9376,27 @@
     <row r="70" spans="1:15">
       <c r="A70" s="13"/>
       <c r="B70" s="28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E70" s="27"/>
       <c r="F70" s="8">
-        <v>12.15</v>
+        <v>13.5</v>
       </c>
       <c r="G70" s="14">
         <f>I70/(1+H70)</f>
-        <v>233.628318584071</v>
+        <v>176.991150442478</v>
       </c>
       <c r="H70" s="16">
         <v>0.13</v>
       </c>
       <c r="I70" s="14">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="J70" s="9"/>
       <c r="K70" s="18">
@@ -9399,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="18">
-        <f>J70*12.95</f>
+        <f>K70+J70/2</f>
         <v>0</v>
       </c>
       <c r="M70" s="17">
@@ -9415,27 +9420,27 @@
     <row r="71" spans="1:15">
       <c r="A71" s="13"/>
       <c r="B71" s="28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E71" s="27"/>
       <c r="F71" s="8">
-        <v>13.5</v>
+        <v>12.15</v>
       </c>
       <c r="G71" s="14">
         <f>I71/(1+H71)</f>
-        <v>176.106194690266</v>
+        <v>233.628318584071</v>
       </c>
       <c r="H71" s="16">
         <v>0.13</v>
       </c>
       <c r="I71" s="14">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="J71" s="9"/>
       <c r="K71" s="18">
@@ -9443,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="18">
-        <f>J71*14.15</f>
+        <f>J71*12.95</f>
         <v>0</v>
       </c>
       <c r="M71" s="17">
@@ -9458,97 +9463,96 @@
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="13"/>
-      <c r="B72" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="16"/>
+      <c r="B72" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" s="27"/>
+      <c r="F72" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="G72" s="14">
+        <f>I72/(1+H72)</f>
+        <v>176.106194690266</v>
+      </c>
+      <c r="H72" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="I72" s="14">
+        <v>199</v>
+      </c>
+      <c r="J72" s="9"/>
+      <c r="K72" s="18">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="L72" s="18">
-        <f>K72+J72/2</f>
-        <v>0</v>
-      </c>
-      <c r="M72" s="2"/>
+        <f>J72*14.15</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N72" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="13"/>
-      <c r="B73" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C73" s="8" t="s">
+      <c r="B73" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="16"/>
+      <c r="L73" s="18">
+        <f>K73+J73/2</f>
+        <v>0</v>
+      </c>
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="13"/>
+      <c r="B74" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D73" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E73" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="F73" s="8">
+      <c r="D74" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F74" s="8">
         <v>2.4</v>
       </c>
-      <c r="G73" s="14">
+      <c r="G74" s="14">
         <f>5575.22/60</f>
         <v>92.9203333333333</v>
       </c>
-      <c r="H73" s="16">
-        <v>0.13</v>
-      </c>
-      <c r="I73" s="17">
-        <f>G73*(1+H73)</f>
-        <v>104.999976666667</v>
-      </c>
-      <c r="J73" s="9"/>
-      <c r="K73" s="18">
-        <f t="shared" ref="K73:K79" si="12">J73*F73</f>
-        <v>0</v>
-      </c>
-      <c r="L73" s="18">
-        <f>K73+J73/2</f>
-        <v>0</v>
-      </c>
-      <c r="M73" s="17">
-        <f t="shared" ref="M73:M79" si="13">J73*I73</f>
-        <v>0</v>
-      </c>
-      <c r="N73" s="19">
-        <f t="shared" ref="N73:N79" si="14">M73+J73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
-      <c r="A74" s="13"/>
-      <c r="B74" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E74" s="27">
-        <v>1000</v>
-      </c>
-      <c r="F74" s="8">
-        <v>7</v>
-      </c>
-      <c r="G74" s="14">
-        <f>I74/(1+H74)</f>
-        <v>230.088495575221</v>
-      </c>
       <c r="H74" s="16">
         <v>0.13</v>
       </c>
       <c r="I74" s="17">
-        <v>260</v>
+        <f>G74*(1+H74)</f>
+        <v>104.999976666667</v>
       </c>
       <c r="J74" s="9"/>
       <c r="K74" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="K74:K80" si="12">J74*F74</f>
         <v>0</v>
       </c>
       <c r="L74" s="18">
@@ -9556,40 +9560,40 @@
         <v>0</v>
       </c>
       <c r="M74" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="M74:M80" si="13">J74*I74</f>
         <v>0</v>
       </c>
       <c r="N74" s="19">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="N74:N80" si="14">M74+J74</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="13"/>
-      <c r="B75" s="26" t="s">
-        <v>201</v>
+      <c r="B75" s="28" t="s">
+        <v>202</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>193</v>
+        <v>201</v>
+      </c>
+      <c r="E75" s="27">
+        <v>1000</v>
       </c>
       <c r="F75" s="8">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="G75" s="14">
         <f>I75/(1+H75)</f>
-        <v>141.592920353982</v>
+        <v>230.088495575221</v>
       </c>
       <c r="H75" s="16">
         <v>0.13</v>
       </c>
       <c r="I75" s="17">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="J75" s="9"/>
       <c r="K75" s="18">
@@ -9597,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="18">
-        <f t="shared" ref="L75:L77" si="15">K75+J75/2</f>
+        <f>K75+J75/2</f>
         <v>0</v>
       </c>
       <c r="M75" s="17">
@@ -9611,18 +9615,20 @@
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="13"/>
-      <c r="B76" s="28" t="s">
-        <v>202</v>
+      <c r="B76" s="26" t="s">
+        <v>203</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E76" s="27"/>
+        <v>201</v>
+      </c>
+      <c r="E76" s="27" t="s">
+        <v>195</v>
+      </c>
       <c r="F76" s="8">
-        <v>5.2</v>
+        <v>9.25</v>
       </c>
       <c r="G76" s="14">
         <f>I76/(1+H76)</f>
@@ -9640,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="L76:L78" si="15">K76+J76/2</f>
         <v>0</v>
       </c>
       <c r="M76" s="17">
@@ -9655,27 +9661,27 @@
     <row r="77" spans="1:15">
       <c r="A77" s="13"/>
       <c r="B77" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E77" s="27"/>
       <c r="F77" s="8">
-        <v>8.55</v>
+        <v>5.2</v>
       </c>
       <c r="G77" s="14">
         <f>I77/(1+H77)</f>
-        <v>224.778761061947</v>
+        <v>141.592920353982</v>
       </c>
       <c r="H77" s="16">
         <v>0.13</v>
       </c>
       <c r="I77" s="17">
-        <v>254</v>
+        <v>160</v>
       </c>
       <c r="J77" s="9"/>
       <c r="K77" s="18">
@@ -9683,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="18">
-        <f>J77*9.7</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M77" s="17">
@@ -9698,27 +9704,27 @@
     <row r="78" spans="1:15">
       <c r="A78" s="13"/>
       <c r="B78" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E78" s="27"/>
       <c r="F78" s="8">
-        <v>10.2</v>
+        <v>8.55</v>
       </c>
       <c r="G78" s="14">
         <f>I78/(1+H78)</f>
-        <v>156.637168141593</v>
+        <v>224.778761061947</v>
       </c>
       <c r="H78" s="16">
         <v>0.13</v>
       </c>
       <c r="I78" s="17">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="J78" s="9"/>
       <c r="K78" s="18">
@@ -9726,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="18">
-        <f>J78*11.8</f>
+        <f>J78*9.7</f>
         <v>0</v>
       </c>
       <c r="M78" s="17">
@@ -9740,74 +9746,72 @@
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="13"/>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E79" s="27"/>
+      <c r="F79" s="8">
+        <v>10.2</v>
+      </c>
+      <c r="G79" s="14">
+        <f>I79/(1+H79)</f>
+        <v>156.637168141593</v>
+      </c>
+      <c r="H79" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="I79" s="17">
+        <v>177</v>
+      </c>
+      <c r="J79" s="9"/>
+      <c r="K79" s="18">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L79" s="18">
+        <f>J79*11.8</f>
+        <v>0</v>
+      </c>
+      <c r="M79" s="17">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N79" s="19">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="13"/>
+      <c r="B80" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="18">
-        <f t="shared" ref="L79:L92" si="16">K79+J79/2</f>
-        <v>0</v>
-      </c>
-      <c r="M79" s="17"/>
-      <c r="N79" s="19">
-        <f t="shared" ref="N79:N102" si="17">M79+J79</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:15">
-      <c r="A80" s="13"/>
-      <c r="B80" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F80" s="8">
-        <v>6.3</v>
-      </c>
-      <c r="G80" s="14">
-        <v>68</v>
-      </c>
-      <c r="H80" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I80" s="17">
-        <f t="shared" ref="I80:I87" si="18">G80*(1+H80)</f>
-        <v>73.44</v>
-      </c>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="17"/>
       <c r="J80" s="9"/>
-      <c r="K80" s="18">
-        <f t="shared" ref="K80:K102" si="19">J80*F80</f>
-        <v>0</v>
-      </c>
+      <c r="K80" s="18"/>
       <c r="L80" s="18">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="17">
-        <f t="shared" ref="M80:M102" si="20">J80*I80</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L80:L93" si="16">K80+J80/2</f>
+        <v>0</v>
+      </c>
+      <c r="M80" s="17"/>
       <c r="N80" s="19">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
+        <f t="shared" ref="N80:N103" si="17">M80+J80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" spans="1:14">
       <c r="A81" s="13"/>
       <c r="B81" s="20" t="s">
         <v>207</v>
@@ -9819,24 +9823,24 @@
         <v>136</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F81" s="8">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G81" s="14">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H81" s="16">
         <v>0.08</v>
       </c>
       <c r="I81" s="17">
-        <f t="shared" si="18"/>
-        <v>79.92</v>
+        <f t="shared" ref="I81:I88" si="18">G81*(1+H81)</f>
+        <v>73.44</v>
       </c>
       <c r="J81" s="9"/>
       <c r="K81" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="K81:K103" si="19">J81*F81</f>
         <v>0</v>
       </c>
       <c r="L81" s="18">
@@ -9844,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="M81:M103" si="20">J81*I81</f>
         <v>0</v>
       </c>
       <c r="N81" s="19">
@@ -9855,7 +9859,7 @@
     <row r="82" spans="1:14">
       <c r="A82" s="13"/>
       <c r="B82" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C82" s="9" t="s">
         <v>91</v>
@@ -9864,20 +9868,20 @@
         <v>136</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F82" s="8">
         <v>7.5</v>
       </c>
       <c r="G82" s="14">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H82" s="16">
         <v>0.08</v>
       </c>
       <c r="I82" s="17">
         <f t="shared" si="18"/>
-        <v>88.56</v>
+        <v>79.92</v>
       </c>
       <c r="J82" s="9"/>
       <c r="K82" s="18">
@@ -9899,8 +9903,8 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="13"/>
-      <c r="B83" s="13" t="s">
-        <v>209</v>
+      <c r="B83" s="20" t="s">
+        <v>210</v>
       </c>
       <c r="C83" s="9" t="s">
         <v>91</v>
@@ -9909,20 +9913,20 @@
         <v>136</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F83" s="8">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G83" s="14">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H83" s="16">
         <v>0.08</v>
       </c>
       <c r="I83" s="17">
         <f t="shared" si="18"/>
-        <v>97.2</v>
+        <v>88.56</v>
       </c>
       <c r="J83" s="9"/>
       <c r="K83" s="18">
@@ -9944,8 +9948,8 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="13"/>
-      <c r="B84" s="20" t="s">
-        <v>210</v>
+      <c r="B84" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>91</v>
@@ -9954,20 +9958,20 @@
         <v>136</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="F84" s="8">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="G84" s="14">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H84" s="16">
         <v>0.08</v>
       </c>
       <c r="I84" s="17">
         <f t="shared" si="18"/>
-        <v>65.88</v>
+        <v>97.2</v>
       </c>
       <c r="J84" s="9"/>
       <c r="K84" s="18">
@@ -9989,8 +9993,8 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="13"/>
-      <c r="B85" s="13" t="s">
-        <v>211</v>
+      <c r="B85" s="20" t="s">
+        <v>212</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>91</v>
@@ -10005,14 +10009,14 @@
         <v>5.5</v>
       </c>
       <c r="G85" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H85" s="16">
         <v>0.08</v>
       </c>
       <c r="I85" s="17">
         <f t="shared" si="18"/>
-        <v>63.72</v>
+        <v>65.88</v>
       </c>
       <c r="J85" s="9"/>
       <c r="K85" s="18">
@@ -10034,8 +10038,8 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="13"/>
-      <c r="B86" s="20" t="s">
-        <v>212</v>
+      <c r="B86" s="13" t="s">
+        <v>213</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>91</v>
@@ -10050,14 +10054,14 @@
         <v>5.5</v>
       </c>
       <c r="G86" s="14">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H86" s="16">
         <v>0.08</v>
       </c>
       <c r="I86" s="17">
         <f t="shared" si="18"/>
-        <v>65.88</v>
+        <v>63.72</v>
       </c>
       <c r="J86" s="9"/>
       <c r="K86" s="18">
@@ -10079,8 +10083,8 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="13"/>
-      <c r="B87" s="20">
-        <v>6828</v>
+      <c r="B87" s="20" t="s">
+        <v>214</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>91</v>
@@ -10095,14 +10099,14 @@
         <v>5.5</v>
       </c>
       <c r="G87" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H87" s="16">
         <v>0.08</v>
       </c>
       <c r="I87" s="17">
         <f t="shared" si="18"/>
-        <v>63.72</v>
+        <v>65.88</v>
       </c>
       <c r="J87" s="9"/>
       <c r="K87" s="18">
@@ -10122,32 +10126,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" s="2" customFormat="1" spans="1:14">
+    <row r="88" spans="1:14">
       <c r="A88" s="13"/>
-      <c r="B88" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="C88" s="30" t="s">
-        <v>214</v>
+      <c r="B88" s="20">
+        <v>6828</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E88" s="31" t="s">
-        <v>129</v>
+      <c r="E88" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="F88" s="8">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="G88" s="14">
-        <f t="shared" ref="G88:G92" si="21">I88-1</f>
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H88" s="16">
         <v>0.08</v>
       </c>
-      <c r="I88" s="14">
-        <v>90</v>
+      <c r="I88" s="17">
+        <f t="shared" si="18"/>
+        <v>63.72</v>
       </c>
       <c r="J88" s="9"/>
       <c r="K88" s="18">
@@ -10173,26 +10177,26 @@
         <v>215</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E89" s="31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F89" s="8">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
       <c r="G89" s="14">
-        <f t="shared" si="21"/>
-        <v>69</v>
+        <f t="shared" ref="G89:G93" si="21">I89-1</f>
+        <v>89</v>
       </c>
       <c r="H89" s="16">
         <v>0.08</v>
       </c>
       <c r="I89" s="14">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J89" s="9"/>
       <c r="K89" s="18">
@@ -10214,30 +10218,30 @@
     </row>
     <row r="90" s="2" customFormat="1" spans="1:14">
       <c r="A90" s="13"/>
-      <c r="B90" s="32" t="s">
+      <c r="B90" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="C90" s="30" t="s">
         <v>216</v>
-      </c>
-      <c r="C90" s="30" t="s">
-        <v>214</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F90" s="8">
-        <v>8.4</v>
+        <v>6.3</v>
       </c>
       <c r="G90" s="14">
         <f t="shared" si="21"/>
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H90" s="16">
         <v>0.08</v>
       </c>
       <c r="I90" s="14">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="18">
@@ -10259,11 +10263,11 @@
     </row>
     <row r="91" s="2" customFormat="1" spans="1:14">
       <c r="A91" s="13"/>
-      <c r="B91" s="30" t="s">
-        <v>217</v>
+      <c r="B91" s="32" t="s">
+        <v>218</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>136</v>
@@ -10272,17 +10276,17 @@
         <v>166</v>
       </c>
       <c r="F91" s="8">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="G91" s="14">
         <f t="shared" si="21"/>
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="H91" s="16">
         <v>0.08</v>
       </c>
       <c r="I91" s="14">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J91" s="9"/>
       <c r="K91" s="18">
@@ -10305,29 +10309,29 @@
     <row r="92" s="2" customFormat="1" spans="1:14">
       <c r="A92" s="13"/>
       <c r="B92" s="30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F92" s="8">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="G92" s="14">
         <f t="shared" si="21"/>
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H92" s="16">
         <v>0.08</v>
       </c>
       <c r="I92" s="14">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J92" s="9"/>
       <c r="K92" s="18">
@@ -10349,11 +10353,11 @@
     </row>
     <row r="93" s="2" customFormat="1" spans="1:14">
       <c r="A93" s="13"/>
-      <c r="B93" s="32" t="s">
-        <v>219</v>
+      <c r="B93" s="30" t="s">
+        <v>220</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>136</v>
@@ -10362,107 +10366,107 @@
         <v>129</v>
       </c>
       <c r="F93" s="8">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
       <c r="G93" s="14">
-        <f t="shared" ref="G93:G98" si="22">I93-1</f>
-        <v>113</v>
+        <f t="shared" si="21"/>
+        <v>89</v>
       </c>
       <c r="H93" s="16">
         <v>0.08</v>
       </c>
       <c r="I93" s="14">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="J93" s="9"/>
       <c r="K93" s="18">
-        <f t="shared" ref="K93:K106" si="23">J93*F93</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L93" s="18">
-        <f t="shared" ref="L93:L106" si="24">K93+J93/2</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M93" s="17">
-        <f t="shared" ref="M93:M106" si="25">J93*I93</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N93" s="19">
-        <f t="shared" ref="N93:N106" si="26">M93+J93</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" s="2" customFormat="1" spans="1:14">
       <c r="A94" s="13"/>
       <c r="B94" s="32" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C94" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E94" s="31" t="s">
-        <v>221</v>
+        <v>129</v>
       </c>
       <c r="F94" s="8">
+        <v>10.2</v>
+      </c>
+      <c r="G94" s="14">
+        <f t="shared" ref="G94:G99" si="22">I94-1</f>
+        <v>113</v>
+      </c>
+      <c r="H94" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I94" s="14">
+        <v>114</v>
+      </c>
+      <c r="J94" s="9"/>
+      <c r="K94" s="18">
+        <f t="shared" ref="K94:K107" si="23">J94*F94</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="18">
+        <f t="shared" ref="L94:L107" si="24">K94+J94/2</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="17">
+        <f t="shared" ref="M94:M107" si="25">J94*I94</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="19">
+        <f t="shared" ref="N94:N107" si="26">M94+J94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" spans="1:14">
+      <c r="A95" s="13"/>
+      <c r="B95" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="F95" s="8">
         <v>7.2</v>
       </c>
-      <c r="G94" s="14">
+      <c r="G95" s="14">
         <f t="shared" si="22"/>
         <v>73</v>
       </c>
-      <c r="H94" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I94" s="14">
-        <v>74</v>
-      </c>
-      <c r="J94" s="9"/>
-      <c r="K94" s="18">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="L94" s="18">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="N94" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" s="2" customFormat="1" spans="1:14">
-      <c r="A95" s="13"/>
-      <c r="B95" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="C95" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E95" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="F95" s="8">
-        <v>6.9</v>
-      </c>
-      <c r="G95" s="14">
-        <f t="shared" si="22"/>
-        <v>73.7</v>
-      </c>
       <c r="H95" s="16">
         <v>0.08</v>
       </c>
       <c r="I95" s="14">
-        <v>74.7</v>
+        <v>74</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="18">
@@ -10485,10 +10489,10 @@
     <row r="96" s="2" customFormat="1" spans="1:14">
       <c r="A96" s="13"/>
       <c r="B96" s="30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>136</v>
@@ -10497,17 +10501,17 @@
         <v>129</v>
       </c>
       <c r="F96" s="8">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="G96" s="14">
         <f t="shared" si="22"/>
-        <v>74.1</v>
+        <v>73.7</v>
       </c>
       <c r="H96" s="16">
         <v>0.08</v>
       </c>
       <c r="I96" s="14">
-        <v>75.1</v>
+        <v>74.7</v>
       </c>
       <c r="J96" s="9"/>
       <c r="K96" s="18">
@@ -10530,29 +10534,29 @@
     <row r="97" s="2" customFormat="1" spans="1:14">
       <c r="A97" s="13"/>
       <c r="B97" s="30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F97" s="8">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="G97" s="14">
         <f t="shared" si="22"/>
-        <v>58.1</v>
+        <v>74.1</v>
       </c>
       <c r="H97" s="16">
         <v>0.08</v>
       </c>
       <c r="I97" s="14">
-        <v>59.1</v>
+        <v>75.1</v>
       </c>
       <c r="J97" s="9"/>
       <c r="K97" s="18">
@@ -10575,10 +10579,10 @@
     <row r="98" s="2" customFormat="1" spans="1:14">
       <c r="A98" s="13"/>
       <c r="B98" s="30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C98" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>136</v>
@@ -10591,13 +10595,13 @@
       </c>
       <c r="G98" s="14">
         <f t="shared" si="22"/>
-        <v>124</v>
+        <v>58.1</v>
       </c>
       <c r="H98" s="16">
         <v>0.08</v>
       </c>
       <c r="I98" s="14">
-        <v>125</v>
+        <v>59.1</v>
       </c>
       <c r="J98" s="9"/>
       <c r="K98" s="18">
@@ -10619,27 +10623,30 @@
     </row>
     <row r="99" s="2" customFormat="1" spans="1:14">
       <c r="A99" s="13"/>
-      <c r="B99" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="C99" s="13" t="s">
+      <c r="B99" s="30" t="s">
         <v>227</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E99" s="13"/>
+      <c r="E99" s="31" t="s">
+        <v>127</v>
+      </c>
       <c r="F99" s="8">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="G99" s="14">
-        <v>80</v>
+        <f t="shared" si="22"/>
+        <v>124</v>
       </c>
       <c r="H99" s="16">
         <v>0.08</v>
       </c>
       <c r="I99" s="14">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="J99" s="9"/>
       <c r="K99" s="18">
@@ -10661,30 +10668,27 @@
     </row>
     <row r="100" s="2" customFormat="1" spans="1:14">
       <c r="A100" s="13"/>
-      <c r="B100" s="20" t="s">
-        <v>205</v>
+      <c r="B100" s="13" t="s">
+        <v>228</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E100" s="15" t="s">
-        <v>206</v>
-      </c>
+      <c r="E100" s="13"/>
       <c r="F100" s="8">
         <v>6.3</v>
       </c>
       <c r="G100" s="14">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H100" s="16">
         <v>0.08</v>
       </c>
-      <c r="I100" s="17">
-        <f t="shared" ref="I100:I103" si="27">G100*(1+H100)</f>
-        <v>73.44</v>
+      <c r="I100" s="14">
+        <v>81</v>
       </c>
       <c r="J100" s="9"/>
       <c r="K100" s="18">
@@ -10710,26 +10714,26 @@
         <v>207</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F101" s="8">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="G101" s="14">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H101" s="16">
         <v>0.08</v>
       </c>
       <c r="I101" s="17">
-        <f t="shared" si="27"/>
-        <v>79.92</v>
+        <f t="shared" ref="I101:I104" si="27">G101*(1+H101)</f>
+        <v>73.44</v>
       </c>
       <c r="J101" s="9"/>
       <c r="K101" s="18">
@@ -10752,29 +10756,29 @@
     <row r="102" s="2" customFormat="1" spans="1:14">
       <c r="A102" s="13"/>
       <c r="B102" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F102" s="8">
         <v>7.5</v>
       </c>
       <c r="G102" s="14">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H102" s="16">
         <v>0.08</v>
       </c>
       <c r="I102" s="17">
         <f t="shared" si="27"/>
-        <v>88.56</v>
+        <v>79.92</v>
       </c>
       <c r="J102" s="9"/>
       <c r="K102" s="18">
@@ -10796,30 +10800,30 @@
     </row>
     <row r="103" s="2" customFormat="1" spans="1:14">
       <c r="A103" s="13"/>
-      <c r="B103" s="13" t="s">
-        <v>209</v>
+      <c r="B103" s="20" t="s">
+        <v>210</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F103" s="8">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G103" s="14">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H103" s="16">
         <v>0.08</v>
       </c>
       <c r="I103" s="17">
         <f t="shared" si="27"/>
-        <v>97.2</v>
+        <v>88.56</v>
       </c>
       <c r="J103" s="9"/>
       <c r="K103" s="18">
@@ -10842,28 +10846,29 @@
     <row r="104" s="2" customFormat="1" spans="1:14">
       <c r="A104" s="13"/>
       <c r="B104" s="13" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="F104" s="8">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="G104" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H104" s="16">
         <v>0.08</v>
       </c>
       <c r="I104" s="17">
-        <v>79</v>
+        <f t="shared" si="27"/>
+        <v>97.2</v>
       </c>
       <c r="J104" s="9"/>
       <c r="K104" s="18">
@@ -10885,30 +10890,29 @@
     </row>
     <row r="105" s="2" customFormat="1" spans="1:14">
       <c r="A105" s="13"/>
-      <c r="B105" s="30" t="s">
+      <c r="B105" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C105" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>227</v>
       </c>
       <c r="D105" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E105" s="31" t="s">
-        <v>127</v>
+      <c r="E105" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="F105" s="8">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="G105" s="14">
-        <f>I105-1</f>
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H105" s="16">
         <v>0.08</v>
       </c>
-      <c r="I105" s="14">
-        <v>70</v>
+      <c r="I105" s="17">
+        <v>79</v>
       </c>
       <c r="J105" s="9"/>
       <c r="K105" s="18">
@@ -10931,29 +10935,29 @@
     <row r="106" s="2" customFormat="1" spans="1:14">
       <c r="A106" s="13"/>
       <c r="B106" s="30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D106" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E106" s="31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F106" s="8">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="G106" s="14">
         <f>I106-1</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="H106" s="16">
         <v>0.08</v>
       </c>
       <c r="I106" s="14">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="J106" s="9"/>
       <c r="K106" s="18">
@@ -10973,109 +10977,109 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" s="2" customFormat="1" spans="1:14">
       <c r="A107" s="13"/>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="14"/>
-      <c r="H107" s="16"/>
-      <c r="I107" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="J107" s="25"/>
-      <c r="K107" s="25"/>
+      <c r="B107" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="F107" s="8">
+        <v>6</v>
+      </c>
+      <c r="G107" s="14">
+        <f>I107-1</f>
+        <v>58</v>
+      </c>
+      <c r="H107" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I107" s="14">
+        <v>59</v>
+      </c>
+      <c r="J107" s="9"/>
+      <c r="K107" s="18">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="L107" s="18">
-        <f t="shared" ref="L107:L122" si="28">K107+J107/2</f>
-        <v>0</v>
-      </c>
-      <c r="M107" s="25"/>
-      <c r="N107" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N107" s="19">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="13"/>
-      <c r="B108" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="12"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="8"/>
       <c r="G108" s="14"/>
       <c r="H108" s="16"/>
-      <c r="I108" s="17"/>
-      <c r="J108" s="9" t="s">
+      <c r="I108" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="K108" s="18"/>
+      <c r="J108" s="25"/>
+      <c r="K108" s="25"/>
       <c r="L108" s="18">
-        <v>0</v>
-      </c>
-      <c r="M108" s="17"/>
-      <c r="N108" s="19">
-        <v>0</v>
-      </c>
+        <f t="shared" ref="L108:L123" si="28">K108+J108/2</f>
+        <v>0</v>
+      </c>
+      <c r="M108" s="25"/>
+      <c r="N108" s="25"/>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="13"/>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="C109" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D109" s="14" t="s">
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="17"/>
+      <c r="J109" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="E109" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F109" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="G109" s="14">
-        <v>50.5</v>
-      </c>
-      <c r="H109" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I109" s="17">
-        <f>G109*(1+H109)</f>
-        <v>54.54</v>
-      </c>
-      <c r="J109" s="9"/>
-      <c r="K109" s="18">
-        <f>J109*F109</f>
-        <v>0</v>
-      </c>
+      <c r="K109" s="18"/>
       <c r="L109" s="18">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="17">
-        <f>J109*I109</f>
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M109" s="17"/>
       <c r="N109" s="19">
-        <f>M109+J109</f>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="13"/>
       <c r="B110" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C110" s="13" t="s">
-        <v>227</v>
+        <v>236</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F110" s="8">
         <v>4.5</v>
@@ -11110,24 +11114,48 @@
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="13"/>
-      <c r="B111" s="13"/>
-      <c r="C111" s="13"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="14"/>
-      <c r="H111" s="16"/>
-      <c r="I111" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="J111" s="25"/>
-      <c r="K111" s="25"/>
+      <c r="B111" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F111" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G111" s="14">
+        <v>50.5</v>
+      </c>
+      <c r="H111" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I111" s="17">
+        <f>G111*(1+H111)</f>
+        <v>54.54</v>
+      </c>
+      <c r="J111" s="9"/>
+      <c r="K111" s="18">
+        <f>J111*F111</f>
+        <v>0</v>
+      </c>
       <c r="L111" s="18">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="M111" s="25"/>
-      <c r="N111" s="25"/>
+      <c r="M111" s="17">
+        <f>J111*I111</f>
+        <v>0</v>
+      </c>
+      <c r="N111" s="19">
+        <f>M111+J111</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="13"/>
@@ -11138,25 +11166,25 @@
       <c r="F112" s="8"/>
       <c r="G112" s="14"/>
       <c r="H112" s="16"/>
-      <c r="I112" s="17"/>
-      <c r="J112" s="9"/>
-      <c r="K112" s="18"/>
+      <c r="I112" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="J112" s="25"/>
+      <c r="K112" s="25"/>
       <c r="L112" s="18">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="M112" s="17"/>
-      <c r="N112" s="19"/>
+      <c r="M112" s="25"/>
+      <c r="N112" s="25"/>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="13"/>
-      <c r="B113" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="12"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="8"/>
       <c r="G113" s="14"/>
       <c r="H113" s="16"/>
       <c r="I113" s="17"/>
@@ -11167,60 +11195,36 @@
         <v>0</v>
       </c>
       <c r="M113" s="17"/>
-      <c r="N113" s="19">
-        <f t="shared" ref="N113:N126" si="29">M113+J113</f>
-        <v>0</v>
-      </c>
+      <c r="N113" s="19"/>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="13"/>
-      <c r="B114" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D114" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E114" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F114" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="G114" s="14">
-        <v>51</v>
-      </c>
-      <c r="H114" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I114" s="17">
-        <f t="shared" ref="I114:I126" si="30">G114*(1+H114)</f>
-        <v>55.08</v>
-      </c>
+      <c r="B114" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="16"/>
+      <c r="I114" s="17"/>
       <c r="J114" s="9"/>
-      <c r="K114" s="18">
-        <f t="shared" ref="K114:K126" si="31">J114*F114</f>
-        <v>0</v>
-      </c>
+      <c r="K114" s="18"/>
       <c r="L114" s="18">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="M114" s="17">
-        <f t="shared" ref="M114:M126" si="32">J114*I114</f>
-        <v>0</v>
-      </c>
+      <c r="M114" s="17"/>
       <c r="N114" s="19">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" ht="14" customHeight="1" spans="1:14">
+        <f t="shared" ref="N114:N127" si="29">M114+J114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115" s="13"/>
-      <c r="B115" s="13" t="s">
-        <v>238</v>
+      <c r="B115" s="20" t="s">
+        <v>239</v>
       </c>
       <c r="C115" s="9" t="s">
         <v>91</v>
@@ -11229,65 +11233,65 @@
         <v>126</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F115" s="8">
         <v>4.5</v>
       </c>
       <c r="G115" s="14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H115" s="16">
         <v>0.08</v>
       </c>
       <c r="I115" s="17">
+        <f t="shared" ref="I115:I127" si="30">G115*(1+H115)</f>
+        <v>55.08</v>
+      </c>
+      <c r="J115" s="9"/>
+      <c r="K115" s="18">
+        <f t="shared" ref="K115:K127" si="31">J115*F115</f>
+        <v>0</v>
+      </c>
+      <c r="L115" s="18">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="17">
+        <f t="shared" ref="M115:M127" si="32">J115*I115</f>
+        <v>0</v>
+      </c>
+      <c r="N115" s="19">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" ht="14" customHeight="1" spans="1:14">
+      <c r="A116" s="13"/>
+      <c r="B116" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F116" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G116" s="14">
+        <v>54</v>
+      </c>
+      <c r="H116" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I116" s="17">
         <f t="shared" si="30"/>
         <v>58.32</v>
-      </c>
-      <c r="J115" s="9"/>
-      <c r="K115" s="18">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="L115" s="18">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="M115" s="17">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="N115" s="19">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
-      <c r="A116" s="13"/>
-      <c r="B116" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D116" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E116" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F116" s="8">
-        <v>5.5</v>
-      </c>
-      <c r="G116" s="14">
-        <v>61</v>
-      </c>
-      <c r="H116" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I116" s="17">
-        <f t="shared" si="30"/>
-        <v>65.88</v>
       </c>
       <c r="J116" s="9"/>
       <c r="K116" s="18">
@@ -11310,7 +11314,7 @@
     <row r="117" spans="1:14">
       <c r="A117" s="13"/>
       <c r="B117" s="20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C117" s="9" t="s">
         <v>91</v>
@@ -11319,20 +11323,20 @@
         <v>126</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F117" s="8">
         <v>5.5</v>
       </c>
       <c r="G117" s="14">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H117" s="16">
         <v>0.08</v>
       </c>
       <c r="I117" s="17">
         <f t="shared" si="30"/>
-        <v>69.12</v>
+        <v>65.88</v>
       </c>
       <c r="J117" s="9"/>
       <c r="K117" s="18">
@@ -11355,7 +11359,7 @@
     <row r="118" spans="1:14">
       <c r="A118" s="13"/>
       <c r="B118" s="20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C118" s="9" t="s">
         <v>91</v>
@@ -11364,14 +11368,21 @@
         <v>126</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F118" s="8"/>
-      <c r="G118" s="14"/>
+        <v>208</v>
+      </c>
+      <c r="F118" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="G118" s="14">
+        <v>64</v>
+      </c>
       <c r="H118" s="16">
         <v>0.08</v>
       </c>
-      <c r="I118" s="17"/>
+      <c r="I118" s="17">
+        <f t="shared" si="30"/>
+        <v>69.12</v>
+      </c>
       <c r="J118" s="9"/>
       <c r="K118" s="18">
         <f t="shared" si="31"/>
@@ -11393,7 +11404,7 @@
     <row r="119" spans="1:14">
       <c r="A119" s="13"/>
       <c r="B119" s="20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C119" s="9" t="s">
         <v>91</v>
@@ -11402,21 +11413,14 @@
         <v>126</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F119" s="8">
-        <v>6.5</v>
-      </c>
-      <c r="G119" s="14">
-        <v>69</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="F119" s="8"/>
+      <c r="G119" s="14"/>
       <c r="H119" s="16">
         <v>0.08</v>
       </c>
-      <c r="I119" s="17">
-        <f t="shared" si="30"/>
-        <v>74.52</v>
-      </c>
+      <c r="I119" s="17"/>
       <c r="J119" s="9"/>
       <c r="K119" s="18">
         <f t="shared" si="31"/>
@@ -11437,8 +11441,8 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="13"/>
-      <c r="B120" s="13" t="s">
-        <v>243</v>
+      <c r="B120" s="20" t="s">
+        <v>244</v>
       </c>
       <c r="C120" s="9" t="s">
         <v>91</v>
@@ -11447,20 +11451,20 @@
         <v>126</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F120" s="8">
         <v>6.5</v>
       </c>
       <c r="G120" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H120" s="16">
         <v>0.08</v>
       </c>
       <c r="I120" s="17">
         <f t="shared" si="30"/>
-        <v>77.76</v>
+        <v>74.52</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="18">
@@ -11482,8 +11486,8 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="13"/>
-      <c r="B121" s="20" t="s">
-        <v>244</v>
+      <c r="B121" s="13" t="s">
+        <v>245</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>91</v>
@@ -11492,20 +11496,20 @@
         <v>126</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F121" s="8">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G121" s="14">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H121" s="16">
         <v>0.08</v>
       </c>
       <c r="I121" s="17">
         <f t="shared" si="30"/>
-        <v>97.2</v>
+        <v>77.76</v>
       </c>
       <c r="J121" s="9"/>
       <c r="K121" s="18">
@@ -11528,7 +11532,7 @@
     <row r="122" spans="1:14">
       <c r="A122" s="13"/>
       <c r="B122" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C122" s="9" t="s">
         <v>91</v>
@@ -11537,22 +11541,22 @@
         <v>126</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F122" s="8">
         <v>8.5</v>
       </c>
       <c r="G122" s="14">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H122" s="16">
         <v>0.08</v>
       </c>
       <c r="I122" s="17">
         <f t="shared" si="30"/>
-        <v>100.44</v>
-      </c>
-      <c r="J122" s="33"/>
+        <v>97.2</v>
+      </c>
+      <c r="J122" s="9"/>
       <c r="K122" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -11572,8 +11576,8 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="13"/>
-      <c r="B123" s="13" t="s">
-        <v>246</v>
+      <c r="B123" s="20" t="s">
+        <v>247</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>91</v>
@@ -11582,21 +11586,28 @@
         <v>126</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F123" s="8"/>
-      <c r="G123" s="14"/>
+        <v>208</v>
+      </c>
+      <c r="F123" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G123" s="14">
+        <v>93</v>
+      </c>
       <c r="H123" s="16">
         <v>0.08</v>
       </c>
-      <c r="I123" s="17"/>
-      <c r="J123" s="9"/>
+      <c r="I123" s="17">
+        <f t="shared" si="30"/>
+        <v>100.44</v>
+      </c>
+      <c r="J123" s="33"/>
       <c r="K123" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L123" s="18">
-        <f t="shared" ref="L123:L128" si="33">K123+J123/2</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M123" s="17">
@@ -11610,8 +11621,8 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="13"/>
-      <c r="B124" s="20" t="s">
-        <v>247</v>
+      <c r="B124" s="13" t="s">
+        <v>248</v>
       </c>
       <c r="C124" s="9" t="s">
         <v>91</v>
@@ -11622,26 +11633,19 @@
       <c r="E124" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F124" s="8">
-        <v>6.8</v>
-      </c>
-      <c r="G124" s="14">
-        <v>71</v>
-      </c>
+      <c r="F124" s="8"/>
+      <c r="G124" s="14"/>
       <c r="H124" s="16">
         <v>0.08</v>
       </c>
-      <c r="I124" s="17">
-        <f t="shared" si="30"/>
-        <v>76.68</v>
-      </c>
+      <c r="I124" s="17"/>
       <c r="J124" s="9"/>
       <c r="K124" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L124" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="L124:L129" si="33">K124+J124/2</f>
         <v>0</v>
       </c>
       <c r="M124" s="17">
@@ -11656,7 +11660,7 @@
     <row r="125" spans="1:14">
       <c r="A125" s="13"/>
       <c r="B125" s="20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>91</v>
@@ -11671,14 +11675,14 @@
         <v>6.8</v>
       </c>
       <c r="G125" s="14">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H125" s="16">
         <v>0.08</v>
       </c>
       <c r="I125" s="17">
         <f t="shared" si="30"/>
-        <v>79.92</v>
+        <v>76.68</v>
       </c>
       <c r="J125" s="9"/>
       <c r="K125" s="18">
@@ -11700,8 +11704,8 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="13"/>
-      <c r="B126" s="13" t="s">
-        <v>249</v>
+      <c r="B126" s="20" t="s">
+        <v>250</v>
       </c>
       <c r="C126" s="9" t="s">
         <v>91</v>
@@ -11712,12 +11716,19 @@
       <c r="E126" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F126" s="8"/>
-      <c r="G126" s="14"/>
+      <c r="F126" s="8">
+        <v>6.8</v>
+      </c>
+      <c r="G126" s="14">
+        <v>74</v>
+      </c>
       <c r="H126" s="16">
         <v>0.08</v>
       </c>
-      <c r="I126" s="17"/>
+      <c r="I126" s="17">
+        <f t="shared" si="30"/>
+        <v>79.92</v>
+      </c>
       <c r="J126" s="9"/>
       <c r="K126" s="18">
         <f t="shared" si="31"/>
@@ -11738,108 +11749,104 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="13"/>
-      <c r="B127" s="13"/>
-      <c r="C127" s="13"/>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
+      <c r="B127" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E127" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="F127" s="8"/>
       <c r="G127" s="14"/>
-      <c r="H127" s="16"/>
-      <c r="I127" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="J127" s="25"/>
-      <c r="K127" s="25"/>
+      <c r="H127" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I127" s="17"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="L127" s="18">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="M127" s="25"/>
-      <c r="N127" s="25"/>
+      <c r="M127" s="17">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="N127" s="19">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="13"/>
-      <c r="B128" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D128" s="14" t="s">
+      <c r="B128" s="13"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="16"/>
+      <c r="I128" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="J128" s="25"/>
+      <c r="K128" s="25"/>
+      <c r="L128" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="25"/>
+      <c r="N128" s="25"/>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="13"/>
+      <c r="B129" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="E128" s="15" t="s">
+      <c r="C129" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F128" s="8">
+      <c r="D129" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="E129" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="F129" s="8">
         <v>4.45</v>
       </c>
-      <c r="G128" s="14">
+      <c r="G129" s="14">
         <v>74</v>
       </c>
-      <c r="H128" s="16">
+      <c r="H129" s="16">
         <v>0.08</v>
       </c>
-      <c r="I128" s="17">
+      <c r="I129" s="17">
         <v>99.5</v>
       </c>
-      <c r="J128" s="9"/>
-      <c r="K128" s="18">
-        <f t="shared" ref="K128:K131" si="34">J128*F128</f>
-        <v>0</v>
-      </c>
-      <c r="L128" s="18">
-        <f>J128*4.73</f>
-        <v>0</v>
-      </c>
-      <c r="M128" s="17">
-        <f t="shared" ref="M128:M131" si="35">J128*I128</f>
-        <v>0</v>
-      </c>
-      <c r="N128" s="19">
-        <f t="shared" ref="N128:N131" si="36">M128+J128</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" s="3" customFormat="1" spans="1:14">
-      <c r="A129" s="34"/>
-      <c r="B129" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C129" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="D129" s="36" t="s">
-        <v>252</v>
-      </c>
-      <c r="E129" s="37"/>
-      <c r="F129" s="38">
-        <v>3.2</v>
-      </c>
-      <c r="G129" s="36">
-        <v>82</v>
-      </c>
-      <c r="H129" s="39">
-        <v>0.08</v>
-      </c>
-      <c r="I129" s="40">
-        <v>83</v>
-      </c>
-      <c r="J129" s="35"/>
-      <c r="K129" s="35">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L129" s="35">
-        <f>J129*4.06</f>
-        <v>0</v>
-      </c>
-      <c r="M129" s="40">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N129" s="41">
-        <f t="shared" si="36"/>
+      <c r="J129" s="9"/>
+      <c r="K129" s="18">
+        <f t="shared" ref="K129:K132" si="34">J129*F129</f>
+        <v>0</v>
+      </c>
+      <c r="L129" s="18">
+        <f>J129*4.73</f>
+        <v>0</v>
+      </c>
+      <c r="M129" s="17">
+        <f t="shared" ref="M129:M132" si="35">J129*I129</f>
+        <v>0</v>
+      </c>
+      <c r="N129" s="19">
+        <f t="shared" ref="N129:N132" si="36">M129+J129</f>
         <v>0</v>
       </c>
     </row>
@@ -11849,23 +11856,23 @@
         <v>256</v>
       </c>
       <c r="C130" s="35" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D130" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E130" s="37"/>
       <c r="F130" s="38">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="G130" s="36">
-        <v>87.18</v>
+        <v>82</v>
       </c>
       <c r="H130" s="39">
         <v>0.08</v>
       </c>
       <c r="I130" s="40">
-        <v>88.18</v>
+        <v>83</v>
       </c>
       <c r="J130" s="35"/>
       <c r="K130" s="35">
@@ -11873,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="35">
-        <f>J130*4.88</f>
+        <f>J130*4.06</f>
         <v>0</v>
       </c>
       <c r="M130" s="40">
@@ -11888,26 +11895,26 @@
     <row r="131" s="3" customFormat="1" spans="1:14">
       <c r="A131" s="34"/>
       <c r="B131" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C131" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="C131" s="35" t="s">
-        <v>255</v>
-      </c>
       <c r="D131" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E131" s="37"/>
       <c r="F131" s="38">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="G131" s="36">
-        <v>101.04</v>
+        <v>87.18</v>
       </c>
       <c r="H131" s="39">
         <v>0.08</v>
       </c>
       <c r="I131" s="40">
-        <v>102.04</v>
+        <v>88.18</v>
       </c>
       <c r="J131" s="35"/>
       <c r="K131" s="35">
@@ -11915,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="35">
-        <f>J131*6.19</f>
+        <f>J131*4.88</f>
         <v>0</v>
       </c>
       <c r="M131" s="40">
@@ -11927,88 +11934,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
-      <c r="A132" s="13"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="14"/>
-      <c r="H132" s="16"/>
-      <c r="I132" s="17"/>
-      <c r="J132" s="9"/>
-      <c r="K132" s="18"/>
-      <c r="L132" s="18">
-        <f t="shared" ref="L132:L179" si="37">K132+J132/2</f>
-        <v>0</v>
-      </c>
-      <c r="M132" s="17"/>
-      <c r="N132" s="19">
-        <f t="shared" ref="N132:N139" si="38">M132+J132</f>
+    <row r="132" s="3" customFormat="1" spans="1:14">
+      <c r="A132" s="34"/>
+      <c r="B132" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="C132" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="D132" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="E132" s="37"/>
+      <c r="F132" s="38">
+        <v>4.95</v>
+      </c>
+      <c r="G132" s="36">
+        <v>101.04</v>
+      </c>
+      <c r="H132" s="39">
+        <v>0.08</v>
+      </c>
+      <c r="I132" s="40">
+        <v>102.04</v>
+      </c>
+      <c r="J132" s="35"/>
+      <c r="K132" s="35">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="L132" s="35">
+        <f>J132*6.19</f>
+        <v>0</v>
+      </c>
+      <c r="M132" s="40">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="N132" s="41">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="13"/>
-      <c r="B133" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="12"/>
+      <c r="F133" s="8"/>
       <c r="G133" s="14"/>
       <c r="H133" s="16"/>
       <c r="I133" s="17"/>
-      <c r="J133" s="5"/>
+      <c r="J133" s="9"/>
       <c r="K133" s="18"/>
       <c r="L133" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="L133:L180" si="37">K133+J133/2</f>
         <v>0</v>
       </c>
       <c r="M133" s="17"/>
       <c r="N133" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="N133:N140" si="38">M133+J133</f>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="13"/>
-      <c r="B134" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="C134" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D134" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E134" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F134" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="G134" s="14">
-        <v>31.5</v>
-      </c>
-      <c r="H134" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I134" s="17">
-        <f t="shared" ref="I134:I139" si="39">G134*(1+H134)</f>
-        <v>34.02</v>
-      </c>
-      <c r="J134" s="9"/>
-      <c r="K134" s="18">
-        <f t="shared" ref="K134:K139" si="40">J134*F134</f>
-        <v>0</v>
-      </c>
+      <c r="B134" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="16"/>
+      <c r="I134" s="17"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="18"/>
       <c r="L134" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M134" s="17">
-        <f t="shared" ref="M134:M139" si="41">J134*I134</f>
-        <v>0</v>
-      </c>
+      <c r="M134" s="17"/>
       <c r="N134" s="19">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -12017,7 +12021,7 @@
     <row r="135" spans="1:14">
       <c r="A135" s="13"/>
       <c r="B135" s="20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C135" s="9" t="s">
         <v>91</v>
@@ -12026,24 +12030,24 @@
         <v>123</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F135" s="8">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G135" s="14">
-        <v>42.5</v>
+        <v>31.5</v>
       </c>
       <c r="H135" s="16">
         <v>0.08</v>
       </c>
       <c r="I135" s="17">
-        <f t="shared" si="39"/>
-        <v>45.9</v>
+        <f t="shared" ref="I135:I140" si="39">G135*(1+H135)</f>
+        <v>34.02</v>
       </c>
       <c r="J135" s="9"/>
       <c r="K135" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="K135:K140" si="40">J135*F135</f>
         <v>0</v>
       </c>
       <c r="L135" s="18">
@@ -12051,7 +12055,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="M135:M140" si="41">J135*I135</f>
         <v>0</v>
       </c>
       <c r="N135" s="19">
@@ -12062,7 +12066,7 @@
     <row r="136" spans="1:14">
       <c r="A136" s="13"/>
       <c r="B136" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C136" s="9" t="s">
         <v>91</v>
@@ -12071,22 +12075,22 @@
         <v>123</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="F136" s="8">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G136" s="14">
-        <v>47</v>
+        <v>42.5</v>
       </c>
       <c r="H136" s="16">
         <v>0.08</v>
       </c>
       <c r="I136" s="17">
         <f t="shared" si="39"/>
-        <v>50.76</v>
-      </c>
-      <c r="J136" s="5"/>
+        <v>45.9</v>
+      </c>
+      <c r="J136" s="9"/>
       <c r="K136" s="18">
         <f t="shared" si="40"/>
         <v>0</v>
@@ -12105,8 +12109,9 @@
       </c>
     </row>
     <row r="137" spans="1:14">
+      <c r="A137" s="13"/>
       <c r="B137" s="20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C137" s="9" t="s">
         <v>91</v>
@@ -12114,19 +12119,21 @@
       <c r="D137" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E137" s="13"/>
+      <c r="E137" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="F137" s="8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G137" s="14">
-        <v>52</v>
-      </c>
-      <c r="H137" s="42">
-        <v>0.095</v>
+        <v>47</v>
+      </c>
+      <c r="H137" s="16">
+        <v>0.08</v>
       </c>
       <c r="I137" s="17">
         <f t="shared" si="39"/>
-        <v>56.94</v>
+        <v>50.76</v>
       </c>
       <c r="J137" s="5"/>
       <c r="K137" s="18">
@@ -12147,8 +12154,8 @@
       </c>
     </row>
     <row r="138" spans="1:14">
-      <c r="B138" s="13" t="s">
-        <v>263</v>
+      <c r="B138" s="20" t="s">
+        <v>264</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>91</v>
@@ -12158,17 +12165,17 @@
       </c>
       <c r="E138" s="13"/>
       <c r="F138" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G138" s="14">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="H138" s="42">
         <v>0.095</v>
       </c>
       <c r="I138" s="17">
         <f t="shared" si="39"/>
-        <v>37.23</v>
+        <v>56.94</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="18">
@@ -12188,10 +12195,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" s="4" customFormat="1" spans="1:14">
-      <c r="A139" s="27"/>
-      <c r="B139" s="20" t="s">
-        <v>264</v>
+    <row r="139" spans="1:14">
+      <c r="B139" s="13" t="s">
+        <v>265</v>
       </c>
       <c r="C139" s="9" t="s">
         <v>91</v>
@@ -12200,20 +12206,20 @@
         <v>123</v>
       </c>
       <c r="E139" s="13"/>
-      <c r="F139" s="43">
-        <v>2.5</v>
-      </c>
-      <c r="G139" s="28">
-        <v>40.5</v>
-      </c>
-      <c r="H139" s="44">
-        <v>0.1</v>
+      <c r="F139" s="8">
+        <v>3</v>
+      </c>
+      <c r="G139" s="14">
+        <v>34</v>
+      </c>
+      <c r="H139" s="42">
+        <v>0.095</v>
       </c>
       <c r="I139" s="17">
         <f t="shared" si="39"/>
-        <v>44.55</v>
-      </c>
-      <c r="J139" s="9"/>
+        <v>37.23</v>
+      </c>
+      <c r="J139" s="5"/>
       <c r="K139" s="18">
         <f t="shared" si="40"/>
         <v>0</v>
@@ -12231,89 +12237,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
-      <c r="B140" s="13"/>
-      <c r="C140" s="13"/>
-      <c r="D140" s="13"/>
+    <row r="140" s="4" customFormat="1" spans="1:14">
+      <c r="A140" s="27"/>
+      <c r="B140" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>123</v>
+      </c>
       <c r="E140" s="13"/>
-      <c r="I140" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="J140" s="45"/>
-      <c r="K140" s="45"/>
+      <c r="F140" s="43">
+        <v>2.5</v>
+      </c>
+      <c r="G140" s="28">
+        <v>40.5</v>
+      </c>
+      <c r="H140" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="I140" s="17">
+        <f t="shared" si="39"/>
+        <v>44.55</v>
+      </c>
+      <c r="J140" s="9"/>
+      <c r="K140" s="18">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
       <c r="L140" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M140" s="45"/>
-      <c r="N140" s="45"/>
+      <c r="M140" s="17">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="N140" s="19">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="141" spans="1:14">
-      <c r="B141" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="12"/>
+      <c r="B141" s="13"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
+      <c r="I141" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="J141" s="45"/>
+      <c r="K141" s="45"/>
       <c r="L141" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="N141" s="19">
-        <f t="shared" ref="N141:N151" si="42">M141+J141</f>
-        <v>0</v>
-      </c>
+      <c r="M141" s="45"/>
+      <c r="N141" s="45"/>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="13"/>
-      <c r="B142" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="C142" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D142" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="E142" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F142" s="8">
-        <v>4</v>
-      </c>
-      <c r="G142" s="14">
-        <v>58</v>
-      </c>
-      <c r="H142" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I142" s="17">
-        <f>G142*(1+H142)</f>
-        <v>62.64</v>
-      </c>
-      <c r="J142" s="9"/>
-      <c r="K142" s="18">
-        <f>J142*F142</f>
-        <v>0</v>
-      </c>
+      <c r="B142" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="12"/>
       <c r="L142" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M142" s="17">
-        <f>J142*I142</f>
-        <v>0</v>
-      </c>
       <c r="N142" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="N142:N152" si="42">M142+J142</f>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="13"/>
-      <c r="B143" s="13" t="s">
-        <v>267</v>
+      <c r="B143" s="20" t="s">
+        <v>268</v>
       </c>
       <c r="C143" s="9" t="s">
         <v>91</v>
@@ -12321,19 +12325,21 @@
       <c r="D143" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E143" s="13"/>
+      <c r="E143" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="F143" s="8">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G143" s="14">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H143" s="16">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I143" s="17">
         <f>G143*(1+H143)</f>
-        <v>82.5</v>
+        <v>62.64</v>
       </c>
       <c r="J143" s="9"/>
       <c r="K143" s="18">
@@ -12355,23 +12361,42 @@
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="13"/>
-      <c r="B144" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="12"/>
-      <c r="G144" s="14"/>
-      <c r="H144" s="16"/>
-      <c r="I144" s="17"/>
+      <c r="B144" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D144" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E144" s="13"/>
+      <c r="F144" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="G144" s="14">
+        <v>75</v>
+      </c>
+      <c r="H144" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I144" s="17">
+        <f>G144*(1+H144)</f>
+        <v>82.5</v>
+      </c>
       <c r="J144" s="9"/>
-      <c r="K144" s="18"/>
+      <c r="K144" s="18">
+        <f>J144*F144</f>
+        <v>0</v>
+      </c>
       <c r="L144" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M144" s="17"/>
+      <c r="M144" s="17">
+        <f>J144*I144</f>
+        <v>0</v>
+      </c>
       <c r="N144" s="19">
         <f t="shared" si="42"/>
         <v>0</v>
@@ -12379,44 +12404,23 @@
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="13"/>
-      <c r="B145" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C145" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D145" s="14" t="s">
+      <c r="B145" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="E145" s="5">
-        <v>1000</v>
-      </c>
-      <c r="F145" s="8">
-        <v>6</v>
-      </c>
-      <c r="G145" s="14">
-        <v>163.5</v>
-      </c>
-      <c r="H145" s="16">
-        <v>0.11</v>
-      </c>
-      <c r="I145" s="17">
-        <f>G145*(1+H145)</f>
-        <v>181.485</v>
-      </c>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="14"/>
+      <c r="H145" s="16"/>
+      <c r="I145" s="17"/>
       <c r="J145" s="9"/>
-      <c r="K145" s="18">
-        <f>J145*F145</f>
-        <v>0</v>
-      </c>
+      <c r="K145" s="18"/>
       <c r="L145" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M145" s="17">
-        <f>J145*I145</f>
-        <v>0</v>
-      </c>
+      <c r="M145" s="17"/>
       <c r="N145" s="19">
         <f t="shared" si="42"/>
         <v>0</v>
@@ -12424,30 +12428,30 @@
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="13"/>
-      <c r="B146" s="5" t="s">
+      <c r="B146" s="2" t="s">
         <v>271</v>
       </c>
       <c r="C146" s="9" t="s">
         <v>100</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E146" s="5">
         <v>1000</v>
       </c>
       <c r="F146" s="8">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G146" s="14">
-        <v>159.1</v>
+        <v>163.5</v>
       </c>
       <c r="H146" s="16">
         <v>0.11</v>
       </c>
       <c r="I146" s="17">
         <f>G146*(1+H146)</f>
-        <v>176.601</v>
+        <v>181.485</v>
       </c>
       <c r="J146" s="9"/>
       <c r="K146" s="18">
@@ -12469,14 +12473,14 @@
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="13"/>
-      <c r="B147" s="2" t="s">
-        <v>272</v>
+      <c r="B147" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="C147" s="9" t="s">
         <v>100</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E147" s="5">
         <v>1000</v>
@@ -12485,14 +12489,14 @@
         <v>3.5</v>
       </c>
       <c r="G147" s="14">
-        <v>124.7</v>
+        <v>159.1</v>
       </c>
       <c r="H147" s="16">
         <v>0.11</v>
       </c>
       <c r="I147" s="17">
         <f>G147*(1+H147)</f>
-        <v>138.417</v>
+        <v>176.601</v>
       </c>
       <c r="J147" s="9"/>
       <c r="K147" s="18">
@@ -12514,14 +12518,14 @@
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="13"/>
-      <c r="B148" s="5" t="s">
-        <v>273</v>
+      <c r="B148" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>100</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E148" s="5">
         <v>1000</v>
@@ -12530,14 +12534,14 @@
         <v>3.5</v>
       </c>
       <c r="G148" s="14">
-        <v>93.5</v>
+        <v>124.7</v>
       </c>
       <c r="H148" s="16">
         <v>0.11</v>
       </c>
       <c r="I148" s="17">
         <f>G148*(1+H148)</f>
-        <v>103.785</v>
+        <v>138.417</v>
       </c>
       <c r="J148" s="9"/>
       <c r="K148" s="18">
@@ -12559,70 +12563,68 @@
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="13"/>
-      <c r="B149" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
-      <c r="F149" s="12"/>
-      <c r="G149" s="14"/>
-      <c r="H149" s="16"/>
-      <c r="I149" s="17"/>
+      <c r="B149" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D149" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="E149" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F149" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="G149" s="14">
+        <v>93.5</v>
+      </c>
+      <c r="H149" s="16">
+        <v>0.11</v>
+      </c>
+      <c r="I149" s="17">
+        <f>G149*(1+H149)</f>
+        <v>103.785</v>
+      </c>
       <c r="J149" s="9"/>
-      <c r="K149" s="18"/>
+      <c r="K149" s="18">
+        <f>J149*F149</f>
+        <v>0</v>
+      </c>
       <c r="L149" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M149" s="17"/>
+      <c r="M149" s="17">
+        <f>J149*I149</f>
+        <v>0</v>
+      </c>
       <c r="N149" s="19">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:14">
-      <c r="A150" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="B150" s="13" t="s">
+      <c r="A150" s="13"/>
+      <c r="B150" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C150" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D150" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="E150" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="F150" s="8">
-        <v>8</v>
-      </c>
-      <c r="G150" s="14">
-        <f t="shared" ref="G150:G157" si="43">I150/(1+H150)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H150" s="16">
-        <v>0.13</v>
-      </c>
-      <c r="I150" s="17">
-        <v>140</v>
-      </c>
+      <c r="C150" s="11"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="14"/>
+      <c r="H150" s="16"/>
+      <c r="I150" s="17"/>
       <c r="J150" s="9"/>
-      <c r="K150" s="18">
-        <f>J150*F150</f>
-        <v>0</v>
-      </c>
+      <c r="K150" s="18"/>
       <c r="L150" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M150" s="17">
-        <f>J150*I150</f>
-        <v>0</v>
-      </c>
+      <c r="M150" s="17"/>
       <c r="N150" s="19">
         <f t="shared" si="42"/>
         <v>0</v>
@@ -12630,32 +12632,32 @@
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="B151" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>278</v>
       </c>
       <c r="C151" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="F151" s="8">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G151" s="14">
-        <f t="shared" si="43"/>
-        <v>153.752212389381</v>
+        <f t="shared" ref="G151:G158" si="43">I151/(1+H151)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H151" s="16">
         <v>0.13</v>
       </c>
       <c r="I151" s="17">
-        <v>173.74</v>
+        <v>140</v>
       </c>
       <c r="J151" s="9"/>
       <c r="K151" s="18">
@@ -12677,36 +12679,36 @@
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C152" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="F152" s="8">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="G152" s="14">
         <f t="shared" si="43"/>
-        <v>176.991150442478</v>
+        <v>153.752212389381</v>
       </c>
       <c r="H152" s="16">
         <v>0.13</v>
       </c>
       <c r="I152" s="17">
-        <v>200</v>
+        <v>173.74</v>
       </c>
       <c r="J152" s="9"/>
       <c r="K152" s="18">
-        <f t="shared" ref="K152:K157" si="44">J152*F152</f>
+        <f>J152*F152</f>
         <v>0</v>
       </c>
       <c r="L152" s="18">
@@ -12714,17 +12716,17 @@
         <v>0</v>
       </c>
       <c r="M152" s="17">
-        <f t="shared" ref="M152:M157" si="45">J152*I152</f>
+        <f>J152*I152</f>
         <v>0</v>
       </c>
       <c r="N152" s="19">
-        <f t="shared" ref="N152:N157" si="46">M152+J152</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B153" s="15" t="s">
         <v>282</v>
@@ -12739,21 +12741,21 @@
         <v>119</v>
       </c>
       <c r="F153" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G153" s="14">
         <f t="shared" si="43"/>
-        <v>123.893805309735</v>
+        <v>176.991150442478</v>
       </c>
       <c r="H153" s="16">
         <v>0.13</v>
       </c>
       <c r="I153" s="17">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J153" s="9"/>
       <c r="K153" s="18">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="K153:K158" si="44">J153*F153</f>
         <v>0</v>
       </c>
       <c r="L153" s="18">
@@ -12761,17 +12763,17 @@
         <v>0</v>
       </c>
       <c r="M153" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="M153:M158" si="45">J153*I153</f>
         <v>0</v>
       </c>
       <c r="N153" s="19">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="N153:N158" si="46">M153+J153</f>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B154" s="15" t="s">
         <v>284</v>
@@ -12780,23 +12782,23 @@
         <v>101</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E154" s="15" t="s">
         <v>119</v>
       </c>
       <c r="F154" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G154" s="14">
         <f t="shared" si="43"/>
-        <v>230.088495575221</v>
+        <v>123.893805309735</v>
       </c>
       <c r="H154" s="16">
         <v>0.13</v>
       </c>
       <c r="I154" s="17">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="J154" s="9"/>
       <c r="K154" s="18">
@@ -12818,32 +12820,32 @@
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="F155" s="8">
         <v>8</v>
       </c>
       <c r="G155" s="14">
         <f t="shared" si="43"/>
-        <v>115.929203539823</v>
+        <v>230.088495575221</v>
       </c>
       <c r="H155" s="16">
         <v>0.13</v>
       </c>
       <c r="I155" s="17">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="J155" s="9"/>
       <c r="K155" s="18">
@@ -12865,32 +12867,32 @@
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C156" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="F156" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G156" s="14">
         <f t="shared" si="43"/>
-        <v>88.495575221239</v>
+        <v>115.929203539823</v>
       </c>
       <c r="H156" s="16">
         <v>0.13</v>
       </c>
       <c r="I156" s="17">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="J156" s="9"/>
       <c r="K156" s="18">
@@ -12910,34 +12912,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" s="4" customFormat="1" spans="1:14">
+    <row r="157" spans="1:14">
       <c r="A157" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="B157" s="20" t="s">
-        <v>287</v>
+        <v>277</v>
+      </c>
+      <c r="B157" s="15" t="s">
+        <v>288</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>288</v>
+        <v>101</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>278</v>
+        <v>119</v>
       </c>
       <c r="F157" s="8">
         <v>6</v>
       </c>
       <c r="G157" s="14">
-        <f>I157-1</f>
-        <v>107</v>
+        <f t="shared" si="43"/>
+        <v>88.495575221239</v>
       </c>
       <c r="H157" s="16">
         <v>0.13</v>
       </c>
       <c r="I157" s="17">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="J157" s="9"/>
       <c r="K157" s="18">
@@ -12957,36 +12959,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
-      <c r="A158" s="15"/>
-      <c r="B158" s="15" t="s">
+    <row r="158" s="4" customFormat="1" spans="1:14">
+      <c r="A158" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="B158" s="20" t="s">
         <v>289</v>
       </c>
       <c r="C158" s="9" t="s">
         <v>290</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F158" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G158" s="14">
-        <f>I158/(1+H158)</f>
-        <v>129.203539823009</v>
+        <f>I158-1</f>
+        <v>107</v>
       </c>
       <c r="H158" s="16">
         <v>0.13</v>
       </c>
       <c r="I158" s="17">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="J158" s="9"/>
       <c r="K158" s="18">
-        <f t="shared" ref="K158:K161" si="47">J158*F158</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="L158" s="18">
@@ -12994,44 +12998,44 @@
         <v>0</v>
       </c>
       <c r="M158" s="17">
-        <f t="shared" ref="M158:M161" si="48">J158*I158</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="N158" s="19">
-        <f t="shared" ref="N158:N161" si="49">M158+J158</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:14">
-      <c r="A159" s="13"/>
-      <c r="B159" s="13" t="s">
+      <c r="A159" s="15"/>
+      <c r="B159" s="15" t="s">
         <v>291</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F159" s="8">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="G159" s="14">
-        <v>140</v>
+        <f>I159/(1+H159)</f>
+        <v>129.203539823009</v>
       </c>
       <c r="H159" s="16">
         <v>0.13</v>
       </c>
       <c r="I159" s="17">
-        <f>G159*(1+H159)</f>
-        <v>158.2</v>
+        <v>146</v>
       </c>
       <c r="J159" s="9"/>
       <c r="K159" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="K159:K162" si="47">J159*F159</f>
         <v>0</v>
       </c>
       <c r="L159" s="18">
@@ -13039,43 +13043,43 @@
         <v>0</v>
       </c>
       <c r="M159" s="17">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="M159:M162" si="48">J159*I159</f>
         <v>0</v>
       </c>
       <c r="N159" s="19">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" s="4" customFormat="1" spans="1:14">
-      <c r="A160" s="27"/>
+        <f t="shared" ref="N159:N162" si="49">M159+J159</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14">
+      <c r="A160" s="13"/>
       <c r="B160" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C160" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="C160" s="9" t="s">
-        <v>290</v>
-      </c>
       <c r="D160" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F160" s="43">
-        <v>7.5</v>
+        <v>280</v>
+      </c>
+      <c r="F160" s="8">
+        <v>9.5</v>
       </c>
       <c r="G160" s="14">
-        <f>I160/(1+H160)</f>
-        <v>103.371681415929</v>
-      </c>
-      <c r="H160" s="44">
+        <v>140</v>
+      </c>
+      <c r="H160" s="16">
         <v>0.13</v>
       </c>
-      <c r="I160" s="46">
-        <v>116.81</v>
-      </c>
-      <c r="J160" s="43"/>
-      <c r="K160" s="47">
+      <c r="I160" s="17">
+        <f>G160*(1+H160)</f>
+        <v>158.2</v>
+      </c>
+      <c r="J160" s="9"/>
+      <c r="K160" s="18">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
@@ -13083,7 +13087,7 @@
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M160" s="46">
+      <c r="M160" s="17">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
@@ -13095,31 +13099,31 @@
     <row r="161" s="4" customFormat="1" spans="1:15">
       <c r="A161" s="27"/>
       <c r="B161" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F161" s="8">
-        <v>10.5</v>
+        <v>208</v>
+      </c>
+      <c r="F161" s="43">
+        <v>7.5</v>
       </c>
       <c r="G161" s="14">
-        <f>I161-1</f>
-        <v>177.2</v>
-      </c>
-      <c r="H161" s="16">
+        <f>I161/(1+H161)</f>
+        <v>103.371681415929</v>
+      </c>
+      <c r="H161" s="44">
         <v>0.13</v>
       </c>
-      <c r="I161" s="17">
-        <v>178.2</v>
-      </c>
-      <c r="J161" s="9"/>
+      <c r="I161" s="46">
+        <v>116.81</v>
+      </c>
+      <c r="J161" s="43"/>
       <c r="K161" s="47">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -13137,36 +13141,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" s="4" customFormat="1" ht="11" customHeight="1" spans="1:15">
+    <row r="162" s="4" customFormat="1" spans="1:15">
       <c r="A162" s="27"/>
-      <c r="B162" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="C162" s="13" t="s">
+      <c r="B162" s="13" t="s">
         <v>295</v>
       </c>
+      <c r="C162" s="9" t="s">
+        <v>292</v>
+      </c>
       <c r="D162" s="14" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="F162" s="43">
-        <v>4.5</v>
+        <v>208</v>
+      </c>
+      <c r="F162" s="8">
+        <v>10.5</v>
       </c>
       <c r="G162" s="14">
-        <f>I162/(1+H162)</f>
-        <v>132.743362831858</v>
-      </c>
-      <c r="H162" s="44">
+        <f>I162-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H162" s="16">
         <v>0.13</v>
       </c>
-      <c r="I162" s="46">
-        <v>150</v>
-      </c>
-      <c r="J162" s="43"/>
+      <c r="I162" s="17">
+        <v>178.2</v>
+      </c>
+      <c r="J162" s="9"/>
       <c r="K162" s="47">
-        <f t="shared" ref="K162:K176" si="50">J162*F162</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L162" s="18">
@@ -13174,44 +13178,44 @@
         <v>0</v>
       </c>
       <c r="M162" s="46">
-        <f t="shared" ref="M162:M176" si="51">J162*I162</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="N162" s="19">
-        <f t="shared" ref="N162:N181" si="52">M162+J162</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" s="4" customFormat="1" spans="1:15">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" s="4" customFormat="1" ht="11" customHeight="1" spans="1:15">
       <c r="A163" s="27"/>
       <c r="B163" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C163" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="D163" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="E163" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C163" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D163" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="E163" s="15" t="s">
-        <v>119</v>
-      </c>
       <c r="F163" s="43">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="G163" s="14">
-        <v>145</v>
+        <f>I163/(1+H163)</f>
+        <v>132.743362831858</v>
       </c>
       <c r="H163" s="44">
         <v>0.13</v>
       </c>
-      <c r="I163" s="17">
-        <f>G163*(1+H163)</f>
-        <v>163.85</v>
+      <c r="I163" s="46">
+        <v>150</v>
       </c>
       <c r="J163" s="43"/>
       <c r="K163" s="47">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="K163:K177" si="50">J163*F163</f>
         <v>0</v>
       </c>
       <c r="L163" s="18">
@@ -13219,40 +13223,40 @@
         <v>0</v>
       </c>
       <c r="M163" s="46">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="M163:M177" si="51">J163*I163</f>
         <v>0</v>
       </c>
       <c r="N163" s="19">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="N163:N182" si="52">M163+J163</f>
         <v>0</v>
       </c>
     </row>
     <row r="164" s="4" customFormat="1" spans="1:15">
       <c r="A164" s="27"/>
       <c r="B164" s="15" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C164" s="9" t="s">
         <v>96</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E164" s="15" t="s">
         <v>119</v>
       </c>
       <c r="F164" s="43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G164" s="14">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="H164" s="44">
         <v>0.13</v>
       </c>
       <c r="I164" s="17">
         <f>G164*(1+H164)</f>
-        <v>114.13</v>
+        <v>163.85</v>
       </c>
       <c r="J164" s="43"/>
       <c r="K164" s="47">
@@ -13274,14 +13278,14 @@
     </row>
     <row r="165" s="4" customFormat="1" spans="1:15">
       <c r="A165" s="27"/>
-      <c r="B165" s="13" t="s">
-        <v>297</v>
+      <c r="B165" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="C165" s="9" t="s">
         <v>96</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>119</v>
@@ -13289,18 +13293,18 @@
       <c r="F165" s="43">
         <v>4</v>
       </c>
-      <c r="G165" s="28">
-        <v>115</v>
+      <c r="G165" s="14">
+        <v>101</v>
       </c>
       <c r="H165" s="44">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I165" s="17">
         <f>G165*(1+H165)</f>
-        <v>124.2</v>
-      </c>
-      <c r="J165" s="9"/>
-      <c r="K165" s="18">
+        <v>114.13</v>
+      </c>
+      <c r="J165" s="43"/>
+      <c r="K165" s="47">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
@@ -13308,7 +13312,7 @@
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M165" s="17">
+      <c r="M165" s="46">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
@@ -13318,9 +13322,9 @@
       </c>
     </row>
     <row r="166" s="4" customFormat="1" spans="1:15">
-      <c r="A166" s="15"/>
-      <c r="B166" s="15" t="s">
-        <v>282</v>
+      <c r="A166" s="27"/>
+      <c r="B166" s="13" t="s">
+        <v>299</v>
       </c>
       <c r="C166" s="9" t="s">
         <v>96</v>
@@ -13331,18 +13335,18 @@
       <c r="E166" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F166" s="8">
+      <c r="F166" s="43">
         <v>4</v>
       </c>
-      <c r="G166" s="14">
-        <f>I166/(1+H166)</f>
-        <v>123.893805309735</v>
-      </c>
-      <c r="H166" s="16">
-        <v>0.13</v>
+      <c r="G166" s="28">
+        <v>115</v>
+      </c>
+      <c r="H166" s="44">
+        <v>0.08</v>
       </c>
       <c r="I166" s="17">
-        <v>140</v>
+        <f>G166*(1+H166)</f>
+        <v>124.2</v>
       </c>
       <c r="J166" s="9"/>
       <c r="K166" s="18">
@@ -13361,30 +13365,33 @@
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="O166" s="2"/>
     </row>
     <row r="167" s="4" customFormat="1" spans="1:15">
-      <c r="A167" s="27"/>
-      <c r="B167" s="13" t="s">
-        <v>298</v>
+      <c r="A167" s="15"/>
+      <c r="B167" s="15" t="s">
+        <v>284</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>299</v>
+        <v>96</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="E167" s="15"/>
-      <c r="F167" s="43">
-        <v>11</v>
-      </c>
-      <c r="G167" s="28">
-        <f>I167-1</f>
-        <v>177.5</v>
-      </c>
-      <c r="H167" s="44"/>
+        <v>285</v>
+      </c>
+      <c r="E167" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F167" s="8">
+        <v>4</v>
+      </c>
+      <c r="G167" s="14">
+        <f>I167/(1+H167)</f>
+        <v>123.893805309735</v>
+      </c>
+      <c r="H167" s="16">
+        <v>0.13</v>
+      </c>
       <c r="I167" s="17">
-        <v>178.5</v>
+        <v>140</v>
       </c>
       <c r="J167" s="9"/>
       <c r="K167" s="18">
@@ -13403,29 +13410,30 @@
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
+      <c r="O167" s="2"/>
     </row>
     <row r="168" s="4" customFormat="1" spans="1:15">
       <c r="A168" s="27"/>
       <c r="B168" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C168" s="9" t="s">
         <v>301</v>
-      </c>
-      <c r="C168" s="9" t="s">
-        <v>299</v>
       </c>
       <c r="D168" s="14" t="s">
         <v>302</v>
       </c>
       <c r="E168" s="15"/>
       <c r="F168" s="43">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G168" s="28">
         <f>I168-1</f>
-        <v>127.5</v>
+        <v>177.5</v>
       </c>
       <c r="H168" s="44"/>
       <c r="I168" s="17">
-        <v>128.5</v>
+        <v>178.5</v>
       </c>
       <c r="J168" s="9"/>
       <c r="K168" s="18">
@@ -13446,31 +13454,27 @@
       </c>
     </row>
     <row r="169" s="4" customFormat="1" spans="1:15">
-      <c r="A169" s="15"/>
-      <c r="B169" s="15" t="s">
-        <v>280</v>
+      <c r="A169" s="27"/>
+      <c r="B169" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="E169" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F169" s="8">
-        <v>6</v>
-      </c>
-      <c r="G169" s="14">
-        <f>I169/(1+H169)</f>
-        <v>176.991150442478</v>
-      </c>
-      <c r="H169" s="16">
-        <v>0.13</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="E169" s="15"/>
+      <c r="F169" s="43">
+        <v>8</v>
+      </c>
+      <c r="G169" s="28">
+        <f>I169-1</f>
+        <v>127.5</v>
+      </c>
+      <c r="H169" s="44"/>
       <c r="I169" s="17">
-        <v>200</v>
+        <v>128.5</v>
       </c>
       <c r="J169" s="9"/>
       <c r="K169" s="18">
@@ -13496,7 +13500,7 @@
         <v>282</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D170" s="14" t="s">
         <v>283</v>
@@ -13505,17 +13509,17 @@
         <v>119</v>
       </c>
       <c r="F170" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G170" s="14">
         <f>I170/(1+H170)</f>
-        <v>123.893805309735</v>
+        <v>176.991150442478</v>
       </c>
       <c r="H170" s="16">
         <v>0.13</v>
       </c>
       <c r="I170" s="17">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J170" s="9"/>
       <c r="K170" s="18">
@@ -13535,16 +13539,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" s="4" customFormat="1" ht="13" customHeight="1" spans="1:15">
-      <c r="A171" s="27"/>
-      <c r="B171" s="13" t="s">
-        <v>297</v>
+    <row r="171" s="4" customFormat="1" spans="1:15">
+      <c r="A171" s="15"/>
+      <c r="B171" s="15" t="s">
+        <v>284</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E171" s="15" t="s">
         <v>119</v>
@@ -13553,14 +13557,14 @@
         <v>4</v>
       </c>
       <c r="G171" s="14">
-        <v>115</v>
+        <f>I171/(1+H171)</f>
+        <v>123.893805309735</v>
       </c>
       <c r="H171" s="16">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="I171" s="17">
-        <f>G171*(1+H171)</f>
-        <v>124.2</v>
+        <v>140</v>
       </c>
       <c r="J171" s="9"/>
       <c r="K171" s="18">
@@ -13580,32 +13584,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" s="4" customFormat="1" spans="1:15">
+    <row r="172" s="4" customFormat="1" ht="13" customHeight="1" spans="1:15">
       <c r="A172" s="27"/>
-      <c r="B172" s="20" t="s">
-        <v>287</v>
+      <c r="B172" s="13" t="s">
+        <v>299</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>278</v>
+        <v>119</v>
       </c>
       <c r="F172" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G172" s="14">
-        <f>I172-1</f>
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H172" s="16">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I172" s="17">
-        <v>108</v>
+        <f>G172*(1+H172)</f>
+        <v>124.2</v>
       </c>
       <c r="J172" s="9"/>
       <c r="K172" s="18">
@@ -13627,33 +13631,33 @@
     </row>
     <row r="173" s="4" customFormat="1" spans="1:15">
       <c r="A173" s="27"/>
-      <c r="B173" s="13" t="s">
-        <v>292</v>
+      <c r="B173" s="20" t="s">
+        <v>289</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="F173" s="8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G173" s="14">
         <f>I173-1</f>
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="H173" s="16">
         <v>0.13</v>
       </c>
-      <c r="I173" s="48">
-        <v>135</v>
-      </c>
-      <c r="J173" s="43"/>
-      <c r="K173" s="47">
+      <c r="I173" s="17">
+        <v>108</v>
+      </c>
+      <c r="J173" s="9"/>
+      <c r="K173" s="18">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
@@ -13661,7 +13665,7 @@
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M173" s="46">
+      <c r="M173" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
@@ -13671,34 +13675,34 @@
       </c>
     </row>
     <row r="174" s="4" customFormat="1" spans="1:15">
-      <c r="A174" s="13"/>
-      <c r="B174" s="20" t="s">
-        <v>291</v>
+      <c r="A174" s="27"/>
+      <c r="B174" s="13" t="s">
+        <v>294</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="F174" s="8">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G174" s="14">
         <f>I174-1</f>
-        <v>150.2</v>
+        <v>134</v>
       </c>
       <c r="H174" s="16">
         <v>0.13</v>
       </c>
-      <c r="I174" s="17">
-        <v>151.2</v>
-      </c>
-      <c r="J174" s="9"/>
-      <c r="K174" s="18">
+      <c r="I174" s="48">
+        <v>135</v>
+      </c>
+      <c r="J174" s="43"/>
+      <c r="K174" s="47">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
@@ -13706,7 +13710,7 @@
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M174" s="17">
+      <c r="M174" s="46">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
@@ -13716,34 +13720,34 @@
       </c>
     </row>
     <row r="175" s="4" customFormat="1" spans="1:15">
-      <c r="A175" s="27"/>
-      <c r="B175" s="13" t="s">
-        <v>303</v>
+      <c r="A175" s="13"/>
+      <c r="B175" s="20" t="s">
+        <v>293</v>
       </c>
       <c r="C175" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="F175" s="8">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G175" s="14">
         <f>I175-1</f>
-        <v>134</v>
+        <v>150.2</v>
       </c>
       <c r="H175" s="16">
         <v>0.13</v>
       </c>
       <c r="I175" s="17">
-        <v>135</v>
+        <v>151.2</v>
       </c>
       <c r="J175" s="9"/>
-      <c r="K175" s="47">
+      <c r="K175" s="18">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
@@ -13751,7 +13755,7 @@
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M175" s="46">
+      <c r="M175" s="17">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
@@ -13763,29 +13767,29 @@
     <row r="176" s="4" customFormat="1" spans="1:15">
       <c r="A176" s="27"/>
       <c r="B176" s="13" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C176" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F176" s="8">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G176" s="14">
         <f>I176-1</f>
-        <v>177.2</v>
+        <v>134</v>
       </c>
       <c r="H176" s="16">
         <v>0.13</v>
       </c>
       <c r="I176" s="17">
-        <v>178.2</v>
+        <v>135</v>
       </c>
       <c r="J176" s="9"/>
       <c r="K176" s="47">
@@ -13807,21 +13811,44 @@
     </row>
     <row r="177" s="4" customFormat="1" spans="1:14">
       <c r="A177" s="27"/>
-      <c r="B177" s="27"/>
-      <c r="C177" s="27"/>
-      <c r="D177" s="27"/>
-      <c r="E177" s="27"/>
-      <c r="F177" s="43"/>
-      <c r="G177" s="28"/>
-      <c r="H177" s="44"/>
-      <c r="I177" s="17"/>
+      <c r="B177" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D177" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E177" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F177" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="G177" s="14">
+        <f>I177-1</f>
+        <v>177.2</v>
+      </c>
+      <c r="H177" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="I177" s="17">
+        <v>178.2</v>
+      </c>
       <c r="J177" s="9"/>
-      <c r="K177" s="18"/>
+      <c r="K177" s="47">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
       <c r="L177" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M177" s="17"/>
+      <c r="M177" s="46">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
       <c r="N177" s="19">
         <f t="shared" si="52"/>
         <v>0</v>
@@ -13829,13 +13856,11 @@
     </row>
     <row r="178" s="4" customFormat="1" spans="1:14">
       <c r="A178" s="27"/>
-      <c r="B178" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11"/>
-      <c r="E178" s="11"/>
-      <c r="F178" s="12"/>
+      <c r="B178" s="27"/>
+      <c r="C178" s="27"/>
+      <c r="D178" s="27"/>
+      <c r="E178" s="27"/>
+      <c r="F178" s="43"/>
       <c r="G178" s="28"/>
       <c r="H178" s="44"/>
       <c r="I178" s="17"/>
@@ -13851,45 +13876,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
-      <c r="B179" s="49" t="s">
-        <v>305</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="E179" s="50">
-        <v>1000</v>
-      </c>
-      <c r="F179" s="8">
-        <v>8</v>
-      </c>
-      <c r="G179" s="14">
-        <v>90</v>
-      </c>
-      <c r="H179" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I179" s="17">
-        <f t="shared" ref="I179:I183" si="53">G179*(1+H179)</f>
-        <v>97.2</v>
-      </c>
+    <row r="179" s="4" customFormat="1" spans="1:14">
+      <c r="A179" s="27"/>
+      <c r="B179" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C179" s="11"/>
+      <c r="D179" s="11"/>
+      <c r="E179" s="11"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="28"/>
+      <c r="H179" s="44"/>
+      <c r="I179" s="17"/>
       <c r="J179" s="9"/>
-      <c r="K179" s="18">
-        <f t="shared" ref="K179:K184" si="54">J179*F179</f>
-        <v>0</v>
-      </c>
+      <c r="K179" s="18"/>
       <c r="L179" s="18">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="M179" s="17">
-        <f t="shared" ref="M179:M184" si="55">J179*I179</f>
-        <v>0</v>
-      </c>
+      <c r="M179" s="17"/>
       <c r="N179" s="19">
         <f t="shared" si="52"/>
         <v>0</v>
@@ -13897,13 +13902,13 @@
     </row>
     <row r="180" spans="1:14">
       <c r="B180" s="49" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C180" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E180" s="50">
         <v>1000</v>
@@ -13912,58 +13917,58 @@
         <v>8</v>
       </c>
       <c r="G180" s="14">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H180" s="16">
         <v>0.08</v>
       </c>
       <c r="I180" s="17">
+        <f t="shared" ref="I180:I184" si="53">G180*(1+H180)</f>
+        <v>97.2</v>
+      </c>
+      <c r="J180" s="9"/>
+      <c r="K180" s="18">
+        <f t="shared" ref="K180:K190" si="54">J180*F180</f>
+        <v>0</v>
+      </c>
+      <c r="L180" s="18">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M180" s="17">
+        <f t="shared" ref="M180:M190" si="55">J180*I180</f>
+        <v>0</v>
+      </c>
+      <c r="N180" s="19">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="B181" s="49" t="s">
+        <v>308</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D181" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E181" s="50">
+        <v>1000</v>
+      </c>
+      <c r="F181" s="8">
+        <v>8</v>
+      </c>
+      <c r="G181" s="14">
+        <v>92</v>
+      </c>
+      <c r="H181" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I181" s="17">
         <f t="shared" si="53"/>
         <v>99.36</v>
-      </c>
-      <c r="J180" s="9"/>
-      <c r="K180" s="18">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="L180" s="18">
-        <f t="shared" ref="L180:L184" si="56">K180+J180/2</f>
-        <v>0</v>
-      </c>
-      <c r="M180" s="17">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="N180" s="19">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14">
-      <c r="B181" s="49" t="s">
-        <v>307</v>
-      </c>
-      <c r="C181" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="E181" s="50">
-        <v>1000</v>
-      </c>
-      <c r="F181" s="8">
-        <v>7</v>
-      </c>
-      <c r="G181" s="14">
-        <v>87</v>
-      </c>
-      <c r="H181" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I181" s="17">
-        <f t="shared" si="53"/>
-        <v>93.96</v>
       </c>
       <c r="J181" s="9"/>
       <c r="K181" s="18">
@@ -13971,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="18">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="L181:L188" si="56">K181+J181/2</f>
         <v>0</v>
       </c>
       <c r="M181" s="17">
@@ -13984,83 +13989,84 @@
       </c>
     </row>
     <row r="182" spans="1:14">
-      <c r="B182" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="C182" s="11"/>
-      <c r="D182" s="11"/>
-      <c r="E182" s="11"/>
-      <c r="F182" s="12"/>
-      <c r="G182" s="14"/>
-      <c r="H182" s="16"/>
-      <c r="I182" s="17"/>
+      <c r="B182" s="49" t="s">
+        <v>309</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D182" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E182" s="50">
+        <v>1000</v>
+      </c>
+      <c r="F182" s="8">
+        <v>7</v>
+      </c>
+      <c r="G182" s="14">
+        <v>87</v>
+      </c>
+      <c r="H182" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I182" s="17">
+        <f t="shared" si="53"/>
+        <v>93.96</v>
+      </c>
       <c r="J182" s="9"/>
-      <c r="K182" s="18"/>
+      <c r="K182" s="18">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
       <c r="L182" s="18">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="M182" s="17"/>
-      <c r="N182" s="19"/>
+      <c r="M182" s="17">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="N182" s="19">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="183" spans="1:14">
-      <c r="B183" s="49" t="s">
-        <v>309</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D183" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="E183" s="50">
-        <v>300</v>
-      </c>
-      <c r="F183" s="8">
-        <v>4.56</v>
-      </c>
-      <c r="G183" s="14">
-        <v>60.7</v>
-      </c>
-      <c r="H183" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="I183" s="17">
-        <v>61.7</v>
-      </c>
+      <c r="B183" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="C183" s="11"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
+      <c r="F183" s="12"/>
+      <c r="G183" s="14"/>
+      <c r="H183" s="16"/>
+      <c r="I183" s="17"/>
       <c r="J183" s="9"/>
-      <c r="K183" s="18">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
+      <c r="K183" s="18"/>
       <c r="L183" s="18">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="M183" s="17">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="N183" s="19">
-        <f>M183+J183</f>
-        <v>0</v>
-      </c>
+      <c r="M183" s="17"/>
+      <c r="N183" s="19"/>
     </row>
     <row r="184" spans="1:14">
       <c r="B184" s="49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C184" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E184" s="50">
         <v>300</v>
       </c>
       <c r="F184" s="8">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="G184" s="14">
         <v>60.7</v>
@@ -14069,7 +14075,7 @@
         <v>0.1</v>
       </c>
       <c r="I184" s="17">
-        <v>61.55</v>
+        <v>61.7</v>
       </c>
       <c r="J184" s="9"/>
       <c r="K184" s="18">
@@ -14091,108 +14097,106 @@
     </row>
     <row r="185" spans="1:14">
       <c r="B185" s="49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C185" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E185" s="50">
         <v>300</v>
       </c>
       <c r="F185" s="8">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="G185" s="14">
-        <v>61.5</v>
+        <v>60.7</v>
       </c>
       <c r="H185" s="16">
         <v>0.1</v>
       </c>
       <c r="I185" s="17">
-        <f>G185*(1+H185)</f>
-        <v>67.65</v>
+        <v>61.55</v>
       </c>
       <c r="J185" s="9"/>
       <c r="K185" s="18">
-        <f>J185*F185</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L185" s="18">
-        <f>K185+J185/2</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M185" s="17">
-        <f>J185*I185</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N185" s="19">
-        <f t="shared" ref="N185:N187" si="57">M185+J185</f>
+        <f>M185+J185</f>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="B186" s="49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C186" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E186" s="50">
         <v>300</v>
       </c>
       <c r="F186" s="8">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="G186" s="14">
-        <v>64.5</v>
+        <v>61.5</v>
       </c>
       <c r="H186" s="16">
         <v>0.1</v>
       </c>
       <c r="I186" s="17">
         <f>G186*(1+H186)</f>
-        <v>70.95</v>
+        <v>67.65</v>
       </c>
       <c r="J186" s="9"/>
       <c r="K186" s="18">
-        <f>J186*F186</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L186" s="18">
-        <f>K186+J186/2</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M186" s="17">
-        <f>J186*I186</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N186" s="19">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" customFormat="1" spans="1:14">
-      <c r="A187" s="2"/>
+        <f t="shared" ref="N186:N188" si="57">M186+J186</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14">
       <c r="B187" s="49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C187" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E187" s="50">
         <v>300</v>
       </c>
       <c r="F187" s="8">
-        <v>5.7</v>
+        <v>5.15</v>
       </c>
       <c r="G187" s="14">
         <v>64.5</v>
@@ -14206,15 +14210,15 @@
       </c>
       <c r="J187" s="9"/>
       <c r="K187" s="18">
-        <f>J187*F187</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L187" s="18">
-        <f>K187+J187/2</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M187" s="17">
-        <f>J187*I187</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N187" s="19">
@@ -14222,54 +14226,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" s="4" customFormat="1" spans="1:14">
-      <c r="A188" s="27"/>
-      <c r="B188" s="45" t="s">
-        <v>314</v>
+    <row r="188" customFormat="1" spans="1:14">
+      <c r="A188" s="2"/>
+      <c r="B188" s="49" t="s">
+        <v>315</v>
       </c>
       <c r="C188" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D188" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E188" s="50">
         <v>300</v>
       </c>
       <c r="F188" s="8">
-        <v>5.9</v>
-      </c>
-      <c r="G188" s="28">
-        <v>73.9</v>
-      </c>
-      <c r="H188" s="44">
+        <v>5.7</v>
+      </c>
+      <c r="G188" s="14">
+        <v>64.5</v>
+      </c>
+      <c r="H188" s="16">
         <v>0.1</v>
       </c>
       <c r="I188" s="17">
-        <v>74.9</v>
+        <f>G188*(1+H188)</f>
+        <v>70.95</v>
       </c>
       <c r="J188" s="9"/>
       <c r="K188" s="18">
-        <f>J188*F188</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L188" s="18">
-        <f t="shared" ref="L188:L212" si="58">K188+J188/2</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M188" s="17">
-        <f>J188*I188</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N188" s="19">
-        <f t="shared" ref="N188:N212" si="59">M188+J188</f>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" s="4" customFormat="1" spans="1:14">
       <c r="A189" s="27"/>
-      <c r="B189" s="2" t="s">
-        <v>315</v>
+      <c r="B189" s="45" t="s">
+        <v>316</v>
       </c>
       <c r="C189" s="9" t="s">
         <v>93</v>
@@ -14281,53 +14286,75 @@
         <v>300</v>
       </c>
       <c r="F189" s="8">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="G189" s="28">
-        <v>94.5</v>
+        <v>73.9</v>
       </c>
       <c r="H189" s="44">
         <v>0.1</v>
       </c>
       <c r="I189" s="17">
-        <f>G189*(1+H189)</f>
-        <v>103.95</v>
+        <v>74.9</v>
       </c>
       <c r="J189" s="9"/>
       <c r="K189" s="18">
-        <f>J189*F189</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L189" s="18">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="L189:L213" si="58">K189+J189/2</f>
         <v>0</v>
       </c>
       <c r="M189" s="17">
-        <f>J189*I189</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N189" s="19">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="N189:N213" si="59">M189+J189</f>
         <v>0</v>
       </c>
     </row>
     <row r="190" s="4" customFormat="1" spans="1:14">
       <c r="A190" s="27"/>
-      <c r="B190" s="28"/>
-      <c r="C190" s="28"/>
-      <c r="D190" s="28"/>
-      <c r="E190" s="28"/>
-      <c r="F190" s="28"/>
-      <c r="G190" s="28"/>
-      <c r="H190" s="44"/>
-      <c r="I190" s="17"/>
+      <c r="B190" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D190" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E190" s="50">
+        <v>300</v>
+      </c>
+      <c r="F190" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="G190" s="28">
+        <v>94.5</v>
+      </c>
+      <c r="H190" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="I190" s="17">
+        <f>G190*(1+H190)</f>
+        <v>103.95</v>
+      </c>
       <c r="J190" s="9"/>
-      <c r="K190" s="18"/>
+      <c r="K190" s="18">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
       <c r="L190" s="18">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="M190" s="17"/>
+      <c r="M190" s="17">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
       <c r="N190" s="19">
         <f t="shared" si="59"/>
         <v>0</v>
@@ -14335,13 +14362,11 @@
     </row>
     <row r="191" s="4" customFormat="1" spans="1:14">
       <c r="A191" s="27"/>
-      <c r="B191" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="C191" s="51"/>
-      <c r="D191" s="51"/>
-      <c r="E191" s="51"/>
-      <c r="F191" s="52"/>
+      <c r="B191" s="28"/>
+      <c r="C191" s="28"/>
+      <c r="D191" s="28"/>
+      <c r="E191" s="28"/>
+      <c r="F191" s="28"/>
       <c r="G191" s="28"/>
       <c r="H191" s="44"/>
       <c r="I191" s="17"/>
@@ -14357,45 +14382,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
-      <c r="B192" s="49" t="s">
-        <v>317</v>
-      </c>
-      <c r="C192" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D192" s="14" t="s">
+    <row r="192" s="4" customFormat="1" spans="1:14">
+      <c r="A192" s="27"/>
+      <c r="B192" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="E192" s="50">
-        <v>500</v>
-      </c>
-      <c r="F192" s="8">
-        <v>5</v>
-      </c>
-      <c r="G192" s="14">
-        <v>67.5</v>
-      </c>
-      <c r="H192" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I192" s="17">
-        <f t="shared" ref="I192:I212" si="60">G192*(1+H192)</f>
-        <v>72.9</v>
-      </c>
+      <c r="C192" s="51"/>
+      <c r="D192" s="51"/>
+      <c r="E192" s="51"/>
+      <c r="F192" s="52"/>
+      <c r="G192" s="28"/>
+      <c r="H192" s="44"/>
+      <c r="I192" s="17"/>
       <c r="J192" s="9"/>
-      <c r="K192" s="18">
-        <f t="shared" ref="K192:K212" si="61">J192*F192</f>
-        <v>0</v>
-      </c>
+      <c r="K192" s="18"/>
       <c r="L192" s="18">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="M192" s="17">
-        <f t="shared" ref="M192:M212" si="62">J192*I192</f>
-        <v>0</v>
-      </c>
+      <c r="M192" s="17"/>
       <c r="N192" s="19">
         <f t="shared" si="59"/>
         <v>0</v>
@@ -14409,61 +14414,68 @@
         <v>94</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E193" s="50">
         <v>500</v>
       </c>
       <c r="F193" s="8">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="G193" s="14">
-        <v>79</v>
+        <v>67.5</v>
       </c>
       <c r="H193" s="16">
         <v>0.08</v>
       </c>
       <c r="I193" s="17">
+        <f t="shared" ref="I193:I213" si="60">G193*(1+H193)</f>
+        <v>72.9</v>
+      </c>
+      <c r="J193" s="9"/>
+      <c r="K193" s="18">
+        <f t="shared" ref="K193:K213" si="61">J193*F193</f>
+        <v>0</v>
+      </c>
+      <c r="L193" s="18">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M193" s="17">
+        <f t="shared" ref="M193:M213" si="62">J193*I193</f>
+        <v>0</v>
+      </c>
+      <c r="N193" s="19">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
+      <c r="B194" s="49" t="s">
+        <v>321</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D194" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="E194" s="50">
+        <v>500</v>
+      </c>
+      <c r="F194" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="G194" s="14">
+        <v>79</v>
+      </c>
+      <c r="H194" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I194" s="17">
         <f t="shared" si="60"/>
         <v>85.32</v>
       </c>
-      <c r="J193" s="9"/>
-      <c r="K193" s="18">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="L193" s="18">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="M193" s="17">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="N193" s="19">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14">
-      <c r="B194" s="50" t="s">
-        <v>320</v>
-      </c>
-      <c r="C194" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D194" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="E194" s="50">
-        <v>500</v>
-      </c>
-      <c r="F194" s="8"/>
-      <c r="G194" s="14"/>
-      <c r="H194" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I194" s="17"/>
       <c r="J194" s="9"/>
       <c r="K194" s="18">
         <f t="shared" si="61"/>
@@ -14483,31 +14495,24 @@
       </c>
     </row>
     <row r="195" spans="1:14">
-      <c r="B195" s="49" t="s">
-        <v>321</v>
+      <c r="B195" s="50" t="s">
+        <v>322</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E195" s="50">
         <v>500</v>
       </c>
-      <c r="F195" s="8">
-        <v>6.5</v>
-      </c>
-      <c r="G195" s="14">
-        <v>105</v>
-      </c>
+      <c r="F195" s="8"/>
+      <c r="G195" s="14"/>
       <c r="H195" s="16">
         <v>0.08</v>
       </c>
-      <c r="I195" s="17">
-        <f t="shared" si="60"/>
-        <v>113.4</v>
-      </c>
+      <c r="I195" s="17"/>
       <c r="J195" s="9"/>
       <c r="K195" s="18">
         <f t="shared" si="61"/>
@@ -14528,29 +14533,29 @@
     </row>
     <row r="196" spans="1:14">
       <c r="B196" s="49" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C196" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E196" s="50">
         <v>500</v>
       </c>
       <c r="F196" s="8">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G196" s="14">
-        <v>117.5</v>
+        <v>105</v>
       </c>
       <c r="H196" s="16">
         <v>0.08</v>
       </c>
       <c r="I196" s="17">
         <f t="shared" si="60"/>
-        <v>126.9</v>
+        <v>113.4</v>
       </c>
       <c r="J196" s="9"/>
       <c r="K196" s="18">
@@ -14571,30 +14576,30 @@
       </c>
     </row>
     <row r="197" spans="1:14">
-      <c r="B197" s="50" t="s">
-        <v>323</v>
+      <c r="B197" s="49" t="s">
+        <v>324</v>
       </c>
       <c r="C197" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E197" s="50">
         <v>500</v>
       </c>
       <c r="F197" s="8">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G197" s="14">
-        <v>122.5</v>
+        <v>117.5</v>
       </c>
       <c r="H197" s="16">
         <v>0.08</v>
       </c>
       <c r="I197" s="17">
         <f t="shared" si="60"/>
-        <v>132.3</v>
+        <v>126.9</v>
       </c>
       <c r="J197" s="9"/>
       <c r="K197" s="18">
@@ -14616,29 +14621,29 @@
     </row>
     <row r="198" spans="1:14">
       <c r="B198" s="50" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D198" s="50" t="s">
-        <v>325</v>
+      <c r="D198" s="14" t="s">
+        <v>320</v>
       </c>
       <c r="E198" s="50">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="F198" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G198" s="14">
-        <v>100</v>
+        <v>122.5</v>
       </c>
       <c r="H198" s="16">
         <v>0.08</v>
       </c>
       <c r="I198" s="17">
         <f t="shared" si="60"/>
-        <v>108</v>
+        <v>132.3</v>
       </c>
       <c r="J198" s="9"/>
       <c r="K198" s="18">
@@ -14659,30 +14664,30 @@
       </c>
     </row>
     <row r="199" spans="1:14">
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="50" t="s">
         <v>326</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E199" s="50">
         <v>5000</v>
       </c>
       <c r="F199" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G199" s="14">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="H199" s="16">
         <v>0.08</v>
       </c>
       <c r="I199" s="17">
         <f t="shared" si="60"/>
-        <v>156.6</v>
+        <v>108</v>
       </c>
       <c r="J199" s="9"/>
       <c r="K199" s="18">
@@ -14703,30 +14708,30 @@
       </c>
     </row>
     <row r="200" spans="1:14">
-      <c r="B200" s="50" t="s">
-        <v>327</v>
+      <c r="B200" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="C200" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E200" s="50">
         <v>5000</v>
       </c>
       <c r="F200" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G200" s="14">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="H200" s="16">
         <v>0.08</v>
       </c>
       <c r="I200" s="17">
         <f t="shared" si="60"/>
-        <v>145.8</v>
+        <v>156.6</v>
       </c>
       <c r="J200" s="9"/>
       <c r="K200" s="18">
@@ -14747,31 +14752,30 @@
       </c>
     </row>
     <row r="201" spans="1:14">
-      <c r="A201" s="7"/>
-      <c r="B201" s="7" t="s">
-        <v>328</v>
+      <c r="B201" s="50" t="s">
+        <v>329</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E201" s="50">
         <v>5000</v>
       </c>
       <c r="F201" s="8">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="G201" s="14">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="H201" s="16">
         <v>0.08</v>
       </c>
       <c r="I201" s="17">
         <f t="shared" si="60"/>
-        <v>189</v>
+        <v>145.8</v>
       </c>
       <c r="J201" s="9"/>
       <c r="K201" s="18">
@@ -14792,30 +14796,31 @@
       </c>
     </row>
     <row r="202" spans="1:14">
-      <c r="B202" s="50" t="s">
-        <v>329</v>
+      <c r="A202" s="7"/>
+      <c r="B202" s="7" t="s">
+        <v>330</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E202" s="50">
         <v>5000</v>
       </c>
       <c r="F202" s="8">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="G202" s="14">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H202" s="16">
         <v>0.08</v>
       </c>
       <c r="I202" s="17">
         <f t="shared" si="60"/>
-        <v>172.8</v>
+        <v>189</v>
       </c>
       <c r="J202" s="9"/>
       <c r="K202" s="18">
@@ -14836,30 +14841,30 @@
       </c>
     </row>
     <row r="203" spans="1:14">
-      <c r="B203" s="53" t="s">
-        <v>330</v>
+      <c r="B203" s="50" t="s">
+        <v>331</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E203" s="50">
         <v>5000</v>
       </c>
       <c r="F203" s="8">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="G203" s="14">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="H203" s="16">
         <v>0.08</v>
       </c>
       <c r="I203" s="17">
         <f t="shared" si="60"/>
-        <v>205.2</v>
+        <v>172.8</v>
       </c>
       <c r="J203" s="9"/>
       <c r="K203" s="18">
@@ -14880,30 +14885,30 @@
       </c>
     </row>
     <row r="204" spans="1:14">
-      <c r="B204" s="50" t="s">
-        <v>331</v>
+      <c r="B204" s="53" t="s">
+        <v>332</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E204" s="50">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F204" s="8">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="G204" s="14">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="H204" s="16">
         <v>0.08</v>
       </c>
       <c r="I204" s="17">
         <f t="shared" si="60"/>
-        <v>58.32</v>
+        <v>205.2</v>
       </c>
       <c r="J204" s="9"/>
       <c r="K204" s="18">
@@ -14924,30 +14929,30 @@
       </c>
     </row>
     <row r="205" spans="1:14">
-      <c r="B205" s="49" t="s">
-        <v>332</v>
+      <c r="B205" s="50" t="s">
+        <v>333</v>
       </c>
       <c r="C205" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E205" s="50">
         <v>1000</v>
       </c>
       <c r="F205" s="8">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G205" s="14">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H205" s="16">
         <v>0.08</v>
       </c>
       <c r="I205" s="17">
         <f t="shared" si="60"/>
-        <v>62.64</v>
+        <v>58.32</v>
       </c>
       <c r="J205" s="9"/>
       <c r="K205" s="18">
@@ -14968,31 +14973,30 @@
       </c>
     </row>
     <row r="206" spans="1:14">
-      <c r="A206" s="7"/>
-      <c r="B206" s="7" t="s">
-        <v>333</v>
+      <c r="B206" s="49" t="s">
+        <v>334</v>
       </c>
       <c r="C206" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E206" s="50">
         <v>1000</v>
       </c>
       <c r="F206" s="8">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="G206" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H206" s="16">
         <v>0.08</v>
       </c>
       <c r="I206" s="17">
         <f t="shared" si="60"/>
-        <v>68.04</v>
+        <v>62.64</v>
       </c>
       <c r="J206" s="9"/>
       <c r="K206" s="18">
@@ -15013,22 +15017,32 @@
       </c>
     </row>
     <row r="207" spans="1:14">
-      <c r="B207" s="50" t="s">
-        <v>334</v>
+      <c r="A207" s="7"/>
+      <c r="B207" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="C207" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E207" s="50">
         <v>1000</v>
       </c>
-      <c r="F207" s="8"/>
-      <c r="G207" s="14"/>
-      <c r="H207" s="16"/>
-      <c r="I207" s="17"/>
+      <c r="F207" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="G207" s="14">
+        <v>63</v>
+      </c>
+      <c r="H207" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="I207" s="17">
+        <f t="shared" si="60"/>
+        <v>68.04</v>
+      </c>
       <c r="J207" s="9"/>
       <c r="K207" s="18">
         <f t="shared" si="61"/>
@@ -15049,13 +15063,13 @@
     </row>
     <row r="208" spans="1:14">
       <c r="B208" s="50" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C208" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E208" s="50">
         <v>1000</v>
@@ -15083,31 +15097,22 @@
       </c>
     </row>
     <row r="209" spans="1:14">
-      <c r="B209" s="49" t="s">
-        <v>336</v>
+      <c r="B209" s="50" t="s">
+        <v>337</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="D209" s="14" t="s">
-        <v>338</v>
+        <v>94</v>
+      </c>
+      <c r="D209" s="50" t="s">
+        <v>327</v>
       </c>
       <c r="E209" s="50">
-        <v>2000</v>
-      </c>
-      <c r="F209" s="8">
-        <v>5</v>
-      </c>
-      <c r="G209" s="14">
-        <v>140</v>
-      </c>
-      <c r="H209" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="I209" s="17">
-        <f t="shared" si="60"/>
-        <v>151.2</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F209" s="8"/>
+      <c r="G209" s="14"/>
+      <c r="H209" s="16"/>
+      <c r="I209" s="17"/>
       <c r="J209" s="9"/>
       <c r="K209" s="18">
         <f t="shared" si="61"/>
@@ -15128,13 +15133,13 @@
     </row>
     <row r="210" spans="1:14">
       <c r="B210" s="49" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>339</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E210" s="50">
         <v>2000</v>
@@ -15171,30 +15176,30 @@
       </c>
     </row>
     <row r="211" spans="1:14">
-      <c r="B211" s="50" t="s">
-        <v>336</v>
+      <c r="B211" s="49" t="s">
+        <v>338</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>96</v>
+        <v>341</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E211" s="50">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F211" s="8">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G211" s="14">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="H211" s="16">
         <v>0.08</v>
       </c>
       <c r="I211" s="17">
         <f t="shared" si="60"/>
-        <v>75.6</v>
+        <v>151.2</v>
       </c>
       <c r="J211" s="9"/>
       <c r="K211" s="18">
@@ -15216,29 +15221,29 @@
     </row>
     <row r="212" spans="1:14">
       <c r="B212" s="50" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>96</v>
       </c>
       <c r="D212" s="14" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="E212" s="50">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F212" s="8">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G212" s="14">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H212" s="16">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I212" s="17">
         <f t="shared" si="60"/>
-        <v>114.13</v>
+        <v>75.6</v>
       </c>
       <c r="J212" s="9"/>
       <c r="K212" s="18">
@@ -15259,35 +15264,58 @@
       </c>
     </row>
     <row r="213" spans="1:14">
-      <c r="F213" s="8"/>
-      <c r="G213" s="14"/>
-      <c r="H213" s="16"/>
-      <c r="J213" s="8" t="s">
-        <v>340</v>
-      </c>
+      <c r="B213" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D213" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="E213" s="50">
+        <v>2000</v>
+      </c>
+      <c r="F213" s="8">
+        <v>4</v>
+      </c>
+      <c r="G213" s="14">
+        <v>101</v>
+      </c>
+      <c r="H213" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="I213" s="17">
+        <f t="shared" si="60"/>
+        <v>114.13</v>
+      </c>
+      <c r="J213" s="9"/>
       <c r="K213" s="18">
-        <f>SUM(J6:J211)</f>
-        <v>0</v>
-      </c>
-      <c r="L213" s="7" t="s">
-        <v>341</v>
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="L213" s="18">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M213" s="17">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N213" s="19">
+        <f t="shared" si="59"/>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:14">
-      <c r="A214" s="54"/>
-      <c r="B214" s="54"/>
-      <c r="C214" s="54"/>
-      <c r="D214" s="54"/>
-      <c r="E214" s="54"/>
       <c r="F214" s="8"/>
       <c r="G214" s="14"/>
       <c r="H214" s="16"/>
-      <c r="I214" s="54"/>
-      <c r="J214" s="50" t="s">
+      <c r="J214" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="K214" s="8">
-        <f>SUM(K6:K211)</f>
+      <c r="K214" s="18">
+        <f>SUM(J6:J212)</f>
         <v>0</v>
       </c>
       <c r="L214" s="7" t="s">
@@ -15300,21 +15328,20 @@
       <c r="C215" s="54"/>
       <c r="D215" s="54"/>
       <c r="E215" s="54"/>
-      <c r="F215" s="54"/>
+      <c r="F215" s="8"/>
       <c r="G215" s="14"/>
       <c r="H215" s="16"/>
       <c r="I215" s="54"/>
       <c r="J215" s="50" t="s">
         <v>344</v>
       </c>
-      <c r="K215" s="5">
-        <f>SUM(L:L)</f>
-        <v>0</v>
-      </c>
-      <c r="L215" s="55" t="s">
-        <v>343</v>
-      </c>
-      <c r="M215" s="50"/>
+      <c r="K215" s="8">
+        <f>SUM(K6:K212)</f>
+        <v>0</v>
+      </c>
+      <c r="L215" s="7" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="54"/>
@@ -15327,13 +15354,15 @@
       <c r="H216" s="16"/>
       <c r="I216" s="54"/>
       <c r="J216" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="K216" s="5">
+        <f>SUM(L:L)</f>
+        <v>0</v>
+      </c>
+      <c r="L216" s="55" t="s">
         <v>345</v>
       </c>
-      <c r="K216" s="54">
-        <f>SUM(N5:N212)</f>
-        <v>0</v>
-      </c>
-      <c r="L216" s="54"/>
       <c r="M216" s="50"/>
     </row>
     <row r="217" spans="1:14">
@@ -15346,8 +15375,13 @@
       <c r="G217" s="14"/>
       <c r="H217" s="16"/>
       <c r="I217" s="54"/>
-      <c r="J217" s="54"/>
-      <c r="K217" s="54"/>
+      <c r="J217" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="K217" s="54">
+        <f>SUM(N5:N213)</f>
+        <v>0</v>
+      </c>
       <c r="L217" s="54"/>
       <c r="M217" s="50"/>
     </row>
@@ -15373,7 +15407,7 @@
       <c r="D219" s="54"/>
       <c r="E219" s="54"/>
       <c r="F219" s="54"/>
-      <c r="G219" s="54"/>
+      <c r="G219" s="14"/>
       <c r="H219" s="16"/>
       <c r="I219" s="54"/>
       <c r="J219" s="54"/>
@@ -15408,9 +15442,7 @@
       <c r="I221" s="54"/>
       <c r="J221" s="54"/>
       <c r="K221" s="54"/>
-      <c r="L221" s="54" t="s">
-        <v>233</v>
-      </c>
+      <c r="L221" s="54"/>
       <c r="M221" s="50"/>
     </row>
     <row r="222" spans="1:14">
@@ -15421,11 +15453,13 @@
       <c r="E222" s="54"/>
       <c r="F222" s="54"/>
       <c r="G222" s="54"/>
-      <c r="H222" s="54"/>
+      <c r="H222" s="16"/>
       <c r="I222" s="54"/>
       <c r="J222" s="54"/>
       <c r="K222" s="54"/>
-      <c r="L222" s="54"/>
+      <c r="L222" s="54" t="s">
+        <v>235</v>
+      </c>
       <c r="M222" s="50"/>
     </row>
     <row r="223" spans="1:14">
@@ -15473,33 +15507,48 @@
       <c r="L225" s="54"/>
       <c r="M225" s="50"/>
     </row>
-    <row r="227" spans="1:13">
-      <c r="B227" s="7"/>
-      <c r="C227" s="7"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
-    </row>
-    <row r="229" spans="1:13">
-      <c r="J229" s="7"/>
+    <row r="226" spans="1:13">
+      <c r="A226" s="54"/>
+      <c r="B226" s="54"/>
+      <c r="C226" s="54"/>
+      <c r="D226" s="54"/>
+      <c r="E226" s="54"/>
+      <c r="F226" s="54"/>
+      <c r="G226" s="54"/>
+      <c r="H226" s="54"/>
+      <c r="I226" s="54"/>
+      <c r="J226" s="54"/>
+      <c r="K226" s="54"/>
+      <c r="L226" s="54"/>
+      <c r="M226" s="50"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="B228" s="7"/>
+      <c r="C228" s="7"/>
+      <c r="D228" s="7"/>
+      <c r="E228" s="7"/>
     </row>
     <row r="230" spans="1:13">
-      <c r="K230" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="J230" s="7"/>
     </row>
     <row r="231" spans="1:13">
-      <c r="B231" s="7"/>
-      <c r="C231" s="7"/>
-      <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
-    </row>
-    <row r="244" spans="5:5">
-      <c r="E244" s="2" t="s">
-        <v>233</v>
+      <c r="K231" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="B232" s="7"/>
+      <c r="C232" s="7"/>
+      <c r="D232" s="7"/>
+      <c r="E232" s="7"/>
+    </row>
+    <row r="245" spans="5:5">
+      <c r="E245" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P216" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P217" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15518,7 +15567,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N212,工作表2!N6:N212&gt;0,"")</f>
+        <f t="array" ref="A1">_xlfn._xlws.FILTER(工作表2!B6:N213,工作表2!N6:N213&gt;0,"")</f>
         <v/>
       </c>
     </row>
